--- a/高橋さん用フォルダ/テンプレート集.xlsx
+++ b/高橋さん用フォルダ/テンプレート集.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\iret_pm\高橋さん用フォルダ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0710A66E-890D-426A-9C8A-8DB4E99B038E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD47E960-674E-4C6F-8046-2A3E3532A74A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" firstSheet="6" activeTab="6" xr2:uid="{C2D9C0E7-7181-4507-8D76-FFF1980A0610}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" firstSheet="4" activeTab="7" xr2:uid="{C2D9C0E7-7181-4507-8D76-FFF1980A0610}"/>
   </bookViews>
   <sheets>
     <sheet name="組織のビジネスモデル" sheetId="1" r:id="rId1"/>
@@ -20,6 +20,7 @@
     <sheet name="【PDM】" sheetId="5" r:id="rId5"/>
     <sheet name="【WBS-&gt;ガントチャート】" sheetId="6" r:id="rId6"/>
     <sheet name="【リスク登録簿】" sheetId="7" r:id="rId7"/>
+    <sheet name="交渉ロールプレイ" sheetId="8" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="126">
   <si>
     <t>キーパートナー</t>
     <phoneticPr fontId="2"/>
@@ -825,6 +826,103 @@
     </rPh>
     <rPh sb="15" eb="17">
       <t>キニュウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>交渉のシナリオ</t>
+    <rPh sb="0" eb="2">
+      <t>コウショウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>こちら側</t>
+    <rPh sb="3" eb="4">
+      <t>ガワ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>相手側</t>
+    <rPh sb="0" eb="2">
+      <t>アイテ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ガワ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>交渉の目的
+オープニング
+ステートメント</t>
+    <rPh sb="0" eb="2">
+      <t>コウショウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>モクテキ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>利害関係
+・対立点
+・ニーズ
+・要求事項
+・譲れない項目</t>
+    <rPh sb="0" eb="2">
+      <t>リガイ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>カンケイ</t>
+    </rPh>
+    <rPh sb="6" eb="9">
+      <t>タイリツテン</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ヨウキュウ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ジコウ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>ユズ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>コウモク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>代替案
+・最高の条件
+・妥当な条件
+・最低の条件
+各々の条件で相手から想定される反論</t>
+    <rPh sb="0" eb="2">
+      <t>ダイカ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>アン</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>サイコウ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ジョウケン</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ダトウ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ジョウケン</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>サイテイ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>ジョウケン</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -890,7 +988,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -939,6 +1037,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="27">
     <border>
@@ -1290,7 +1394,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1304,9 +1408,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1">
@@ -1390,7 +1491,7 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1417,7 +1518,7 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1">
@@ -1474,6 +1575,15 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="14" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="12" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="12" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1483,14 +1593,11 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="14" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="12" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="12" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="12" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2199,7 +2306,7 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="3390900" y="2082800"/>
+          <a:off x="3321050" y="2082800"/>
           <a:ext cx="177800" cy="3359150"/>
           <a:chOff x="3321050" y="1847850"/>
           <a:chExt cx="177800" cy="3359150"/>
@@ -2414,7 +2521,7 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="4883150" y="2082800"/>
+          <a:off x="4781550" y="2082800"/>
           <a:ext cx="177800" cy="3359150"/>
           <a:chOff x="3321050" y="1847850"/>
           <a:chExt cx="177800" cy="3359150"/>
@@ -2629,8 +2736,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="6381750" y="2082800"/>
-          <a:ext cx="184150" cy="3359150"/>
+          <a:off x="6248400" y="2082800"/>
+          <a:ext cx="177800" cy="3359150"/>
           <a:chOff x="3321050" y="1847850"/>
           <a:chExt cx="177800" cy="3359150"/>
         </a:xfrm>
@@ -2844,7 +2951,7 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="7867650" y="2082800"/>
+          <a:off x="7702550" y="2082800"/>
           <a:ext cx="177800" cy="3359150"/>
           <a:chOff x="3321050" y="1847850"/>
           <a:chExt cx="177800" cy="3359150"/>
@@ -3059,7 +3166,7 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="1898650" y="2082800"/>
+          <a:off x="1860550" y="2082800"/>
           <a:ext cx="177800" cy="3359150"/>
           <a:chOff x="3321050" y="1847850"/>
           <a:chExt cx="177800" cy="3359150"/>
@@ -3274,8 +3381,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="412750" y="2082800"/>
-          <a:ext cx="184150" cy="3359150"/>
+          <a:off x="406400" y="2082800"/>
+          <a:ext cx="177800" cy="3359150"/>
           <a:chOff x="3321050" y="1847850"/>
           <a:chExt cx="177800" cy="3359150"/>
         </a:xfrm>
@@ -3489,8 +3596,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="895350" y="927100"/>
-          <a:ext cx="7461250" cy="450850"/>
+          <a:off x="876300" y="927100"/>
+          <a:ext cx="7302500" cy="450850"/>
           <a:chOff x="876300" y="927100"/>
           <a:chExt cx="7302500" cy="450850"/>
         </a:xfrm>
@@ -4838,43 +4945,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0959A804-C26C-4B86-9033-45087ECCAC0D}">
-  <dimension ref="A1:AF26"/>
+  <dimension ref="C1:AF25"/>
   <sheetFormatPr defaultColWidth="4.58203125" defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="34" width="3.58203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" ht="18.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1" s="5"/>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
-      <c r="I1" s="5"/>
-      <c r="J1" s="5"/>
-      <c r="K1" s="5"/>
-      <c r="L1" s="5"/>
-      <c r="M1" s="5"/>
-      <c r="N1" s="5"/>
-      <c r="O1" s="5"/>
-      <c r="P1" s="5"/>
-      <c r="Q1" s="5"/>
-      <c r="R1" s="5"/>
-      <c r="S1" s="5"/>
-      <c r="T1" s="5"/>
-      <c r="U1" s="5"/>
-      <c r="V1" s="5"/>
-      <c r="W1" s="5"/>
-      <c r="X1" s="5"/>
-      <c r="Y1" s="5"/>
-      <c r="Z1" s="5"/>
-    </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="5"/>
-      <c r="B2" s="5"/>
+    <row r="1" spans="3:32" ht="18.5" thickBot="1" x14ac:dyDescent="0.6"/>
+    <row r="2" spans="3:32" x14ac:dyDescent="0.55000000000000004">
       <c r="C2" s="1" t="s">
         <v>0</v>
       </c>
@@ -4916,287 +4994,72 @@
       <c r="AE2" s="2"/>
       <c r="AF2" s="3"/>
     </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="5"/>
-      <c r="B3" s="5"/>
+    <row r="3" spans="3:32" x14ac:dyDescent="0.55000000000000004">
       <c r="C3" s="4"/>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5"/>
-      <c r="H3" s="5"/>
       <c r="I3" s="4"/>
-      <c r="J3" s="5"/>
-      <c r="K3" s="5"/>
-      <c r="L3" s="5"/>
-      <c r="M3" s="5"/>
-      <c r="N3" s="6"/>
-      <c r="O3" s="5"/>
-      <c r="P3" s="5"/>
-      <c r="Q3" s="5"/>
-      <c r="R3" s="5"/>
-      <c r="S3" s="5"/>
-      <c r="T3" s="5"/>
+      <c r="N3" s="5"/>
       <c r="U3" s="4"/>
-      <c r="V3" s="5"/>
-      <c r="W3" s="5"/>
-      <c r="X3" s="5"/>
-      <c r="Y3" s="5"/>
-      <c r="Z3" s="6"/>
-      <c r="AA3" s="5"/>
-      <c r="AB3" s="5"/>
-      <c r="AC3" s="5"/>
-      <c r="AD3" s="5"/>
-      <c r="AE3" s="5"/>
-      <c r="AF3" s="6"/>
-    </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="5"/>
-      <c r="B4" s="5"/>
+      <c r="Z3" s="5"/>
+      <c r="AF3" s="5"/>
+    </row>
+    <row r="4" spans="3:32" x14ac:dyDescent="0.55000000000000004">
       <c r="C4" s="4"/>
-      <c r="D4" s="5"/>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5"/>
-      <c r="G4" s="5"/>
-      <c r="H4" s="5"/>
       <c r="I4" s="4"/>
-      <c r="J4" s="5"/>
-      <c r="K4" s="5"/>
-      <c r="L4" s="5"/>
-      <c r="M4" s="5"/>
-      <c r="N4" s="6"/>
-      <c r="O4" s="5"/>
-      <c r="P4" s="5"/>
-      <c r="Q4" s="5"/>
-      <c r="R4" s="5"/>
-      <c r="S4" s="5"/>
-      <c r="T4" s="5"/>
+      <c r="N4" s="5"/>
       <c r="U4" s="4"/>
-      <c r="V4" s="5"/>
-      <c r="W4" s="5"/>
-      <c r="X4" s="5"/>
-      <c r="Y4" s="5"/>
-      <c r="Z4" s="6"/>
-      <c r="AA4" s="5"/>
-      <c r="AB4" s="5"/>
-      <c r="AC4" s="5"/>
-      <c r="AD4" s="5"/>
-      <c r="AE4" s="5"/>
-      <c r="AF4" s="6"/>
-    </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="5"/>
-      <c r="B5" s="5"/>
+      <c r="Z4" s="5"/>
+      <c r="AF4" s="5"/>
+    </row>
+    <row r="5" spans="3:32" x14ac:dyDescent="0.55000000000000004">
       <c r="C5" s="4"/>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5"/>
       <c r="I5" s="4"/>
-      <c r="J5" s="5"/>
-      <c r="K5" s="5"/>
-      <c r="L5" s="5"/>
-      <c r="M5" s="5"/>
-      <c r="N5" s="6"/>
-      <c r="O5" s="5"/>
-      <c r="P5" s="5"/>
-      <c r="Q5" s="5"/>
-      <c r="R5" s="5"/>
-      <c r="S5" s="5"/>
-      <c r="T5" s="5"/>
+      <c r="N5" s="5"/>
       <c r="U5" s="4"/>
-      <c r="V5" s="5"/>
-      <c r="W5" s="5"/>
-      <c r="X5" s="5"/>
-      <c r="Y5" s="5"/>
-      <c r="Z5" s="6"/>
-      <c r="AA5" s="5"/>
-      <c r="AB5" s="5"/>
-      <c r="AC5" s="5"/>
-      <c r="AD5" s="5"/>
-      <c r="AE5" s="5"/>
-      <c r="AF5" s="6"/>
-    </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="5"/>
-      <c r="B6" s="5"/>
+      <c r="Z5" s="5"/>
+      <c r="AF5" s="5"/>
+    </row>
+    <row r="6" spans="3:32" x14ac:dyDescent="0.55000000000000004">
       <c r="C6" s="4"/>
-      <c r="D6" s="5"/>
-      <c r="E6" s="5"/>
-      <c r="F6" s="5"/>
-      <c r="G6" s="5"/>
-      <c r="H6" s="5"/>
       <c r="I6" s="4"/>
-      <c r="J6" s="5"/>
-      <c r="K6" s="5"/>
-      <c r="L6" s="5"/>
-      <c r="M6" s="5"/>
-      <c r="N6" s="6"/>
-      <c r="O6" s="5"/>
-      <c r="P6" s="5"/>
-      <c r="Q6" s="5"/>
-      <c r="R6" s="5"/>
-      <c r="S6" s="5"/>
-      <c r="T6" s="5"/>
+      <c r="N6" s="5"/>
       <c r="U6" s="4"/>
-      <c r="V6" s="5"/>
-      <c r="W6" s="5"/>
-      <c r="X6" s="5"/>
-      <c r="Y6" s="5"/>
-      <c r="Z6" s="6"/>
-      <c r="AA6" s="5"/>
-      <c r="AB6" s="5"/>
-      <c r="AC6" s="5"/>
-      <c r="AD6" s="5"/>
-      <c r="AE6" s="5"/>
-      <c r="AF6" s="6"/>
-    </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="5"/>
-      <c r="B7" s="5"/>
+      <c r="Z6" s="5"/>
+      <c r="AF6" s="5"/>
+    </row>
+    <row r="7" spans="3:32" x14ac:dyDescent="0.55000000000000004">
       <c r="C7" s="4"/>
-      <c r="D7" s="5"/>
-      <c r="E7" s="5"/>
-      <c r="F7" s="5"/>
-      <c r="G7" s="5"/>
-      <c r="H7" s="5"/>
       <c r="I7" s="4"/>
-      <c r="J7" s="5"/>
-      <c r="K7" s="5"/>
-      <c r="L7" s="5"/>
-      <c r="M7" s="5"/>
-      <c r="N7" s="6"/>
-      <c r="O7" s="5"/>
-      <c r="P7" s="5"/>
-      <c r="Q7" s="5"/>
-      <c r="R7" s="5"/>
-      <c r="S7" s="5"/>
-      <c r="T7" s="5"/>
+      <c r="N7" s="5"/>
       <c r="U7" s="4"/>
-      <c r="V7" s="5"/>
-      <c r="W7" s="5"/>
-      <c r="X7" s="5"/>
-      <c r="Y7" s="5"/>
-      <c r="Z7" s="6"/>
-      <c r="AA7" s="5"/>
-      <c r="AB7" s="5"/>
-      <c r="AC7" s="5"/>
-      <c r="AD7" s="5"/>
-      <c r="AE7" s="5"/>
-      <c r="AF7" s="6"/>
-    </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="5"/>
-      <c r="B8" s="5"/>
+      <c r="Z7" s="5"/>
+      <c r="AF7" s="5"/>
+    </row>
+    <row r="8" spans="3:32" x14ac:dyDescent="0.55000000000000004">
       <c r="C8" s="4"/>
-      <c r="D8" s="5"/>
-      <c r="E8" s="5"/>
-      <c r="F8" s="5"/>
-      <c r="G8" s="5"/>
-      <c r="H8" s="5"/>
       <c r="I8" s="4"/>
-      <c r="J8" s="5"/>
-      <c r="K8" s="5"/>
-      <c r="L8" s="5"/>
-      <c r="M8" s="5"/>
-      <c r="N8" s="6"/>
-      <c r="O8" s="5"/>
-      <c r="P8" s="5"/>
-      <c r="Q8" s="5"/>
-      <c r="R8" s="5"/>
-      <c r="S8" s="5"/>
-      <c r="T8" s="5"/>
+      <c r="N8" s="5"/>
       <c r="U8" s="4"/>
-      <c r="V8" s="5"/>
-      <c r="W8" s="5"/>
-      <c r="X8" s="5"/>
-      <c r="Y8" s="5"/>
-      <c r="Z8" s="6"/>
-      <c r="AA8" s="5"/>
-      <c r="AB8" s="5"/>
-      <c r="AC8" s="5"/>
-      <c r="AD8" s="5"/>
-      <c r="AE8" s="5"/>
-      <c r="AF8" s="6"/>
-    </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="5"/>
-      <c r="B9" s="5"/>
+      <c r="Z8" s="5"/>
+      <c r="AF8" s="5"/>
+    </row>
+    <row r="9" spans="3:32" x14ac:dyDescent="0.55000000000000004">
       <c r="C9" s="4"/>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
-      <c r="F9" s="5"/>
-      <c r="G9" s="5"/>
-      <c r="H9" s="5"/>
       <c r="I9" s="4"/>
-      <c r="J9" s="5"/>
-      <c r="K9" s="5"/>
-      <c r="L9" s="5"/>
-      <c r="M9" s="5"/>
-      <c r="N9" s="6"/>
-      <c r="O9" s="5"/>
-      <c r="P9" s="5"/>
-      <c r="Q9" s="5"/>
-      <c r="R9" s="5"/>
-      <c r="S9" s="5"/>
-      <c r="T9" s="5"/>
+      <c r="N9" s="5"/>
       <c r="U9" s="4"/>
-      <c r="V9" s="5"/>
-      <c r="W9" s="5"/>
-      <c r="X9" s="5"/>
-      <c r="Y9" s="5"/>
-      <c r="Z9" s="6"/>
-      <c r="AA9" s="5"/>
-      <c r="AB9" s="5"/>
-      <c r="AC9" s="5"/>
-      <c r="AD9" s="5"/>
-      <c r="AE9" s="5"/>
-      <c r="AF9" s="6"/>
-    </row>
-    <row r="10" spans="1:32" ht="18.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A10" s="5"/>
-      <c r="B10" s="5"/>
+      <c r="Z9" s="5"/>
+      <c r="AF9" s="5"/>
+    </row>
+    <row r="10" spans="3:32" ht="18.5" thickBot="1" x14ac:dyDescent="0.6">
       <c r="C10" s="4"/>
-      <c r="D10" s="5"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
-      <c r="G10" s="5"/>
-      <c r="H10" s="5"/>
       <c r="I10" s="4"/>
-      <c r="J10" s="5"/>
-      <c r="K10" s="5"/>
-      <c r="L10" s="5"/>
-      <c r="M10" s="5"/>
-      <c r="N10" s="6"/>
-      <c r="O10" s="5"/>
-      <c r="P10" s="5"/>
-      <c r="Q10" s="5"/>
-      <c r="R10" s="5"/>
-      <c r="S10" s="5"/>
-      <c r="T10" s="5"/>
+      <c r="N10" s="5"/>
       <c r="U10" s="4"/>
-      <c r="V10" s="5"/>
-      <c r="W10" s="5"/>
-      <c r="X10" s="5"/>
-      <c r="Y10" s="5"/>
-      <c r="Z10" s="6"/>
-      <c r="AA10" s="5"/>
-      <c r="AB10" s="5"/>
-      <c r="AC10" s="5"/>
-      <c r="AD10" s="5"/>
-      <c r="AE10" s="5"/>
-      <c r="AF10" s="6"/>
-    </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="5"/>
-      <c r="B11" s="5"/>
+      <c r="Z10" s="5"/>
+      <c r="AF10" s="5"/>
+    </row>
+    <row r="11" spans="3:32" x14ac:dyDescent="0.55000000000000004">
       <c r="C11" s="4"/>
-      <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
-      <c r="F11" s="5"/>
-      <c r="G11" s="5"/>
-      <c r="H11" s="5"/>
       <c r="I11" s="1" t="s">
         <v>3</v>
       </c>
@@ -5205,12 +5068,6 @@
       <c r="L11" s="2"/>
       <c r="M11" s="2"/>
       <c r="N11" s="3"/>
-      <c r="O11" s="5"/>
-      <c r="P11" s="5"/>
-      <c r="Q11" s="5"/>
-      <c r="R11" s="5"/>
-      <c r="S11" s="5"/>
-      <c r="T11" s="5"/>
       <c r="U11" s="1" t="s">
         <v>5</v>
       </c>
@@ -5219,288 +5076,81 @@
       <c r="X11" s="2"/>
       <c r="Y11" s="2"/>
       <c r="Z11" s="3"/>
-      <c r="AA11" s="5"/>
-      <c r="AB11" s="5"/>
-      <c r="AC11" s="5"/>
-      <c r="AD11" s="5"/>
-      <c r="AE11" s="5"/>
-      <c r="AF11" s="6"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" s="5"/>
-      <c r="B12" s="5"/>
+      <c r="AF11" s="5"/>
+    </row>
+    <row r="12" spans="3:32" x14ac:dyDescent="0.55000000000000004">
       <c r="C12" s="4"/>
-      <c r="D12" s="5"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
-      <c r="G12" s="5"/>
-      <c r="H12" s="5"/>
       <c r="I12" s="4"/>
-      <c r="J12" s="5"/>
-      <c r="K12" s="5"/>
-      <c r="L12" s="5"/>
-      <c r="M12" s="5"/>
-      <c r="N12" s="6"/>
-      <c r="O12" s="5"/>
-      <c r="P12" s="5"/>
-      <c r="Q12" s="5"/>
-      <c r="R12" s="5"/>
-      <c r="S12" s="5"/>
-      <c r="T12" s="5"/>
+      <c r="N12" s="5"/>
       <c r="U12" s="4"/>
-      <c r="V12" s="5"/>
-      <c r="W12" s="5"/>
-      <c r="X12" s="5"/>
-      <c r="Y12" s="5"/>
-      <c r="Z12" s="6"/>
-      <c r="AA12" s="5"/>
-      <c r="AB12" s="5"/>
-      <c r="AC12" s="5"/>
-      <c r="AD12" s="5"/>
-      <c r="AE12" s="5"/>
-      <c r="AF12" s="6"/>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="5"/>
-      <c r="B13" s="5"/>
+      <c r="Z12" s="5"/>
+      <c r="AF12" s="5"/>
+    </row>
+    <row r="13" spans="3:32" x14ac:dyDescent="0.55000000000000004">
       <c r="C13" s="4"/>
-      <c r="D13" s="5"/>
-      <c r="E13" s="5"/>
-      <c r="F13" s="5"/>
-      <c r="G13" s="5"/>
-      <c r="H13" s="5"/>
       <c r="I13" s="4"/>
-      <c r="J13" s="5"/>
-      <c r="K13" s="5"/>
-      <c r="L13" s="5"/>
-      <c r="M13" s="5"/>
-      <c r="N13" s="6"/>
-      <c r="O13" s="5"/>
-      <c r="P13" s="5"/>
-      <c r="Q13" s="5"/>
-      <c r="R13" s="5"/>
-      <c r="S13" s="5"/>
-      <c r="T13" s="5"/>
+      <c r="N13" s="5"/>
       <c r="U13" s="4"/>
-      <c r="V13" s="5"/>
-      <c r="W13" s="5"/>
-      <c r="X13" s="5"/>
-      <c r="Y13" s="5"/>
-      <c r="Z13" s="6"/>
-      <c r="AA13" s="5"/>
-      <c r="AB13" s="5"/>
-      <c r="AC13" s="5"/>
-      <c r="AD13" s="5"/>
-      <c r="AE13" s="5"/>
-      <c r="AF13" s="6"/>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="5"/>
-      <c r="B14" s="5"/>
+      <c r="Z13" s="5"/>
+      <c r="AF13" s="5"/>
+    </row>
+    <row r="14" spans="3:32" x14ac:dyDescent="0.55000000000000004">
       <c r="C14" s="4"/>
-      <c r="D14" s="5"/>
-      <c r="E14" s="5"/>
-      <c r="F14" s="5"/>
-      <c r="G14" s="5"/>
-      <c r="H14" s="5"/>
       <c r="I14" s="4"/>
-      <c r="J14" s="5"/>
-      <c r="K14" s="5"/>
-      <c r="L14" s="5"/>
-      <c r="M14" s="5"/>
-      <c r="N14" s="6"/>
-      <c r="O14" s="5"/>
-      <c r="P14" s="5"/>
-      <c r="Q14" s="5"/>
-      <c r="R14" s="5"/>
-      <c r="S14" s="5"/>
-      <c r="T14" s="5"/>
+      <c r="N14" s="5"/>
       <c r="U14" s="4"/>
-      <c r="V14" s="5"/>
-      <c r="W14" s="5"/>
-      <c r="X14" s="5"/>
-      <c r="Y14" s="5"/>
-      <c r="Z14" s="6"/>
-      <c r="AA14" s="5"/>
-      <c r="AB14" s="5"/>
-      <c r="AC14" s="5"/>
-      <c r="AD14" s="5"/>
-      <c r="AE14" s="5"/>
-      <c r="AF14" s="6"/>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="5"/>
-      <c r="B15" s="5"/>
+      <c r="Z14" s="5"/>
+      <c r="AF14" s="5"/>
+    </row>
+    <row r="15" spans="3:32" x14ac:dyDescent="0.55000000000000004">
       <c r="C15" s="4"/>
-      <c r="D15" s="5"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="5"/>
-      <c r="G15" s="5"/>
-      <c r="H15" s="5"/>
       <c r="I15" s="4"/>
-      <c r="J15" s="5"/>
-      <c r="K15" s="5"/>
-      <c r="L15" s="5"/>
-      <c r="M15" s="5"/>
-      <c r="N15" s="6"/>
-      <c r="O15" s="5"/>
-      <c r="P15" s="5"/>
-      <c r="Q15" s="5"/>
-      <c r="R15" s="5"/>
-      <c r="S15" s="5"/>
-      <c r="T15" s="5"/>
+      <c r="N15" s="5"/>
       <c r="U15" s="4"/>
-      <c r="V15" s="5"/>
-      <c r="W15" s="5"/>
-      <c r="X15" s="5"/>
-      <c r="Y15" s="5"/>
-      <c r="Z15" s="6"/>
-      <c r="AA15" s="5"/>
-      <c r="AB15" s="5"/>
-      <c r="AC15" s="5"/>
-      <c r="AD15" s="5"/>
-      <c r="AE15" s="5"/>
-      <c r="AF15" s="6"/>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="5"/>
-      <c r="B16" s="5"/>
+      <c r="Z15" s="5"/>
+      <c r="AF15" s="5"/>
+    </row>
+    <row r="16" spans="3:32" x14ac:dyDescent="0.55000000000000004">
       <c r="C16" s="4"/>
-      <c r="D16" s="5"/>
-      <c r="E16" s="5"/>
-      <c r="F16" s="5"/>
-      <c r="G16" s="5"/>
-      <c r="H16" s="5"/>
       <c r="I16" s="4"/>
-      <c r="J16" s="5"/>
-      <c r="K16" s="5"/>
-      <c r="L16" s="5"/>
-      <c r="M16" s="5"/>
-      <c r="N16" s="6"/>
-      <c r="O16" s="5"/>
-      <c r="P16" s="5"/>
-      <c r="Q16" s="5"/>
-      <c r="R16" s="5"/>
-      <c r="S16" s="5"/>
-      <c r="T16" s="5"/>
+      <c r="N16" s="5"/>
       <c r="U16" s="4"/>
-      <c r="V16" s="5"/>
-      <c r="W16" s="5"/>
-      <c r="X16" s="5"/>
-      <c r="Y16" s="5"/>
-      <c r="Z16" s="6"/>
-      <c r="AA16" s="5"/>
-      <c r="AB16" s="5"/>
-      <c r="AC16" s="5"/>
-      <c r="AD16" s="5"/>
-      <c r="AE16" s="5"/>
-      <c r="AF16" s="6"/>
-    </row>
-    <row r="17" spans="1:32" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17" s="5"/>
-      <c r="B17" s="5"/>
+      <c r="Z16" s="5"/>
+      <c r="AF16" s="5"/>
+    </row>
+    <row r="17" spans="3:32" x14ac:dyDescent="0.55000000000000004">
       <c r="C17" s="4"/>
-      <c r="D17" s="5"/>
-      <c r="E17" s="5"/>
-      <c r="F17" s="5"/>
-      <c r="G17" s="5"/>
-      <c r="H17" s="5"/>
       <c r="I17" s="4"/>
-      <c r="J17" s="5"/>
-      <c r="K17" s="5"/>
-      <c r="L17" s="5"/>
-      <c r="M17" s="5"/>
-      <c r="N17" s="6"/>
-      <c r="O17" s="5"/>
-      <c r="P17" s="5"/>
-      <c r="Q17" s="5"/>
-      <c r="R17" s="5"/>
-      <c r="S17" s="5"/>
-      <c r="T17" s="5"/>
+      <c r="N17" s="5"/>
       <c r="U17" s="4"/>
-      <c r="V17" s="5"/>
-      <c r="W17" s="5"/>
-      <c r="X17" s="5"/>
-      <c r="Y17" s="5"/>
-      <c r="Z17" s="6"/>
-      <c r="AA17" s="5"/>
-      <c r="AB17" s="5"/>
-      <c r="AC17" s="5"/>
-      <c r="AD17" s="5"/>
-      <c r="AE17" s="5"/>
-      <c r="AF17" s="6"/>
-    </row>
-    <row r="18" spans="1:32" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18" s="5"/>
-      <c r="B18" s="5"/>
+      <c r="Z17" s="5"/>
+      <c r="AF17" s="5"/>
+    </row>
+    <row r="18" spans="3:32" x14ac:dyDescent="0.55000000000000004">
       <c r="C18" s="4"/>
-      <c r="D18" s="5"/>
-      <c r="E18" s="5"/>
-      <c r="F18" s="5"/>
-      <c r="G18" s="5"/>
-      <c r="H18" s="5"/>
       <c r="I18" s="4"/>
-      <c r="J18" s="5"/>
-      <c r="K18" s="5"/>
-      <c r="L18" s="5"/>
-      <c r="M18" s="5"/>
-      <c r="N18" s="6"/>
-      <c r="O18" s="5"/>
-      <c r="P18" s="5"/>
-      <c r="Q18" s="5"/>
-      <c r="R18" s="5"/>
-      <c r="S18" s="5"/>
-      <c r="T18" s="5"/>
+      <c r="N18" s="5"/>
       <c r="U18" s="4"/>
-      <c r="V18" s="5"/>
-      <c r="W18" s="5"/>
-      <c r="X18" s="5"/>
-      <c r="Y18" s="5"/>
-      <c r="Z18" s="6"/>
-      <c r="AA18" s="5"/>
-      <c r="AB18" s="5"/>
-      <c r="AC18" s="5"/>
-      <c r="AD18" s="5"/>
-      <c r="AE18" s="5"/>
-      <c r="AF18" s="6"/>
-    </row>
-    <row r="19" spans="1:32" ht="18.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A19" s="5"/>
-      <c r="B19" s="5"/>
+      <c r="Z18" s="5"/>
+      <c r="AF18" s="5"/>
+    </row>
+    <row r="19" spans="3:32" ht="18.5" thickBot="1" x14ac:dyDescent="0.6">
       <c r="C19" s="4"/>
-      <c r="D19" s="5"/>
-      <c r="E19" s="5"/>
-      <c r="F19" s="5"/>
-      <c r="G19" s="5"/>
-      <c r="H19" s="5"/>
-      <c r="I19" s="7"/>
-      <c r="J19" s="8"/>
-      <c r="K19" s="8"/>
-      <c r="L19" s="8"/>
-      <c r="M19" s="8"/>
-      <c r="N19" s="9"/>
-      <c r="O19" s="5"/>
-      <c r="P19" s="5"/>
-      <c r="Q19" s="5"/>
-      <c r="R19" s="5"/>
-      <c r="S19" s="5"/>
-      <c r="T19" s="5"/>
-      <c r="U19" s="7"/>
-      <c r="V19" s="8"/>
-      <c r="W19" s="8"/>
-      <c r="X19" s="8"/>
-      <c r="Y19" s="8"/>
-      <c r="Z19" s="9"/>
-      <c r="AA19" s="5"/>
-      <c r="AB19" s="5"/>
-      <c r="AC19" s="5"/>
-      <c r="AD19" s="5"/>
-      <c r="AE19" s="5"/>
-      <c r="AF19" s="6"/>
-    </row>
-    <row r="20" spans="1:32" x14ac:dyDescent="0.55000000000000004">
-      <c r="A20" s="5"/>
-      <c r="B20" s="5"/>
+      <c r="I19" s="6"/>
+      <c r="J19" s="7"/>
+      <c r="K19" s="7"/>
+      <c r="L19" s="7"/>
+      <c r="M19" s="7"/>
+      <c r="N19" s="8"/>
+      <c r="U19" s="6"/>
+      <c r="V19" s="7"/>
+      <c r="W19" s="7"/>
+      <c r="X19" s="7"/>
+      <c r="Y19" s="7"/>
+      <c r="Z19" s="8"/>
+      <c r="AF19" s="5"/>
+    </row>
+    <row r="20" spans="3:32" x14ac:dyDescent="0.55000000000000004">
       <c r="C20" s="1" t="s">
         <v>7</v>
       </c>
@@ -5536,203 +5186,61 @@
       <c r="AE20" s="2"/>
       <c r="AF20" s="3"/>
     </row>
-    <row r="21" spans="1:32" x14ac:dyDescent="0.55000000000000004">
-      <c r="A21" s="5"/>
-      <c r="B21" s="5"/>
+    <row r="21" spans="3:32" x14ac:dyDescent="0.55000000000000004">
       <c r="C21" s="4"/>
-      <c r="D21" s="5"/>
-      <c r="E21" s="5"/>
-      <c r="F21" s="5"/>
-      <c r="G21" s="5"/>
-      <c r="H21" s="5"/>
-      <c r="I21" s="5"/>
-      <c r="J21" s="5"/>
-      <c r="K21" s="5"/>
-      <c r="L21" s="5"/>
-      <c r="M21" s="5"/>
-      <c r="N21" s="5"/>
-      <c r="O21" s="5"/>
-      <c r="P21" s="5"/>
-      <c r="Q21" s="6"/>
+      <c r="Q21" s="5"/>
       <c r="R21" s="4"/>
-      <c r="S21" s="5"/>
-      <c r="T21" s="5"/>
-      <c r="U21" s="5"/>
-      <c r="V21" s="5"/>
-      <c r="W21" s="5"/>
-      <c r="X21" s="5"/>
-      <c r="Y21" s="5"/>
-      <c r="Z21" s="5"/>
-      <c r="AA21" s="5"/>
-      <c r="AB21" s="5"/>
-      <c r="AC21" s="5"/>
-      <c r="AD21" s="5"/>
-      <c r="AE21" s="5"/>
-      <c r="AF21" s="6"/>
-    </row>
-    <row r="22" spans="1:32" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22" s="5"/>
-      <c r="B22" s="5"/>
+      <c r="AF21" s="5"/>
+    </row>
+    <row r="22" spans="3:32" x14ac:dyDescent="0.55000000000000004">
       <c r="C22" s="4"/>
-      <c r="D22" s="5"/>
-      <c r="E22" s="5"/>
-      <c r="F22" s="5"/>
-      <c r="G22" s="5"/>
-      <c r="H22" s="5"/>
-      <c r="I22" s="5"/>
-      <c r="J22" s="5"/>
-      <c r="K22" s="5"/>
-      <c r="L22" s="5"/>
-      <c r="M22" s="5"/>
-      <c r="N22" s="5"/>
-      <c r="O22" s="5"/>
-      <c r="P22" s="5"/>
-      <c r="Q22" s="6"/>
+      <c r="Q22" s="5"/>
       <c r="R22" s="4"/>
-      <c r="S22" s="5"/>
-      <c r="T22" s="5"/>
-      <c r="U22" s="5"/>
-      <c r="V22" s="5"/>
-      <c r="W22" s="5"/>
-      <c r="X22" s="5"/>
-      <c r="Y22" s="5"/>
-      <c r="Z22" s="5"/>
-      <c r="AA22" s="5"/>
-      <c r="AB22" s="5"/>
-      <c r="AC22" s="5"/>
-      <c r="AD22" s="5"/>
-      <c r="AE22" s="5"/>
-      <c r="AF22" s="6"/>
-    </row>
-    <row r="23" spans="1:32" x14ac:dyDescent="0.55000000000000004">
-      <c r="A23" s="5"/>
-      <c r="B23" s="5"/>
+      <c r="AF22" s="5"/>
+    </row>
+    <row r="23" spans="3:32" x14ac:dyDescent="0.55000000000000004">
       <c r="C23" s="4"/>
-      <c r="D23" s="5"/>
-      <c r="E23" s="5"/>
-      <c r="F23" s="5"/>
-      <c r="G23" s="5"/>
-      <c r="H23" s="5"/>
-      <c r="I23" s="5"/>
-      <c r="J23" s="5"/>
-      <c r="K23" s="5"/>
-      <c r="L23" s="5"/>
-      <c r="M23" s="5"/>
-      <c r="N23" s="5"/>
-      <c r="O23" s="5"/>
-      <c r="P23" s="5"/>
-      <c r="Q23" s="6"/>
+      <c r="Q23" s="5"/>
       <c r="R23" s="4"/>
-      <c r="S23" s="5"/>
-      <c r="T23" s="5"/>
-      <c r="U23" s="5"/>
-      <c r="V23" s="5"/>
-      <c r="W23" s="5"/>
-      <c r="X23" s="5"/>
-      <c r="Y23" s="5"/>
-      <c r="Z23" s="5"/>
-      <c r="AA23" s="5"/>
-      <c r="AB23" s="5"/>
-      <c r="AC23" s="5"/>
-      <c r="AD23" s="5"/>
-      <c r="AE23" s="5"/>
-      <c r="AF23" s="6"/>
-    </row>
-    <row r="24" spans="1:32" x14ac:dyDescent="0.55000000000000004">
-      <c r="A24" s="5"/>
-      <c r="B24" s="5"/>
+      <c r="AF23" s="5"/>
+    </row>
+    <row r="24" spans="3:32" x14ac:dyDescent="0.55000000000000004">
       <c r="C24" s="4"/>
-      <c r="D24" s="5"/>
-      <c r="E24" s="5"/>
-      <c r="F24" s="5"/>
-      <c r="G24" s="5"/>
-      <c r="H24" s="5"/>
-      <c r="I24" s="5"/>
-      <c r="J24" s="5"/>
-      <c r="K24" s="5"/>
-      <c r="L24" s="5"/>
-      <c r="M24" s="5"/>
-      <c r="N24" s="5"/>
-      <c r="O24" s="5"/>
-      <c r="P24" s="5"/>
-      <c r="Q24" s="6"/>
+      <c r="Q24" s="5"/>
       <c r="R24" s="4"/>
-      <c r="S24" s="5"/>
-      <c r="T24" s="5"/>
-      <c r="U24" s="5"/>
-      <c r="V24" s="5"/>
-      <c r="W24" s="5"/>
-      <c r="X24" s="5"/>
-      <c r="Y24" s="5"/>
-      <c r="Z24" s="5"/>
-      <c r="AA24" s="5"/>
-      <c r="AB24" s="5"/>
-      <c r="AC24" s="5"/>
-      <c r="AD24" s="5"/>
-      <c r="AE24" s="5"/>
-      <c r="AF24" s="6"/>
-    </row>
-    <row r="25" spans="1:32" ht="18.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A25" s="5"/>
-      <c r="B25" s="5"/>
-      <c r="C25" s="7"/>
-      <c r="D25" s="8"/>
-      <c r="E25" s="8"/>
-      <c r="F25" s="8"/>
-      <c r="G25" s="8"/>
-      <c r="H25" s="8"/>
-      <c r="I25" s="8"/>
-      <c r="J25" s="8"/>
-      <c r="K25" s="8"/>
-      <c r="L25" s="8"/>
-      <c r="M25" s="8"/>
-      <c r="N25" s="8"/>
-      <c r="O25" s="8"/>
-      <c r="P25" s="8"/>
-      <c r="Q25" s="9"/>
-      <c r="R25" s="7"/>
-      <c r="S25" s="8"/>
-      <c r="T25" s="8"/>
-      <c r="U25" s="8"/>
-      <c r="V25" s="8"/>
-      <c r="W25" s="8"/>
-      <c r="X25" s="8"/>
-      <c r="Y25" s="8"/>
-      <c r="Z25" s="8"/>
-      <c r="AA25" s="8"/>
-      <c r="AB25" s="8"/>
-      <c r="AC25" s="8"/>
-      <c r="AD25" s="8"/>
-      <c r="AE25" s="8"/>
-      <c r="AF25" s="9"/>
-    </row>
-    <row r="26" spans="1:32" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26" s="5"/>
-      <c r="B26" s="5"/>
-      <c r="C26" s="5"/>
-      <c r="D26" s="5"/>
-      <c r="E26" s="5"/>
-      <c r="F26" s="5"/>
-      <c r="G26" s="5"/>
-      <c r="H26" s="5"/>
-      <c r="I26" s="5"/>
-      <c r="J26" s="5"/>
-      <c r="K26" s="5"/>
-      <c r="L26" s="5"/>
-      <c r="M26" s="5"/>
-      <c r="N26" s="5"/>
-      <c r="O26" s="5"/>
-      <c r="P26" s="5"/>
-      <c r="Q26" s="5"/>
-      <c r="R26" s="5"/>
-      <c r="S26" s="5"/>
-      <c r="T26" s="5"/>
-      <c r="U26" s="5"/>
-      <c r="V26" s="5"/>
-      <c r="W26" s="5"/>
-      <c r="X26" s="5"/>
-      <c r="Y26" s="5"/>
-      <c r="Z26" s="5"/>
+      <c r="AF24" s="5"/>
+    </row>
+    <row r="25" spans="3:32" ht="18.5" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="C25" s="6"/>
+      <c r="D25" s="7"/>
+      <c r="E25" s="7"/>
+      <c r="F25" s="7"/>
+      <c r="G25" s="7"/>
+      <c r="H25" s="7"/>
+      <c r="I25" s="7"/>
+      <c r="J25" s="7"/>
+      <c r="K25" s="7"/>
+      <c r="L25" s="7"/>
+      <c r="M25" s="7"/>
+      <c r="N25" s="7"/>
+      <c r="O25" s="7"/>
+      <c r="P25" s="7"/>
+      <c r="Q25" s="8"/>
+      <c r="R25" s="6"/>
+      <c r="S25" s="7"/>
+      <c r="T25" s="7"/>
+      <c r="U25" s="7"/>
+      <c r="V25" s="7"/>
+      <c r="W25" s="7"/>
+      <c r="X25" s="7"/>
+      <c r="Y25" s="7"/>
+      <c r="Z25" s="7"/>
+      <c r="AA25" s="7"/>
+      <c r="AB25" s="7"/>
+      <c r="AC25" s="7"/>
+      <c r="AD25" s="7"/>
+      <c r="AE25" s="7"/>
+      <c r="AF25" s="8"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>
@@ -5759,16 +5267,16 @@
       </c>
     </row>
     <row r="2" spans="1:17" ht="18.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B2" s="10"/>
-      <c r="C2" s="11"/>
-      <c r="D2" s="11"/>
-      <c r="E2" s="11"/>
-      <c r="F2" s="11"/>
-      <c r="G2" s="11"/>
-      <c r="H2" s="11"/>
-      <c r="I2" s="11"/>
-      <c r="J2" s="11"/>
-      <c r="K2" s="12"/>
+      <c r="B2" s="9"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="10"/>
+      <c r="J2" s="10"/>
+      <c r="K2" s="11"/>
     </row>
     <row r="3" spans="1:17" ht="18.5" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A3" t="s">
@@ -5776,16 +5284,16 @@
       </c>
     </row>
     <row r="4" spans="1:17" ht="18.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B4" s="10"/>
-      <c r="C4" s="11"/>
-      <c r="D4" s="11"/>
-      <c r="E4" s="11"/>
-      <c r="F4" s="11"/>
-      <c r="G4" s="11"/>
-      <c r="H4" s="11"/>
-      <c r="I4" s="11"/>
-      <c r="J4" s="11"/>
-      <c r="K4" s="12"/>
+      <c r="B4" s="9"/>
+      <c r="C4" s="10"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="10"/>
+      <c r="G4" s="10"/>
+      <c r="H4" s="10"/>
+      <c r="I4" s="10"/>
+      <c r="J4" s="10"/>
+      <c r="K4" s="11"/>
     </row>
     <row r="5" spans="1:17" ht="18.5" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A5" t="s">
@@ -5793,16 +5301,16 @@
       </c>
     </row>
     <row r="6" spans="1:17" ht="18.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B6" s="10"/>
-      <c r="C6" s="11"/>
-      <c r="D6" s="11"/>
-      <c r="E6" s="11"/>
-      <c r="F6" s="11"/>
-      <c r="G6" s="11"/>
-      <c r="H6" s="11"/>
-      <c r="I6" s="11"/>
-      <c r="J6" s="11"/>
-      <c r="K6" s="12"/>
+      <c r="B6" s="9"/>
+      <c r="C6" s="10"/>
+      <c r="D6" s="10"/>
+      <c r="E6" s="10"/>
+      <c r="F6" s="10"/>
+      <c r="G6" s="10"/>
+      <c r="H6" s="10"/>
+      <c r="I6" s="10"/>
+      <c r="J6" s="10"/>
+      <c r="K6" s="11"/>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
@@ -5810,10 +5318,10 @@
       </c>
     </row>
     <row r="8" spans="1:17" ht="11.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B8" s="14" t="s">
+      <c r="B8" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F8" s="14"/>
+      <c r="F8" s="13"/>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B9" s="1"/>
@@ -5826,7 +5334,7 @@
       <c r="I9" s="2"/>
       <c r="J9" s="2"/>
       <c r="K9" s="3"/>
-      <c r="M9" s="13" t="s">
+      <c r="M9" s="12" t="s">
         <v>20</v>
       </c>
       <c r="N9" s="2"/>
@@ -5836,54 +5344,32 @@
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B10" s="4"/>
-      <c r="C10" s="5"/>
-      <c r="D10" s="5"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
-      <c r="G10" s="5"/>
-      <c r="H10" s="5"/>
-      <c r="I10" s="5"/>
-      <c r="J10" s="5"/>
-      <c r="K10" s="6"/>
+      <c r="K10" s="5"/>
       <c r="M10" s="4"/>
-      <c r="N10" s="5"/>
-      <c r="O10" s="5"/>
-      <c r="P10" s="5"/>
-      <c r="Q10" s="6"/>
+      <c r="Q10" s="5"/>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B11" s="4"/>
-      <c r="C11" s="5"/>
-      <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
-      <c r="F11" s="5"/>
-      <c r="G11" s="5"/>
-      <c r="H11" s="5"/>
-      <c r="I11" s="5"/>
-      <c r="J11" s="5"/>
-      <c r="K11" s="6"/>
+      <c r="K11" s="5"/>
       <c r="M11" s="4"/>
-      <c r="N11" s="5"/>
-      <c r="O11" s="5"/>
-      <c r="P11" s="5"/>
-      <c r="Q11" s="6"/>
+      <c r="Q11" s="5"/>
     </row>
     <row r="12" spans="1:17" ht="18.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B12" s="7"/>
-      <c r="C12" s="8"/>
-      <c r="D12" s="8"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="8"/>
-      <c r="G12" s="8"/>
-      <c r="H12" s="8"/>
-      <c r="I12" s="8"/>
-      <c r="J12" s="8"/>
-      <c r="K12" s="9"/>
-      <c r="M12" s="7"/>
-      <c r="N12" s="8"/>
-      <c r="O12" s="8"/>
-      <c r="P12" s="8"/>
-      <c r="Q12" s="9"/>
+      <c r="B12" s="6"/>
+      <c r="C12" s="7"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="7"/>
+      <c r="G12" s="7"/>
+      <c r="H12" s="7"/>
+      <c r="I12" s="7"/>
+      <c r="J12" s="7"/>
+      <c r="K12" s="8"/>
+      <c r="M12" s="6"/>
+      <c r="N12" s="7"/>
+      <c r="O12" s="7"/>
+      <c r="P12" s="7"/>
+      <c r="Q12" s="8"/>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" t="s">
@@ -5891,10 +5377,10 @@
       </c>
     </row>
     <row r="14" spans="1:17" ht="11.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B14" s="14" t="s">
+      <c r="B14" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="F14" s="14"/>
+      <c r="F14" s="13"/>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B15" s="1"/>
@@ -5910,36 +5396,28 @@
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B16" s="4"/>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5"/>
-      <c r="E16" s="5"/>
-      <c r="F16" s="5"/>
-      <c r="G16" s="5"/>
-      <c r="H16" s="5"/>
-      <c r="I16" s="5"/>
-      <c r="J16" s="5"/>
-      <c r="K16" s="6"/>
+      <c r="K16" s="5"/>
     </row>
     <row r="17" spans="1:17" ht="18.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B17" s="7"/>
-      <c r="C17" s="8"/>
-      <c r="D17" s="8"/>
-      <c r="E17" s="8"/>
-      <c r="F17" s="8"/>
-      <c r="G17" s="8"/>
-      <c r="H17" s="8"/>
-      <c r="I17" s="8"/>
-      <c r="J17" s="8"/>
-      <c r="K17" s="9"/>
+      <c r="B17" s="6"/>
+      <c r="C17" s="7"/>
+      <c r="D17" s="7"/>
+      <c r="E17" s="7"/>
+      <c r="F17" s="7"/>
+      <c r="G17" s="7"/>
+      <c r="H17" s="7"/>
+      <c r="I17" s="7"/>
+      <c r="J17" s="7"/>
+      <c r="K17" s="8"/>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18" s="15" t="s">
+      <c r="A18" s="14" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="19" spans="1:17" ht="11.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A19" s="15"/>
-      <c r="B19" s="14" t="s">
+      <c r="A19" s="14"/>
+      <c r="B19" s="13" t="s">
         <v>22</v>
       </c>
     </row>
@@ -5954,7 +5432,7 @@
       <c r="I20" s="2"/>
       <c r="J20" s="2"/>
       <c r="K20" s="3"/>
-      <c r="M20" s="13" t="s">
+      <c r="M20" s="12" t="s">
         <v>20</v>
       </c>
       <c r="N20" s="2"/>
@@ -5964,71 +5442,38 @@
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B21" s="4"/>
-      <c r="C21" s="5"/>
-      <c r="D21" s="5"/>
-      <c r="E21" s="5"/>
-      <c r="F21" s="5"/>
-      <c r="G21" s="5"/>
-      <c r="H21" s="5"/>
-      <c r="I21" s="5"/>
-      <c r="J21" s="5"/>
-      <c r="K21" s="6"/>
+      <c r="K21" s="5"/>
       <c r="M21" s="4"/>
-      <c r="N21" s="5"/>
-      <c r="O21" s="5"/>
-      <c r="P21" s="5"/>
-      <c r="Q21" s="6"/>
+      <c r="Q21" s="5"/>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B22" s="4"/>
-      <c r="C22" s="5"/>
-      <c r="D22" s="5"/>
-      <c r="E22" s="5"/>
-      <c r="F22" s="5"/>
-      <c r="G22" s="5"/>
-      <c r="H22" s="5"/>
-      <c r="I22" s="5"/>
-      <c r="J22" s="5"/>
-      <c r="K22" s="6"/>
+      <c r="K22" s="5"/>
       <c r="M22" s="4"/>
-      <c r="N22" s="5"/>
-      <c r="O22" s="5"/>
-      <c r="P22" s="5"/>
-      <c r="Q22" s="6"/>
+      <c r="Q22" s="5"/>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B23" s="4"/>
-      <c r="C23" s="5"/>
-      <c r="D23" s="5"/>
-      <c r="E23" s="5"/>
-      <c r="F23" s="5"/>
-      <c r="G23" s="5"/>
-      <c r="H23" s="5"/>
-      <c r="I23" s="5"/>
-      <c r="J23" s="5"/>
-      <c r="K23" s="6"/>
+      <c r="K23" s="5"/>
       <c r="M23" s="4"/>
-      <c r="N23" s="5"/>
-      <c r="O23" s="5"/>
-      <c r="P23" s="5"/>
-      <c r="Q23" s="6"/>
+      <c r="Q23" s="5"/>
     </row>
     <row r="24" spans="1:17" ht="18.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B24" s="7"/>
-      <c r="C24" s="8"/>
-      <c r="D24" s="8"/>
-      <c r="E24" s="8"/>
-      <c r="F24" s="8"/>
-      <c r="G24" s="8"/>
-      <c r="H24" s="8"/>
-      <c r="I24" s="8"/>
-      <c r="J24" s="8"/>
-      <c r="K24" s="9"/>
-      <c r="M24" s="7"/>
-      <c r="N24" s="8"/>
-      <c r="O24" s="8"/>
-      <c r="P24" s="8"/>
-      <c r="Q24" s="9"/>
+      <c r="B24" s="6"/>
+      <c r="C24" s="7"/>
+      <c r="D24" s="7"/>
+      <c r="E24" s="7"/>
+      <c r="F24" s="7"/>
+      <c r="G24" s="7"/>
+      <c r="H24" s="7"/>
+      <c r="I24" s="7"/>
+      <c r="J24" s="7"/>
+      <c r="K24" s="8"/>
+      <c r="M24" s="6"/>
+      <c r="N24" s="7"/>
+      <c r="O24" s="7"/>
+      <c r="P24" s="7"/>
+      <c r="Q24" s="8"/>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" t="s">
@@ -6036,7 +5481,7 @@
       </c>
     </row>
     <row r="26" spans="1:17" ht="11.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B26" s="14" t="s">
+      <c r="B26" s="13" t="s">
         <v>24</v>
       </c>
     </row>
@@ -6054,51 +5499,27 @@
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B28" s="4"/>
-      <c r="C28" s="5"/>
-      <c r="D28" s="5"/>
-      <c r="E28" s="5"/>
-      <c r="F28" s="5"/>
-      <c r="G28" s="5"/>
-      <c r="H28" s="5"/>
-      <c r="I28" s="5"/>
-      <c r="J28" s="5"/>
-      <c r="K28" s="6"/>
+      <c r="K28" s="5"/>
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B29" s="4"/>
-      <c r="C29" s="5"/>
-      <c r="D29" s="5"/>
-      <c r="E29" s="5"/>
-      <c r="F29" s="5"/>
-      <c r="G29" s="5"/>
-      <c r="H29" s="5"/>
-      <c r="I29" s="5"/>
-      <c r="J29" s="5"/>
-      <c r="K29" s="6"/>
+      <c r="K29" s="5"/>
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B30" s="4"/>
-      <c r="C30" s="5"/>
-      <c r="D30" s="5"/>
-      <c r="E30" s="5"/>
-      <c r="F30" s="5"/>
-      <c r="G30" s="5"/>
-      <c r="H30" s="5"/>
-      <c r="I30" s="5"/>
-      <c r="J30" s="5"/>
-      <c r="K30" s="6"/>
+      <c r="K30" s="5"/>
     </row>
     <row r="31" spans="1:17" ht="18.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B31" s="7"/>
-      <c r="C31" s="8"/>
-      <c r="D31" s="8"/>
-      <c r="E31" s="8"/>
-      <c r="F31" s="8"/>
-      <c r="G31" s="8"/>
-      <c r="H31" s="8"/>
-      <c r="I31" s="8"/>
-      <c r="J31" s="8"/>
-      <c r="K31" s="9"/>
+      <c r="B31" s="6"/>
+      <c r="C31" s="7"/>
+      <c r="D31" s="7"/>
+      <c r="E31" s="7"/>
+      <c r="F31" s="7"/>
+      <c r="G31" s="7"/>
+      <c r="H31" s="7"/>
+      <c r="I31" s="7"/>
+      <c r="J31" s="7"/>
+      <c r="K31" s="8"/>
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" t="s">
@@ -6106,7 +5527,7 @@
       </c>
     </row>
     <row r="33" spans="1:17" ht="11.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B33" s="14" t="s">
+      <c r="B33" s="13" t="s">
         <v>25</v>
       </c>
     </row>
@@ -6121,8 +5542,7 @@
       <c r="I34" s="2"/>
       <c r="J34" s="2"/>
       <c r="K34" s="3"/>
-      <c r="L34" s="5"/>
-      <c r="M34" s="13" t="s">
+      <c r="M34" s="12" t="s">
         <v>20</v>
       </c>
       <c r="N34" s="2"/>
@@ -6132,57 +5552,32 @@
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B35" s="4"/>
-      <c r="C35" s="5"/>
-      <c r="D35" s="5"/>
-      <c r="E35" s="5"/>
-      <c r="F35" s="5"/>
-      <c r="G35" s="5"/>
-      <c r="H35" s="5"/>
-      <c r="I35" s="5"/>
-      <c r="J35" s="5"/>
-      <c r="K35" s="6"/>
-      <c r="L35" s="5"/>
+      <c r="K35" s="5"/>
       <c r="M35" s="4"/>
-      <c r="N35" s="5"/>
-      <c r="O35" s="5"/>
-      <c r="P35" s="5"/>
-      <c r="Q35" s="6"/>
+      <c r="Q35" s="5"/>
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B36" s="4"/>
-      <c r="C36" s="5"/>
-      <c r="D36" s="5"/>
-      <c r="E36" s="5"/>
-      <c r="F36" s="5"/>
-      <c r="G36" s="5"/>
-      <c r="H36" s="5"/>
-      <c r="I36" s="5"/>
-      <c r="J36" s="5"/>
-      <c r="K36" s="6"/>
-      <c r="L36" s="5"/>
+      <c r="K36" s="5"/>
       <c r="M36" s="4"/>
-      <c r="N36" s="5"/>
-      <c r="O36" s="5"/>
-      <c r="P36" s="5"/>
-      <c r="Q36" s="6"/>
+      <c r="Q36" s="5"/>
     </row>
     <row r="37" spans="1:17" ht="18.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B37" s="7"/>
-      <c r="C37" s="8"/>
-      <c r="D37" s="8"/>
-      <c r="E37" s="8"/>
-      <c r="F37" s="8"/>
-      <c r="G37" s="8"/>
-      <c r="H37" s="8"/>
-      <c r="I37" s="8"/>
-      <c r="J37" s="8"/>
-      <c r="K37" s="9"/>
-      <c r="L37" s="5"/>
-      <c r="M37" s="7"/>
-      <c r="N37" s="8"/>
-      <c r="O37" s="8"/>
-      <c r="P37" s="8"/>
-      <c r="Q37" s="9"/>
+      <c r="B37" s="6"/>
+      <c r="C37" s="7"/>
+      <c r="D37" s="7"/>
+      <c r="E37" s="7"/>
+      <c r="F37" s="7"/>
+      <c r="G37" s="7"/>
+      <c r="H37" s="7"/>
+      <c r="I37" s="7"/>
+      <c r="J37" s="7"/>
+      <c r="K37" s="8"/>
+      <c r="M37" s="6"/>
+      <c r="N37" s="7"/>
+      <c r="O37" s="7"/>
+      <c r="P37" s="7"/>
+      <c r="Q37" s="8"/>
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" t="s">
@@ -6191,25 +5586,18 @@
       <c r="J38" t="s">
         <v>19</v>
       </c>
-      <c r="K38" s="5"/>
-      <c r="L38" s="5"/>
-      <c r="M38" s="5"/>
-      <c r="N38" s="5"/>
-      <c r="O38" s="5"/>
-      <c r="P38" s="5"/>
-      <c r="Q38" s="5"/>
     </row>
     <row r="39" spans="1:17" ht="18.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B39" s="8"/>
-      <c r="C39" s="8"/>
-      <c r="D39" s="8"/>
-      <c r="E39" s="8"/>
-      <c r="F39" s="8"/>
-      <c r="G39" s="8"/>
-      <c r="J39" s="8"/>
-      <c r="K39" s="8"/>
-      <c r="L39" s="8"/>
-      <c r="M39" s="8"/>
+      <c r="B39" s="7"/>
+      <c r="C39" s="7"/>
+      <c r="D39" s="7"/>
+      <c r="E39" s="7"/>
+      <c r="F39" s="7"/>
+      <c r="G39" s="7"/>
+      <c r="J39" s="7"/>
+      <c r="K39" s="7"/>
+      <c r="L39" s="7"/>
+      <c r="M39" s="7"/>
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" t="s">
@@ -6220,16 +5608,16 @@
       </c>
     </row>
     <row r="41" spans="1:17" ht="18.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B41" s="8"/>
-      <c r="C41" s="8"/>
-      <c r="D41" s="8"/>
-      <c r="E41" s="8"/>
-      <c r="F41" s="8"/>
-      <c r="G41" s="8"/>
-      <c r="J41" s="8"/>
-      <c r="K41" s="8"/>
-      <c r="L41" s="8"/>
-      <c r="M41" s="8"/>
+      <c r="B41" s="7"/>
+      <c r="C41" s="7"/>
+      <c r="D41" s="7"/>
+      <c r="E41" s="7"/>
+      <c r="F41" s="7"/>
+      <c r="G41" s="7"/>
+      <c r="J41" s="7"/>
+      <c r="K41" s="7"/>
+      <c r="L41" s="7"/>
+      <c r="M41" s="7"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>
@@ -6260,11 +5648,11 @@
       </c>
     </row>
     <row r="2" spans="1:6" ht="26" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B2" s="10"/>
-      <c r="C2" s="11"/>
-      <c r="D2" s="11"/>
-      <c r="E2" s="11"/>
-      <c r="F2" s="12"/>
+      <c r="B2" s="9"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="11"/>
     </row>
     <row r="3" spans="1:6" ht="11.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
     <row r="4" spans="1:6" x14ac:dyDescent="0.55000000000000004">
@@ -6274,19 +5662,19 @@
     </row>
     <row r="5" spans="1:6" ht="11.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.6"/>
     <row r="6" spans="1:6" ht="54.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B6" s="25" t="s">
+      <c r="B6" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="C6" s="26" t="s">
+      <c r="C6" s="25" t="s">
         <v>28</v>
       </c>
-      <c r="D6" s="27" t="s">
+      <c r="D6" s="26" t="s">
         <v>29</v>
       </c>
-      <c r="E6" s="27" t="s">
+      <c r="E6" s="26" t="s">
         <v>31</v>
       </c>
-      <c r="F6" s="28" t="s">
+      <c r="F6" s="27" t="s">
         <v>30</v>
       </c>
     </row>
@@ -6294,101 +5682,101 @@
       <c r="A7">
         <v>1</v>
       </c>
-      <c r="B7" s="22"/>
-      <c r="C7" s="23"/>
-      <c r="D7" s="23"/>
-      <c r="E7" s="23"/>
-      <c r="F7" s="24"/>
+      <c r="B7" s="21"/>
+      <c r="C7" s="22"/>
+      <c r="D7" s="22"/>
+      <c r="E7" s="22"/>
+      <c r="F7" s="23"/>
     </row>
     <row r="8" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A8">
         <v>2</v>
       </c>
-      <c r="B8" s="17"/>
-      <c r="C8" s="16"/>
-      <c r="D8" s="16"/>
-      <c r="E8" s="16"/>
-      <c r="F8" s="18"/>
+      <c r="B8" s="16"/>
+      <c r="C8" s="15"/>
+      <c r="D8" s="15"/>
+      <c r="E8" s="15"/>
+      <c r="F8" s="17"/>
     </row>
     <row r="9" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A9">
         <v>3</v>
       </c>
-      <c r="B9" s="17"/>
-      <c r="C9" s="16"/>
-      <c r="D9" s="16"/>
-      <c r="E9" s="16"/>
-      <c r="F9" s="18"/>
+      <c r="B9" s="16"/>
+      <c r="C9" s="15"/>
+      <c r="D9" s="15"/>
+      <c r="E9" s="15"/>
+      <c r="F9" s="17"/>
     </row>
     <row r="10" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A10">
         <v>4</v>
       </c>
-      <c r="B10" s="17"/>
-      <c r="C10" s="16"/>
-      <c r="D10" s="16"/>
-      <c r="E10" s="16"/>
-      <c r="F10" s="18"/>
+      <c r="B10" s="16"/>
+      <c r="C10" s="15"/>
+      <c r="D10" s="15"/>
+      <c r="E10" s="15"/>
+      <c r="F10" s="17"/>
     </row>
     <row r="11" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A11">
         <v>5</v>
       </c>
-      <c r="B11" s="17"/>
-      <c r="C11" s="16"/>
-      <c r="D11" s="16"/>
-      <c r="E11" s="16"/>
-      <c r="F11" s="18"/>
+      <c r="B11" s="16"/>
+      <c r="C11" s="15"/>
+      <c r="D11" s="15"/>
+      <c r="E11" s="15"/>
+      <c r="F11" s="17"/>
     </row>
     <row r="12" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A12">
         <v>6</v>
       </c>
-      <c r="B12" s="17"/>
-      <c r="C12" s="16"/>
-      <c r="D12" s="16"/>
-      <c r="E12" s="16"/>
-      <c r="F12" s="18"/>
+      <c r="B12" s="16"/>
+      <c r="C12" s="15"/>
+      <c r="D12" s="15"/>
+      <c r="E12" s="15"/>
+      <c r="F12" s="17"/>
     </row>
     <row r="13" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A13">
         <v>7</v>
       </c>
-      <c r="B13" s="17"/>
-      <c r="C13" s="16"/>
-      <c r="D13" s="16"/>
-      <c r="E13" s="16"/>
-      <c r="F13" s="18"/>
+      <c r="B13" s="16"/>
+      <c r="C13" s="15"/>
+      <c r="D13" s="15"/>
+      <c r="E13" s="15"/>
+      <c r="F13" s="17"/>
     </row>
     <row r="14" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A14">
         <v>8</v>
       </c>
-      <c r="B14" s="17"/>
-      <c r="C14" s="16"/>
-      <c r="D14" s="16"/>
-      <c r="E14" s="16"/>
-      <c r="F14" s="18"/>
+      <c r="B14" s="16"/>
+      <c r="C14" s="15"/>
+      <c r="D14" s="15"/>
+      <c r="E14" s="15"/>
+      <c r="F14" s="17"/>
     </row>
     <row r="15" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A15">
         <v>9</v>
       </c>
-      <c r="B15" s="17"/>
-      <c r="C15" s="16"/>
-      <c r="D15" s="16"/>
-      <c r="E15" s="16"/>
-      <c r="F15" s="18"/>
+      <c r="B15" s="16"/>
+      <c r="C15" s="15"/>
+      <c r="D15" s="15"/>
+      <c r="E15" s="15"/>
+      <c r="F15" s="17"/>
     </row>
     <row r="16" spans="1:6" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A16">
         <v>10</v>
       </c>
-      <c r="B16" s="19"/>
-      <c r="C16" s="20"/>
-      <c r="D16" s="20"/>
-      <c r="E16" s="20"/>
-      <c r="F16" s="21"/>
+      <c r="B16" s="18"/>
+      <c r="C16" s="19"/>
+      <c r="D16" s="19"/>
+      <c r="E16" s="19"/>
+      <c r="F16" s="20"/>
     </row>
     <row r="17" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
     <row r="18" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
@@ -6422,126 +5810,116 @@
   <sheetData>
     <row r="1" spans="2:30" ht="18.5" thickBot="1" x14ac:dyDescent="0.6"/>
     <row r="2" spans="2:30" x14ac:dyDescent="0.55000000000000004">
-      <c r="N2" s="29"/>
-      <c r="O2" s="30"/>
-      <c r="P2" s="30"/>
-      <c r="Q2" s="30"/>
-      <c r="R2" s="31"/>
-      <c r="U2" s="47" t="s">
+      <c r="N2" s="28"/>
+      <c r="O2" s="29"/>
+      <c r="P2" s="29"/>
+      <c r="Q2" s="29"/>
+      <c r="R2" s="30"/>
+      <c r="U2" s="46" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="3" spans="2:30" x14ac:dyDescent="0.55000000000000004">
-      <c r="L3" s="5"/>
-      <c r="M3" s="5"/>
-      <c r="N3" s="32" t="s">
+      <c r="N3" s="31" t="s">
         <v>32</v>
       </c>
-      <c r="O3" s="33"/>
-      <c r="P3" s="33"/>
-      <c r="Q3" s="33"/>
-      <c r="R3" s="34"/>
-      <c r="U3" s="48" t="s">
+      <c r="O3" s="32"/>
+      <c r="P3" s="32"/>
+      <c r="Q3" s="32"/>
+      <c r="R3" s="33"/>
+      <c r="U3" s="47" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="4" spans="2:30" ht="18.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="L4" s="5"/>
-      <c r="M4" s="5"/>
-      <c r="N4" s="35"/>
-      <c r="O4" s="36"/>
-      <c r="P4" s="36"/>
-      <c r="Q4" s="36"/>
-      <c r="R4" s="37"/>
-    </row>
-    <row r="5" spans="2:30" x14ac:dyDescent="0.55000000000000004">
-      <c r="L5" s="5"/>
-      <c r="M5" s="5"/>
-      <c r="N5" s="5"/>
-      <c r="O5" s="5"/>
+      <c r="N4" s="34"/>
+      <c r="O4" s="35"/>
+      <c r="P4" s="35"/>
+      <c r="Q4" s="35"/>
+      <c r="R4" s="36"/>
     </row>
     <row r="6" spans="2:30" ht="18.5" thickBot="1" x14ac:dyDescent="0.6"/>
     <row r="7" spans="2:30" x14ac:dyDescent="0.55000000000000004">
-      <c r="B7" s="38">
+      <c r="B7" s="37">
         <v>1</v>
       </c>
-      <c r="C7" s="39"/>
-      <c r="D7" s="39"/>
-      <c r="E7" s="40"/>
-      <c r="G7" s="38">
+      <c r="C7" s="38"/>
+      <c r="D7" s="38"/>
+      <c r="E7" s="39"/>
+      <c r="G7" s="37">
         <v>2</v>
       </c>
-      <c r="H7" s="39"/>
-      <c r="I7" s="39"/>
-      <c r="J7" s="40"/>
-      <c r="L7" s="38"/>
-      <c r="M7" s="39"/>
-      <c r="N7" s="39"/>
-      <c r="O7" s="40"/>
-      <c r="Q7" s="38"/>
-      <c r="R7" s="39"/>
-      <c r="S7" s="39"/>
-      <c r="T7" s="40"/>
-      <c r="V7" s="38"/>
-      <c r="W7" s="39"/>
-      <c r="X7" s="39"/>
-      <c r="Y7" s="40"/>
-      <c r="AA7" s="38"/>
-      <c r="AB7" s="39"/>
-      <c r="AC7" s="39"/>
-      <c r="AD7" s="40"/>
+      <c r="H7" s="38"/>
+      <c r="I7" s="38"/>
+      <c r="J7" s="39"/>
+      <c r="L7" s="37"/>
+      <c r="M7" s="38"/>
+      <c r="N7" s="38"/>
+      <c r="O7" s="39"/>
+      <c r="Q7" s="37"/>
+      <c r="R7" s="38"/>
+      <c r="S7" s="38"/>
+      <c r="T7" s="39"/>
+      <c r="V7" s="37"/>
+      <c r="W7" s="38"/>
+      <c r="X7" s="38"/>
+      <c r="Y7" s="39"/>
+      <c r="AA7" s="37"/>
+      <c r="AB7" s="38"/>
+      <c r="AC7" s="38"/>
+      <c r="AD7" s="39"/>
     </row>
     <row r="8" spans="2:30" x14ac:dyDescent="0.55000000000000004">
-      <c r="B8" s="41"/>
-      <c r="C8" s="42"/>
-      <c r="D8" s="42"/>
-      <c r="E8" s="43"/>
-      <c r="G8" s="41"/>
-      <c r="H8" s="42"/>
-      <c r="I8" s="42"/>
-      <c r="J8" s="43"/>
-      <c r="L8" s="41"/>
-      <c r="M8" s="42"/>
-      <c r="N8" s="42"/>
-      <c r="O8" s="43"/>
-      <c r="Q8" s="41"/>
-      <c r="R8" s="42"/>
-      <c r="S8" s="42"/>
-      <c r="T8" s="43"/>
-      <c r="V8" s="41"/>
-      <c r="W8" s="42"/>
-      <c r="X8" s="42"/>
-      <c r="Y8" s="43"/>
-      <c r="AA8" s="41"/>
-      <c r="AB8" s="42"/>
-      <c r="AC8" s="42"/>
-      <c r="AD8" s="43"/>
+      <c r="B8" s="40"/>
+      <c r="C8" s="41"/>
+      <c r="D8" s="41"/>
+      <c r="E8" s="42"/>
+      <c r="G8" s="40"/>
+      <c r="H8" s="41"/>
+      <c r="I8" s="41"/>
+      <c r="J8" s="42"/>
+      <c r="L8" s="40"/>
+      <c r="M8" s="41"/>
+      <c r="N8" s="41"/>
+      <c r="O8" s="42"/>
+      <c r="Q8" s="40"/>
+      <c r="R8" s="41"/>
+      <c r="S8" s="41"/>
+      <c r="T8" s="42"/>
+      <c r="V8" s="40"/>
+      <c r="W8" s="41"/>
+      <c r="X8" s="41"/>
+      <c r="Y8" s="42"/>
+      <c r="AA8" s="40"/>
+      <c r="AB8" s="41"/>
+      <c r="AC8" s="41"/>
+      <c r="AD8" s="42"/>
     </row>
     <row r="9" spans="2:30" ht="18.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B9" s="44"/>
-      <c r="C9" s="45"/>
-      <c r="D9" s="45"/>
-      <c r="E9" s="46"/>
-      <c r="G9" s="44"/>
-      <c r="H9" s="45"/>
-      <c r="I9" s="45"/>
-      <c r="J9" s="46"/>
-      <c r="L9" s="44"/>
-      <c r="M9" s="45"/>
-      <c r="N9" s="45"/>
-      <c r="O9" s="46"/>
-      <c r="Q9" s="44"/>
-      <c r="R9" s="45"/>
-      <c r="S9" s="45"/>
-      <c r="T9" s="46"/>
-      <c r="V9" s="44"/>
-      <c r="W9" s="45"/>
-      <c r="X9" s="45"/>
-      <c r="Y9" s="46"/>
-      <c r="AA9" s="44"/>
-      <c r="AB9" s="45"/>
-      <c r="AC9" s="45"/>
-      <c r="AD9" s="46"/>
+      <c r="B9" s="43"/>
+      <c r="C9" s="44"/>
+      <c r="D9" s="44"/>
+      <c r="E9" s="45"/>
+      <c r="G9" s="43"/>
+      <c r="H9" s="44"/>
+      <c r="I9" s="44"/>
+      <c r="J9" s="45"/>
+      <c r="L9" s="43"/>
+      <c r="M9" s="44"/>
+      <c r="N9" s="44"/>
+      <c r="O9" s="45"/>
+      <c r="Q9" s="43"/>
+      <c r="R9" s="44"/>
+      <c r="S9" s="44"/>
+      <c r="T9" s="45"/>
+      <c r="V9" s="43"/>
+      <c r="W9" s="44"/>
+      <c r="X9" s="44"/>
+      <c r="Y9" s="45"/>
+      <c r="AA9" s="43"/>
+      <c r="AB9" s="44"/>
+      <c r="AC9" s="44"/>
+      <c r="AD9" s="45"/>
     </row>
     <row r="10" spans="2:30" ht="18.5" thickBot="1" x14ac:dyDescent="0.6"/>
     <row r="11" spans="2:30" x14ac:dyDescent="0.55000000000000004">
@@ -6570,43 +5948,37 @@
     </row>
     <row r="12" spans="2:30" x14ac:dyDescent="0.55000000000000004">
       <c r="C12" s="4"/>
-      <c r="D12" s="5"/>
-      <c r="E12" s="6"/>
+      <c r="E12" s="5"/>
       <c r="H12" s="4"/>
-      <c r="I12" s="5"/>
-      <c r="J12" s="6"/>
+      <c r="J12" s="5"/>
       <c r="M12" s="4"/>
-      <c r="N12" s="5"/>
-      <c r="O12" s="6"/>
+      <c r="O12" s="5"/>
       <c r="R12" s="4"/>
-      <c r="S12" s="5"/>
-      <c r="T12" s="6"/>
+      <c r="T12" s="5"/>
       <c r="W12" s="4"/>
-      <c r="X12" s="5"/>
-      <c r="Y12" s="6"/>
+      <c r="Y12" s="5"/>
       <c r="AB12" s="4"/>
-      <c r="AC12" s="5"/>
-      <c r="AD12" s="6"/>
+      <c r="AD12" s="5"/>
     </row>
     <row r="13" spans="2:30" ht="18.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="C13" s="7"/>
-      <c r="D13" s="8"/>
-      <c r="E13" s="9"/>
-      <c r="H13" s="7"/>
-      <c r="I13" s="8"/>
-      <c r="J13" s="9"/>
-      <c r="M13" s="7"/>
-      <c r="N13" s="8"/>
-      <c r="O13" s="9"/>
-      <c r="R13" s="7"/>
-      <c r="S13" s="8"/>
-      <c r="T13" s="9"/>
-      <c r="W13" s="7"/>
-      <c r="X13" s="8"/>
-      <c r="Y13" s="9"/>
-      <c r="AB13" s="7"/>
-      <c r="AC13" s="8"/>
-      <c r="AD13" s="9"/>
+      <c r="C13" s="6"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="8"/>
+      <c r="H13" s="6"/>
+      <c r="I13" s="7"/>
+      <c r="J13" s="8"/>
+      <c r="M13" s="6"/>
+      <c r="N13" s="7"/>
+      <c r="O13" s="8"/>
+      <c r="R13" s="6"/>
+      <c r="S13" s="7"/>
+      <c r="T13" s="8"/>
+      <c r="W13" s="6"/>
+      <c r="X13" s="7"/>
+      <c r="Y13" s="8"/>
+      <c r="AB13" s="6"/>
+      <c r="AC13" s="7"/>
+      <c r="AD13" s="8"/>
     </row>
     <row r="14" spans="2:30" ht="18.5" thickBot="1" x14ac:dyDescent="0.6"/>
     <row r="15" spans="2:30" x14ac:dyDescent="0.55000000000000004">
@@ -6635,43 +6007,37 @@
     </row>
     <row r="16" spans="2:30" x14ac:dyDescent="0.55000000000000004">
       <c r="C16" s="4"/>
-      <c r="D16" s="5"/>
-      <c r="E16" s="6"/>
+      <c r="E16" s="5"/>
       <c r="H16" s="4"/>
-      <c r="I16" s="5"/>
-      <c r="J16" s="6"/>
+      <c r="J16" s="5"/>
       <c r="M16" s="4"/>
-      <c r="N16" s="5"/>
-      <c r="O16" s="6"/>
+      <c r="O16" s="5"/>
       <c r="R16" s="4"/>
-      <c r="S16" s="5"/>
-      <c r="T16" s="6"/>
+      <c r="T16" s="5"/>
       <c r="W16" s="4"/>
-      <c r="X16" s="5"/>
-      <c r="Y16" s="6"/>
+      <c r="Y16" s="5"/>
       <c r="AB16" s="4"/>
-      <c r="AC16" s="5"/>
-      <c r="AD16" s="6"/>
+      <c r="AD16" s="5"/>
     </row>
     <row r="17" spans="3:30" ht="18.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="C17" s="7"/>
-      <c r="D17" s="8"/>
-      <c r="E17" s="9"/>
-      <c r="H17" s="7"/>
-      <c r="I17" s="8"/>
-      <c r="J17" s="9"/>
-      <c r="M17" s="7"/>
-      <c r="N17" s="8"/>
-      <c r="O17" s="9"/>
-      <c r="R17" s="7"/>
-      <c r="S17" s="8"/>
-      <c r="T17" s="9"/>
-      <c r="W17" s="7"/>
-      <c r="X17" s="8"/>
-      <c r="Y17" s="9"/>
-      <c r="AB17" s="7"/>
-      <c r="AC17" s="8"/>
-      <c r="AD17" s="9"/>
+      <c r="C17" s="6"/>
+      <c r="D17" s="7"/>
+      <c r="E17" s="8"/>
+      <c r="H17" s="6"/>
+      <c r="I17" s="7"/>
+      <c r="J17" s="8"/>
+      <c r="M17" s="6"/>
+      <c r="N17" s="7"/>
+      <c r="O17" s="8"/>
+      <c r="R17" s="6"/>
+      <c r="S17" s="7"/>
+      <c r="T17" s="8"/>
+      <c r="W17" s="6"/>
+      <c r="X17" s="7"/>
+      <c r="Y17" s="8"/>
+      <c r="AB17" s="6"/>
+      <c r="AC17" s="7"/>
+      <c r="AD17" s="8"/>
     </row>
     <row r="18" spans="3:30" ht="18.5" thickBot="1" x14ac:dyDescent="0.6"/>
     <row r="19" spans="3:30" x14ac:dyDescent="0.55000000000000004">
@@ -6700,43 +6066,37 @@
     </row>
     <row r="20" spans="3:30" x14ac:dyDescent="0.55000000000000004">
       <c r="C20" s="4"/>
-      <c r="D20" s="5"/>
-      <c r="E20" s="6"/>
+      <c r="E20" s="5"/>
       <c r="H20" s="4"/>
-      <c r="I20" s="5"/>
-      <c r="J20" s="6"/>
+      <c r="J20" s="5"/>
       <c r="M20" s="4"/>
-      <c r="N20" s="5"/>
-      <c r="O20" s="6"/>
+      <c r="O20" s="5"/>
       <c r="R20" s="4"/>
-      <c r="S20" s="5"/>
-      <c r="T20" s="6"/>
+      <c r="T20" s="5"/>
       <c r="W20" s="4"/>
-      <c r="X20" s="5"/>
-      <c r="Y20" s="6"/>
+      <c r="Y20" s="5"/>
       <c r="AB20" s="4"/>
-      <c r="AC20" s="5"/>
-      <c r="AD20" s="6"/>
+      <c r="AD20" s="5"/>
     </row>
     <row r="21" spans="3:30" ht="18.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="C21" s="7"/>
-      <c r="D21" s="8"/>
-      <c r="E21" s="9"/>
-      <c r="H21" s="7"/>
-      <c r="I21" s="8"/>
-      <c r="J21" s="9"/>
-      <c r="M21" s="7"/>
-      <c r="N21" s="8"/>
-      <c r="O21" s="9"/>
-      <c r="R21" s="7"/>
-      <c r="S21" s="8"/>
-      <c r="T21" s="9"/>
-      <c r="W21" s="7"/>
-      <c r="X21" s="8"/>
-      <c r="Y21" s="9"/>
-      <c r="AB21" s="7"/>
-      <c r="AC21" s="8"/>
-      <c r="AD21" s="9"/>
+      <c r="C21" s="6"/>
+      <c r="D21" s="7"/>
+      <c r="E21" s="8"/>
+      <c r="H21" s="6"/>
+      <c r="I21" s="7"/>
+      <c r="J21" s="8"/>
+      <c r="M21" s="6"/>
+      <c r="N21" s="7"/>
+      <c r="O21" s="8"/>
+      <c r="R21" s="6"/>
+      <c r="S21" s="7"/>
+      <c r="T21" s="8"/>
+      <c r="W21" s="6"/>
+      <c r="X21" s="7"/>
+      <c r="Y21" s="8"/>
+      <c r="AB21" s="6"/>
+      <c r="AC21" s="7"/>
+      <c r="AD21" s="8"/>
     </row>
     <row r="22" spans="3:30" ht="18.5" thickBot="1" x14ac:dyDescent="0.6"/>
     <row r="23" spans="3:30" x14ac:dyDescent="0.55000000000000004">
@@ -6761,43 +6121,37 @@
     </row>
     <row r="24" spans="3:30" x14ac:dyDescent="0.55000000000000004">
       <c r="C24" s="4"/>
-      <c r="D24" s="5"/>
-      <c r="E24" s="6"/>
+      <c r="E24" s="5"/>
       <c r="H24" s="4"/>
-      <c r="I24" s="5"/>
-      <c r="J24" s="6"/>
+      <c r="J24" s="5"/>
       <c r="M24" s="4"/>
-      <c r="N24" s="5"/>
-      <c r="O24" s="6"/>
+      <c r="O24" s="5"/>
       <c r="R24" s="4"/>
-      <c r="S24" s="5"/>
-      <c r="T24" s="6"/>
+      <c r="T24" s="5"/>
       <c r="W24" s="4"/>
-      <c r="X24" s="5"/>
-      <c r="Y24" s="6"/>
+      <c r="Y24" s="5"/>
       <c r="AB24" s="4"/>
-      <c r="AC24" s="5"/>
-      <c r="AD24" s="6"/>
+      <c r="AD24" s="5"/>
     </row>
     <row r="25" spans="3:30" ht="18.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="C25" s="7"/>
-      <c r="D25" s="8"/>
-      <c r="E25" s="9"/>
-      <c r="H25" s="7"/>
-      <c r="I25" s="8"/>
-      <c r="J25" s="9"/>
-      <c r="M25" s="7"/>
-      <c r="N25" s="8"/>
-      <c r="O25" s="9"/>
-      <c r="R25" s="7"/>
-      <c r="S25" s="8"/>
-      <c r="T25" s="9"/>
-      <c r="W25" s="7"/>
-      <c r="X25" s="8"/>
-      <c r="Y25" s="9"/>
-      <c r="AB25" s="7"/>
-      <c r="AC25" s="8"/>
-      <c r="AD25" s="9"/>
+      <c r="C25" s="6"/>
+      <c r="D25" s="7"/>
+      <c r="E25" s="8"/>
+      <c r="H25" s="6"/>
+      <c r="I25" s="7"/>
+      <c r="J25" s="8"/>
+      <c r="M25" s="6"/>
+      <c r="N25" s="7"/>
+      <c r="O25" s="8"/>
+      <c r="R25" s="6"/>
+      <c r="S25" s="7"/>
+      <c r="T25" s="8"/>
+      <c r="W25" s="6"/>
+      <c r="X25" s="7"/>
+      <c r="Y25" s="8"/>
+      <c r="AB25" s="6"/>
+      <c r="AC25" s="7"/>
+      <c r="AD25" s="8"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>
@@ -6822,311 +6176,92 @@
     </row>
     <row r="3" spans="1:26" ht="18.5" thickBot="1" x14ac:dyDescent="0.6"/>
     <row r="4" spans="1:26" ht="18.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="E4" s="49" t="s">
+      <c r="E4" s="48" t="s">
         <v>39</v>
       </c>
-      <c r="F4" s="11"/>
-      <c r="G4" s="11"/>
-      <c r="H4" s="11"/>
-      <c r="I4" s="12"/>
-      <c r="L4" s="10" t="s">
+      <c r="F4" s="10"/>
+      <c r="G4" s="10"/>
+      <c r="H4" s="10"/>
+      <c r="I4" s="11"/>
+      <c r="L4" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="M4" s="11"/>
-      <c r="N4" s="11"/>
-      <c r="O4" s="11"/>
-      <c r="P4" s="12"/>
-      <c r="S4" s="10" t="s">
+      <c r="M4" s="10"/>
+      <c r="N4" s="10"/>
+      <c r="O4" s="10"/>
+      <c r="P4" s="11"/>
+      <c r="S4" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="T4" s="11"/>
-      <c r="U4" s="11"/>
-      <c r="V4" s="12"/>
-    </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.55000000000000004">
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5"/>
-      <c r="I5" s="5"/>
-      <c r="J5" s="5"/>
-      <c r="K5" s="5"/>
-      <c r="L5" s="5"/>
-      <c r="M5" s="5"/>
-      <c r="N5" s="5"/>
-      <c r="O5" s="5"/>
-      <c r="P5" s="5"/>
-      <c r="Q5" s="5"/>
-      <c r="R5" s="5"/>
-      <c r="S5" s="5"/>
-      <c r="T5" s="5"/>
-      <c r="U5" s="5"/>
-      <c r="V5" s="5"/>
-      <c r="W5" s="5"/>
-      <c r="X5" s="5"/>
-      <c r="Y5" s="5"/>
-    </row>
-    <row r="6" spans="1:26" ht="18.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="E6" s="5"/>
-      <c r="F6" s="5"/>
-      <c r="G6" s="5"/>
-      <c r="H6" s="5"/>
-      <c r="I6" s="5"/>
-      <c r="J6" s="5"/>
-      <c r="K6" s="5"/>
-      <c r="L6" s="5"/>
-      <c r="M6" s="5"/>
-      <c r="N6" s="5"/>
-      <c r="O6" s="5"/>
-      <c r="P6" s="5"/>
-      <c r="Q6" s="5"/>
-      <c r="R6" s="5"/>
-      <c r="S6" s="5"/>
-      <c r="T6" s="5"/>
-      <c r="U6" s="5"/>
-      <c r="V6" s="5"/>
-      <c r="W6" s="5"/>
-      <c r="X6" s="5"/>
-      <c r="Y6" s="5"/>
-    </row>
+      <c r="T4" s="10"/>
+      <c r="U4" s="10"/>
+      <c r="V4" s="11"/>
+    </row>
+    <row r="6" spans="1:26" ht="18.5" thickBot="1" x14ac:dyDescent="0.6"/>
     <row r="7" spans="1:26" ht="18.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="E7" s="10" t="s">
+      <c r="E7" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="F7" s="11"/>
-      <c r="G7" s="11"/>
-      <c r="H7" s="11"/>
-      <c r="I7" s="12"/>
-      <c r="L7" s="10" t="s">
+      <c r="F7" s="10"/>
+      <c r="G7" s="10"/>
+      <c r="H7" s="10"/>
+      <c r="I7" s="11"/>
+      <c r="L7" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="M7" s="11"/>
-      <c r="N7" s="11"/>
-      <c r="O7" s="11"/>
-      <c r="P7" s="12"/>
-      <c r="S7" s="10" t="s">
+      <c r="M7" s="10"/>
+      <c r="N7" s="10"/>
+      <c r="O7" s="10"/>
+      <c r="P7" s="11"/>
+      <c r="S7" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="T7" s="11"/>
-      <c r="U7" s="11"/>
-      <c r="V7" s="12"/>
-      <c r="W7" s="5"/>
-      <c r="X7" s="5"/>
-      <c r="Y7" s="5"/>
+      <c r="T7" s="10"/>
+      <c r="U7" s="10"/>
+      <c r="V7" s="11"/>
     </row>
     <row r="8" spans="1:26" ht="18.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A8" s="10" t="s">
+      <c r="A8" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="B8" s="12"/>
-      <c r="C8" s="5"/>
-      <c r="D8" s="5"/>
-      <c r="E8" s="5"/>
-      <c r="F8" s="5"/>
-      <c r="G8" s="5"/>
-      <c r="H8" s="5"/>
-      <c r="I8" s="5"/>
-      <c r="J8" s="5"/>
-      <c r="K8" s="5"/>
-      <c r="L8" s="5"/>
-      <c r="M8" s="5"/>
-      <c r="N8" s="5"/>
-      <c r="O8" s="5"/>
-      <c r="P8" s="5"/>
-      <c r="Q8" s="5"/>
-      <c r="R8" s="5"/>
-      <c r="S8" s="5"/>
-      <c r="T8" s="5"/>
-      <c r="U8" s="5"/>
-      <c r="V8" s="5"/>
-      <c r="W8" s="5"/>
-      <c r="X8" s="5"/>
-    </row>
-    <row r="9" spans="1:26" ht="18.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="E9" s="5"/>
-      <c r="F9" s="5"/>
-      <c r="G9" s="5"/>
-      <c r="H9" s="5"/>
-      <c r="I9" s="5"/>
-      <c r="J9" s="5"/>
-      <c r="K9" s="5"/>
-      <c r="L9" s="5"/>
-      <c r="M9" s="5"/>
-      <c r="N9" s="5"/>
-      <c r="O9" s="5"/>
-      <c r="P9" s="5"/>
-      <c r="Q9" s="5"/>
-      <c r="R9" s="5"/>
-      <c r="S9" s="5"/>
-      <c r="T9" s="5"/>
-      <c r="U9" s="5"/>
-      <c r="V9" s="5"/>
-      <c r="W9" s="5"/>
-      <c r="X9" s="5"/>
-      <c r="Y9" s="5"/>
-    </row>
+      <c r="B8" s="11"/>
+    </row>
+    <row r="9" spans="1:26" ht="18.5" thickBot="1" x14ac:dyDescent="0.6"/>
     <row r="10" spans="1:26" ht="18.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="E10" s="10" t="s">
+      <c r="E10" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="F10" s="11"/>
-      <c r="G10" s="11"/>
-      <c r="H10" s="11"/>
-      <c r="I10" s="12"/>
-      <c r="L10" s="10" t="s">
+      <c r="F10" s="10"/>
+      <c r="G10" s="10"/>
+      <c r="H10" s="10"/>
+      <c r="I10" s="11"/>
+      <c r="L10" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="M10" s="11"/>
-      <c r="N10" s="11"/>
-      <c r="O10" s="11"/>
-      <c r="P10" s="12"/>
-      <c r="S10" s="10" t="s">
+      <c r="M10" s="10"/>
+      <c r="N10" s="10"/>
+      <c r="O10" s="10"/>
+      <c r="P10" s="11"/>
+      <c r="S10" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="T10" s="11"/>
-      <c r="U10" s="11"/>
-      <c r="V10" s="12"/>
-      <c r="W10" s="5"/>
-      <c r="X10" s="5"/>
-      <c r="Y10" s="10" t="s">
+      <c r="T10" s="10"/>
+      <c r="U10" s="10"/>
+      <c r="V10" s="11"/>
+      <c r="Y10" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="Z10" s="12"/>
-    </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.55000000000000004">
-      <c r="E11" s="5"/>
-      <c r="F11" s="5"/>
-      <c r="G11" s="5"/>
-      <c r="H11" s="5"/>
-      <c r="I11" s="5"/>
-      <c r="J11" s="5"/>
-      <c r="K11" s="5"/>
-      <c r="L11" s="5"/>
-      <c r="M11" s="5"/>
-      <c r="N11" s="5"/>
-      <c r="O11" s="5"/>
-      <c r="P11" s="5"/>
-      <c r="Q11" s="5"/>
-      <c r="R11" s="5"/>
-      <c r="S11" s="5"/>
-      <c r="T11" s="5"/>
-      <c r="U11" s="5"/>
-      <c r="V11" s="5"/>
-      <c r="W11" s="5"/>
-      <c r="X11" s="5"/>
-      <c r="Y11" s="5"/>
-    </row>
-    <row r="12" spans="1:26" ht="18.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="F12" s="5"/>
-      <c r="G12" s="5"/>
-      <c r="H12" s="5"/>
-      <c r="I12" s="5"/>
-      <c r="J12" s="5"/>
-      <c r="K12" s="5"/>
-      <c r="L12" s="5"/>
-      <c r="M12" s="5"/>
-      <c r="N12" s="5"/>
-      <c r="O12" s="5"/>
-      <c r="P12" s="5"/>
-      <c r="Q12" s="5"/>
-      <c r="R12" s="5"/>
-      <c r="S12" s="5"/>
-      <c r="T12" s="5"/>
-      <c r="U12" s="5"/>
-      <c r="V12" s="5"/>
-      <c r="W12" s="5"/>
-      <c r="X12" s="5"/>
-      <c r="Y12" s="5"/>
-    </row>
+      <c r="Z10" s="11"/>
+    </row>
+    <row r="12" spans="1:26" ht="18.5" thickBot="1" x14ac:dyDescent="0.6"/>
     <row r="13" spans="1:26" ht="18.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="F13" s="5"/>
-      <c r="G13" s="5"/>
-      <c r="H13" s="5"/>
-      <c r="I13" s="5"/>
-      <c r="J13" s="5"/>
-      <c r="K13" s="5"/>
-      <c r="L13" s="10" t="s">
+      <c r="L13" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="M13" s="11"/>
-      <c r="N13" s="11"/>
-      <c r="O13" s="11"/>
-      <c r="P13" s="12"/>
-      <c r="Q13" s="5"/>
-      <c r="R13" s="5"/>
-      <c r="S13" s="5"/>
-      <c r="T13" s="5"/>
-      <c r="U13" s="5"/>
-      <c r="V13" s="5"/>
-      <c r="W13" s="5"/>
-      <c r="X13" s="5"/>
-      <c r="Y13" s="5"/>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.55000000000000004">
-      <c r="F14" s="5"/>
-      <c r="G14" s="5"/>
-      <c r="H14" s="5"/>
-      <c r="I14" s="5"/>
-      <c r="J14" s="5"/>
-      <c r="K14" s="5"/>
-      <c r="L14" s="5"/>
-      <c r="M14" s="5"/>
-      <c r="N14" s="5"/>
-      <c r="O14" s="5"/>
-      <c r="P14" s="5"/>
-      <c r="Q14" s="5"/>
-      <c r="R14" s="5"/>
-      <c r="S14" s="5"/>
-      <c r="T14" s="5"/>
-      <c r="U14" s="5"/>
-      <c r="V14" s="5"/>
-      <c r="W14" s="5"/>
-      <c r="X14" s="5"/>
-      <c r="Y14" s="5"/>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.55000000000000004">
-      <c r="F15" s="5"/>
-      <c r="G15" s="5"/>
-      <c r="H15" s="5"/>
-      <c r="I15" s="5"/>
-      <c r="J15" s="5"/>
-      <c r="K15" s="5"/>
-      <c r="L15" s="5"/>
-      <c r="M15" s="5"/>
-      <c r="N15" s="5"/>
-      <c r="O15" s="5"/>
-      <c r="P15" s="5"/>
-      <c r="Q15" s="5"/>
-      <c r="R15" s="5"/>
-      <c r="S15" s="5"/>
-      <c r="T15" s="5"/>
-      <c r="U15" s="5"/>
-      <c r="V15" s="5"/>
-      <c r="W15" s="5"/>
-      <c r="X15" s="5"/>
-      <c r="Y15" s="5"/>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.55000000000000004">
-      <c r="F16" s="5"/>
-      <c r="G16" s="5"/>
-      <c r="H16" s="5"/>
-      <c r="I16" s="5"/>
-      <c r="J16" s="5"/>
-      <c r="K16" s="5"/>
-      <c r="L16" s="5"/>
-      <c r="M16" s="5"/>
-      <c r="N16" s="5"/>
-      <c r="O16" s="5"/>
-      <c r="P16" s="5"/>
-      <c r="Q16" s="5"/>
-      <c r="R16" s="5"/>
-      <c r="S16" s="5"/>
-      <c r="T16" s="5"/>
-      <c r="U16" s="5"/>
-      <c r="V16" s="5"/>
-      <c r="W16" s="5"/>
-      <c r="X16" s="5"/>
-      <c r="Y16" s="5"/>
+      <c r="M13" s="10"/>
+      <c r="N13" s="10"/>
+      <c r="O13" s="10"/>
+      <c r="P13" s="11"/>
     </row>
     <row r="20" spans="6:6" x14ac:dyDescent="0.55000000000000004">
       <c r="F20" t="s">
@@ -7160,937 +6295,937 @@
       <c r="F1" t="s">
         <v>101</v>
       </c>
-      <c r="K1" s="47" t="s">
+      <c r="K1" s="46" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="2" spans="1:17" ht="18.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="F2" s="61"/>
-      <c r="G2" s="62"/>
-      <c r="H2" s="62"/>
-      <c r="I2" s="62"/>
-      <c r="J2" s="62"/>
-      <c r="K2" s="62"/>
-      <c r="L2" s="62"/>
-      <c r="M2" s="62"/>
-      <c r="N2" s="62"/>
-      <c r="O2" s="62"/>
-      <c r="P2" s="62"/>
-      <c r="Q2" s="63"/>
+      <c r="F2" s="63"/>
+      <c r="G2" s="64"/>
+      <c r="H2" s="64"/>
+      <c r="I2" s="64"/>
+      <c r="J2" s="64"/>
+      <c r="K2" s="64"/>
+      <c r="L2" s="64"/>
+      <c r="M2" s="64"/>
+      <c r="N2" s="64"/>
+      <c r="O2" s="64"/>
+      <c r="P2" s="64"/>
+      <c r="Q2" s="65"/>
     </row>
     <row r="3" spans="1:17" ht="32" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B3" s="25" t="s">
+      <c r="B3" s="24" t="s">
         <v>47</v>
       </c>
-      <c r="C3" s="27" t="s">
+      <c r="C3" s="26" t="s">
         <v>57</v>
       </c>
-      <c r="D3" s="27" t="s">
+      <c r="D3" s="26" t="s">
         <v>56</v>
       </c>
-      <c r="E3" s="58" t="s">
+      <c r="E3" s="57" t="s">
         <v>48</v>
       </c>
-      <c r="F3" s="59" t="s">
+      <c r="F3" s="58" t="s">
         <v>49</v>
       </c>
-      <c r="G3" s="59" t="s">
+      <c r="G3" s="58" t="s">
         <v>50</v>
       </c>
-      <c r="H3" s="59" t="s">
+      <c r="H3" s="58" t="s">
         <v>51</v>
       </c>
-      <c r="I3" s="59" t="s">
+      <c r="I3" s="58" t="s">
         <v>52</v>
       </c>
-      <c r="J3" s="59" t="s">
+      <c r="J3" s="58" t="s">
         <v>53</v>
       </c>
-      <c r="K3" s="59" t="s">
+      <c r="K3" s="58" t="s">
         <v>54</v>
       </c>
-      <c r="L3" s="59" t="s">
+      <c r="L3" s="58" t="s">
         <v>55</v>
       </c>
-      <c r="M3" s="59" t="s">
+      <c r="M3" s="58" t="s">
         <v>58</v>
       </c>
-      <c r="N3" s="59" t="s">
+      <c r="N3" s="58" t="s">
         <v>59</v>
       </c>
-      <c r="O3" s="59" t="s">
+      <c r="O3" s="58" t="s">
         <v>60</v>
       </c>
-      <c r="P3" s="59" t="s">
+      <c r="P3" s="58" t="s">
         <v>61</v>
       </c>
-      <c r="Q3" s="60" t="s">
+      <c r="Q3" s="59" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="4" spans="1:17" ht="10" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="51">
+      <c r="A4" s="50">
         <v>1</v>
       </c>
-      <c r="B4" s="64" t="s">
+      <c r="B4" s="60" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="64"/>
-      <c r="D4" s="64"/>
-      <c r="E4" s="53"/>
-      <c r="F4" s="52"/>
-      <c r="G4" s="52"/>
-      <c r="H4" s="52"/>
-      <c r="I4" s="52"/>
-      <c r="J4" s="52"/>
-      <c r="K4" s="52"/>
-      <c r="L4" s="52"/>
-      <c r="M4" s="52"/>
-      <c r="N4" s="52"/>
-      <c r="O4" s="52"/>
-      <c r="P4" s="52"/>
-      <c r="Q4" s="54"/>
+      <c r="C4" s="60"/>
+      <c r="D4" s="60"/>
+      <c r="E4" s="52"/>
+      <c r="F4" s="51"/>
+      <c r="G4" s="51"/>
+      <c r="H4" s="51"/>
+      <c r="I4" s="51"/>
+      <c r="J4" s="51"/>
+      <c r="K4" s="51"/>
+      <c r="L4" s="51"/>
+      <c r="M4" s="51"/>
+      <c r="N4" s="51"/>
+      <c r="O4" s="51"/>
+      <c r="P4" s="51"/>
+      <c r="Q4" s="53"/>
     </row>
     <row r="5" spans="1:17" ht="10" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="55">
+      <c r="A5" s="54">
         <v>1.1000000000000001</v>
       </c>
-      <c r="B5" s="16"/>
-      <c r="C5" s="16" t="s">
+      <c r="B5" s="15"/>
+      <c r="C5" s="15" t="s">
         <v>94</v>
       </c>
-      <c r="D5" s="16"/>
-      <c r="E5" s="50" t="s">
+      <c r="D5" s="15"/>
+      <c r="E5" s="49" t="s">
         <v>103</v>
       </c>
-      <c r="F5" s="16"/>
-      <c r="G5" s="16"/>
-      <c r="H5" s="16"/>
-      <c r="I5" s="16"/>
-      <c r="J5" s="16"/>
-      <c r="K5" s="16"/>
-      <c r="L5" s="16"/>
-      <c r="M5" s="16"/>
-      <c r="N5" s="16"/>
-      <c r="O5" s="16"/>
-      <c r="P5" s="16"/>
-      <c r="Q5" s="18"/>
+      <c r="F5" s="15"/>
+      <c r="G5" s="15"/>
+      <c r="H5" s="15"/>
+      <c r="I5" s="15"/>
+      <c r="J5" s="15"/>
+      <c r="K5" s="15"/>
+      <c r="L5" s="15"/>
+      <c r="M5" s="15"/>
+      <c r="N5" s="15"/>
+      <c r="O5" s="15"/>
+      <c r="P5" s="15"/>
+      <c r="Q5" s="17"/>
     </row>
     <row r="6" spans="1:17" ht="10" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="55" t="s">
+      <c r="A6" s="54" t="s">
         <v>64</v>
       </c>
-      <c r="B6" s="16"/>
-      <c r="C6" s="16"/>
-      <c r="D6" s="16"/>
-      <c r="E6" s="50" t="s">
+      <c r="B6" s="15"/>
+      <c r="C6" s="15"/>
+      <c r="D6" s="15"/>
+      <c r="E6" s="49" t="s">
         <v>104</v>
       </c>
-      <c r="F6" s="16"/>
-      <c r="G6" s="16"/>
-      <c r="H6" s="16"/>
-      <c r="I6" s="16"/>
-      <c r="J6" s="16"/>
-      <c r="K6" s="16"/>
-      <c r="L6" s="16"/>
-      <c r="M6" s="16"/>
-      <c r="N6" s="16"/>
-      <c r="O6" s="16"/>
-      <c r="P6" s="16"/>
-      <c r="Q6" s="18"/>
+      <c r="F6" s="15"/>
+      <c r="G6" s="15"/>
+      <c r="H6" s="15"/>
+      <c r="I6" s="15"/>
+      <c r="J6" s="15"/>
+      <c r="K6" s="15"/>
+      <c r="L6" s="15"/>
+      <c r="M6" s="15"/>
+      <c r="N6" s="15"/>
+      <c r="O6" s="15"/>
+      <c r="P6" s="15"/>
+      <c r="Q6" s="17"/>
     </row>
     <row r="7" spans="1:17" ht="10" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="55" t="s">
+      <c r="A7" s="54" t="s">
         <v>65</v>
       </c>
-      <c r="B7" s="16"/>
-      <c r="C7" s="16"/>
-      <c r="D7" s="16"/>
-      <c r="E7" s="50" t="s">
+      <c r="B7" s="15"/>
+      <c r="C7" s="15"/>
+      <c r="D7" s="15"/>
+      <c r="E7" s="49" t="s">
         <v>105</v>
       </c>
-      <c r="F7" s="16"/>
-      <c r="G7" s="16"/>
-      <c r="H7" s="16"/>
-      <c r="I7" s="16"/>
-      <c r="J7" s="16"/>
-      <c r="K7" s="16"/>
-      <c r="L7" s="16"/>
-      <c r="M7" s="16"/>
-      <c r="N7" s="16"/>
-      <c r="O7" s="16"/>
-      <c r="P7" s="16"/>
-      <c r="Q7" s="18"/>
+      <c r="F7" s="15"/>
+      <c r="G7" s="15"/>
+      <c r="H7" s="15"/>
+      <c r="I7" s="15"/>
+      <c r="J7" s="15"/>
+      <c r="K7" s="15"/>
+      <c r="L7" s="15"/>
+      <c r="M7" s="15"/>
+      <c r="N7" s="15"/>
+      <c r="O7" s="15"/>
+      <c r="P7" s="15"/>
+      <c r="Q7" s="17"/>
     </row>
     <row r="8" spans="1:17" ht="10" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="55">
+      <c r="A8" s="54">
         <v>1.2</v>
       </c>
-      <c r="B8" s="16"/>
-      <c r="C8" s="16" t="s">
+      <c r="B8" s="15"/>
+      <c r="C8" s="15" t="s">
         <v>95</v>
       </c>
-      <c r="D8" s="16"/>
-      <c r="E8" s="50"/>
-      <c r="F8" s="16"/>
-      <c r="G8" s="16"/>
-      <c r="H8" s="16"/>
-      <c r="I8" s="16"/>
-      <c r="J8" s="16"/>
-      <c r="K8" s="16"/>
-      <c r="L8" s="16"/>
-      <c r="M8" s="16"/>
-      <c r="N8" s="16"/>
-      <c r="O8" s="16"/>
-      <c r="P8" s="16"/>
-      <c r="Q8" s="18"/>
+      <c r="D8" s="15"/>
+      <c r="E8" s="49"/>
+      <c r="F8" s="15"/>
+      <c r="G8" s="15"/>
+      <c r="H8" s="15"/>
+      <c r="I8" s="15"/>
+      <c r="J8" s="15"/>
+      <c r="K8" s="15"/>
+      <c r="L8" s="15"/>
+      <c r="M8" s="15"/>
+      <c r="N8" s="15"/>
+      <c r="O8" s="15"/>
+      <c r="P8" s="15"/>
+      <c r="Q8" s="17"/>
     </row>
     <row r="9" spans="1:17" ht="10" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="55" t="s">
+      <c r="A9" s="54" t="s">
         <v>66</v>
       </c>
-      <c r="B9" s="16"/>
-      <c r="C9" s="16"/>
-      <c r="D9" s="16"/>
-      <c r="E9" s="50"/>
-      <c r="F9" s="16"/>
-      <c r="G9" s="16"/>
-      <c r="H9" s="16"/>
-      <c r="I9" s="16"/>
-      <c r="J9" s="16"/>
-      <c r="K9" s="16"/>
-      <c r="L9" s="16"/>
-      <c r="M9" s="16"/>
-      <c r="N9" s="16"/>
-      <c r="O9" s="16"/>
-      <c r="P9" s="16"/>
-      <c r="Q9" s="18"/>
+      <c r="B9" s="15"/>
+      <c r="C9" s="15"/>
+      <c r="D9" s="15"/>
+      <c r="E9" s="49"/>
+      <c r="F9" s="15"/>
+      <c r="G9" s="15"/>
+      <c r="H9" s="15"/>
+      <c r="I9" s="15"/>
+      <c r="J9" s="15"/>
+      <c r="K9" s="15"/>
+      <c r="L9" s="15"/>
+      <c r="M9" s="15"/>
+      <c r="N9" s="15"/>
+      <c r="O9" s="15"/>
+      <c r="P9" s="15"/>
+      <c r="Q9" s="17"/>
     </row>
     <row r="10" spans="1:17" ht="10" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="55" t="s">
+      <c r="A10" s="54" t="s">
         <v>67</v>
       </c>
-      <c r="B10" s="16"/>
-      <c r="C10" s="16"/>
-      <c r="D10" s="16"/>
-      <c r="E10" s="50"/>
-      <c r="F10" s="16"/>
-      <c r="G10" s="16"/>
-      <c r="H10" s="16"/>
-      <c r="I10" s="16"/>
-      <c r="J10" s="16"/>
-      <c r="K10" s="16"/>
-      <c r="L10" s="16"/>
-      <c r="M10" s="16"/>
-      <c r="N10" s="16"/>
-      <c r="O10" s="16"/>
-      <c r="P10" s="16"/>
-      <c r="Q10" s="18"/>
+      <c r="B10" s="15"/>
+      <c r="C10" s="15"/>
+      <c r="D10" s="15"/>
+      <c r="E10" s="49"/>
+      <c r="F10" s="15"/>
+      <c r="G10" s="15"/>
+      <c r="H10" s="15"/>
+      <c r="I10" s="15"/>
+      <c r="J10" s="15"/>
+      <c r="K10" s="15"/>
+      <c r="L10" s="15"/>
+      <c r="M10" s="15"/>
+      <c r="N10" s="15"/>
+      <c r="O10" s="15"/>
+      <c r="P10" s="15"/>
+      <c r="Q10" s="17"/>
     </row>
     <row r="11" spans="1:17" ht="10" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="55" t="s">
+      <c r="A11" s="54" t="s">
         <v>68</v>
       </c>
-      <c r="B11" s="16"/>
-      <c r="C11" s="16"/>
-      <c r="D11" s="16"/>
-      <c r="E11" s="50"/>
-      <c r="F11" s="16"/>
-      <c r="G11" s="16"/>
-      <c r="H11" s="16"/>
-      <c r="I11" s="16"/>
-      <c r="J11" s="16"/>
-      <c r="K11" s="16"/>
-      <c r="L11" s="16"/>
-      <c r="M11" s="16"/>
-      <c r="N11" s="16"/>
-      <c r="O11" s="16"/>
-      <c r="P11" s="16"/>
-      <c r="Q11" s="18"/>
+      <c r="B11" s="15"/>
+      <c r="C11" s="15"/>
+      <c r="D11" s="15"/>
+      <c r="E11" s="49"/>
+      <c r="F11" s="15"/>
+      <c r="G11" s="15"/>
+      <c r="H11" s="15"/>
+      <c r="I11" s="15"/>
+      <c r="J11" s="15"/>
+      <c r="K11" s="15"/>
+      <c r="L11" s="15"/>
+      <c r="M11" s="15"/>
+      <c r="N11" s="15"/>
+      <c r="O11" s="15"/>
+      <c r="P11" s="15"/>
+      <c r="Q11" s="17"/>
     </row>
     <row r="12" spans="1:17" ht="10" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" s="55">
+      <c r="A12" s="54">
         <v>2</v>
       </c>
-      <c r="B12" s="65" t="s">
+      <c r="B12" s="61" t="s">
         <v>69</v>
       </c>
-      <c r="C12" s="65"/>
-      <c r="D12" s="65"/>
-      <c r="E12" s="50"/>
-      <c r="F12" s="16"/>
-      <c r="G12" s="16"/>
-      <c r="H12" s="16"/>
-      <c r="I12" s="16"/>
-      <c r="J12" s="16"/>
-      <c r="K12" s="16"/>
-      <c r="L12" s="16"/>
-      <c r="M12" s="16"/>
-      <c r="N12" s="16"/>
-      <c r="O12" s="16"/>
-      <c r="P12" s="16"/>
-      <c r="Q12" s="18"/>
+      <c r="C12" s="61"/>
+      <c r="D12" s="61"/>
+      <c r="E12" s="49"/>
+      <c r="F12" s="15"/>
+      <c r="G12" s="15"/>
+      <c r="H12" s="15"/>
+      <c r="I12" s="15"/>
+      <c r="J12" s="15"/>
+      <c r="K12" s="15"/>
+      <c r="L12" s="15"/>
+      <c r="M12" s="15"/>
+      <c r="N12" s="15"/>
+      <c r="O12" s="15"/>
+      <c r="P12" s="15"/>
+      <c r="Q12" s="17"/>
     </row>
     <row r="13" spans="1:17" ht="10" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="55">
+      <c r="A13" s="54">
         <v>2.1</v>
       </c>
-      <c r="B13" s="16"/>
-      <c r="C13" s="16" t="s">
+      <c r="B13" s="15"/>
+      <c r="C13" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="D13" s="16"/>
-      <c r="E13" s="50"/>
-      <c r="F13" s="16"/>
-      <c r="G13" s="16"/>
-      <c r="H13" s="16"/>
-      <c r="I13" s="16"/>
-      <c r="J13" s="16"/>
-      <c r="K13" s="16"/>
-      <c r="L13" s="16"/>
-      <c r="M13" s="16"/>
-      <c r="N13" s="16"/>
-      <c r="O13" s="16"/>
-      <c r="P13" s="16"/>
-      <c r="Q13" s="18"/>
+      <c r="D13" s="15"/>
+      <c r="E13" s="49"/>
+      <c r="F13" s="15"/>
+      <c r="G13" s="15"/>
+      <c r="H13" s="15"/>
+      <c r="I13" s="15"/>
+      <c r="J13" s="15"/>
+      <c r="K13" s="15"/>
+      <c r="L13" s="15"/>
+      <c r="M13" s="15"/>
+      <c r="N13" s="15"/>
+      <c r="O13" s="15"/>
+      <c r="P13" s="15"/>
+      <c r="Q13" s="17"/>
     </row>
     <row r="14" spans="1:17" ht="10" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="55" t="s">
+      <c r="A14" s="54" t="s">
         <v>70</v>
       </c>
-      <c r="B14" s="16"/>
-      <c r="C14" s="16"/>
-      <c r="D14" s="16"/>
-      <c r="E14" s="50"/>
-      <c r="F14" s="16"/>
-      <c r="G14" s="16"/>
-      <c r="H14" s="16"/>
-      <c r="I14" s="16"/>
-      <c r="J14" s="16"/>
-      <c r="K14" s="16"/>
-      <c r="L14" s="16"/>
-      <c r="M14" s="16"/>
-      <c r="N14" s="16"/>
-      <c r="O14" s="16"/>
-      <c r="P14" s="16"/>
-      <c r="Q14" s="18"/>
+      <c r="B14" s="15"/>
+      <c r="C14" s="15"/>
+      <c r="D14" s="15"/>
+      <c r="E14" s="49"/>
+      <c r="F14" s="15"/>
+      <c r="G14" s="15"/>
+      <c r="H14" s="15"/>
+      <c r="I14" s="15"/>
+      <c r="J14" s="15"/>
+      <c r="K14" s="15"/>
+      <c r="L14" s="15"/>
+      <c r="M14" s="15"/>
+      <c r="N14" s="15"/>
+      <c r="O14" s="15"/>
+      <c r="P14" s="15"/>
+      <c r="Q14" s="17"/>
     </row>
     <row r="15" spans="1:17" ht="10" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="55" t="s">
+      <c r="A15" s="54" t="s">
         <v>71</v>
       </c>
-      <c r="B15" s="16"/>
-      <c r="C15" s="16"/>
-      <c r="D15" s="16"/>
-      <c r="E15" s="50"/>
-      <c r="F15" s="16"/>
-      <c r="G15" s="16"/>
-      <c r="H15" s="16"/>
-      <c r="I15" s="16"/>
-      <c r="J15" s="16"/>
-      <c r="K15" s="16"/>
-      <c r="L15" s="16"/>
-      <c r="M15" s="16"/>
-      <c r="N15" s="16"/>
-      <c r="O15" s="16"/>
-      <c r="P15" s="16"/>
-      <c r="Q15" s="18"/>
+      <c r="B15" s="15"/>
+      <c r="C15" s="15"/>
+      <c r="D15" s="15"/>
+      <c r="E15" s="49"/>
+      <c r="F15" s="15"/>
+      <c r="G15" s="15"/>
+      <c r="H15" s="15"/>
+      <c r="I15" s="15"/>
+      <c r="J15" s="15"/>
+      <c r="K15" s="15"/>
+      <c r="L15" s="15"/>
+      <c r="M15" s="15"/>
+      <c r="N15" s="15"/>
+      <c r="O15" s="15"/>
+      <c r="P15" s="15"/>
+      <c r="Q15" s="17"/>
     </row>
     <row r="16" spans="1:17" ht="10" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="55" t="s">
+      <c r="A16" s="54" t="s">
         <v>72</v>
       </c>
-      <c r="B16" s="16"/>
-      <c r="C16" s="16"/>
-      <c r="D16" s="16"/>
-      <c r="E16" s="50"/>
-      <c r="F16" s="16"/>
-      <c r="G16" s="16"/>
-      <c r="H16" s="16"/>
-      <c r="I16" s="16"/>
-      <c r="J16" s="16"/>
-      <c r="K16" s="16"/>
-      <c r="L16" s="16"/>
-      <c r="M16" s="16"/>
-      <c r="N16" s="16"/>
-      <c r="O16" s="16"/>
-      <c r="P16" s="16"/>
-      <c r="Q16" s="18"/>
+      <c r="B16" s="15"/>
+      <c r="C16" s="15"/>
+      <c r="D16" s="15"/>
+      <c r="E16" s="49"/>
+      <c r="F16" s="15"/>
+      <c r="G16" s="15"/>
+      <c r="H16" s="15"/>
+      <c r="I16" s="15"/>
+      <c r="J16" s="15"/>
+      <c r="K16" s="15"/>
+      <c r="L16" s="15"/>
+      <c r="M16" s="15"/>
+      <c r="N16" s="15"/>
+      <c r="O16" s="15"/>
+      <c r="P16" s="15"/>
+      <c r="Q16" s="17"/>
     </row>
     <row r="17" spans="1:17" ht="10" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17" s="55" t="s">
+      <c r="A17" s="54" t="s">
         <v>73</v>
       </c>
-      <c r="B17" s="16"/>
-      <c r="C17" s="16"/>
-      <c r="D17" s="16"/>
-      <c r="E17" s="50"/>
-      <c r="F17" s="16"/>
-      <c r="G17" s="16"/>
-      <c r="H17" s="16"/>
-      <c r="I17" s="16"/>
-      <c r="J17" s="16"/>
-      <c r="K17" s="16"/>
-      <c r="L17" s="16"/>
-      <c r="M17" s="16"/>
-      <c r="N17" s="16"/>
-      <c r="O17" s="16"/>
-      <c r="P17" s="16"/>
-      <c r="Q17" s="18"/>
+      <c r="B17" s="15"/>
+      <c r="C17" s="15"/>
+      <c r="D17" s="15"/>
+      <c r="E17" s="49"/>
+      <c r="F17" s="15"/>
+      <c r="G17" s="15"/>
+      <c r="H17" s="15"/>
+      <c r="I17" s="15"/>
+      <c r="J17" s="15"/>
+      <c r="K17" s="15"/>
+      <c r="L17" s="15"/>
+      <c r="M17" s="15"/>
+      <c r="N17" s="15"/>
+      <c r="O17" s="15"/>
+      <c r="P17" s="15"/>
+      <c r="Q17" s="17"/>
     </row>
     <row r="18" spans="1:17" ht="10" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18" s="55">
+      <c r="A18" s="54">
         <v>2.2000000000000002</v>
       </c>
-      <c r="B18" s="16"/>
-      <c r="C18" s="16" t="s">
+      <c r="B18" s="15"/>
+      <c r="C18" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="D18" s="16"/>
-      <c r="E18" s="50"/>
-      <c r="F18" s="16"/>
-      <c r="G18" s="16"/>
-      <c r="H18" s="16"/>
-      <c r="I18" s="16"/>
-      <c r="J18" s="16"/>
-      <c r="K18" s="16"/>
-      <c r="L18" s="16"/>
-      <c r="M18" s="16"/>
-      <c r="N18" s="16"/>
-      <c r="O18" s="16"/>
-      <c r="P18" s="16"/>
-      <c r="Q18" s="18"/>
+      <c r="D18" s="15"/>
+      <c r="E18" s="49"/>
+      <c r="F18" s="15"/>
+      <c r="G18" s="15"/>
+      <c r="H18" s="15"/>
+      <c r="I18" s="15"/>
+      <c r="J18" s="15"/>
+      <c r="K18" s="15"/>
+      <c r="L18" s="15"/>
+      <c r="M18" s="15"/>
+      <c r="N18" s="15"/>
+      <c r="O18" s="15"/>
+      <c r="P18" s="15"/>
+      <c r="Q18" s="17"/>
     </row>
     <row r="19" spans="1:17" ht="10" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19" s="55" t="s">
+      <c r="A19" s="54" t="s">
         <v>74</v>
       </c>
-      <c r="B19" s="16"/>
-      <c r="C19" s="16"/>
-      <c r="D19" s="16"/>
-      <c r="E19" s="50"/>
-      <c r="F19" s="16"/>
-      <c r="G19" s="16"/>
-      <c r="H19" s="16"/>
-      <c r="I19" s="16"/>
-      <c r="J19" s="16"/>
-      <c r="K19" s="16"/>
-      <c r="L19" s="16"/>
-      <c r="M19" s="16"/>
-      <c r="N19" s="16"/>
-      <c r="O19" s="16"/>
-      <c r="P19" s="16"/>
-      <c r="Q19" s="18"/>
+      <c r="B19" s="15"/>
+      <c r="C19" s="15"/>
+      <c r="D19" s="15"/>
+      <c r="E19" s="49"/>
+      <c r="F19" s="15"/>
+      <c r="G19" s="15"/>
+      <c r="H19" s="15"/>
+      <c r="I19" s="15"/>
+      <c r="J19" s="15"/>
+      <c r="K19" s="15"/>
+      <c r="L19" s="15"/>
+      <c r="M19" s="15"/>
+      <c r="N19" s="15"/>
+      <c r="O19" s="15"/>
+      <c r="P19" s="15"/>
+      <c r="Q19" s="17"/>
     </row>
     <row r="20" spans="1:17" ht="10" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A20" s="55" t="s">
+      <c r="A20" s="54" t="s">
         <v>75</v>
       </c>
-      <c r="B20" s="16"/>
-      <c r="C20" s="16"/>
-      <c r="D20" s="16"/>
-      <c r="E20" s="50"/>
-      <c r="F20" s="16"/>
-      <c r="G20" s="16"/>
-      <c r="H20" s="16"/>
-      <c r="I20" s="16"/>
-      <c r="J20" s="16"/>
-      <c r="K20" s="16"/>
-      <c r="L20" s="16"/>
-      <c r="M20" s="16"/>
-      <c r="N20" s="16"/>
-      <c r="O20" s="16"/>
-      <c r="P20" s="16"/>
-      <c r="Q20" s="18"/>
+      <c r="B20" s="15"/>
+      <c r="C20" s="15"/>
+      <c r="D20" s="15"/>
+      <c r="E20" s="49"/>
+      <c r="F20" s="15"/>
+      <c r="G20" s="15"/>
+      <c r="H20" s="15"/>
+      <c r="I20" s="15"/>
+      <c r="J20" s="15"/>
+      <c r="K20" s="15"/>
+      <c r="L20" s="15"/>
+      <c r="M20" s="15"/>
+      <c r="N20" s="15"/>
+      <c r="O20" s="15"/>
+      <c r="P20" s="15"/>
+      <c r="Q20" s="17"/>
     </row>
     <row r="21" spans="1:17" ht="10" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A21" s="55" t="s">
+      <c r="A21" s="54" t="s">
         <v>76</v>
       </c>
-      <c r="B21" s="16"/>
-      <c r="C21" s="16"/>
-      <c r="D21" s="16"/>
-      <c r="E21" s="50"/>
-      <c r="F21" s="16"/>
-      <c r="G21" s="16"/>
-      <c r="H21" s="16"/>
-      <c r="I21" s="16"/>
-      <c r="J21" s="16"/>
-      <c r="K21" s="16"/>
-      <c r="L21" s="16"/>
-      <c r="M21" s="16"/>
-      <c r="N21" s="16"/>
-      <c r="O21" s="16"/>
-      <c r="P21" s="16"/>
-      <c r="Q21" s="18"/>
+      <c r="B21" s="15"/>
+      <c r="C21" s="15"/>
+      <c r="D21" s="15"/>
+      <c r="E21" s="49"/>
+      <c r="F21" s="15"/>
+      <c r="G21" s="15"/>
+      <c r="H21" s="15"/>
+      <c r="I21" s="15"/>
+      <c r="J21" s="15"/>
+      <c r="K21" s="15"/>
+      <c r="L21" s="15"/>
+      <c r="M21" s="15"/>
+      <c r="N21" s="15"/>
+      <c r="O21" s="15"/>
+      <c r="P21" s="15"/>
+      <c r="Q21" s="17"/>
     </row>
     <row r="22" spans="1:17" ht="10" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22" s="55" t="s">
+      <c r="A22" s="54" t="s">
         <v>77</v>
       </c>
-      <c r="B22" s="16"/>
-      <c r="C22" s="16"/>
-      <c r="D22" s="16"/>
-      <c r="E22" s="50"/>
-      <c r="F22" s="16"/>
-      <c r="G22" s="16"/>
-      <c r="H22" s="16"/>
-      <c r="I22" s="16"/>
-      <c r="J22" s="16"/>
-      <c r="K22" s="16"/>
-      <c r="L22" s="16"/>
-      <c r="M22" s="16"/>
-      <c r="N22" s="16"/>
-      <c r="O22" s="16"/>
-      <c r="P22" s="16"/>
-      <c r="Q22" s="18"/>
+      <c r="B22" s="15"/>
+      <c r="C22" s="15"/>
+      <c r="D22" s="15"/>
+      <c r="E22" s="49"/>
+      <c r="F22" s="15"/>
+      <c r="G22" s="15"/>
+      <c r="H22" s="15"/>
+      <c r="I22" s="15"/>
+      <c r="J22" s="15"/>
+      <c r="K22" s="15"/>
+      <c r="L22" s="15"/>
+      <c r="M22" s="15"/>
+      <c r="N22" s="15"/>
+      <c r="O22" s="15"/>
+      <c r="P22" s="15"/>
+      <c r="Q22" s="17"/>
     </row>
     <row r="23" spans="1:17" ht="10" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A23" s="55">
+      <c r="A23" s="54">
         <v>3.1</v>
       </c>
-      <c r="B23" s="16"/>
-      <c r="C23" s="16" t="s">
+      <c r="B23" s="15"/>
+      <c r="C23" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="D23" s="16"/>
-      <c r="E23" s="50"/>
-      <c r="F23" s="16"/>
-      <c r="G23" s="16"/>
-      <c r="H23" s="16"/>
-      <c r="I23" s="16"/>
-      <c r="J23" s="16"/>
-      <c r="K23" s="16"/>
-      <c r="L23" s="16"/>
-      <c r="M23" s="16"/>
-      <c r="N23" s="16"/>
-      <c r="O23" s="16"/>
-      <c r="P23" s="16"/>
-      <c r="Q23" s="18"/>
+      <c r="D23" s="15"/>
+      <c r="E23" s="49"/>
+      <c r="F23" s="15"/>
+      <c r="G23" s="15"/>
+      <c r="H23" s="15"/>
+      <c r="I23" s="15"/>
+      <c r="J23" s="15"/>
+      <c r="K23" s="15"/>
+      <c r="L23" s="15"/>
+      <c r="M23" s="15"/>
+      <c r="N23" s="15"/>
+      <c r="O23" s="15"/>
+      <c r="P23" s="15"/>
+      <c r="Q23" s="17"/>
     </row>
     <row r="24" spans="1:17" ht="10" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A24" s="55" t="s">
+      <c r="A24" s="54" t="s">
         <v>78</v>
       </c>
-      <c r="B24" s="16"/>
-      <c r="C24" s="16"/>
-      <c r="D24" s="16"/>
-      <c r="E24" s="50"/>
-      <c r="F24" s="16"/>
-      <c r="G24" s="16"/>
-      <c r="H24" s="16"/>
-      <c r="I24" s="16"/>
-      <c r="J24" s="16"/>
-      <c r="K24" s="16"/>
-      <c r="L24" s="16"/>
-      <c r="M24" s="16"/>
-      <c r="N24" s="16"/>
-      <c r="O24" s="16"/>
-      <c r="P24" s="16"/>
-      <c r="Q24" s="18"/>
+      <c r="B24" s="15"/>
+      <c r="C24" s="15"/>
+      <c r="D24" s="15"/>
+      <c r="E24" s="49"/>
+      <c r="F24" s="15"/>
+      <c r="G24" s="15"/>
+      <c r="H24" s="15"/>
+      <c r="I24" s="15"/>
+      <c r="J24" s="15"/>
+      <c r="K24" s="15"/>
+      <c r="L24" s="15"/>
+      <c r="M24" s="15"/>
+      <c r="N24" s="15"/>
+      <c r="O24" s="15"/>
+      <c r="P24" s="15"/>
+      <c r="Q24" s="17"/>
     </row>
     <row r="25" spans="1:17" ht="10" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A25" s="55" t="s">
+      <c r="A25" s="54" t="s">
         <v>79</v>
       </c>
-      <c r="B25" s="16"/>
-      <c r="C25" s="16"/>
-      <c r="D25" s="16"/>
-      <c r="E25" s="50"/>
-      <c r="F25" s="16"/>
-      <c r="G25" s="16"/>
-      <c r="H25" s="16"/>
-      <c r="I25" s="16"/>
-      <c r="J25" s="16"/>
-      <c r="K25" s="16"/>
-      <c r="L25" s="16"/>
-      <c r="M25" s="16"/>
-      <c r="N25" s="16"/>
-      <c r="O25" s="16"/>
-      <c r="P25" s="16"/>
-      <c r="Q25" s="18"/>
+      <c r="B25" s="15"/>
+      <c r="C25" s="15"/>
+      <c r="D25" s="15"/>
+      <c r="E25" s="49"/>
+      <c r="F25" s="15"/>
+      <c r="G25" s="15"/>
+      <c r="H25" s="15"/>
+      <c r="I25" s="15"/>
+      <c r="J25" s="15"/>
+      <c r="K25" s="15"/>
+      <c r="L25" s="15"/>
+      <c r="M25" s="15"/>
+      <c r="N25" s="15"/>
+      <c r="O25" s="15"/>
+      <c r="P25" s="15"/>
+      <c r="Q25" s="17"/>
     </row>
     <row r="26" spans="1:17" ht="10" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26" s="55" t="s">
+      <c r="A26" s="54" t="s">
         <v>80</v>
       </c>
-      <c r="B26" s="16"/>
-      <c r="C26" s="16"/>
-      <c r="D26" s="16"/>
-      <c r="E26" s="50"/>
-      <c r="F26" s="16"/>
-      <c r="G26" s="16"/>
-      <c r="H26" s="16"/>
-      <c r="I26" s="16"/>
-      <c r="J26" s="16"/>
-      <c r="K26" s="16"/>
-      <c r="L26" s="16"/>
-      <c r="M26" s="16"/>
-      <c r="N26" s="16"/>
-      <c r="O26" s="16"/>
-      <c r="P26" s="16"/>
-      <c r="Q26" s="18"/>
+      <c r="B26" s="15"/>
+      <c r="C26" s="15"/>
+      <c r="D26" s="15"/>
+      <c r="E26" s="49"/>
+      <c r="F26" s="15"/>
+      <c r="G26" s="15"/>
+      <c r="H26" s="15"/>
+      <c r="I26" s="15"/>
+      <c r="J26" s="15"/>
+      <c r="K26" s="15"/>
+      <c r="L26" s="15"/>
+      <c r="M26" s="15"/>
+      <c r="N26" s="15"/>
+      <c r="O26" s="15"/>
+      <c r="P26" s="15"/>
+      <c r="Q26" s="17"/>
     </row>
     <row r="27" spans="1:17" ht="10" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A27" s="55" t="s">
+      <c r="A27" s="54" t="s">
         <v>81</v>
       </c>
-      <c r="B27" s="16"/>
-      <c r="C27" s="16"/>
-      <c r="D27" s="16"/>
-      <c r="E27" s="50"/>
-      <c r="F27" s="16"/>
-      <c r="G27" s="16"/>
-      <c r="H27" s="16"/>
-      <c r="I27" s="16"/>
-      <c r="J27" s="16"/>
-      <c r="K27" s="16"/>
-      <c r="L27" s="16"/>
-      <c r="M27" s="16"/>
-      <c r="N27" s="16"/>
-      <c r="O27" s="16"/>
-      <c r="P27" s="16"/>
-      <c r="Q27" s="18"/>
+      <c r="B27" s="15"/>
+      <c r="C27" s="15"/>
+      <c r="D27" s="15"/>
+      <c r="E27" s="49"/>
+      <c r="F27" s="15"/>
+      <c r="G27" s="15"/>
+      <c r="H27" s="15"/>
+      <c r="I27" s="15"/>
+      <c r="J27" s="15"/>
+      <c r="K27" s="15"/>
+      <c r="L27" s="15"/>
+      <c r="M27" s="15"/>
+      <c r="N27" s="15"/>
+      <c r="O27" s="15"/>
+      <c r="P27" s="15"/>
+      <c r="Q27" s="17"/>
     </row>
     <row r="28" spans="1:17" ht="10" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A28" s="55">
+      <c r="A28" s="54">
         <v>3.2</v>
       </c>
-      <c r="B28" s="16"/>
-      <c r="C28" s="16" t="s">
+      <c r="B28" s="15"/>
+      <c r="C28" s="15" t="s">
         <v>99</v>
       </c>
-      <c r="D28" s="16"/>
-      <c r="E28" s="50"/>
-      <c r="F28" s="16"/>
-      <c r="G28" s="16"/>
-      <c r="H28" s="16"/>
-      <c r="I28" s="16"/>
-      <c r="J28" s="16"/>
-      <c r="K28" s="16"/>
-      <c r="L28" s="16"/>
-      <c r="M28" s="16"/>
-      <c r="N28" s="16"/>
-      <c r="O28" s="16"/>
-      <c r="P28" s="16"/>
-      <c r="Q28" s="18"/>
+      <c r="D28" s="15"/>
+      <c r="E28" s="49"/>
+      <c r="F28" s="15"/>
+      <c r="G28" s="15"/>
+      <c r="H28" s="15"/>
+      <c r="I28" s="15"/>
+      <c r="J28" s="15"/>
+      <c r="K28" s="15"/>
+      <c r="L28" s="15"/>
+      <c r="M28" s="15"/>
+      <c r="N28" s="15"/>
+      <c r="O28" s="15"/>
+      <c r="P28" s="15"/>
+      <c r="Q28" s="17"/>
     </row>
     <row r="29" spans="1:17" ht="10" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A29" s="55" t="s">
+      <c r="A29" s="54" t="s">
         <v>82</v>
       </c>
-      <c r="B29" s="16"/>
-      <c r="C29" s="16"/>
-      <c r="D29" s="16"/>
-      <c r="E29" s="50"/>
-      <c r="F29" s="16"/>
-      <c r="G29" s="16"/>
-      <c r="H29" s="16"/>
-      <c r="I29" s="16"/>
-      <c r="J29" s="16"/>
-      <c r="K29" s="16"/>
-      <c r="L29" s="16"/>
-      <c r="M29" s="16"/>
-      <c r="N29" s="16"/>
-      <c r="O29" s="16"/>
-      <c r="P29" s="16"/>
-      <c r="Q29" s="18"/>
+      <c r="B29" s="15"/>
+      <c r="C29" s="15"/>
+      <c r="D29" s="15"/>
+      <c r="E29" s="49"/>
+      <c r="F29" s="15"/>
+      <c r="G29" s="15"/>
+      <c r="H29" s="15"/>
+      <c r="I29" s="15"/>
+      <c r="J29" s="15"/>
+      <c r="K29" s="15"/>
+      <c r="L29" s="15"/>
+      <c r="M29" s="15"/>
+      <c r="N29" s="15"/>
+      <c r="O29" s="15"/>
+      <c r="P29" s="15"/>
+      <c r="Q29" s="17"/>
     </row>
     <row r="30" spans="1:17" ht="10" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A30" s="55" t="s">
+      <c r="A30" s="54" t="s">
         <v>83</v>
       </c>
-      <c r="B30" s="16"/>
-      <c r="C30" s="16"/>
-      <c r="D30" s="16"/>
-      <c r="E30" s="50"/>
-      <c r="F30" s="16"/>
-      <c r="G30" s="16"/>
-      <c r="H30" s="16"/>
-      <c r="I30" s="16"/>
-      <c r="J30" s="16"/>
-      <c r="K30" s="16"/>
-      <c r="L30" s="16"/>
-      <c r="M30" s="16"/>
-      <c r="N30" s="16"/>
-      <c r="O30" s="16"/>
-      <c r="P30" s="16"/>
-      <c r="Q30" s="18"/>
+      <c r="B30" s="15"/>
+      <c r="C30" s="15"/>
+      <c r="D30" s="15"/>
+      <c r="E30" s="49"/>
+      <c r="F30" s="15"/>
+      <c r="G30" s="15"/>
+      <c r="H30" s="15"/>
+      <c r="I30" s="15"/>
+      <c r="J30" s="15"/>
+      <c r="K30" s="15"/>
+      <c r="L30" s="15"/>
+      <c r="M30" s="15"/>
+      <c r="N30" s="15"/>
+      <c r="O30" s="15"/>
+      <c r="P30" s="15"/>
+      <c r="Q30" s="17"/>
     </row>
     <row r="31" spans="1:17" ht="10" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A31" s="55" t="s">
+      <c r="A31" s="54" t="s">
         <v>84</v>
       </c>
-      <c r="B31" s="16"/>
-      <c r="C31" s="16"/>
-      <c r="D31" s="16"/>
-      <c r="E31" s="50"/>
-      <c r="F31" s="16"/>
-      <c r="G31" s="16"/>
-      <c r="H31" s="16"/>
-      <c r="I31" s="16"/>
-      <c r="J31" s="16"/>
-      <c r="K31" s="16"/>
-      <c r="L31" s="16"/>
-      <c r="M31" s="16"/>
-      <c r="N31" s="16"/>
-      <c r="O31" s="16"/>
-      <c r="P31" s="16"/>
-      <c r="Q31" s="18"/>
+      <c r="B31" s="15"/>
+      <c r="C31" s="15"/>
+      <c r="D31" s="15"/>
+      <c r="E31" s="49"/>
+      <c r="F31" s="15"/>
+      <c r="G31" s="15"/>
+      <c r="H31" s="15"/>
+      <c r="I31" s="15"/>
+      <c r="J31" s="15"/>
+      <c r="K31" s="15"/>
+      <c r="L31" s="15"/>
+      <c r="M31" s="15"/>
+      <c r="N31" s="15"/>
+      <c r="O31" s="15"/>
+      <c r="P31" s="15"/>
+      <c r="Q31" s="17"/>
     </row>
     <row r="32" spans="1:17" ht="10" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A32" s="55">
+      <c r="A32" s="54">
         <v>3.3</v>
       </c>
-      <c r="B32" s="16"/>
-      <c r="C32" s="16" t="s">
+      <c r="B32" s="15"/>
+      <c r="C32" s="15" t="s">
         <v>100</v>
       </c>
-      <c r="D32" s="16"/>
-      <c r="E32" s="50"/>
-      <c r="F32" s="16"/>
-      <c r="G32" s="16"/>
-      <c r="H32" s="16"/>
-      <c r="I32" s="16"/>
-      <c r="J32" s="16"/>
-      <c r="K32" s="16"/>
-      <c r="L32" s="16"/>
-      <c r="M32" s="16"/>
-      <c r="N32" s="16"/>
-      <c r="O32" s="16"/>
-      <c r="P32" s="16"/>
-      <c r="Q32" s="18"/>
+      <c r="D32" s="15"/>
+      <c r="E32" s="49"/>
+      <c r="F32" s="15"/>
+      <c r="G32" s="15"/>
+      <c r="H32" s="15"/>
+      <c r="I32" s="15"/>
+      <c r="J32" s="15"/>
+      <c r="K32" s="15"/>
+      <c r="L32" s="15"/>
+      <c r="M32" s="15"/>
+      <c r="N32" s="15"/>
+      <c r="O32" s="15"/>
+      <c r="P32" s="15"/>
+      <c r="Q32" s="17"/>
     </row>
     <row r="33" spans="1:17" ht="10" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A33" s="55" t="s">
+      <c r="A33" s="54" t="s">
         <v>85</v>
       </c>
-      <c r="B33" s="16"/>
-      <c r="C33" s="16"/>
-      <c r="D33" s="16"/>
-      <c r="E33" s="50"/>
-      <c r="F33" s="16"/>
-      <c r="G33" s="16"/>
-      <c r="H33" s="16"/>
-      <c r="I33" s="16"/>
-      <c r="J33" s="16"/>
-      <c r="K33" s="16"/>
-      <c r="L33" s="16"/>
-      <c r="M33" s="16"/>
-      <c r="N33" s="16"/>
-      <c r="O33" s="16"/>
-      <c r="P33" s="16"/>
-      <c r="Q33" s="18"/>
+      <c r="B33" s="15"/>
+      <c r="C33" s="15"/>
+      <c r="D33" s="15"/>
+      <c r="E33" s="49"/>
+      <c r="F33" s="15"/>
+      <c r="G33" s="15"/>
+      <c r="H33" s="15"/>
+      <c r="I33" s="15"/>
+      <c r="J33" s="15"/>
+      <c r="K33" s="15"/>
+      <c r="L33" s="15"/>
+      <c r="M33" s="15"/>
+      <c r="N33" s="15"/>
+      <c r="O33" s="15"/>
+      <c r="P33" s="15"/>
+      <c r="Q33" s="17"/>
     </row>
     <row r="34" spans="1:17" ht="10" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A34" s="55" t="s">
+      <c r="A34" s="54" t="s">
         <v>86</v>
       </c>
-      <c r="B34" s="16"/>
-      <c r="C34" s="16"/>
-      <c r="D34" s="16"/>
-      <c r="E34" s="50"/>
-      <c r="F34" s="16"/>
-      <c r="G34" s="16"/>
-      <c r="H34" s="16"/>
-      <c r="I34" s="16"/>
-      <c r="J34" s="16"/>
-      <c r="K34" s="16"/>
-      <c r="L34" s="16"/>
-      <c r="M34" s="16"/>
-      <c r="N34" s="16"/>
-      <c r="O34" s="16"/>
-      <c r="P34" s="16"/>
-      <c r="Q34" s="18"/>
+      <c r="B34" s="15"/>
+      <c r="C34" s="15"/>
+      <c r="D34" s="15"/>
+      <c r="E34" s="49"/>
+      <c r="F34" s="15"/>
+      <c r="G34" s="15"/>
+      <c r="H34" s="15"/>
+      <c r="I34" s="15"/>
+      <c r="J34" s="15"/>
+      <c r="K34" s="15"/>
+      <c r="L34" s="15"/>
+      <c r="M34" s="15"/>
+      <c r="N34" s="15"/>
+      <c r="O34" s="15"/>
+      <c r="P34" s="15"/>
+      <c r="Q34" s="17"/>
     </row>
     <row r="35" spans="1:17" ht="10" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A35" s="55" t="s">
+      <c r="A35" s="54" t="s">
         <v>87</v>
       </c>
-      <c r="B35" s="16"/>
-      <c r="C35" s="16"/>
-      <c r="D35" s="16"/>
-      <c r="E35" s="50"/>
-      <c r="F35" s="16"/>
-      <c r="G35" s="16"/>
-      <c r="H35" s="16"/>
-      <c r="I35" s="16"/>
-      <c r="J35" s="16"/>
-      <c r="K35" s="16"/>
-      <c r="L35" s="16"/>
-      <c r="M35" s="16"/>
-      <c r="N35" s="16"/>
-      <c r="O35" s="16"/>
-      <c r="P35" s="16"/>
-      <c r="Q35" s="18"/>
+      <c r="B35" s="15"/>
+      <c r="C35" s="15"/>
+      <c r="D35" s="15"/>
+      <c r="E35" s="49"/>
+      <c r="F35" s="15"/>
+      <c r="G35" s="15"/>
+      <c r="H35" s="15"/>
+      <c r="I35" s="15"/>
+      <c r="J35" s="15"/>
+      <c r="K35" s="15"/>
+      <c r="L35" s="15"/>
+      <c r="M35" s="15"/>
+      <c r="N35" s="15"/>
+      <c r="O35" s="15"/>
+      <c r="P35" s="15"/>
+      <c r="Q35" s="17"/>
     </row>
     <row r="36" spans="1:17" ht="10" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A36" s="55">
+      <c r="A36" s="54">
         <v>4.0999999999999996</v>
       </c>
-      <c r="B36" s="16"/>
-      <c r="C36" s="16"/>
-      <c r="D36" s="16"/>
-      <c r="E36" s="50"/>
-      <c r="F36" s="16"/>
-      <c r="G36" s="16"/>
-      <c r="H36" s="16"/>
-      <c r="I36" s="16"/>
-      <c r="J36" s="16"/>
-      <c r="K36" s="16"/>
-      <c r="L36" s="16"/>
-      <c r="M36" s="16"/>
-      <c r="N36" s="16"/>
-      <c r="O36" s="16"/>
-      <c r="P36" s="16"/>
-      <c r="Q36" s="18"/>
+      <c r="B36" s="15"/>
+      <c r="C36" s="15"/>
+      <c r="D36" s="15"/>
+      <c r="E36" s="49"/>
+      <c r="F36" s="15"/>
+      <c r="G36" s="15"/>
+      <c r="H36" s="15"/>
+      <c r="I36" s="15"/>
+      <c r="J36" s="15"/>
+      <c r="K36" s="15"/>
+      <c r="L36" s="15"/>
+      <c r="M36" s="15"/>
+      <c r="N36" s="15"/>
+      <c r="O36" s="15"/>
+      <c r="P36" s="15"/>
+      <c r="Q36" s="17"/>
     </row>
     <row r="37" spans="1:17" ht="10" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A37" s="55" t="s">
+      <c r="A37" s="54" t="s">
         <v>88</v>
       </c>
-      <c r="B37" s="16"/>
-      <c r="C37" s="16"/>
-      <c r="D37" s="16"/>
-      <c r="E37" s="50"/>
-      <c r="F37" s="16"/>
-      <c r="G37" s="16"/>
-      <c r="H37" s="16"/>
-      <c r="I37" s="16"/>
-      <c r="J37" s="16"/>
-      <c r="K37" s="16"/>
-      <c r="L37" s="16"/>
-      <c r="M37" s="16"/>
-      <c r="N37" s="16"/>
-      <c r="O37" s="16"/>
-      <c r="P37" s="16"/>
-      <c r="Q37" s="18"/>
+      <c r="B37" s="15"/>
+      <c r="C37" s="15"/>
+      <c r="D37" s="15"/>
+      <c r="E37" s="49"/>
+      <c r="F37" s="15"/>
+      <c r="G37" s="15"/>
+      <c r="H37" s="15"/>
+      <c r="I37" s="15"/>
+      <c r="J37" s="15"/>
+      <c r="K37" s="15"/>
+      <c r="L37" s="15"/>
+      <c r="M37" s="15"/>
+      <c r="N37" s="15"/>
+      <c r="O37" s="15"/>
+      <c r="P37" s="15"/>
+      <c r="Q37" s="17"/>
     </row>
     <row r="38" spans="1:17" ht="10" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A38" s="55" t="s">
+      <c r="A38" s="54" t="s">
         <v>89</v>
       </c>
-      <c r="B38" s="16"/>
-      <c r="C38" s="16"/>
-      <c r="D38" s="16"/>
-      <c r="E38" s="50"/>
-      <c r="F38" s="16"/>
-      <c r="G38" s="16"/>
-      <c r="H38" s="16"/>
-      <c r="I38" s="16"/>
-      <c r="J38" s="16"/>
-      <c r="K38" s="16"/>
-      <c r="L38" s="16"/>
-      <c r="M38" s="16"/>
-      <c r="N38" s="16"/>
-      <c r="O38" s="16"/>
-      <c r="P38" s="16"/>
-      <c r="Q38" s="18"/>
+      <c r="B38" s="15"/>
+      <c r="C38" s="15"/>
+      <c r="D38" s="15"/>
+      <c r="E38" s="49"/>
+      <c r="F38" s="15"/>
+      <c r="G38" s="15"/>
+      <c r="H38" s="15"/>
+      <c r="I38" s="15"/>
+      <c r="J38" s="15"/>
+      <c r="K38" s="15"/>
+      <c r="L38" s="15"/>
+      <c r="M38" s="15"/>
+      <c r="N38" s="15"/>
+      <c r="O38" s="15"/>
+      <c r="P38" s="15"/>
+      <c r="Q38" s="17"/>
     </row>
     <row r="39" spans="1:17" ht="10" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A39" s="55" t="s">
+      <c r="A39" s="54" t="s">
         <v>90</v>
       </c>
-      <c r="B39" s="16"/>
-      <c r="C39" s="16"/>
-      <c r="D39" s="16"/>
-      <c r="E39" s="50"/>
-      <c r="F39" s="16"/>
-      <c r="G39" s="16"/>
-      <c r="H39" s="16"/>
-      <c r="I39" s="16"/>
-      <c r="J39" s="16"/>
-      <c r="K39" s="16"/>
-      <c r="L39" s="16"/>
-      <c r="M39" s="16"/>
-      <c r="N39" s="16"/>
-      <c r="O39" s="16"/>
-      <c r="P39" s="16"/>
-      <c r="Q39" s="18"/>
+      <c r="B39" s="15"/>
+      <c r="C39" s="15"/>
+      <c r="D39" s="15"/>
+      <c r="E39" s="49"/>
+      <c r="F39" s="15"/>
+      <c r="G39" s="15"/>
+      <c r="H39" s="15"/>
+      <c r="I39" s="15"/>
+      <c r="J39" s="15"/>
+      <c r="K39" s="15"/>
+      <c r="L39" s="15"/>
+      <c r="M39" s="15"/>
+      <c r="N39" s="15"/>
+      <c r="O39" s="15"/>
+      <c r="P39" s="15"/>
+      <c r="Q39" s="17"/>
     </row>
     <row r="40" spans="1:17" ht="10" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A40" s="55">
+      <c r="A40" s="54">
         <v>4.2</v>
       </c>
-      <c r="B40" s="16"/>
-      <c r="C40" s="16"/>
-      <c r="D40" s="16"/>
-      <c r="E40" s="50"/>
-      <c r="F40" s="16"/>
-      <c r="G40" s="16"/>
-      <c r="H40" s="16"/>
-      <c r="I40" s="16"/>
-      <c r="J40" s="16"/>
-      <c r="K40" s="16"/>
-      <c r="L40" s="16"/>
-      <c r="M40" s="16"/>
-      <c r="N40" s="16"/>
-      <c r="O40" s="16"/>
-      <c r="P40" s="16"/>
-      <c r="Q40" s="18"/>
+      <c r="B40" s="15"/>
+      <c r="C40" s="15"/>
+      <c r="D40" s="15"/>
+      <c r="E40" s="49"/>
+      <c r="F40" s="15"/>
+      <c r="G40" s="15"/>
+      <c r="H40" s="15"/>
+      <c r="I40" s="15"/>
+      <c r="J40" s="15"/>
+      <c r="K40" s="15"/>
+      <c r="L40" s="15"/>
+      <c r="M40" s="15"/>
+      <c r="N40" s="15"/>
+      <c r="O40" s="15"/>
+      <c r="P40" s="15"/>
+      <c r="Q40" s="17"/>
     </row>
     <row r="41" spans="1:17" ht="10" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A41" s="55" t="s">
+      <c r="A41" s="54" t="s">
         <v>91</v>
       </c>
-      <c r="B41" s="16"/>
-      <c r="C41" s="16"/>
-      <c r="D41" s="16"/>
-      <c r="E41" s="50"/>
-      <c r="F41" s="16"/>
-      <c r="G41" s="16"/>
-      <c r="H41" s="16"/>
-      <c r="I41" s="16"/>
-      <c r="J41" s="16"/>
-      <c r="K41" s="16"/>
-      <c r="L41" s="16"/>
-      <c r="M41" s="16"/>
-      <c r="N41" s="16"/>
-      <c r="O41" s="16"/>
-      <c r="P41" s="16"/>
-      <c r="Q41" s="18"/>
+      <c r="B41" s="15"/>
+      <c r="C41" s="15"/>
+      <c r="D41" s="15"/>
+      <c r="E41" s="49"/>
+      <c r="F41" s="15"/>
+      <c r="G41" s="15"/>
+      <c r="H41" s="15"/>
+      <c r="I41" s="15"/>
+      <c r="J41" s="15"/>
+      <c r="K41" s="15"/>
+      <c r="L41" s="15"/>
+      <c r="M41" s="15"/>
+      <c r="N41" s="15"/>
+      <c r="O41" s="15"/>
+      <c r="P41" s="15"/>
+      <c r="Q41" s="17"/>
     </row>
     <row r="42" spans="1:17" ht="10" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A42" s="55" t="s">
+      <c r="A42" s="54" t="s">
         <v>92</v>
       </c>
-      <c r="B42" s="16"/>
-      <c r="C42" s="16"/>
-      <c r="D42" s="16"/>
-      <c r="E42" s="50"/>
-      <c r="F42" s="16"/>
-      <c r="G42" s="16"/>
-      <c r="H42" s="16"/>
-      <c r="I42" s="16"/>
-      <c r="J42" s="16"/>
-      <c r="K42" s="16"/>
-      <c r="L42" s="16"/>
-      <c r="M42" s="16"/>
-      <c r="N42" s="16"/>
-      <c r="O42" s="16"/>
-      <c r="P42" s="16"/>
-      <c r="Q42" s="18"/>
+      <c r="B42" s="15"/>
+      <c r="C42" s="15"/>
+      <c r="D42" s="15"/>
+      <c r="E42" s="49"/>
+      <c r="F42" s="15"/>
+      <c r="G42" s="15"/>
+      <c r="H42" s="15"/>
+      <c r="I42" s="15"/>
+      <c r="J42" s="15"/>
+      <c r="K42" s="15"/>
+      <c r="L42" s="15"/>
+      <c r="M42" s="15"/>
+      <c r="N42" s="15"/>
+      <c r="O42" s="15"/>
+      <c r="P42" s="15"/>
+      <c r="Q42" s="17"/>
     </row>
     <row r="43" spans="1:17" ht="10" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A43" s="56" t="s">
+      <c r="A43" s="55" t="s">
         <v>93</v>
       </c>
-      <c r="B43" s="20"/>
-      <c r="C43" s="20"/>
-      <c r="D43" s="20"/>
-      <c r="E43" s="57"/>
-      <c r="F43" s="20"/>
-      <c r="G43" s="20"/>
-      <c r="H43" s="20"/>
-      <c r="I43" s="20"/>
-      <c r="J43" s="20"/>
-      <c r="K43" s="20"/>
-      <c r="L43" s="20"/>
-      <c r="M43" s="20"/>
-      <c r="N43" s="20"/>
-      <c r="O43" s="20"/>
-      <c r="P43" s="20"/>
-      <c r="Q43" s="21"/>
+      <c r="B43" s="19"/>
+      <c r="C43" s="19"/>
+      <c r="D43" s="19"/>
+      <c r="E43" s="56"/>
+      <c r="F43" s="19"/>
+      <c r="G43" s="19"/>
+      <c r="H43" s="19"/>
+      <c r="I43" s="19"/>
+      <c r="J43" s="19"/>
+      <c r="K43" s="19"/>
+      <c r="L43" s="19"/>
+      <c r="M43" s="19"/>
+      <c r="N43" s="19"/>
+      <c r="O43" s="19"/>
+      <c r="P43" s="19"/>
+      <c r="Q43" s="20"/>
     </row>
     <row r="44" spans="1:17" ht="10" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
     <row r="45" spans="1:17" ht="10" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
@@ -8144,30 +7279,30 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="E2" s="15" t="s">
+      <c r="E2" s="14" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="B4" s="66" t="s">
+      <c r="B4" s="62" t="s">
         <v>106</v>
       </c>
-      <c r="C4" s="66" t="s">
+      <c r="C4" s="62" t="s">
         <v>107</v>
       </c>
-      <c r="D4" s="66" t="s">
+      <c r="D4" s="62" t="s">
         <v>108</v>
       </c>
-      <c r="E4" s="66" t="s">
+      <c r="E4" s="62" t="s">
         <v>109</v>
       </c>
-      <c r="F4" s="66" t="s">
+      <c r="F4" s="62" t="s">
         <v>110</v>
       </c>
-      <c r="G4" s="66" t="s">
+      <c r="G4" s="62" t="s">
         <v>111</v>
       </c>
-      <c r="H4" s="66" t="s">
+      <c r="H4" s="62" t="s">
         <v>112</v>
       </c>
     </row>
@@ -8175,178 +7310,178 @@
       <c r="A5" t="s">
         <v>118</v>
       </c>
-      <c r="B5" s="16" t="s">
+      <c r="B5" s="15" t="s">
         <v>113</v>
       </c>
-      <c r="C5" s="16" t="s">
+      <c r="C5" s="15" t="s">
         <v>114</v>
       </c>
-      <c r="D5" s="16" t="s">
+      <c r="D5" s="15" t="s">
         <v>115</v>
       </c>
-      <c r="E5" s="16" t="s">
+      <c r="E5" s="15" t="s">
         <v>116</v>
       </c>
-      <c r="F5" s="16" t="s">
+      <c r="F5" s="15" t="s">
         <v>117</v>
       </c>
-      <c r="G5" s="16" t="s">
+      <c r="G5" s="15" t="s">
         <v>117</v>
       </c>
-      <c r="H5" s="16"/>
+      <c r="H5" s="15"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="B6" s="16"/>
-      <c r="C6" s="16"/>
-      <c r="D6" s="16"/>
-      <c r="E6" s="16"/>
-      <c r="F6" s="16"/>
-      <c r="G6" s="16"/>
-      <c r="H6" s="16"/>
+      <c r="B6" s="15"/>
+      <c r="C6" s="15"/>
+      <c r="D6" s="15"/>
+      <c r="E6" s="15"/>
+      <c r="F6" s="15"/>
+      <c r="G6" s="15"/>
+      <c r="H6" s="15"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="B7" s="16"/>
-      <c r="C7" s="16"/>
-      <c r="D7" s="16"/>
-      <c r="E7" s="16"/>
-      <c r="F7" s="16"/>
-      <c r="G7" s="16"/>
-      <c r="H7" s="16"/>
+      <c r="B7" s="15"/>
+      <c r="C7" s="15"/>
+      <c r="D7" s="15"/>
+      <c r="E7" s="15"/>
+      <c r="F7" s="15"/>
+      <c r="G7" s="15"/>
+      <c r="H7" s="15"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="B8" s="16"/>
-      <c r="C8" s="16"/>
-      <c r="D8" s="16"/>
-      <c r="E8" s="16"/>
-      <c r="F8" s="16"/>
-      <c r="G8" s="16"/>
-      <c r="H8" s="16"/>
+      <c r="B8" s="15"/>
+      <c r="C8" s="15"/>
+      <c r="D8" s="15"/>
+      <c r="E8" s="15"/>
+      <c r="F8" s="15"/>
+      <c r="G8" s="15"/>
+      <c r="H8" s="15"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="B9" s="16"/>
-      <c r="C9" s="16"/>
-      <c r="D9" s="16"/>
-      <c r="E9" s="16"/>
-      <c r="F9" s="16"/>
-      <c r="G9" s="16"/>
-      <c r="H9" s="16"/>
+      <c r="B9" s="15"/>
+      <c r="C9" s="15"/>
+      <c r="D9" s="15"/>
+      <c r="E9" s="15"/>
+      <c r="F9" s="15"/>
+      <c r="G9" s="15"/>
+      <c r="H9" s="15"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="B10" s="16"/>
-      <c r="C10" s="16"/>
-      <c r="D10" s="16"/>
-      <c r="E10" s="16"/>
-      <c r="F10" s="16"/>
-      <c r="G10" s="16"/>
-      <c r="H10" s="16"/>
+      <c r="B10" s="15"/>
+      <c r="C10" s="15"/>
+      <c r="D10" s="15"/>
+      <c r="E10" s="15"/>
+      <c r="F10" s="15"/>
+      <c r="G10" s="15"/>
+      <c r="H10" s="15"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="B11" s="16"/>
-      <c r="C11" s="16"/>
-      <c r="D11" s="16"/>
-      <c r="E11" s="16"/>
-      <c r="F11" s="16"/>
-      <c r="G11" s="16"/>
-      <c r="H11" s="16"/>
+      <c r="B11" s="15"/>
+      <c r="C11" s="15"/>
+      <c r="D11" s="15"/>
+      <c r="E11" s="15"/>
+      <c r="F11" s="15"/>
+      <c r="G11" s="15"/>
+      <c r="H11" s="15"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="B12" s="16"/>
-      <c r="C12" s="16"/>
-      <c r="D12" s="16"/>
-      <c r="E12" s="16"/>
-      <c r="F12" s="16"/>
-      <c r="G12" s="16"/>
-      <c r="H12" s="16"/>
+      <c r="B12" s="15"/>
+      <c r="C12" s="15"/>
+      <c r="D12" s="15"/>
+      <c r="E12" s="15"/>
+      <c r="F12" s="15"/>
+      <c r="G12" s="15"/>
+      <c r="H12" s="15"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="B13" s="16"/>
-      <c r="C13" s="16"/>
-      <c r="D13" s="16"/>
-      <c r="E13" s="16"/>
-      <c r="F13" s="16"/>
-      <c r="G13" s="16"/>
-      <c r="H13" s="16"/>
+      <c r="B13" s="15"/>
+      <c r="C13" s="15"/>
+      <c r="D13" s="15"/>
+      <c r="E13" s="15"/>
+      <c r="F13" s="15"/>
+      <c r="G13" s="15"/>
+      <c r="H13" s="15"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="B14" s="16"/>
-      <c r="C14" s="16"/>
-      <c r="D14" s="16"/>
-      <c r="E14" s="16"/>
-      <c r="F14" s="16"/>
-      <c r="G14" s="16"/>
-      <c r="H14" s="16"/>
+      <c r="B14" s="15"/>
+      <c r="C14" s="15"/>
+      <c r="D14" s="15"/>
+      <c r="E14" s="15"/>
+      <c r="F14" s="15"/>
+      <c r="G14" s="15"/>
+      <c r="H14" s="15"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="B15" s="16"/>
-      <c r="C15" s="16"/>
-      <c r="D15" s="16"/>
-      <c r="E15" s="16"/>
-      <c r="F15" s="16"/>
-      <c r="G15" s="16"/>
-      <c r="H15" s="16"/>
+      <c r="B15" s="15"/>
+      <c r="C15" s="15"/>
+      <c r="D15" s="15"/>
+      <c r="E15" s="15"/>
+      <c r="F15" s="15"/>
+      <c r="G15" s="15"/>
+      <c r="H15" s="15"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="B16" s="16"/>
-      <c r="C16" s="16"/>
-      <c r="D16" s="16"/>
-      <c r="E16" s="16"/>
-      <c r="F16" s="16"/>
-      <c r="G16" s="16"/>
-      <c r="H16" s="16"/>
+      <c r="B16" s="15"/>
+      <c r="C16" s="15"/>
+      <c r="D16" s="15"/>
+      <c r="E16" s="15"/>
+      <c r="F16" s="15"/>
+      <c r="G16" s="15"/>
+      <c r="H16" s="15"/>
     </row>
     <row r="17" spans="2:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="B17" s="16"/>
-      <c r="C17" s="16"/>
-      <c r="D17" s="16"/>
-      <c r="E17" s="16"/>
-      <c r="F17" s="16"/>
-      <c r="G17" s="16"/>
-      <c r="H17" s="16"/>
+      <c r="B17" s="15"/>
+      <c r="C17" s="15"/>
+      <c r="D17" s="15"/>
+      <c r="E17" s="15"/>
+      <c r="F17" s="15"/>
+      <c r="G17" s="15"/>
+      <c r="H17" s="15"/>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="B18" s="16"/>
-      <c r="C18" s="16"/>
-      <c r="D18" s="16"/>
-      <c r="E18" s="16"/>
-      <c r="F18" s="16"/>
-      <c r="G18" s="16"/>
-      <c r="H18" s="16"/>
+      <c r="B18" s="15"/>
+      <c r="C18" s="15"/>
+      <c r="D18" s="15"/>
+      <c r="E18" s="15"/>
+      <c r="F18" s="15"/>
+      <c r="G18" s="15"/>
+      <c r="H18" s="15"/>
     </row>
     <row r="19" spans="2:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="B19" s="16"/>
-      <c r="C19" s="16"/>
-      <c r="D19" s="16"/>
-      <c r="E19" s="16"/>
-      <c r="F19" s="16"/>
-      <c r="G19" s="16"/>
-      <c r="H19" s="16"/>
+      <c r="B19" s="15"/>
+      <c r="C19" s="15"/>
+      <c r="D19" s="15"/>
+      <c r="E19" s="15"/>
+      <c r="F19" s="15"/>
+      <c r="G19" s="15"/>
+      <c r="H19" s="15"/>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="B20" s="16"/>
-      <c r="C20" s="16"/>
-      <c r="D20" s="16"/>
-      <c r="E20" s="16"/>
-      <c r="F20" s="16"/>
-      <c r="G20" s="16"/>
-      <c r="H20" s="16"/>
+      <c r="B20" s="15"/>
+      <c r="C20" s="15"/>
+      <c r="D20" s="15"/>
+      <c r="E20" s="15"/>
+      <c r="F20" s="15"/>
+      <c r="G20" s="15"/>
+      <c r="H20" s="15"/>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="B21" s="16"/>
-      <c r="C21" s="16"/>
-      <c r="D21" s="16"/>
-      <c r="E21" s="16"/>
-      <c r="F21" s="16"/>
-      <c r="G21" s="16"/>
-      <c r="H21" s="16"/>
+      <c r="B21" s="15"/>
+      <c r="C21" s="15"/>
+      <c r="D21" s="15"/>
+      <c r="E21" s="15"/>
+      <c r="F21" s="15"/>
+      <c r="G21" s="15"/>
+      <c r="H21" s="15"/>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="B22" s="16"/>
-      <c r="C22" s="16"/>
-      <c r="D22" s="16"/>
-      <c r="E22" s="16"/>
-      <c r="F22" s="16"/>
-      <c r="G22" s="16"/>
-      <c r="H22" s="16"/>
+      <c r="B22" s="15"/>
+      <c r="C22" s="15"/>
+      <c r="D22" s="15"/>
+      <c r="E22" s="15"/>
+      <c r="F22" s="15"/>
+      <c r="G22" s="15"/>
+      <c r="H22" s="15"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>
@@ -8356,4 +7491,55 @@
     <oddHeader>&amp;L【リスク登録簿】</oddHeader>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA56C622-71B9-4025-A522-F5135B2D2FB3}">
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="1" max="3" width="37.58203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="11.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="2" spans="1:3" ht="26.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" s="66" t="s">
+        <v>120</v>
+      </c>
+      <c r="B2" s="66" t="s">
+        <v>121</v>
+      </c>
+      <c r="C2" s="66" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="120" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" s="67" t="s">
+        <v>123</v>
+      </c>
+      <c r="B3" s="15"/>
+      <c r="C3" s="15"/>
+    </row>
+    <row r="4" spans="1:3" ht="131.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" s="67" t="s">
+        <v>124</v>
+      </c>
+      <c r="B4" s="15"/>
+      <c r="C4" s="15"/>
+    </row>
+    <row r="5" spans="1:3" ht="171" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" s="67" t="s">
+        <v>125</v>
+      </c>
+      <c r="B5" s="15"/>
+      <c r="C5" s="15"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
+  <headerFooter>
+    <oddHeader>&amp;L【交渉ロールプレイ】</oddHeader>
+  </headerFooter>
+</worksheet>
 </file>
--- a/高橋さん用フォルダ/テンプレート集.xlsx
+++ b/高橋さん用フォルダ/テンプレート集.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD47E960-674E-4C6F-8046-2A3E3532A74A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" firstSheet="4" activeTab="7" xr2:uid="{C2D9C0E7-7181-4507-8D76-FFF1980A0610}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" firstSheet="2" activeTab="7" xr2:uid="{C2D9C0E7-7181-4507-8D76-FFF1980A0610}"/>
   </bookViews>
   <sheets>
     <sheet name="組織のビジネスモデル" sheetId="1" r:id="rId1"/>
@@ -1584,6 +1584,12 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="12" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="12" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1592,12 +1598,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="12" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -6300,18 +6300,18 @@
       </c>
     </row>
     <row r="2" spans="1:17" ht="18.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="F2" s="63"/>
-      <c r="G2" s="64"/>
-      <c r="H2" s="64"/>
-      <c r="I2" s="64"/>
-      <c r="J2" s="64"/>
-      <c r="K2" s="64"/>
-      <c r="L2" s="64"/>
-      <c r="M2" s="64"/>
-      <c r="N2" s="64"/>
-      <c r="O2" s="64"/>
-      <c r="P2" s="64"/>
-      <c r="Q2" s="65"/>
+      <c r="F2" s="65"/>
+      <c r="G2" s="66"/>
+      <c r="H2" s="66"/>
+      <c r="I2" s="66"/>
+      <c r="J2" s="66"/>
+      <c r="K2" s="66"/>
+      <c r="L2" s="66"/>
+      <c r="M2" s="66"/>
+      <c r="N2" s="66"/>
+      <c r="O2" s="66"/>
+      <c r="P2" s="66"/>
+      <c r="Q2" s="67"/>
     </row>
     <row r="3" spans="1:17" ht="32" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="B3" s="24" t="s">
@@ -7503,32 +7503,32 @@
   <sheetData>
     <row r="1" spans="1:3" ht="11.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
     <row r="2" spans="1:3" ht="26.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="66" t="s">
+      <c r="A2" s="63" t="s">
         <v>120</v>
       </c>
-      <c r="B2" s="66" t="s">
+      <c r="B2" s="63" t="s">
         <v>121</v>
       </c>
-      <c r="C2" s="66" t="s">
+      <c r="C2" s="63" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="120" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="67" t="s">
+      <c r="A3" s="64" t="s">
         <v>123</v>
       </c>
       <c r="B3" s="15"/>
       <c r="C3" s="15"/>
     </row>
     <row r="4" spans="1:3" ht="131.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="67" t="s">
+      <c r="A4" s="64" t="s">
         <v>124</v>
       </c>
       <c r="B4" s="15"/>
       <c r="C4" s="15"/>
     </row>
     <row r="5" spans="1:3" ht="171" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="67" t="s">
+      <c r="A5" s="64" t="s">
         <v>125</v>
       </c>
       <c r="B5" s="15"/>

--- a/高橋さん用フォルダ/テンプレート集.xlsx
+++ b/高橋さん用フォルダ/テンプレート集.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\iret_pm\高橋さん用フォルダ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD47E960-674E-4C6F-8046-2A3E3532A74A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4FBAA3E-AB07-416A-88E0-6E97C3E6FC43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" firstSheet="2" activeTab="7" xr2:uid="{C2D9C0E7-7181-4507-8D76-FFF1980A0610}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" xr2:uid="{C2D9C0E7-7181-4507-8D76-FFF1980A0610}"/>
   </bookViews>
   <sheets>
     <sheet name="組織のビジネスモデル" sheetId="1" r:id="rId1"/>
@@ -41,14 +41,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="114">
   <si>
     <t>キーパートナー</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>キーアクティビティ</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>与える価値</t>
@@ -58,11 +58,11 @@
     <rPh sb="3" eb="5">
       <t>カチ</t>
     </rPh>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>キーリソース</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>顧客との関係</t>
@@ -72,36 +72,36 @@
     <rPh sb="4" eb="6">
       <t>カンケイ</t>
     </rPh>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>チャネル</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>顧客</t>
     <rPh sb="0" eb="2">
       <t>コキャク</t>
     </rPh>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>コスト</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>収入</t>
     <rPh sb="0" eb="2">
       <t>シュウニュウ</t>
     </rPh>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>プロジェクト名</t>
     <rPh sb="6" eb="7">
       <t>メイ</t>
     </rPh>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>開始日と終了日</t>
@@ -114,14 +114,14 @@
     <rPh sb="4" eb="7">
       <t>シュウリョウビ</t>
     </rPh>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>予算</t>
     <rPh sb="0" eb="2">
       <t>ヨサン</t>
     </rPh>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>作業範囲記述書(SOW)</t>
@@ -134,7 +134,7 @@
     <rPh sb="4" eb="7">
       <t>キジュツショ</t>
     </rPh>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>プロジェクトの要素成果物</t>
@@ -144,7 +144,7 @@
     <rPh sb="9" eb="12">
       <t>セイカブツ</t>
     </rPh>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>ビジネス・ケース（このプロジェクトのビジネス上の価値）</t>
@@ -154,7 +154,7 @@
     <rPh sb="24" eb="26">
       <t>カチ</t>
     </rPh>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>プロジェクト組織の構造</t>
@@ -164,7 +164,7 @@
     <rPh sb="9" eb="11">
       <t>コウゾウ</t>
     </rPh>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>プロジェクトの制約条件</t>
@@ -174,7 +174,7 @@
     <rPh sb="9" eb="11">
       <t>ジョウケン</t>
     </rPh>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>顧客の署名</t>
@@ -184,31 +184,21 @@
     <rPh sb="3" eb="5">
       <t>ショメイ</t>
     </rPh>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>スポンサーの署名</t>
     <rPh sb="6" eb="8">
       <t>ショメイ</t>
     </rPh>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>日付</t>
     <rPh sb="0" eb="2">
       <t>ヒヅケ</t>
     </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>どこから情報を入手するか？</t>
-    <rPh sb="4" eb="6">
-      <t>ジョウホウ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>ニュウシュ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>※プロジェクトを完成するためのプロダクト、サービスあるいは所産を記述してください</t>
@@ -221,7 +211,7 @@
     <rPh sb="32" eb="34">
       <t>キジュツ</t>
     </rPh>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>※プロジェクトが要求される投資の価値があるかどうか判断するために、事業場の見地から必要な情報を提供してください</t>
@@ -252,7 +242,7 @@
     <rPh sb="47" eb="49">
       <t>テイキョウ</t>
     </rPh>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>※プロジェクトが生み出す主要な成果物を記述してください</t>
@@ -271,7 +261,7 @@
     <rPh sb="19" eb="21">
       <t>キジュツ</t>
     </rPh>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>※プロジェクト組織の構造を記述してください(プロジェクト・マネージャーの名前やメンバーの名前など)</t>
@@ -290,7 +280,7 @@
     <rPh sb="44" eb="46">
       <t>ナマエ</t>
     </rPh>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>※プロジェクト・チームのアクションを制限または指示するものを全て識別してください</t>
@@ -306,7 +296,7 @@
     <rPh sb="32" eb="34">
       <t>シキベツ</t>
     </rPh>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>主なステークホルダー（ステークホルダー登録簿）</t>
@@ -316,66 +306,32 @@
     <rPh sb="19" eb="22">
       <t>トウロクボ</t>
     </rPh>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>名前</t>
     <rPh sb="0" eb="2">
       <t>ナマエ</t>
     </rPh>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>ポジション</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>いつ、どこから
 （だれから）
 情報を入手したか</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>コミュニケーション活動
 （会議体、頻度、アプローチなど）</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>ステークホルダーのプロジェクトへの
-状況（不認識、中立、抵抗、支持）や、期待値</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>関東営業所設立</t>
-  </si>
-  <si>
-    <t>＊階層、タスクなど自由に変えてください。</t>
-    <rPh sb="1" eb="3">
-      <t>カイソウ</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>ジユウ</t>
-    </rPh>
-    <rPh sb="12" eb="13">
-      <t>カ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>⁂成果物、タスクの横に、識別番号をつけてください。</t>
-    <rPh sb="1" eb="4">
-      <t>セイカブツ</t>
-    </rPh>
-    <rPh sb="9" eb="10">
-      <t>ヨコ</t>
-    </rPh>
-    <rPh sb="12" eb="14">
-      <t>シキベツ</t>
-    </rPh>
-    <rPh sb="14" eb="16">
-      <t>バンゴウ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>⁂ボックス、→などは自由に変えてください。</t>
@@ -385,7 +341,7 @@
     <rPh sb="13" eb="14">
       <t>カ</t>
     </rPh>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>＊クリティカルパスを算出してください（何日　何か月）</t>
@@ -401,72 +357,29 @@
     <rPh sb="24" eb="25">
       <t>ゲツ</t>
     </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>スタート</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>終了</t>
-    <rPh sb="0" eb="2">
-      <t>シュウリョウ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>1.1 task:所要時間（2時間）</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>1.3 task</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>1.2 task</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>2.1 task:所要時間</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>2.2 task</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>2.3 task</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>2.4 task</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>x.x</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>成果物</t>
     <rPh sb="0" eb="3">
       <t>セイカブツ</t>
     </rPh>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>責任者</t>
     <rPh sb="0" eb="3">
       <t>セキニンシャ</t>
     </rPh>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>WK1</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>WK2</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>WK3</t>
@@ -482,22 +395,6 @@
   </si>
   <si>
     <t>WK7</t>
-  </si>
-  <si>
-    <t>アクティビティ
-内容</t>
-    <rPh sb="8" eb="10">
-      <t>ナイヨウ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>アクティビティ
-番号</t>
-    <rPh sb="8" eb="10">
-      <t>バンゴウ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>WK8</t>
@@ -519,158 +416,158 @@
     <rPh sb="0" eb="2">
       <t>キカク</t>
     </rPh>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>1.1.1</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>1.1.2</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>1.2.1</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>1.2.2</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>1.2.3</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>計画書</t>
     <rPh sb="0" eb="3">
       <t>ケイカクショ</t>
     </rPh>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>2.1.1</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>2.1.2</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>2.1.3</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>2.1.4</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>2.2.1</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>2.2.2</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>2.2.3</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>2.2.4</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>3.1.1</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>3.1.2</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>3.1.3</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>3.1.4</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>3.2.1</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>3.2.2</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>3.2.3</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>3.3.1</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>3.3.2</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>3.3.3</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>4.1.1</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>4.1.2</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>4.1.3</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>4.2.1</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>4.2.2</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>4.2.3</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>アクティビティ1.1</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>アクティビティ1.2</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>アクティビティ2.1</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>アクティビティ2.2</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>アクティビティ3.1</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>アクティビティ3.2</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>アクティビティ3.3</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>単位　週</t>
@@ -680,7 +577,7 @@
     <rPh sb="3" eb="4">
       <t>シュウ</t>
     </rPh>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>⁂単位、識別番号など自由に変えてください</t>
@@ -699,33 +596,33 @@
     <rPh sb="13" eb="14">
       <t>カ</t>
     </rPh>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>HM</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>YK</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>EN</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>観点</t>
     <rPh sb="0" eb="2">
       <t>カンテン</t>
     </rPh>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>リスク項目</t>
     <rPh sb="3" eb="5">
       <t>コウモク</t>
     </rPh>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>対応策</t>
@@ -735,42 +632,42 @@
     <rPh sb="2" eb="3">
       <t>サク</t>
     </rPh>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>担当者</t>
     <rPh sb="0" eb="3">
       <t>タントウシャ</t>
     </rPh>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>期日</t>
     <rPh sb="0" eb="2">
       <t>キジツ</t>
     </rPh>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>完了日</t>
     <rPh sb="0" eb="3">
       <t>カンリョウビ</t>
     </rPh>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>備考</t>
     <rPh sb="0" eb="2">
       <t>ビコウ</t>
     </rPh>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>開発リスク</t>
     <rPh sb="0" eb="2">
       <t>カイハツ</t>
     </rPh>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>本業との時間のコンフリクト</t>
@@ -780,7 +677,7 @@
     <rPh sb="4" eb="6">
       <t>ジカン</t>
     </rPh>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>メンバーと上司と事前に交渉する</t>
@@ -793,22 +690,15 @@
     <rPh sb="11" eb="13">
       <t>コウショウ</t>
     </rPh>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>Mr.AAA</t>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>YY/MM/DD</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>※例</t>
-    <rPh sb="1" eb="2">
-      <t>レイ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>⁂観点、リスク項目、対応策のみ記入ください</t>
@@ -827,21 +717,21 @@
     <rPh sb="15" eb="17">
       <t>キニュウ</t>
     </rPh>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>交渉のシナリオ</t>
     <rPh sb="0" eb="2">
       <t>コウショウ</t>
     </rPh>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>こちら側</t>
     <rPh sb="3" eb="4">
       <t>ガワ</t>
     </rPh>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>相手側</t>
@@ -851,7 +741,7 @@
     <rPh sb="2" eb="3">
       <t>ガワ</t>
     </rPh>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>交渉の目的
@@ -863,7 +753,7 @@
     <rPh sb="3" eb="5">
       <t>モクテキ</t>
     </rPh>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>利害関係
@@ -892,7 +782,7 @@
     <rPh sb="26" eb="28">
       <t>コウモク</t>
     </rPh>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>代替案
@@ -924,25 +814,64 @@
     <rPh sb="22" eb="24">
       <t>ジョウケン</t>
     </rPh>
-    <phoneticPr fontId="2"/>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ステークホルダーのプロジェクトへの状況（不認識、中立、抵抗、支持）や、期待値</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>＊階層、タスクなど自由に変えてください</t>
+    <rPh sb="1" eb="3">
+      <t>カイソウ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ジユウ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>⁂成果物、タスクの横に識別番号をつけてください</t>
+    <rPh sb="1" eb="4">
+      <t>セイカブツ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ヨコ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>シキベツ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>バンゴウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アクティビティ内容</t>
+    <rPh sb="7" eb="9">
+      <t>ナイヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アクティビティ番号</t>
+    <rPh sb="7" eb="9">
+      <t>バンゴウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="游ゴシック"/>
-      <family val="2"/>
-      <charset val="128"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="游ゴシック"/>
       <family val="2"/>
       <charset val="128"/>
@@ -980,10 +909,66 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
+      <sz val="14"/>
       <color theme="1"/>
       <name val="游ゴシック"/>
       <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FFFF0000"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
@@ -1044,7 +1029,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="27">
+  <borders count="29">
     <border>
       <left/>
       <right/>
@@ -1388,17 +1373,32 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="97">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1">
@@ -1422,22 +1422,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1">
@@ -1467,18 +1458,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
@@ -1486,9 +1465,6 @@
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -1506,67 +1482,7 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="12" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="14" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="19" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1575,29 +1491,203 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="14" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="12" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="12" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="12" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1620,13 +1710,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
+      <xdr:col>0</xdr:col>
       <xdr:colOff>215900</xdr:colOff>
       <xdr:row>4</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
+      <xdr:col>5</xdr:col>
       <xdr:colOff>69850</xdr:colOff>
       <xdr:row>9</xdr:row>
       <xdr:rowOff>63500</xdr:rowOff>
@@ -1687,13 +1777,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>8</xdr:col>
+      <xdr:col>6</xdr:col>
       <xdr:colOff>203200</xdr:colOff>
       <xdr:row>3</xdr:row>
       <xdr:rowOff>12700</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
+      <xdr:col>11</xdr:col>
       <xdr:colOff>57150</xdr:colOff>
       <xdr:row>8</xdr:row>
       <xdr:rowOff>76200</xdr:rowOff>
@@ -1754,13 +1844,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>8</xdr:col>
+      <xdr:col>6</xdr:col>
       <xdr:colOff>190500</xdr:colOff>
       <xdr:row>12</xdr:row>
       <xdr:rowOff>82550</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
+      <xdr:col>11</xdr:col>
       <xdr:colOff>44450</xdr:colOff>
       <xdr:row>17</xdr:row>
       <xdr:rowOff>146050</xdr:rowOff>
@@ -1821,13 +1911,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>14</xdr:col>
+      <xdr:col>12</xdr:col>
       <xdr:colOff>234950</xdr:colOff>
       <xdr:row>3</xdr:row>
       <xdr:rowOff>222250</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>19</xdr:col>
+      <xdr:col>17</xdr:col>
       <xdr:colOff>88900</xdr:colOff>
       <xdr:row>9</xdr:row>
       <xdr:rowOff>57150</xdr:rowOff>
@@ -1888,13 +1978,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>20</xdr:col>
+      <xdr:col>18</xdr:col>
       <xdr:colOff>222250</xdr:colOff>
       <xdr:row>3</xdr:row>
       <xdr:rowOff>12700</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>25</xdr:col>
+      <xdr:col>23</xdr:col>
       <xdr:colOff>76200</xdr:colOff>
       <xdr:row>8</xdr:row>
       <xdr:rowOff>76200</xdr:rowOff>
@@ -1955,13 +2045,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>20</xdr:col>
+      <xdr:col>18</xdr:col>
       <xdr:colOff>209550</xdr:colOff>
       <xdr:row>12</xdr:row>
       <xdr:rowOff>82550</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>25</xdr:col>
+      <xdr:col>23</xdr:col>
       <xdr:colOff>63500</xdr:colOff>
       <xdr:row>17</xdr:row>
       <xdr:rowOff>146050</xdr:rowOff>
@@ -2022,13 +2112,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>26</xdr:col>
+      <xdr:col>24</xdr:col>
       <xdr:colOff>222250</xdr:colOff>
       <xdr:row>4</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>31</xdr:col>
+      <xdr:col>29</xdr:col>
       <xdr:colOff>76200</xdr:colOff>
       <xdr:row>9</xdr:row>
       <xdr:rowOff>63500</xdr:rowOff>
@@ -2094,16 +2184,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>38100</xdr:colOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>25400</xdr:colOff>
       <xdr:row>9</xdr:row>
-      <xdr:rowOff>31750</xdr:rowOff>
+      <xdr:rowOff>19050</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>254000</xdr:colOff>
       <xdr:row>10</xdr:row>
-      <xdr:rowOff>209550</xdr:rowOff>
+      <xdr:rowOff>279400</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2118,8 +2208,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3879850" y="1905000"/>
-          <a:ext cx="266700" cy="406400"/>
+          <a:off x="3848100" y="2590800"/>
+          <a:ext cx="228600" cy="546100"/>
         </a:xfrm>
         <a:prstGeom prst="leftArrow">
           <a:avLst/>
@@ -2155,23 +2245,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>38100</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>57150</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>209550</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>22</xdr:row>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>12700</xdr:colOff>
+      <xdr:row>36</xdr:row>
       <xdr:rowOff>101600</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="3" name="矢印: 左 2">
+        <xdr:cNvPr id="4" name="矢印: 左 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9687D08C-FE24-4FAC-834F-17778C9B7F77}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4745DF3F-EB91-498F-9D29-48442D0F6FDD}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2179,8 +2269,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3879850" y="4108450"/>
-          <a:ext cx="266700" cy="406400"/>
+          <a:off x="3879850" y="9925050"/>
+          <a:ext cx="228600" cy="463550"/>
         </a:xfrm>
         <a:prstGeom prst="leftArrow">
           <a:avLst/>
@@ -2216,23 +2306,737 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>31750</xdr:colOff>
-      <xdr:row>34</xdr:row>
-      <xdr:rowOff>25400</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>6350</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>279400</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>298450</xdr:colOff>
-      <xdr:row>35</xdr:row>
-      <xdr:rowOff>203200</xdr:rowOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>266700</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>12700</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="4" name="矢印: 左 3">
+        <xdr:cNvPr id="5" name="テキスト ボックス 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4745DF3F-EB91-498F-9D29-48442D0F6FDD}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C73B80C6-B74D-8182-C229-FD9AD99E27F3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6350" y="279400"/>
+          <a:ext cx="3536950" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>266700</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="テキスト ボックス 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5A0929A8-634D-49CF-876F-D39569311DC2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="857250"/>
+          <a:ext cx="3543300" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>260350</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7" name="テキスト ボックス 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{80AD104B-12D2-46C8-A0DC-D8F3C1F086CF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="1428750"/>
+          <a:ext cx="3536950" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>266700</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8" name="テキスト ボックス 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F441371D-278D-46DB-A050-BCB88472F4E2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="2286000"/>
+          <a:ext cx="3549650" cy="1123950"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>12700</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>12700</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>29</xdr:col>
+      <xdr:colOff>12700</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>279400</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="10" name="テキスト ボックス 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{06E94DC2-173E-4B5C-A2A7-503B6F832839}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4381500" y="2298700"/>
+          <a:ext cx="3549650" cy="1123950"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="ja-JP" sz="1200" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>どこから情報を入手するか？</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="ja-JP" sz="1200">
+              <a:effectLst/>
+            </a:rPr>
+            <a:t> </a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>254000</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>6350</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="11" name="テキスト ボックス 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7F978608-932B-46F8-9711-354AF8A570AC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="4000500"/>
+          <a:ext cx="3530600" cy="863600"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>260350</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>12700</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="12" name="テキスト ボックス 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7A68F6E4-074E-4E36-B925-718B8D070DFA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="5429250"/>
+          <a:ext cx="3536950" cy="1441450"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>266700</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>12700</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="14" name="テキスト ボックス 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9B23B69D-3358-485B-ACA5-1C6A04E15453}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="7429500"/>
+          <a:ext cx="3543300" cy="1441450"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>6350</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>12700</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="15" name="テキスト ボックス 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BA7047A6-ADD3-4900-B7E1-FD6885FF0954}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="9429750"/>
+          <a:ext cx="3556000" cy="1441450"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>12700</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>6350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>29</xdr:col>
+      <xdr:colOff>6350</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="16" name="テキスト ボックス 15">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6CAF2FD2-C4A7-40D9-8DB5-DFFCAD3B8020}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4381500" y="9436100"/>
+          <a:ext cx="3543300" cy="1441450"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="ja-JP" sz="1200" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>どこから情報を入手するか？</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="ja-JP" sz="1200">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> </a:t>
+          </a:r>
+          <a:endParaRPr lang="ja-JP" altLang="ja-JP" sz="1200">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>57150</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>146050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>12700</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="17" name="矢印: 左 16">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{63A0A79A-5545-BE26-3681-2DCC477C36CD}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2240,8 +3044,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3873500" y="7448550"/>
-          <a:ext cx="266700" cy="406400"/>
+          <a:off x="3879850" y="5861050"/>
+          <a:ext cx="228600" cy="520700"/>
         </a:xfrm>
         <a:prstGeom prst="leftArrow">
           <a:avLst/>
@@ -2275,6 +3079,117 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>12700</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>279400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>29</xdr:col>
+      <xdr:colOff>6350</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>279400</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="18" name="テキスト ボックス 17">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{03DFCD24-7048-A335-ABF3-E0FE71EAB075}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4381500" y="5422900"/>
+          <a:ext cx="3543300" cy="1428750"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="ja-JP" sz="1200" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>どこから情報を入手するか？</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="ja-JP" sz="1200">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> </a:t>
+          </a:r>
+          <a:endParaRPr lang="ja-JP" altLang="ja-JP" sz="1200">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -2282,13 +3197,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>11</xdr:col>
+      <xdr:col>10</xdr:col>
       <xdr:colOff>107950</xdr:colOff>
       <xdr:row>9</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
+      <xdr:col>10</xdr:col>
       <xdr:colOff>285750</xdr:colOff>
       <xdr:row>23</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
@@ -2306,8 +3221,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="3321050" y="2082800"/>
-          <a:ext cx="177800" cy="3359150"/>
+          <a:off x="3219450" y="2292350"/>
+          <a:ext cx="177800" cy="3714750"/>
           <a:chOff x="3321050" y="1847850"/>
           <a:chExt cx="177800" cy="3359150"/>
         </a:xfrm>
@@ -2497,13 +3412,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>16</xdr:col>
+      <xdr:col>15</xdr:col>
       <xdr:colOff>107950</xdr:colOff>
       <xdr:row>9</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
+      <xdr:col>15</xdr:col>
       <xdr:colOff>285750</xdr:colOff>
       <xdr:row>23</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
@@ -2521,8 +3436,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="4781550" y="2082800"/>
-          <a:ext cx="177800" cy="3359150"/>
+          <a:off x="4775200" y="2292350"/>
+          <a:ext cx="177800" cy="3714750"/>
           <a:chOff x="3321050" y="1847850"/>
           <a:chExt cx="177800" cy="3359150"/>
         </a:xfrm>
@@ -2712,13 +3627,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>21</xdr:col>
+      <xdr:col>20</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
       <xdr:row>9</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>22</xdr:col>
+      <xdr:col>21</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>23</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
@@ -2736,8 +3651,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="6248400" y="2082800"/>
-          <a:ext cx="177800" cy="3359150"/>
+          <a:off x="6337300" y="2292350"/>
+          <a:ext cx="196850" cy="3714750"/>
           <a:chOff x="3321050" y="1847850"/>
           <a:chExt cx="177800" cy="3359150"/>
         </a:xfrm>
@@ -2927,13 +3842,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>26</xdr:col>
+      <xdr:col>25</xdr:col>
       <xdr:colOff>107950</xdr:colOff>
       <xdr:row>9</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>26</xdr:col>
+      <xdr:col>25</xdr:col>
       <xdr:colOff>285750</xdr:colOff>
       <xdr:row>23</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
@@ -2951,8 +3866,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="7702550" y="2082800"/>
-          <a:ext cx="177800" cy="3359150"/>
+          <a:off x="7886700" y="2292350"/>
+          <a:ext cx="177800" cy="3714750"/>
           <a:chOff x="3321050" y="1847850"/>
           <a:chExt cx="177800" cy="3359150"/>
         </a:xfrm>
@@ -3142,13 +4057,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
+      <xdr:col>5</xdr:col>
       <xdr:colOff>107950</xdr:colOff>
       <xdr:row>9</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>6</xdr:col>
+      <xdr:col>5</xdr:col>
       <xdr:colOff>285750</xdr:colOff>
       <xdr:row>23</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
@@ -3166,8 +4081,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="1860550" y="2082800"/>
-          <a:ext cx="177800" cy="3359150"/>
+          <a:off x="1663700" y="2292350"/>
+          <a:ext cx="177800" cy="3714750"/>
           <a:chOff x="3321050" y="1847850"/>
           <a:chExt cx="177800" cy="3359150"/>
         </a:xfrm>
@@ -3357,13 +4272,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>1</xdr:col>
+      <xdr:col>0</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
       <xdr:row>9</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>2</xdr:col>
+      <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>23</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
@@ -3381,8 +4296,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="406400" y="2082800"/>
-          <a:ext cx="177800" cy="3359150"/>
+          <a:off x="114300" y="2292350"/>
+          <a:ext cx="196850" cy="3714750"/>
           <a:chOff x="3321050" y="1847850"/>
           <a:chExt cx="177800" cy="3359150"/>
         </a:xfrm>
@@ -3572,13 +4487,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>3</xdr:col>
+      <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>4</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>28</xdr:col>
+      <xdr:col>27</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>5</xdr:row>
       <xdr:rowOff>222250</xdr:rowOff>
@@ -3596,8 +4511,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="876300" y="927100"/>
-          <a:ext cx="7302500" cy="450850"/>
+          <a:off x="622300" y="1009650"/>
+          <a:ext cx="7778750" cy="476250"/>
           <a:chOff x="876300" y="927100"/>
           <a:chExt cx="7302500" cy="450850"/>
         </a:xfrm>
@@ -3900,32 +4815,35 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>342900</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>95250</xdr:rowOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>336998</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>309941</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>342900</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>107950</xdr:rowOff>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>325059</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>717</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="3" name="直線矢印コネクタ 2">
+        <xdr:cNvPr id="23" name="直線矢印コネクタ 22">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B9FEA623-C91F-F581-F08F-2D6D66448063}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{01B8C172-C326-4CEB-932D-9264248D157F}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="22" idx="3"/>
+          <a:endCxn id="51" idx="1"/>
+        </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipV="1">
-          <a:off x="692150" y="787400"/>
-          <a:ext cx="698500" cy="946150"/>
+          <a:off x="5900808" y="3802441"/>
+          <a:ext cx="2074489" cy="8276"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -3953,32 +4871,35 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>342900</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>120650</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>316783</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>336550</xdr:colOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>6350</xdr:colOff>
       <xdr:row>7</xdr:row>
-      <xdr:rowOff>107950</xdr:rowOff>
+      <xdr:rowOff>22679</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="7" name="直線矢印コネクタ 6">
+        <xdr:cNvPr id="3" name="直線矢印コネクタ 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E4C401DA-2CD1-4963-A282-4EB1F35B16D8}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B9FEA623-C91F-F581-F08F-2D6D66448063}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="31" idx="3"/>
+          <a:endCxn id="4" idx="1"/>
+        </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipV="1">
-          <a:off x="692150" y="1511300"/>
-          <a:ext cx="692150" cy="222250"/>
+          <a:off x="1043214" y="951783"/>
+          <a:ext cx="701826" cy="1293396"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -4006,16 +4927,72 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>342900</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>107950</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>2697</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>4</xdr:col>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>10</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>22679</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="7" name="直線矢印コネクタ 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E4C401DA-2CD1-4963-A282-4EB1F35B16D8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="31" idx="3"/>
+          <a:endCxn id="2" idx="1"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="1043214" y="1907697"/>
+          <a:ext cx="695486" cy="337482"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="19050">
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>22679</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>9</xdr:row>
-      <xdr:rowOff>101600</xdr:rowOff>
+      <xdr:rowOff>717</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -4026,12 +5003,15 @@
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="31" idx="3"/>
+          <a:endCxn id="16" idx="1"/>
+        </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="692150" y="1733550"/>
-          <a:ext cx="704850" cy="463550"/>
+          <a:off x="1043214" y="2245179"/>
+          <a:ext cx="695476" cy="613038"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -4060,15 +5040,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+      <xdr:colOff>336998</xdr:colOff>
       <xdr:row>9</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
+      <xdr:rowOff>717</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>342900</xdr:colOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>12</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
+      <xdr:rowOff>717</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -4079,65 +5059,15 @@
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="16" idx="3"/>
+          <a:endCxn id="22" idx="1"/>
+        </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3143250" y="2209800"/>
-          <a:ext cx="692150" cy="698500"/>
-        </a:xfrm>
-        <a:prstGeom prst="straightConnector1">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="19050">
-          <a:tailEnd type="triangle"/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="dk1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="dk1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="dk1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>342900</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="14" name="直線矢印コネクタ 13">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0655B085-EBB0-4132-B774-F25DBE4141E2}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="3136900" y="806450"/>
-          <a:ext cx="704850" cy="0"/>
+          <a:off x="3466641" y="2858217"/>
+          <a:ext cx="706216" cy="952500"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -4166,31 +5096,34 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>120650</xdr:rowOff>
+      <xdr:colOff>343348</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>316783</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>6350</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>120650</xdr:rowOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>717</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="17" name="直線矢印コネクタ 16">
+        <xdr:cNvPr id="14" name="直線矢印コネクタ 13">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BFF2F91D-094B-4B32-86E1-02EEFA846031}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0655B085-EBB0-4132-B774-F25DBE4141E2}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="4" idx="3"/>
+          <a:endCxn id="15" idx="1"/>
+        </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3143250" y="1511300"/>
-          <a:ext cx="704850" cy="0"/>
+          <a:off x="3472991" y="951783"/>
+          <a:ext cx="699866" cy="1434"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -4218,13 +5151,69 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>16</xdr:col>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>337008</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>717</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>2697</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="17" name="直線矢印コネクタ 16">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BFF2F91D-094B-4B32-86E1-02EEFA846031}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="2" idx="3"/>
+          <a:endCxn id="25" idx="1"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="3466651" y="1905717"/>
+          <a:ext cx="706206" cy="1980"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="19050">
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>17</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>3</xdr:row>
       <xdr:rowOff>120650</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>18</xdr:col>
+      <xdr:col>19</xdr:col>
       <xdr:colOff>6350</xdr:colOff>
       <xdr:row>3</xdr:row>
       <xdr:rowOff>120650</xdr:rowOff>
@@ -4271,13 +5260,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>16</xdr:col>
+      <xdr:col>17</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>6</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>18</xdr:col>
+      <xdr:col>19</xdr:col>
       <xdr:colOff>6350</xdr:colOff>
       <xdr:row>6</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
@@ -4324,16 +5313,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>15</xdr:col>
+      <xdr:col>16</xdr:col>
       <xdr:colOff>342900</xdr:colOff>
       <xdr:row>6</xdr:row>
       <xdr:rowOff>107950</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>6350</xdr:colOff>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>9</xdr:row>
-      <xdr:rowOff>120650</xdr:rowOff>
+      <xdr:rowOff>717</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -4344,12 +5333,14 @@
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
+        <xdr:cNvCxnSpPr>
+          <a:endCxn id="30" idx="1"/>
+        </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5581650" y="1498600"/>
-          <a:ext cx="711200" cy="717550"/>
+          <a:off x="5906710" y="2012950"/>
+          <a:ext cx="700314" cy="845267"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -4378,15 +5369,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>9</xdr:col>
+      <xdr:colOff>336998</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>717</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>9</xdr:row>
-      <xdr:rowOff>107950</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>6350</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>107950</xdr:rowOff>
+      <xdr:rowOff>8276</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -4397,12 +5388,15 @@
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="16" idx="3"/>
+          <a:endCxn id="24" idx="1"/>
+        </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3143250" y="2203450"/>
-          <a:ext cx="704850" cy="0"/>
+          <a:off x="3466641" y="2858217"/>
+          <a:ext cx="706216" cy="7559"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -4428,34 +5422,1196 @@
     </xdr:cxnSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>347748</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>1980</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1727951" cy="636434"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="テキスト ボックス 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{063B8696-07E5-5615-8F45-FC137630E5ED}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1392425" y="1589480"/>
+          <a:ext cx="1727951" cy="636434"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
+        <a:ln w="19050">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="ja-JP" sz="1200" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>1.2 task</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="ja-JP" sz="1200">
+              <a:effectLst/>
+            </a:rPr>
+            <a:t> </a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>6350</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>316066</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1727951" cy="636434"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="テキスト ボックス 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A2F8BD9D-245F-7A2F-660A-11D1BC498F8D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1399253" y="633566"/>
+          <a:ext cx="1727951" cy="636434"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
+        <a:ln w="19050">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="ja-JP" sz="1200" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>1.1 task:</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="ja-JP" sz="1200" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="ja-JP" sz="1200" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>所要時間（2時間）</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="ja-JP" sz="1200">
+              <a:effectLst/>
+            </a:rPr>
+            <a:t> </a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1727951" cy="636434"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="15" name="テキスト ボックス 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1B192088-01BD-4461-A82A-C0A9B94AD76E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3825119" y="635000"/>
+          <a:ext cx="1727951" cy="636434"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
+        <a:ln w="19050">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="ja-JP" sz="1200" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>2.1 task:所要時間</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="ja-JP" sz="1200">
+              <a:effectLst/>
+            </a:rPr>
+            <a:t> </a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1727951" cy="636434"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="16" name="テキスト ボックス 15">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{85161EE2-3E68-4A41-922F-3F9D412186E6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1390952" y="2540000"/>
+          <a:ext cx="1727951" cy="636434"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
+        <a:ln w="19050">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="ja-JP" sz="1200" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>1.</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1200" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>3</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="ja-JP" sz="1200" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> task</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="ja-JP" sz="1200">
+              <a:effectLst/>
+            </a:rPr>
+            <a:t> </a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1727951" cy="636434"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="22" name="テキスト ボックス 21">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CAE64A9B-5660-4576-ADD0-6AFFF4ABE739}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3825119" y="3492500"/>
+          <a:ext cx="1727951" cy="636434"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
+        <a:ln w="19050">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1200" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>2.4</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="ja-JP" sz="1200" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> task</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="ja-JP" sz="1200">
+              <a:effectLst/>
+            </a:rPr>
+            <a:t> </a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>7559</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1727951" cy="636434"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="24" name="テキスト ボックス 23">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8DD60B69-D3CA-4F96-8E25-109481A383B4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4172857" y="2547559"/>
+          <a:ext cx="1727951" cy="636434"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
+        <a:ln w="19050">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1200" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>2.3</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="ja-JP" sz="1200" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> task</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="ja-JP" sz="1200">
+              <a:effectLst/>
+            </a:rPr>
+            <a:t> </a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1727951" cy="636434"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="25" name="テキスト ボックス 24">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1363B8E0-9CD1-43EE-AB21-00A5B343926A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3825119" y="1587500"/>
+          <a:ext cx="1727951" cy="636434"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
+        <a:ln w="19050">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1200" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>2.2</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="ja-JP" sz="1200" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> task</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="ja-JP" sz="1200">
+              <a:effectLst/>
+            </a:rPr>
+            <a:t> </a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1727951" cy="636434"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="26" name="テキスト ボックス 25">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A1DE7A08-36BA-45F3-AF01-63515CD9E81E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6259286" y="635000"/>
+          <a:ext cx="1727951" cy="636434"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
+        <a:ln w="19050">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1200" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>X</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="ja-JP" sz="1200" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>.</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1200" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>X</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="ja-JP" sz="1200" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="ja-JP" sz="1200">
+              <a:effectLst/>
+            </a:rPr>
+            <a:t> </a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1727951" cy="636434"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="29" name="テキスト ボックス 28">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EDCCF80D-F08D-4DA6-A4BA-F1DBF491A20C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6259286" y="1587500"/>
+          <a:ext cx="1727951" cy="636434"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
+        <a:ln w="19050">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1200" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>X</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="ja-JP" sz="1200" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>.</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1200" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>X</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="ja-JP" sz="1200" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="ja-JP" sz="1200">
+              <a:effectLst/>
+            </a:rPr>
+            <a:t> </a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1727951" cy="636434"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="30" name="テキスト ボックス 29">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CA2B68B0-8825-4C44-9B52-F6B3AE75E076}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6259286" y="2540000"/>
+          <a:ext cx="1727951" cy="636434"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
+        <a:ln w="19050">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1200" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>X</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="ja-JP" sz="1200" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>.</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ja-JP" sz="1200" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>X</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="ja-JP" sz="1200" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="ja-JP" sz="1200">
+              <a:effectLst/>
+            </a:rPr>
+            <a:t> </a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>30238</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1043214" cy="619881"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="31" name="テキスト ボックス 30">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{705BFD31-ADF0-49B5-B3CE-60FB89806087}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="1935238"/>
+          <a:ext cx="1043214" cy="619881"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
+        <a:ln w="19050">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1600" b="1" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>スタート</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="ja-JP" sz="1200" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="ja-JP" sz="1200">
+              <a:effectLst/>
+            </a:rPr>
+            <a:t> </a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>325059</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1043214" cy="619881"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="51" name="テキスト ボックス 50">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A5B770E9-625C-4340-995F-76DA92716984}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7975297" y="3492500"/>
+          <a:ext cx="1043214" cy="619881"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
+        <a:ln w="19050">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="0" lang="ja-JP" altLang="en-US" sz="1600" b="1" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>終了</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1600" b="1"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>16</xdr:col>
-      <xdr:colOff>6350</xdr:colOff>
+      <xdr:colOff>336998</xdr:colOff>
       <xdr:row>9</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
+      <xdr:rowOff>717</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>24</xdr:col>
+      <xdr:col>19</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>120650</xdr:rowOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>8276</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="23" name="直線矢印コネクタ 22">
+        <xdr:cNvPr id="53" name="直線矢印コネクタ 52">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{01B8C172-C326-4CEB-932D-9264248D157F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0BB04E84-B4A4-442A-9D1E-922671AA6571}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="24" idx="3"/>
+          <a:endCxn id="30" idx="1"/>
+        </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipV="1">
-          <a:off x="5594350" y="2209800"/>
-          <a:ext cx="2787650" cy="704850"/>
+          <a:off x="5900808" y="2858217"/>
+          <a:ext cx="706216" cy="7559"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -4945,305 +7101,305 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0959A804-C26C-4B86-9033-45087ECCAC0D}">
-  <dimension ref="C1:AF25"/>
+  <dimension ref="A1:AD25"/>
   <sheetFormatPr defaultColWidth="4.58203125" defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="34" width="3.58203125" customWidth="1"/>
+    <col min="1" max="32" width="3.58203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:32" ht="18.5" thickBot="1" x14ac:dyDescent="0.6"/>
-    <row r="2" spans="3:32" x14ac:dyDescent="0.55000000000000004">
-      <c r="C2" s="1" t="s">
+    <row r="1" spans="1:30" ht="18.5" thickBot="1" x14ac:dyDescent="0.6"/>
+    <row r="2" spans="1:30" ht="22.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" s="31" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="1" t="s">
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="31" t="s">
         <v>1</v>
       </c>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
       <c r="L2" s="2"/>
-      <c r="M2" s="2"/>
-      <c r="N2" s="3"/>
-      <c r="O2" s="2" t="s">
+      <c r="M2" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="P2" s="2"/>
-      <c r="Q2" s="2"/>
-      <c r="R2" s="2"/>
-      <c r="S2" s="2"/>
-      <c r="T2" s="2"/>
-      <c r="U2" s="1" t="s">
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+      <c r="Q2" s="1"/>
+      <c r="R2" s="1"/>
+      <c r="S2" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="V2" s="2"/>
-      <c r="W2" s="2"/>
+      <c r="T2" s="1"/>
+      <c r="U2" s="1"/>
+      <c r="V2" s="1"/>
+      <c r="W2" s="1"/>
       <c r="X2" s="2"/>
-      <c r="Y2" s="2"/>
-      <c r="Z2" s="3"/>
-      <c r="AA2" s="2" t="s">
+      <c r="Y2" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="AB2" s="2"/>
-      <c r="AC2" s="2"/>
+      <c r="Z2" s="1"/>
+      <c r="AA2" s="1"/>
+      <c r="AB2" s="1"/>
+      <c r="AC2" s="1"/>
       <c r="AD2" s="2"/>
-      <c r="AE2" s="2"/>
-      <c r="AF2" s="3"/>
-    </row>
-    <row r="3" spans="3:32" x14ac:dyDescent="0.55000000000000004">
-      <c r="C3" s="4"/>
-      <c r="I3" s="4"/>
-      <c r="N3" s="5"/>
-      <c r="U3" s="4"/>
-      <c r="Z3" s="5"/>
-      <c r="AF3" s="5"/>
-    </row>
-    <row r="4" spans="3:32" x14ac:dyDescent="0.55000000000000004">
-      <c r="C4" s="4"/>
-      <c r="I4" s="4"/>
-      <c r="N4" s="5"/>
-      <c r="U4" s="4"/>
-      <c r="Z4" s="5"/>
-      <c r="AF4" s="5"/>
-    </row>
-    <row r="5" spans="3:32" x14ac:dyDescent="0.55000000000000004">
-      <c r="C5" s="4"/>
-      <c r="I5" s="4"/>
-      <c r="N5" s="5"/>
-      <c r="U5" s="4"/>
-      <c r="Z5" s="5"/>
-      <c r="AF5" s="5"/>
-    </row>
-    <row r="6" spans="3:32" x14ac:dyDescent="0.55000000000000004">
-      <c r="C6" s="4"/>
-      <c r="I6" s="4"/>
-      <c r="N6" s="5"/>
-      <c r="U6" s="4"/>
-      <c r="Z6" s="5"/>
-      <c r="AF6" s="5"/>
-    </row>
-    <row r="7" spans="3:32" x14ac:dyDescent="0.55000000000000004">
-      <c r="C7" s="4"/>
-      <c r="I7" s="4"/>
-      <c r="N7" s="5"/>
-      <c r="U7" s="4"/>
-      <c r="Z7" s="5"/>
-      <c r="AF7" s="5"/>
-    </row>
-    <row r="8" spans="3:32" x14ac:dyDescent="0.55000000000000004">
-      <c r="C8" s="4"/>
-      <c r="I8" s="4"/>
-      <c r="N8" s="5"/>
-      <c r="U8" s="4"/>
-      <c r="Z8" s="5"/>
-      <c r="AF8" s="5"/>
-    </row>
-    <row r="9" spans="3:32" x14ac:dyDescent="0.55000000000000004">
-      <c r="C9" s="4"/>
-      <c r="I9" s="4"/>
-      <c r="N9" s="5"/>
-      <c r="U9" s="4"/>
-      <c r="Z9" s="5"/>
-      <c r="AF9" s="5"/>
-    </row>
-    <row r="10" spans="3:32" ht="18.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="C10" s="4"/>
-      <c r="I10" s="4"/>
-      <c r="N10" s="5"/>
-      <c r="U10" s="4"/>
-      <c r="Z10" s="5"/>
-      <c r="AF10" s="5"/>
-    </row>
-    <row r="11" spans="3:32" x14ac:dyDescent="0.55000000000000004">
-      <c r="C11" s="4"/>
-      <c r="I11" s="1" t="s">
+    </row>
+    <row r="3" spans="1:30" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="L3" s="4"/>
+      <c r="S3" s="3"/>
+      <c r="X3" s="4"/>
+      <c r="AD3" s="4"/>
+    </row>
+    <row r="4" spans="1:30" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="L4" s="4"/>
+      <c r="S4" s="3"/>
+      <c r="X4" s="4"/>
+      <c r="AD4" s="4"/>
+    </row>
+    <row r="5" spans="1:30" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" s="3"/>
+      <c r="G5" s="3"/>
+      <c r="L5" s="4"/>
+      <c r="S5" s="3"/>
+      <c r="X5" s="4"/>
+      <c r="AD5" s="4"/>
+    </row>
+    <row r="6" spans="1:30" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" s="3"/>
+      <c r="G6" s="3"/>
+      <c r="L6" s="4"/>
+      <c r="S6" s="3"/>
+      <c r="X6" s="4"/>
+      <c r="AD6" s="4"/>
+    </row>
+    <row r="7" spans="1:30" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="L7" s="4"/>
+      <c r="S7" s="3"/>
+      <c r="X7" s="4"/>
+      <c r="AD7" s="4"/>
+    </row>
+    <row r="8" spans="1:30" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" s="3"/>
+      <c r="G8" s="3"/>
+      <c r="L8" s="4"/>
+      <c r="S8" s="3"/>
+      <c r="X8" s="4"/>
+      <c r="AD8" s="4"/>
+    </row>
+    <row r="9" spans="1:30" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" s="3"/>
+      <c r="G9" s="3"/>
+      <c r="L9" s="4"/>
+      <c r="S9" s="3"/>
+      <c r="X9" s="4"/>
+      <c r="AD9" s="4"/>
+    </row>
+    <row r="10" spans="1:30" ht="18.5" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A10" s="3"/>
+      <c r="G10" s="3"/>
+      <c r="L10" s="4"/>
+      <c r="S10" s="3"/>
+      <c r="X10" s="4"/>
+      <c r="AD10" s="4"/>
+    </row>
+    <row r="11" spans="1:30" ht="22.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" s="3"/>
+      <c r="G11" s="33" t="s">
         <v>3</v>
       </c>
-      <c r="J11" s="2"/>
-      <c r="K11" s="2"/>
+      <c r="H11" s="1"/>
+      <c r="I11" s="1"/>
+      <c r="J11" s="1"/>
+      <c r="K11" s="1"/>
       <c r="L11" s="2"/>
-      <c r="M11" s="2"/>
-      <c r="N11" s="3"/>
-      <c r="U11" s="1" t="s">
+      <c r="S11" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="V11" s="2"/>
-      <c r="W11" s="2"/>
+      <c r="T11" s="1"/>
+      <c r="U11" s="1"/>
+      <c r="V11" s="1"/>
+      <c r="W11" s="1"/>
       <c r="X11" s="2"/>
-      <c r="Y11" s="2"/>
-      <c r="Z11" s="3"/>
-      <c r="AF11" s="5"/>
-    </row>
-    <row r="12" spans="3:32" x14ac:dyDescent="0.55000000000000004">
-      <c r="C12" s="4"/>
-      <c r="I12" s="4"/>
-      <c r="N12" s="5"/>
-      <c r="U12" s="4"/>
-      <c r="Z12" s="5"/>
-      <c r="AF12" s="5"/>
-    </row>
-    <row r="13" spans="3:32" x14ac:dyDescent="0.55000000000000004">
-      <c r="C13" s="4"/>
-      <c r="I13" s="4"/>
-      <c r="N13" s="5"/>
-      <c r="U13" s="4"/>
-      <c r="Z13" s="5"/>
-      <c r="AF13" s="5"/>
-    </row>
-    <row r="14" spans="3:32" x14ac:dyDescent="0.55000000000000004">
-      <c r="C14" s="4"/>
-      <c r="I14" s="4"/>
-      <c r="N14" s="5"/>
-      <c r="U14" s="4"/>
-      <c r="Z14" s="5"/>
-      <c r="AF14" s="5"/>
-    </row>
-    <row r="15" spans="3:32" x14ac:dyDescent="0.55000000000000004">
-      <c r="C15" s="4"/>
-      <c r="I15" s="4"/>
-      <c r="N15" s="5"/>
-      <c r="U15" s="4"/>
-      <c r="Z15" s="5"/>
-      <c r="AF15" s="5"/>
-    </row>
-    <row r="16" spans="3:32" x14ac:dyDescent="0.55000000000000004">
-      <c r="C16" s="4"/>
-      <c r="I16" s="4"/>
-      <c r="N16" s="5"/>
-      <c r="U16" s="4"/>
-      <c r="Z16" s="5"/>
-      <c r="AF16" s="5"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.55000000000000004">
-      <c r="C17" s="4"/>
-      <c r="I17" s="4"/>
-      <c r="N17" s="5"/>
-      <c r="U17" s="4"/>
-      <c r="Z17" s="5"/>
-      <c r="AF17" s="5"/>
-    </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.55000000000000004">
-      <c r="C18" s="4"/>
-      <c r="I18" s="4"/>
-      <c r="N18" s="5"/>
-      <c r="U18" s="4"/>
-      <c r="Z18" s="5"/>
-      <c r="AF18" s="5"/>
-    </row>
-    <row r="19" spans="3:32" ht="18.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="C19" s="4"/>
+      <c r="AD11" s="4"/>
+    </row>
+    <row r="12" spans="1:30" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" s="3"/>
+      <c r="G12" s="3"/>
+      <c r="L12" s="4"/>
+      <c r="S12" s="3"/>
+      <c r="X12" s="4"/>
+      <c r="AD12" s="4"/>
+    </row>
+    <row r="13" spans="1:30" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" s="3"/>
+      <c r="G13" s="3"/>
+      <c r="L13" s="4"/>
+      <c r="S13" s="3"/>
+      <c r="X13" s="4"/>
+      <c r="AD13" s="4"/>
+    </row>
+    <row r="14" spans="1:30" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" s="3"/>
+      <c r="G14" s="3"/>
+      <c r="L14" s="4"/>
+      <c r="S14" s="3"/>
+      <c r="X14" s="4"/>
+      <c r="AD14" s="4"/>
+    </row>
+    <row r="15" spans="1:30" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" s="3"/>
+      <c r="G15" s="3"/>
+      <c r="L15" s="4"/>
+      <c r="S15" s="3"/>
+      <c r="X15" s="4"/>
+      <c r="AD15" s="4"/>
+    </row>
+    <row r="16" spans="1:30" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" s="3"/>
+      <c r="G16" s="3"/>
+      <c r="L16" s="4"/>
+      <c r="S16" s="3"/>
+      <c r="X16" s="4"/>
+      <c r="AD16" s="4"/>
+    </row>
+    <row r="17" spans="1:30" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" s="3"/>
+      <c r="G17" s="3"/>
+      <c r="L17" s="4"/>
+      <c r="S17" s="3"/>
+      <c r="X17" s="4"/>
+      <c r="AD17" s="4"/>
+    </row>
+    <row r="18" spans="1:30" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18" s="3"/>
+      <c r="G18" s="3"/>
+      <c r="L18" s="4"/>
+      <c r="S18" s="3"/>
+      <c r="X18" s="4"/>
+      <c r="AD18" s="4"/>
+    </row>
+    <row r="19" spans="1:30" ht="18.5" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A19" s="3"/>
+      <c r="G19" s="5"/>
+      <c r="H19" s="6"/>
       <c r="I19" s="6"/>
-      <c r="J19" s="7"/>
-      <c r="K19" s="7"/>
+      <c r="J19" s="6"/>
+      <c r="K19" s="6"/>
       <c r="L19" s="7"/>
-      <c r="M19" s="7"/>
-      <c r="N19" s="8"/>
+      <c r="S19" s="5"/>
+      <c r="T19" s="6"/>
       <c r="U19" s="6"/>
-      <c r="V19" s="7"/>
-      <c r="W19" s="7"/>
+      <c r="V19" s="6"/>
+      <c r="W19" s="6"/>
       <c r="X19" s="7"/>
-      <c r="Y19" s="7"/>
-      <c r="Z19" s="8"/>
-      <c r="AF19" s="5"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.55000000000000004">
-      <c r="C20" s="1" t="s">
+      <c r="AD19" s="4"/>
+    </row>
+    <row r="20" spans="1:30" ht="22.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A20" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="D20" s="2"/>
-      <c r="E20" s="2"/>
-      <c r="F20" s="2"/>
-      <c r="G20" s="2"/>
-      <c r="H20" s="2"/>
-      <c r="I20" s="2"/>
-      <c r="J20" s="2"/>
-      <c r="K20" s="2"/>
-      <c r="L20" s="2"/>
-      <c r="M20" s="2"/>
-      <c r="N20" s="2"/>
+      <c r="B20" s="1"/>
+      <c r="C20" s="1"/>
+      <c r="D20" s="1"/>
+      <c r="E20" s="1"/>
+      <c r="F20" s="1"/>
+      <c r="G20" s="1"/>
+      <c r="H20" s="1"/>
+      <c r="I20" s="1"/>
+      <c r="J20" s="1"/>
+      <c r="K20" s="1"/>
+      <c r="L20" s="1"/>
+      <c r="M20" s="1"/>
+      <c r="N20" s="1"/>
       <c r="O20" s="2"/>
-      <c r="P20" s="2"/>
-      <c r="Q20" s="3"/>
-      <c r="R20" s="1" t="s">
+      <c r="P20" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="S20" s="2"/>
-      <c r="T20" s="2"/>
-      <c r="U20" s="2"/>
-      <c r="V20" s="2"/>
-      <c r="W20" s="2"/>
-      <c r="X20" s="2"/>
-      <c r="Y20" s="2"/>
-      <c r="Z20" s="2"/>
-      <c r="AA20" s="2"/>
-      <c r="AB20" s="2"/>
-      <c r="AC20" s="2"/>
+      <c r="Q20" s="1"/>
+      <c r="R20" s="1"/>
+      <c r="S20" s="1"/>
+      <c r="T20" s="1"/>
+      <c r="U20" s="1"/>
+      <c r="V20" s="1"/>
+      <c r="W20" s="1"/>
+      <c r="X20" s="1"/>
+      <c r="Y20" s="1"/>
+      <c r="Z20" s="1"/>
+      <c r="AA20" s="1"/>
+      <c r="AB20" s="1"/>
+      <c r="AC20" s="1"/>
       <c r="AD20" s="2"/>
-      <c r="AE20" s="2"/>
-      <c r="AF20" s="3"/>
-    </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.55000000000000004">
-      <c r="C21" s="4"/>
-      <c r="Q21" s="5"/>
-      <c r="R21" s="4"/>
-      <c r="AF21" s="5"/>
-    </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.55000000000000004">
-      <c r="C22" s="4"/>
-      <c r="Q22" s="5"/>
-      <c r="R22" s="4"/>
-      <c r="AF22" s="5"/>
-    </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.55000000000000004">
-      <c r="C23" s="4"/>
-      <c r="Q23" s="5"/>
-      <c r="R23" s="4"/>
-      <c r="AF23" s="5"/>
-    </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.55000000000000004">
-      <c r="C24" s="4"/>
-      <c r="Q24" s="5"/>
-      <c r="R24" s="4"/>
-      <c r="AF24" s="5"/>
-    </row>
-    <row r="25" spans="3:32" ht="18.5" thickBot="1" x14ac:dyDescent="0.6">
+    </row>
+    <row r="21" spans="1:30" x14ac:dyDescent="0.55000000000000004">
+      <c r="A21" s="3"/>
+      <c r="O21" s="4"/>
+      <c r="P21" s="3"/>
+      <c r="AD21" s="4"/>
+    </row>
+    <row r="22" spans="1:30" x14ac:dyDescent="0.55000000000000004">
+      <c r="A22" s="3"/>
+      <c r="O22" s="4"/>
+      <c r="P22" s="3"/>
+      <c r="AD22" s="4"/>
+    </row>
+    <row r="23" spans="1:30" x14ac:dyDescent="0.55000000000000004">
+      <c r="A23" s="3"/>
+      <c r="O23" s="4"/>
+      <c r="P23" s="3"/>
+      <c r="AD23" s="4"/>
+    </row>
+    <row r="24" spans="1:30" x14ac:dyDescent="0.55000000000000004">
+      <c r="A24" s="3"/>
+      <c r="O24" s="4"/>
+      <c r="P24" s="3"/>
+      <c r="AD24" s="4"/>
+    </row>
+    <row r="25" spans="1:30" ht="18.5" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A25" s="5"/>
+      <c r="B25" s="6"/>
       <c r="C25" s="6"/>
-      <c r="D25" s="7"/>
-      <c r="E25" s="7"/>
-      <c r="F25" s="7"/>
-      <c r="G25" s="7"/>
-      <c r="H25" s="7"/>
-      <c r="I25" s="7"/>
-      <c r="J25" s="7"/>
-      <c r="K25" s="7"/>
-      <c r="L25" s="7"/>
-      <c r="M25" s="7"/>
-      <c r="N25" s="7"/>
+      <c r="D25" s="6"/>
+      <c r="E25" s="6"/>
+      <c r="F25" s="6"/>
+      <c r="G25" s="6"/>
+      <c r="H25" s="6"/>
+      <c r="I25" s="6"/>
+      <c r="J25" s="6"/>
+      <c r="K25" s="6"/>
+      <c r="L25" s="6"/>
+      <c r="M25" s="6"/>
+      <c r="N25" s="6"/>
       <c r="O25" s="7"/>
-      <c r="P25" s="7"/>
-      <c r="Q25" s="8"/>
+      <c r="P25" s="5"/>
+      <c r="Q25" s="6"/>
       <c r="R25" s="6"/>
-      <c r="S25" s="7"/>
-      <c r="T25" s="7"/>
-      <c r="U25" s="7"/>
-      <c r="V25" s="7"/>
-      <c r="W25" s="7"/>
-      <c r="X25" s="7"/>
-      <c r="Y25" s="7"/>
-      <c r="Z25" s="7"/>
-      <c r="AA25" s="7"/>
-      <c r="AB25" s="7"/>
-      <c r="AC25" s="7"/>
+      <c r="S25" s="6"/>
+      <c r="T25" s="6"/>
+      <c r="U25" s="6"/>
+      <c r="V25" s="6"/>
+      <c r="W25" s="6"/>
+      <c r="X25" s="6"/>
+      <c r="Y25" s="6"/>
+      <c r="Z25" s="6"/>
+      <c r="AA25" s="6"/>
+      <c r="AB25" s="6"/>
+      <c r="AC25" s="6"/>
       <c r="AD25" s="7"/>
-      <c r="AE25" s="7"/>
-      <c r="AF25" s="8"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="2"/>
+  <phoneticPr fontId="1"/>
   <pageMargins left="0.51181102362204722" right="0.51181102362204722" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
   <headerFooter>
@@ -5255,374 +7411,492 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A1D089F-0221-4E40-8DDE-87C4BED11CF2}">
-  <dimension ref="A1:Q41"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
-  <cols>
-    <col min="1" max="44" width="4.58203125" customWidth="1"/>
-  </cols>
+  <dimension ref="A1:P42"/>
+  <sheetFormatPr defaultColWidth="3.58203125" defaultRowHeight="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
   <sheetData>
-    <row r="1" spans="1:17" ht="18.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1" t="s">
+    <row r="1" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" s="34" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="18.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B2" s="9"/>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10"/>
-      <c r="H2" s="10"/>
-      <c r="I2" s="10"/>
-      <c r="J2" s="10"/>
-      <c r="K2" s="11"/>
-    </row>
-    <row r="3" spans="1:17" ht="18.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A3" t="s">
+    <row r="2" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" s="38"/>
+      <c r="B2" s="38"/>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="38"/>
+      <c r="F2" s="38"/>
+      <c r="G2" s="38"/>
+      <c r="H2" s="38"/>
+      <c r="I2" s="38"/>
+      <c r="J2" s="38"/>
+    </row>
+    <row r="3" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" s="35" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:17" ht="18.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B4" s="9"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="10"/>
-      <c r="H4" s="10"/>
-      <c r="I4" s="10"/>
-      <c r="J4" s="10"/>
-      <c r="K4" s="11"/>
-    </row>
-    <row r="5" spans="1:17" ht="18.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A5" t="s">
+    <row r="4" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" s="38"/>
+      <c r="B4" s="38"/>
+      <c r="C4" s="38"/>
+      <c r="D4" s="38"/>
+      <c r="E4" s="38"/>
+      <c r="F4" s="38"/>
+      <c r="G4" s="38"/>
+      <c r="H4" s="38"/>
+      <c r="I4" s="38"/>
+      <c r="J4" s="38"/>
+    </row>
+    <row r="5" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" s="35" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="18.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B6" s="9"/>
-      <c r="C6" s="10"/>
-      <c r="D6" s="10"/>
-      <c r="E6" s="10"/>
-      <c r="F6" s="10"/>
-      <c r="G6" s="10"/>
-      <c r="H6" s="10"/>
-      <c r="I6" s="10"/>
-      <c r="J6" s="10"/>
-      <c r="K6" s="11"/>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" t="s">
+    <row r="6" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" s="39"/>
+      <c r="B6" s="38"/>
+      <c r="C6" s="38"/>
+      <c r="D6" s="38"/>
+      <c r="E6" s="38"/>
+      <c r="F6" s="38"/>
+      <c r="G6" s="38"/>
+      <c r="H6" s="38"/>
+      <c r="I6" s="38"/>
+      <c r="J6" s="38"/>
+    </row>
+    <row r="7" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" s="35" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="11.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B8" s="13" t="s">
+    <row r="8" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="E8" s="10"/>
+    </row>
+    <row r="9" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" s="38"/>
+      <c r="B9" s="38"/>
+      <c r="C9" s="38"/>
+      <c r="D9" s="38"/>
+      <c r="E9" s="38"/>
+      <c r="F9" s="38"/>
+      <c r="G9" s="38"/>
+      <c r="H9" s="38"/>
+      <c r="I9" s="38"/>
+      <c r="J9" s="38"/>
+      <c r="L9" s="37"/>
+      <c r="M9" s="38"/>
+      <c r="N9" s="38"/>
+      <c r="O9" s="38"/>
+      <c r="P9" s="38"/>
+    </row>
+    <row r="10" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" s="38"/>
+      <c r="B10" s="38"/>
+      <c r="C10" s="38"/>
+      <c r="D10" s="38"/>
+      <c r="E10" s="38"/>
+      <c r="F10" s="38"/>
+      <c r="G10" s="38"/>
+      <c r="H10" s="38"/>
+      <c r="I10" s="38"/>
+      <c r="J10" s="38"/>
+      <c r="L10" s="38"/>
+      <c r="M10" s="38"/>
+      <c r="N10" s="38"/>
+      <c r="O10" s="38"/>
+      <c r="P10" s="38"/>
+    </row>
+    <row r="11" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" s="38"/>
+      <c r="B11" s="38"/>
+      <c r="C11" s="38"/>
+      <c r="D11" s="38"/>
+      <c r="E11" s="38"/>
+      <c r="F11" s="38"/>
+      <c r="G11" s="38"/>
+      <c r="H11" s="38"/>
+      <c r="I11" s="38"/>
+      <c r="J11" s="38"/>
+      <c r="L11" s="38"/>
+      <c r="M11" s="38"/>
+      <c r="N11" s="38"/>
+      <c r="O11" s="38"/>
+      <c r="P11" s="38"/>
+    </row>
+    <row r="12" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" s="38"/>
+      <c r="B12" s="38"/>
+      <c r="C12" s="38"/>
+      <c r="D12" s="38"/>
+      <c r="E12" s="38"/>
+      <c r="F12" s="38"/>
+      <c r="G12" s="38"/>
+      <c r="H12" s="38"/>
+      <c r="I12" s="38"/>
+      <c r="J12" s="38"/>
+      <c r="L12" s="38"/>
+      <c r="M12" s="38"/>
+      <c r="N12" s="38"/>
+      <c r="O12" s="38"/>
+      <c r="P12" s="38"/>
+    </row>
+    <row r="13" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" s="35" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" s="36" t="s">
+        <v>22</v>
+      </c>
+      <c r="E14" s="10"/>
+    </row>
+    <row r="15" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" s="38"/>
+      <c r="B15" s="38"/>
+      <c r="C15" s="38"/>
+      <c r="D15" s="38"/>
+      <c r="E15" s="38"/>
+      <c r="F15" s="38"/>
+      <c r="G15" s="38"/>
+      <c r="H15" s="38"/>
+      <c r="I15" s="38"/>
+      <c r="J15" s="38"/>
+    </row>
+    <row r="16" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" s="38"/>
+      <c r="B16" s="38"/>
+      <c r="C16" s="38"/>
+      <c r="D16" s="38"/>
+      <c r="E16" s="38"/>
+      <c r="F16" s="38"/>
+      <c r="G16" s="38"/>
+      <c r="H16" s="38"/>
+      <c r="I16" s="38"/>
+      <c r="J16" s="38"/>
+    </row>
+    <row r="17" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" s="38"/>
+      <c r="B17" s="38"/>
+      <c r="C17" s="38"/>
+      <c r="D17" s="38"/>
+      <c r="E17" s="38"/>
+      <c r="F17" s="38"/>
+      <c r="G17" s="38"/>
+      <c r="H17" s="38"/>
+      <c r="I17" s="38"/>
+      <c r="J17" s="38"/>
+    </row>
+    <row r="18" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18" s="40" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A19" s="36" t="s">
         <v>21</v>
       </c>
-      <c r="F8" s="13"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="B9" s="1"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
-      <c r="I9" s="2"/>
-      <c r="J9" s="2"/>
-      <c r="K9" s="3"/>
-      <c r="M9" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="N9" s="2"/>
-      <c r="O9" s="2"/>
-      <c r="P9" s="2"/>
-      <c r="Q9" s="3"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="B10" s="4"/>
-      <c r="K10" s="5"/>
-      <c r="M10" s="4"/>
-      <c r="Q10" s="5"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="B11" s="4"/>
-      <c r="K11" s="5"/>
-      <c r="M11" s="4"/>
-      <c r="Q11" s="5"/>
-    </row>
-    <row r="12" spans="1:17" ht="18.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B12" s="6"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="7"/>
-      <c r="G12" s="7"/>
-      <c r="H12" s="7"/>
-      <c r="I12" s="7"/>
-      <c r="J12" s="7"/>
-      <c r="K12" s="8"/>
-      <c r="M12" s="6"/>
-      <c r="N12" s="7"/>
-      <c r="O12" s="7"/>
-      <c r="P12" s="7"/>
-      <c r="Q12" s="8"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="14" spans="1:17" ht="11.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B14" s="13" t="s">
+    </row>
+    <row r="20" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A20" s="38"/>
+      <c r="B20" s="38"/>
+      <c r="C20" s="38"/>
+      <c r="D20" s="38"/>
+      <c r="E20" s="38"/>
+      <c r="F20" s="38"/>
+      <c r="G20" s="38"/>
+      <c r="H20" s="38"/>
+      <c r="I20" s="38"/>
+      <c r="J20" s="38"/>
+      <c r="L20" s="41"/>
+      <c r="M20" s="38"/>
+      <c r="N20" s="38"/>
+      <c r="O20" s="38"/>
+      <c r="P20" s="38"/>
+    </row>
+    <row r="21" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A21" s="38"/>
+      <c r="B21" s="38"/>
+      <c r="C21" s="38"/>
+      <c r="D21" s="38"/>
+      <c r="E21" s="38"/>
+      <c r="F21" s="38"/>
+      <c r="G21" s="38"/>
+      <c r="H21" s="38"/>
+      <c r="I21" s="38"/>
+      <c r="J21" s="38"/>
+      <c r="L21" s="38"/>
+      <c r="M21" s="38"/>
+      <c r="N21" s="38"/>
+      <c r="O21" s="38"/>
+      <c r="P21" s="38"/>
+    </row>
+    <row r="22" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A22" s="38"/>
+      <c r="B22" s="38"/>
+      <c r="C22" s="38"/>
+      <c r="D22" s="38"/>
+      <c r="E22" s="38"/>
+      <c r="F22" s="38"/>
+      <c r="G22" s="38"/>
+      <c r="H22" s="38"/>
+      <c r="I22" s="38"/>
+      <c r="J22" s="38"/>
+      <c r="L22" s="38"/>
+      <c r="M22" s="38"/>
+      <c r="N22" s="38"/>
+      <c r="O22" s="38"/>
+      <c r="P22" s="38"/>
+    </row>
+    <row r="23" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A23" s="38"/>
+      <c r="B23" s="38"/>
+      <c r="C23" s="38"/>
+      <c r="D23" s="38"/>
+      <c r="E23" s="38"/>
+      <c r="F23" s="38"/>
+      <c r="G23" s="38"/>
+      <c r="H23" s="38"/>
+      <c r="I23" s="38"/>
+      <c r="J23" s="38"/>
+      <c r="L23" s="38"/>
+      <c r="M23" s="38"/>
+      <c r="N23" s="38"/>
+      <c r="O23" s="38"/>
+      <c r="P23" s="38"/>
+    </row>
+    <row r="24" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A24" s="38"/>
+      <c r="B24" s="38"/>
+      <c r="C24" s="38"/>
+      <c r="D24" s="38"/>
+      <c r="E24" s="38"/>
+      <c r="F24" s="38"/>
+      <c r="G24" s="38"/>
+      <c r="H24" s="38"/>
+      <c r="I24" s="38"/>
+      <c r="J24" s="38"/>
+      <c r="L24" s="38"/>
+      <c r="M24" s="38"/>
+      <c r="N24" s="38"/>
+      <c r="O24" s="38"/>
+      <c r="P24" s="38"/>
+    </row>
+    <row r="25" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A25" s="34" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A26" s="36" t="s">
         <v>23</v>
       </c>
-      <c r="F14" s="13"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="B15" s="1"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
-      <c r="H15" s="2"/>
-      <c r="I15" s="2"/>
-      <c r="J15" s="2"/>
-      <c r="K15" s="3"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="B16" s="4"/>
-      <c r="K16" s="5"/>
-    </row>
-    <row r="17" spans="1:17" ht="18.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B17" s="6"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="7"/>
-      <c r="G17" s="7"/>
-      <c r="H17" s="7"/>
-      <c r="I17" s="7"/>
-      <c r="J17" s="7"/>
-      <c r="K17" s="8"/>
-    </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18" s="14" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="19" spans="1:17" ht="11.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A19" s="14"/>
-      <c r="B19" s="13" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="B20" s="1"/>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2"/>
-      <c r="E20" s="2"/>
-      <c r="F20" s="2"/>
-      <c r="G20" s="2"/>
-      <c r="H20" s="2"/>
-      <c r="I20" s="2"/>
-      <c r="J20" s="2"/>
-      <c r="K20" s="3"/>
-      <c r="M20" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="N20" s="2"/>
-      <c r="O20" s="2"/>
-      <c r="P20" s="2"/>
-      <c r="Q20" s="3"/>
-    </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="B21" s="4"/>
-      <c r="K21" s="5"/>
-      <c r="M21" s="4"/>
-      <c r="Q21" s="5"/>
-    </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="B22" s="4"/>
-      <c r="K22" s="5"/>
-      <c r="M22" s="4"/>
-      <c r="Q22" s="5"/>
-    </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="B23" s="4"/>
-      <c r="K23" s="5"/>
-      <c r="M23" s="4"/>
-      <c r="Q23" s="5"/>
-    </row>
-    <row r="24" spans="1:17" ht="18.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B24" s="6"/>
-      <c r="C24" s="7"/>
-      <c r="D24" s="7"/>
-      <c r="E24" s="7"/>
-      <c r="F24" s="7"/>
-      <c r="G24" s="7"/>
-      <c r="H24" s="7"/>
-      <c r="I24" s="7"/>
-      <c r="J24" s="7"/>
-      <c r="K24" s="8"/>
-      <c r="M24" s="6"/>
-      <c r="N24" s="7"/>
-      <c r="O24" s="7"/>
-      <c r="P24" s="7"/>
-      <c r="Q24" s="8"/>
-    </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A25" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="26" spans="1:17" ht="11.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B26" s="13" t="s">
+    </row>
+    <row r="27" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A27" s="38"/>
+      <c r="B27" s="38"/>
+      <c r="C27" s="38"/>
+      <c r="D27" s="38"/>
+      <c r="E27" s="38"/>
+      <c r="F27" s="38"/>
+      <c r="G27" s="38"/>
+      <c r="H27" s="38"/>
+      <c r="I27" s="38"/>
+      <c r="J27" s="38"/>
+    </row>
+    <row r="28" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A28" s="38"/>
+      <c r="B28" s="38"/>
+      <c r="C28" s="38"/>
+      <c r="D28" s="38"/>
+      <c r="E28" s="38"/>
+      <c r="F28" s="38"/>
+      <c r="G28" s="38"/>
+      <c r="H28" s="38"/>
+      <c r="I28" s="38"/>
+      <c r="J28" s="38"/>
+    </row>
+    <row r="29" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A29" s="38"/>
+      <c r="B29" s="38"/>
+      <c r="C29" s="38"/>
+      <c r="D29" s="38"/>
+      <c r="E29" s="38"/>
+      <c r="F29" s="38"/>
+      <c r="G29" s="38"/>
+      <c r="H29" s="38"/>
+      <c r="I29" s="38"/>
+      <c r="J29" s="38"/>
+    </row>
+    <row r="30" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A30" s="38"/>
+      <c r="B30" s="38"/>
+      <c r="C30" s="38"/>
+      <c r="D30" s="38"/>
+      <c r="E30" s="38"/>
+      <c r="F30" s="38"/>
+      <c r="G30" s="38"/>
+      <c r="H30" s="38"/>
+      <c r="I30" s="38"/>
+      <c r="J30" s="38"/>
+    </row>
+    <row r="31" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A31" s="38"/>
+      <c r="B31" s="38"/>
+      <c r="C31" s="38"/>
+      <c r="D31" s="38"/>
+      <c r="E31" s="38"/>
+      <c r="F31" s="38"/>
+      <c r="G31" s="38"/>
+      <c r="H31" s="38"/>
+      <c r="I31" s="38"/>
+      <c r="J31" s="38"/>
+    </row>
+    <row r="32" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A32" s="34" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A33" s="36" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="B27" s="1"/>
-      <c r="C27" s="2"/>
-      <c r="D27" s="2"/>
-      <c r="E27" s="2"/>
-      <c r="F27" s="2"/>
-      <c r="G27" s="2"/>
-      <c r="H27" s="2"/>
-      <c r="I27" s="2"/>
-      <c r="J27" s="2"/>
-      <c r="K27" s="3"/>
-    </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="B28" s="4"/>
-      <c r="K28" s="5"/>
-    </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="B29" s="4"/>
-      <c r="K29" s="5"/>
-    </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="B30" s="4"/>
-      <c r="K30" s="5"/>
-    </row>
-    <row r="31" spans="1:17" ht="18.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B31" s="6"/>
-      <c r="C31" s="7"/>
-      <c r="D31" s="7"/>
-      <c r="E31" s="7"/>
-      <c r="F31" s="7"/>
-      <c r="G31" s="7"/>
-      <c r="H31" s="7"/>
-      <c r="I31" s="7"/>
-      <c r="J31" s="7"/>
-      <c r="K31" s="8"/>
-    </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A32" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="33" spans="1:17" ht="11.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B33" s="13" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="B34" s="1"/>
-      <c r="C34" s="2"/>
-      <c r="D34" s="2"/>
-      <c r="E34" s="2"/>
-      <c r="F34" s="2"/>
-      <c r="G34" s="2"/>
-      <c r="H34" s="2"/>
-      <c r="I34" s="2"/>
-      <c r="J34" s="2"/>
-      <c r="K34" s="3"/>
-      <c r="M34" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="N34" s="2"/>
-      <c r="O34" s="2"/>
-      <c r="P34" s="2"/>
-      <c r="Q34" s="3"/>
-    </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="B35" s="4"/>
-      <c r="K35" s="5"/>
-      <c r="M35" s="4"/>
-      <c r="Q35" s="5"/>
-    </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="B36" s="4"/>
-      <c r="K36" s="5"/>
-      <c r="M36" s="4"/>
-      <c r="Q36" s="5"/>
-    </row>
-    <row r="37" spans="1:17" ht="18.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B37" s="6"/>
-      <c r="C37" s="7"/>
-      <c r="D37" s="7"/>
-      <c r="E37" s="7"/>
-      <c r="F37" s="7"/>
-      <c r="G37" s="7"/>
-      <c r="H37" s="7"/>
-      <c r="I37" s="7"/>
-      <c r="J37" s="7"/>
-      <c r="K37" s="8"/>
-      <c r="M37" s="6"/>
-      <c r="N37" s="7"/>
-      <c r="O37" s="7"/>
-      <c r="P37" s="7"/>
-      <c r="Q37" s="8"/>
-    </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A38" t="s">
+    <row r="34" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A34" s="38"/>
+      <c r="B34" s="38"/>
+      <c r="C34" s="38"/>
+      <c r="D34" s="38"/>
+      <c r="E34" s="38"/>
+      <c r="F34" s="38"/>
+      <c r="G34" s="38"/>
+      <c r="H34" s="38"/>
+      <c r="I34" s="38"/>
+      <c r="J34" s="38"/>
+      <c r="L34" s="41"/>
+      <c r="M34" s="38"/>
+      <c r="N34" s="38"/>
+      <c r="O34" s="38"/>
+      <c r="P34" s="38"/>
+    </row>
+    <row r="35" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A35" s="38"/>
+      <c r="B35" s="38"/>
+      <c r="C35" s="38"/>
+      <c r="D35" s="38"/>
+      <c r="E35" s="38"/>
+      <c r="F35" s="38"/>
+      <c r="G35" s="38"/>
+      <c r="H35" s="38"/>
+      <c r="I35" s="38"/>
+      <c r="J35" s="38"/>
+      <c r="L35" s="38"/>
+      <c r="M35" s="38"/>
+      <c r="N35" s="38"/>
+      <c r="O35" s="38"/>
+      <c r="P35" s="38"/>
+    </row>
+    <row r="36" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A36" s="38"/>
+      <c r="B36" s="38"/>
+      <c r="C36" s="38"/>
+      <c r="D36" s="38"/>
+      <c r="E36" s="38"/>
+      <c r="F36" s="38"/>
+      <c r="G36" s="38"/>
+      <c r="H36" s="38"/>
+      <c r="I36" s="38"/>
+      <c r="J36" s="38"/>
+      <c r="L36" s="38"/>
+      <c r="M36" s="38"/>
+      <c r="N36" s="38"/>
+      <c r="O36" s="38"/>
+      <c r="P36" s="38"/>
+    </row>
+    <row r="37" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A37" s="38"/>
+      <c r="B37" s="38"/>
+      <c r="C37" s="38"/>
+      <c r="D37" s="38"/>
+      <c r="E37" s="38"/>
+      <c r="F37" s="38"/>
+      <c r="G37" s="38"/>
+      <c r="H37" s="38"/>
+      <c r="I37" s="38"/>
+      <c r="J37" s="38"/>
+      <c r="L37" s="38"/>
+      <c r="M37" s="38"/>
+      <c r="N37" s="38"/>
+      <c r="O37" s="38"/>
+      <c r="P37" s="38"/>
+    </row>
+    <row r="39" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A39" t="s">
         <v>17</v>
       </c>
-      <c r="J38" t="s">
+      <c r="B39" s="38"/>
+      <c r="C39" s="38"/>
+      <c r="D39" s="38"/>
+      <c r="E39" s="38"/>
+      <c r="F39" s="38"/>
+      <c r="I39" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="39" spans="1:17" ht="18.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B39" s="7"/>
-      <c r="C39" s="7"/>
-      <c r="D39" s="7"/>
-      <c r="E39" s="7"/>
-      <c r="F39" s="7"/>
-      <c r="G39" s="7"/>
-      <c r="J39" s="7"/>
-      <c r="K39" s="7"/>
-      <c r="L39" s="7"/>
-      <c r="M39" s="7"/>
-    </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A40" t="s">
+      <c r="J39" s="38"/>
+      <c r="K39" s="38"/>
+      <c r="L39" s="38"/>
+    </row>
+    <row r="40" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A40" s="42"/>
+      <c r="B40" s="42"/>
+      <c r="C40" s="42"/>
+      <c r="D40" s="42"/>
+      <c r="E40" s="42"/>
+      <c r="F40" s="38"/>
+      <c r="G40" s="38"/>
+      <c r="H40" s="38"/>
+      <c r="I40" s="42"/>
+      <c r="J40" s="42"/>
+      <c r="K40" s="42"/>
+      <c r="L40" s="42"/>
+    </row>
+    <row r="41" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A41" s="38" t="s">
         <v>18</v>
       </c>
-      <c r="J40" t="s">
+      <c r="B41" s="38"/>
+      <c r="C41" s="38"/>
+      <c r="D41" s="38"/>
+      <c r="E41" s="38"/>
+      <c r="F41" s="38"/>
+      <c r="G41" s="38"/>
+      <c r="H41" s="38"/>
+      <c r="I41" s="43" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="41" spans="1:17" ht="18.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B41" s="7"/>
-      <c r="C41" s="7"/>
-      <c r="D41" s="7"/>
-      <c r="E41" s="7"/>
-      <c r="F41" s="7"/>
-      <c r="G41" s="7"/>
-      <c r="J41" s="7"/>
-      <c r="K41" s="7"/>
-      <c r="L41" s="7"/>
-      <c r="M41" s="7"/>
+      <c r="J41" s="43"/>
+      <c r="K41" s="43"/>
+      <c r="L41" s="43"/>
+    </row>
+    <row r="42" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A42" s="42"/>
+      <c r="B42" s="42"/>
+      <c r="C42" s="42"/>
+      <c r="D42" s="42"/>
+      <c r="E42" s="42"/>
+      <c r="I42" s="44"/>
+      <c r="J42" s="44"/>
+      <c r="K42" s="44"/>
+      <c r="L42" s="44"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="2"/>
+  <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
   <headerFooter>
     <oddHeader>&amp;Lプロジェクト憲章</oddHeader>
   </headerFooter>
@@ -5632,151 +7906,129 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFA0EC34-8F05-4D7B-BDBC-DEA24361978B}">
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr defaultColWidth="4.58203125" defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="2" max="2" width="11.25" customWidth="1"/>
-    <col min="3" max="3" width="14.1640625" customWidth="1"/>
-    <col min="4" max="4" width="19.4140625" customWidth="1"/>
-    <col min="5" max="5" width="34.1640625" customWidth="1"/>
-    <col min="6" max="6" width="31.25" customWidth="1"/>
+    <col min="1" max="1" width="10.58203125" customWidth="1"/>
+    <col min="2" max="2" width="13.58203125" customWidth="1"/>
+    <col min="3" max="3" width="20.58203125" customWidth="1"/>
+    <col min="4" max="4" width="36.83203125" customWidth="1"/>
+    <col min="5" max="5" width="38.58203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="18.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1" t="s">
+    <row r="1" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A1" s="94" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" ht="26" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B2" s="9"/>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="11"/>
-    </row>
-    <row r="3" spans="1:6" ht="11.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" t="s">
+      <c r="B1" s="94"/>
+      <c r="C1" s="94"/>
+    </row>
+    <row r="2" spans="1:5" ht="26" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A2" s="95"/>
+      <c r="B2" s="96"/>
+      <c r="C2" s="96"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="9"/>
+    </row>
+    <row r="3" spans="1:5" ht="11.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" s="94"/>
+      <c r="B3" s="94"/>
+      <c r="C3" s="94"/>
+    </row>
+    <row r="4" spans="1:5" ht="26.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" s="94" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4" s="94"/>
+      <c r="C4" s="94"/>
+    </row>
+    <row r="5" spans="1:5" ht="11.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.6"/>
+    <row r="6" spans="1:5" ht="68" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A6" s="45" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" ht="11.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.6"/>
-    <row r="6" spans="1:6" ht="54.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B6" s="24" t="s">
+      <c r="B6" s="46" t="s">
         <v>27</v>
       </c>
-      <c r="C6" s="25" t="s">
+      <c r="C6" s="47" t="s">
         <v>28</v>
       </c>
-      <c r="D6" s="26" t="s">
+      <c r="D6" s="47" t="s">
+        <v>109</v>
+      </c>
+      <c r="E6" s="48" t="s">
         <v>29</v>
       </c>
-      <c r="E6" s="26" t="s">
-        <v>31</v>
-      </c>
-      <c r="F6" s="27" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7">
-        <v>1</v>
-      </c>
-      <c r="B7" s="21"/>
-      <c r="C7" s="22"/>
-      <c r="D7" s="22"/>
-      <c r="E7" s="22"/>
-      <c r="F7" s="23"/>
-    </row>
-    <row r="8" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8">
-        <v>2</v>
-      </c>
-      <c r="B8" s="16"/>
-      <c r="C8" s="15"/>
-      <c r="D8" s="15"/>
-      <c r="E8" s="15"/>
-      <c r="F8" s="17"/>
-    </row>
-    <row r="9" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9">
-        <v>3</v>
-      </c>
-      <c r="B9" s="16"/>
-      <c r="C9" s="15"/>
-      <c r="D9" s="15"/>
-      <c r="E9" s="15"/>
-      <c r="F9" s="17"/>
-    </row>
-    <row r="10" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10">
-        <v>4</v>
-      </c>
-      <c r="B10" s="16"/>
-      <c r="C10" s="15"/>
-      <c r="D10" s="15"/>
-      <c r="E10" s="15"/>
-      <c r="F10" s="17"/>
-    </row>
-    <row r="11" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11">
-        <v>5</v>
-      </c>
-      <c r="B11" s="16"/>
-      <c r="C11" s="15"/>
-      <c r="D11" s="15"/>
-      <c r="E11" s="15"/>
-      <c r="F11" s="17"/>
-    </row>
-    <row r="12" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12">
-        <v>6</v>
-      </c>
-      <c r="B12" s="16"/>
-      <c r="C12" s="15"/>
-      <c r="D12" s="15"/>
-      <c r="E12" s="15"/>
-      <c r="F12" s="17"/>
-    </row>
-    <row r="13" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13">
-        <v>7</v>
-      </c>
-      <c r="B13" s="16"/>
-      <c r="C13" s="15"/>
-      <c r="D13" s="15"/>
-      <c r="E13" s="15"/>
-      <c r="F13" s="17"/>
-    </row>
-    <row r="14" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14">
-        <v>8</v>
-      </c>
-      <c r="B14" s="16"/>
-      <c r="C14" s="15"/>
-      <c r="D14" s="15"/>
-      <c r="E14" s="15"/>
-      <c r="F14" s="17"/>
-    </row>
-    <row r="15" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15">
-        <v>9</v>
-      </c>
-      <c r="B15" s="16"/>
-      <c r="C15" s="15"/>
-      <c r="D15" s="15"/>
-      <c r="E15" s="15"/>
-      <c r="F15" s="17"/>
-    </row>
-    <row r="16" spans="1:6" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A16">
-        <v>10</v>
-      </c>
-      <c r="B16" s="18"/>
-      <c r="C16" s="19"/>
-      <c r="D16" s="19"/>
-      <c r="E16" s="19"/>
-      <c r="F16" s="20"/>
+    </row>
+    <row r="7" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" s="17"/>
+      <c r="B7" s="18"/>
+      <c r="C7" s="18"/>
+      <c r="D7" s="18"/>
+      <c r="E7" s="19"/>
+    </row>
+    <row r="8" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" s="12"/>
+      <c r="B8" s="11"/>
+      <c r="C8" s="11"/>
+      <c r="D8" s="11"/>
+      <c r="E8" s="13"/>
+    </row>
+    <row r="9" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" s="12"/>
+      <c r="B9" s="11"/>
+      <c r="C9" s="11"/>
+      <c r="D9" s="11"/>
+      <c r="E9" s="13"/>
+    </row>
+    <row r="10" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" s="12"/>
+      <c r="B10" s="11"/>
+      <c r="C10" s="11"/>
+      <c r="D10" s="11"/>
+      <c r="E10" s="13"/>
+    </row>
+    <row r="11" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" s="12"/>
+      <c r="B11" s="11"/>
+      <c r="C11" s="11"/>
+      <c r="D11" s="11"/>
+      <c r="E11" s="13"/>
+    </row>
+    <row r="12" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" s="12"/>
+      <c r="B12" s="11"/>
+      <c r="C12" s="11"/>
+      <c r="D12" s="11"/>
+      <c r="E12" s="13"/>
+    </row>
+    <row r="13" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" s="12"/>
+      <c r="B13" s="11"/>
+      <c r="C13" s="11"/>
+      <c r="D13" s="11"/>
+      <c r="E13" s="13"/>
+    </row>
+    <row r="14" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" s="12"/>
+      <c r="B14" s="11"/>
+      <c r="C14" s="11"/>
+      <c r="D14" s="11"/>
+      <c r="E14" s="13"/>
+    </row>
+    <row r="15" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" s="12"/>
+      <c r="B15" s="11"/>
+      <c r="C15" s="11"/>
+      <c r="D15" s="11"/>
+      <c r="E15" s="13"/>
+    </row>
+    <row r="16" spans="1:5" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A16" s="14"/>
+      <c r="B16" s="15"/>
+      <c r="C16" s="15"/>
+      <c r="D16" s="15"/>
+      <c r="E16" s="16"/>
     </row>
     <row r="17" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
     <row r="18" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
@@ -5794,7 +8046,7 @@
     <row r="30" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
     <row r="31" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
   </sheetData>
-  <phoneticPr fontId="2"/>
+  <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
   <headerFooter>
@@ -5805,356 +8057,792 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82E3D39F-65D2-42BA-A239-D5CEA31193C4}">
-  <dimension ref="B1:AD25"/>
-  <sheetFormatPr defaultColWidth="3.83203125" defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <dimension ref="A1:AD27"/>
+  <sheetFormatPr defaultColWidth="4.08203125" defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <sheetData>
-    <row r="1" spans="2:30" ht="18.5" thickBot="1" x14ac:dyDescent="0.6"/>
-    <row r="2" spans="2:30" x14ac:dyDescent="0.55000000000000004">
-      <c r="N2" s="28"/>
-      <c r="O2" s="29"/>
-      <c r="P2" s="29"/>
-      <c r="Q2" s="29"/>
-      <c r="R2" s="30"/>
-      <c r="U2" s="46" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="3" spans="2:30" x14ac:dyDescent="0.55000000000000004">
-      <c r="N3" s="31" t="s">
-        <v>32</v>
-      </c>
-      <c r="O3" s="32"/>
-      <c r="P3" s="32"/>
-      <c r="Q3" s="32"/>
-      <c r="R3" s="33"/>
-      <c r="U3" s="47" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="4" spans="2:30" ht="18.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="N4" s="34"/>
-      <c r="O4" s="35"/>
-      <c r="P4" s="35"/>
-      <c r="Q4" s="35"/>
-      <c r="R4" s="36"/>
-    </row>
-    <row r="6" spans="2:30" ht="18.5" thickBot="1" x14ac:dyDescent="0.6"/>
-    <row r="7" spans="2:30" x14ac:dyDescent="0.55000000000000004">
-      <c r="B7" s="37">
+    <row r="1" spans="1:30" ht="18.5" thickBot="1" x14ac:dyDescent="0.6"/>
+    <row r="2" spans="1:30" x14ac:dyDescent="0.55000000000000004">
+      <c r="M2" s="20"/>
+      <c r="N2" s="21"/>
+      <c r="O2" s="21"/>
+      <c r="P2" s="21"/>
+      <c r="Q2" s="22"/>
+    </row>
+    <row r="3" spans="1:30" ht="22.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="M3" s="49" t="s">
+        <v>30</v>
+      </c>
+      <c r="N3" s="23"/>
+      <c r="O3" s="23"/>
+      <c r="P3" s="23"/>
+      <c r="Q3" s="24"/>
+    </row>
+    <row r="4" spans="1:30" ht="20.5" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="M4" s="25"/>
+      <c r="N4" s="26"/>
+      <c r="O4" s="26"/>
+      <c r="P4" s="26"/>
+      <c r="Q4" s="27"/>
+      <c r="R4" s="50" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="5" spans="1:30" ht="20" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" s="36"/>
+      <c r="B5" s="36"/>
+      <c r="C5" s="36"/>
+      <c r="D5" s="36"/>
+      <c r="E5" s="36"/>
+      <c r="F5" s="36"/>
+      <c r="G5" s="36"/>
+      <c r="H5" s="36"/>
+      <c r="I5" s="36"/>
+      <c r="J5" s="36"/>
+      <c r="K5" s="36"/>
+      <c r="L5" s="36"/>
+      <c r="M5" s="36"/>
+      <c r="N5" s="36"/>
+      <c r="O5" s="36"/>
+      <c r="P5" s="36"/>
+      <c r="Q5" s="36"/>
+      <c r="R5" s="50" t="s">
+        <v>111</v>
+      </c>
+      <c r="S5" s="36"/>
+      <c r="T5" s="36"/>
+      <c r="U5" s="36"/>
+      <c r="V5" s="36"/>
+      <c r="W5" s="36"/>
+      <c r="X5" s="36"/>
+      <c r="Y5" s="36"/>
+      <c r="Z5" s="36"/>
+      <c r="AA5" s="36"/>
+      <c r="AB5" s="36"/>
+      <c r="AC5" s="36"/>
+      <c r="AD5" s="36"/>
+    </row>
+    <row r="6" spans="1:30" ht="20.5" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A6" s="36"/>
+      <c r="B6" s="36"/>
+      <c r="C6" s="36"/>
+      <c r="D6" s="36"/>
+      <c r="E6" s="36"/>
+      <c r="F6" s="36"/>
+      <c r="G6" s="36"/>
+      <c r="H6" s="36"/>
+      <c r="I6" s="36"/>
+      <c r="J6" s="36"/>
+      <c r="K6" s="36"/>
+      <c r="L6" s="36"/>
+      <c r="M6" s="36"/>
+      <c r="N6" s="36"/>
+      <c r="O6" s="36"/>
+      <c r="P6" s="36"/>
+      <c r="Q6" s="36"/>
+      <c r="R6" s="36"/>
+      <c r="S6" s="36"/>
+      <c r="T6" s="36"/>
+      <c r="U6" s="36"/>
+      <c r="V6" s="36"/>
+      <c r="W6" s="36"/>
+      <c r="X6" s="36"/>
+      <c r="Y6" s="36"/>
+      <c r="Z6" s="36"/>
+      <c r="AA6" s="36"/>
+      <c r="AB6" s="36"/>
+      <c r="AC6" s="36"/>
+      <c r="AD6" s="36"/>
+    </row>
+    <row r="7" spans="1:30" ht="20" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" s="51">
         <v>1</v>
       </c>
-      <c r="C7" s="38"/>
-      <c r="D7" s="38"/>
-      <c r="E7" s="39"/>
-      <c r="G7" s="37">
+      <c r="B7" s="52"/>
+      <c r="C7" s="52"/>
+      <c r="D7" s="53"/>
+      <c r="E7" s="36"/>
+      <c r="F7" s="51">
         <v>2</v>
       </c>
-      <c r="H7" s="38"/>
-      <c r="I7" s="38"/>
-      <c r="J7" s="39"/>
-      <c r="L7" s="37"/>
-      <c r="M7" s="38"/>
-      <c r="N7" s="38"/>
-      <c r="O7" s="39"/>
-      <c r="Q7" s="37"/>
-      <c r="R7" s="38"/>
-      <c r="S7" s="38"/>
-      <c r="T7" s="39"/>
-      <c r="V7" s="37"/>
-      <c r="W7" s="38"/>
-      <c r="X7" s="38"/>
-      <c r="Y7" s="39"/>
-      <c r="AA7" s="37"/>
-      <c r="AB7" s="38"/>
-      <c r="AC7" s="38"/>
-      <c r="AD7" s="39"/>
-    </row>
-    <row r="8" spans="2:30" x14ac:dyDescent="0.55000000000000004">
-      <c r="B8" s="40"/>
-      <c r="C8" s="41"/>
-      <c r="D8" s="41"/>
-      <c r="E8" s="42"/>
-      <c r="G8" s="40"/>
-      <c r="H8" s="41"/>
-      <c r="I8" s="41"/>
-      <c r="J8" s="42"/>
-      <c r="L8" s="40"/>
-      <c r="M8" s="41"/>
-      <c r="N8" s="41"/>
-      <c r="O8" s="42"/>
-      <c r="Q8" s="40"/>
-      <c r="R8" s="41"/>
-      <c r="S8" s="41"/>
-      <c r="T8" s="42"/>
-      <c r="V8" s="40"/>
-      <c r="W8" s="41"/>
-      <c r="X8" s="41"/>
-      <c r="Y8" s="42"/>
-      <c r="AA8" s="40"/>
-      <c r="AB8" s="41"/>
-      <c r="AC8" s="41"/>
-      <c r="AD8" s="42"/>
-    </row>
-    <row r="9" spans="2:30" ht="18.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B9" s="43"/>
-      <c r="C9" s="44"/>
-      <c r="D9" s="44"/>
-      <c r="E9" s="45"/>
-      <c r="G9" s="43"/>
-      <c r="H9" s="44"/>
-      <c r="I9" s="44"/>
-      <c r="J9" s="45"/>
-      <c r="L9" s="43"/>
-      <c r="M9" s="44"/>
-      <c r="N9" s="44"/>
-      <c r="O9" s="45"/>
-      <c r="Q9" s="43"/>
-      <c r="R9" s="44"/>
-      <c r="S9" s="44"/>
-      <c r="T9" s="45"/>
-      <c r="V9" s="43"/>
-      <c r="W9" s="44"/>
-      <c r="X9" s="44"/>
-      <c r="Y9" s="45"/>
-      <c r="AA9" s="43"/>
-      <c r="AB9" s="44"/>
-      <c r="AC9" s="44"/>
-      <c r="AD9" s="45"/>
-    </row>
-    <row r="10" spans="2:30" ht="18.5" thickBot="1" x14ac:dyDescent="0.6"/>
-    <row r="11" spans="2:30" x14ac:dyDescent="0.55000000000000004">
-      <c r="C11" s="1">
+      <c r="G7" s="52"/>
+      <c r="H7" s="52"/>
+      <c r="I7" s="53"/>
+      <c r="J7" s="36"/>
+      <c r="K7" s="51"/>
+      <c r="L7" s="52"/>
+      <c r="M7" s="52"/>
+      <c r="N7" s="53"/>
+      <c r="O7" s="36"/>
+      <c r="P7" s="51"/>
+      <c r="Q7" s="52"/>
+      <c r="R7" s="52"/>
+      <c r="S7" s="53"/>
+      <c r="T7" s="36"/>
+      <c r="U7" s="51"/>
+      <c r="V7" s="52"/>
+      <c r="W7" s="52"/>
+      <c r="X7" s="53"/>
+      <c r="Y7" s="36"/>
+      <c r="Z7" s="51"/>
+      <c r="AA7" s="52"/>
+      <c r="AB7" s="52"/>
+      <c r="AC7" s="53"/>
+      <c r="AD7" s="36"/>
+    </row>
+    <row r="8" spans="1:30" ht="20" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" s="54"/>
+      <c r="B8" s="55"/>
+      <c r="C8" s="55"/>
+      <c r="D8" s="56"/>
+      <c r="E8" s="36"/>
+      <c r="F8" s="54"/>
+      <c r="G8" s="55"/>
+      <c r="H8" s="55"/>
+      <c r="I8" s="56"/>
+      <c r="J8" s="36"/>
+      <c r="K8" s="54"/>
+      <c r="L8" s="55"/>
+      <c r="M8" s="55"/>
+      <c r="N8" s="56"/>
+      <c r="O8" s="36"/>
+      <c r="P8" s="54"/>
+      <c r="Q8" s="55"/>
+      <c r="R8" s="55"/>
+      <c r="S8" s="56"/>
+      <c r="T8" s="36"/>
+      <c r="U8" s="54"/>
+      <c r="V8" s="55"/>
+      <c r="W8" s="55"/>
+      <c r="X8" s="56"/>
+      <c r="Y8" s="36"/>
+      <c r="Z8" s="54"/>
+      <c r="AA8" s="55"/>
+      <c r="AB8" s="55"/>
+      <c r="AC8" s="56"/>
+      <c r="AD8" s="36"/>
+    </row>
+    <row r="9" spans="1:30" ht="20.5" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A9" s="57"/>
+      <c r="B9" s="58"/>
+      <c r="C9" s="58"/>
+      <c r="D9" s="59"/>
+      <c r="E9" s="36"/>
+      <c r="F9" s="57"/>
+      <c r="G9" s="58"/>
+      <c r="H9" s="58"/>
+      <c r="I9" s="59"/>
+      <c r="J9" s="36"/>
+      <c r="K9" s="57"/>
+      <c r="L9" s="58"/>
+      <c r="M9" s="58"/>
+      <c r="N9" s="59"/>
+      <c r="O9" s="36"/>
+      <c r="P9" s="57"/>
+      <c r="Q9" s="58"/>
+      <c r="R9" s="58"/>
+      <c r="S9" s="59"/>
+      <c r="T9" s="36"/>
+      <c r="U9" s="57"/>
+      <c r="V9" s="58"/>
+      <c r="W9" s="58"/>
+      <c r="X9" s="59"/>
+      <c r="Y9" s="36"/>
+      <c r="Z9" s="57"/>
+      <c r="AA9" s="58"/>
+      <c r="AB9" s="58"/>
+      <c r="AC9" s="59"/>
+      <c r="AD9" s="36"/>
+    </row>
+    <row r="10" spans="1:30" ht="20.5" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A10" s="36"/>
+      <c r="B10" s="36"/>
+      <c r="C10" s="36"/>
+      <c r="D10" s="36"/>
+      <c r="E10" s="36"/>
+      <c r="F10" s="36"/>
+      <c r="G10" s="36"/>
+      <c r="H10" s="36"/>
+      <c r="I10" s="36"/>
+      <c r="J10" s="36"/>
+      <c r="K10" s="36"/>
+      <c r="L10" s="36"/>
+      <c r="M10" s="36"/>
+      <c r="N10" s="36"/>
+      <c r="O10" s="36"/>
+      <c r="P10" s="36"/>
+      <c r="Q10" s="36"/>
+      <c r="R10" s="36"/>
+      <c r="S10" s="36"/>
+      <c r="T10" s="36"/>
+      <c r="U10" s="36"/>
+      <c r="V10" s="36"/>
+      <c r="W10" s="36"/>
+      <c r="X10" s="36"/>
+      <c r="Y10" s="36"/>
+      <c r="Z10" s="36"/>
+      <c r="AA10" s="36"/>
+      <c r="AB10" s="36"/>
+      <c r="AC10" s="36"/>
+      <c r="AD10" s="36"/>
+    </row>
+    <row r="11" spans="1:30" ht="20" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" s="36"/>
+      <c r="B11" s="68">
         <v>1.1000000000000001</v>
       </c>
-      <c r="D11" s="2"/>
-      <c r="E11" s="3"/>
-      <c r="H11" s="1">
+      <c r="C11" s="61"/>
+      <c r="D11" s="62"/>
+      <c r="E11" s="36"/>
+      <c r="F11" s="36"/>
+      <c r="G11" s="60">
         <v>2.1</v>
       </c>
-      <c r="I11" s="2"/>
-      <c r="J11" s="3"/>
-      <c r="M11" s="1"/>
-      <c r="N11" s="2"/>
-      <c r="O11" s="3"/>
-      <c r="R11" s="1"/>
-      <c r="S11" s="2"/>
-      <c r="T11" s="3"/>
-      <c r="W11" s="1"/>
-      <c r="X11" s="2"/>
-      <c r="Y11" s="3"/>
-      <c r="AB11" s="1"/>
-      <c r="AC11" s="2"/>
-      <c r="AD11" s="3"/>
-    </row>
-    <row r="12" spans="2:30" x14ac:dyDescent="0.55000000000000004">
-      <c r="C12" s="4"/>
-      <c r="E12" s="5"/>
-      <c r="H12" s="4"/>
-      <c r="J12" s="5"/>
-      <c r="M12" s="4"/>
-      <c r="O12" s="5"/>
-      <c r="R12" s="4"/>
-      <c r="T12" s="5"/>
-      <c r="W12" s="4"/>
-      <c r="Y12" s="5"/>
-      <c r="AB12" s="4"/>
-      <c r="AD12" s="5"/>
-    </row>
-    <row r="13" spans="2:30" ht="18.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="C13" s="6"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="8"/>
-      <c r="H13" s="6"/>
-      <c r="I13" s="7"/>
-      <c r="J13" s="8"/>
-      <c r="M13" s="6"/>
-      <c r="N13" s="7"/>
-      <c r="O13" s="8"/>
-      <c r="R13" s="6"/>
-      <c r="S13" s="7"/>
-      <c r="T13" s="8"/>
-      <c r="W13" s="6"/>
-      <c r="X13" s="7"/>
-      <c r="Y13" s="8"/>
-      <c r="AB13" s="6"/>
-      <c r="AC13" s="7"/>
-      <c r="AD13" s="8"/>
-    </row>
-    <row r="14" spans="2:30" ht="18.5" thickBot="1" x14ac:dyDescent="0.6"/>
-    <row r="15" spans="2:30" x14ac:dyDescent="0.55000000000000004">
-      <c r="C15" s="1">
+      <c r="H11" s="61"/>
+      <c r="I11" s="62"/>
+      <c r="J11" s="36"/>
+      <c r="K11" s="36"/>
+      <c r="L11" s="60"/>
+      <c r="M11" s="61"/>
+      <c r="N11" s="62"/>
+      <c r="O11" s="36"/>
+      <c r="P11" s="36"/>
+      <c r="Q11" s="60"/>
+      <c r="R11" s="61"/>
+      <c r="S11" s="62"/>
+      <c r="T11" s="36"/>
+      <c r="U11" s="36"/>
+      <c r="V11" s="60"/>
+      <c r="W11" s="61"/>
+      <c r="X11" s="62"/>
+      <c r="Y11" s="36"/>
+      <c r="Z11" s="36"/>
+      <c r="AA11" s="60"/>
+      <c r="AB11" s="61"/>
+      <c r="AC11" s="62"/>
+      <c r="AD11" s="36"/>
+    </row>
+    <row r="12" spans="1:30" ht="20" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" s="36"/>
+      <c r="B12" s="63"/>
+      <c r="C12" s="36"/>
+      <c r="D12" s="64"/>
+      <c r="E12" s="36"/>
+      <c r="F12" s="36"/>
+      <c r="G12" s="63"/>
+      <c r="H12" s="36"/>
+      <c r="I12" s="64"/>
+      <c r="J12" s="36"/>
+      <c r="K12" s="36"/>
+      <c r="L12" s="63"/>
+      <c r="M12" s="36"/>
+      <c r="N12" s="64"/>
+      <c r="O12" s="36"/>
+      <c r="P12" s="36"/>
+      <c r="Q12" s="63"/>
+      <c r="R12" s="36"/>
+      <c r="S12" s="64"/>
+      <c r="T12" s="36"/>
+      <c r="U12" s="36"/>
+      <c r="V12" s="63"/>
+      <c r="W12" s="36"/>
+      <c r="X12" s="64"/>
+      <c r="Y12" s="36"/>
+      <c r="Z12" s="36"/>
+      <c r="AA12" s="63"/>
+      <c r="AB12" s="36"/>
+      <c r="AC12" s="64"/>
+      <c r="AD12" s="36"/>
+    </row>
+    <row r="13" spans="1:30" ht="20.5" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A13" s="36"/>
+      <c r="B13" s="65"/>
+      <c r="C13" s="66"/>
+      <c r="D13" s="67"/>
+      <c r="E13" s="36"/>
+      <c r="F13" s="36"/>
+      <c r="G13" s="65"/>
+      <c r="H13" s="66"/>
+      <c r="I13" s="67"/>
+      <c r="J13" s="36"/>
+      <c r="K13" s="36"/>
+      <c r="L13" s="65"/>
+      <c r="M13" s="66"/>
+      <c r="N13" s="67"/>
+      <c r="O13" s="36"/>
+      <c r="P13" s="36"/>
+      <c r="Q13" s="65"/>
+      <c r="R13" s="66"/>
+      <c r="S13" s="67"/>
+      <c r="T13" s="36"/>
+      <c r="U13" s="36"/>
+      <c r="V13" s="65"/>
+      <c r="W13" s="66"/>
+      <c r="X13" s="67"/>
+      <c r="Y13" s="36"/>
+      <c r="Z13" s="36"/>
+      <c r="AA13" s="65"/>
+      <c r="AB13" s="66"/>
+      <c r="AC13" s="67"/>
+      <c r="AD13" s="36"/>
+    </row>
+    <row r="14" spans="1:30" ht="20.5" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A14" s="36"/>
+      <c r="B14" s="36"/>
+      <c r="C14" s="36"/>
+      <c r="D14" s="36"/>
+      <c r="E14" s="36"/>
+      <c r="F14" s="36"/>
+      <c r="G14" s="36"/>
+      <c r="H14" s="36"/>
+      <c r="I14" s="36"/>
+      <c r="J14" s="36"/>
+      <c r="K14" s="36"/>
+      <c r="L14" s="36"/>
+      <c r="M14" s="36"/>
+      <c r="N14" s="36"/>
+      <c r="O14" s="36"/>
+      <c r="P14" s="36"/>
+      <c r="Q14" s="36"/>
+      <c r="R14" s="36"/>
+      <c r="S14" s="36"/>
+      <c r="T14" s="36"/>
+      <c r="U14" s="36"/>
+      <c r="V14" s="36"/>
+      <c r="W14" s="36"/>
+      <c r="X14" s="36"/>
+      <c r="Y14" s="36"/>
+      <c r="Z14" s="36"/>
+      <c r="AA14" s="36"/>
+      <c r="AB14" s="36"/>
+      <c r="AC14" s="36"/>
+      <c r="AD14" s="36"/>
+    </row>
+    <row r="15" spans="1:30" ht="20" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" s="36"/>
+      <c r="B15" s="60">
         <v>1.2</v>
       </c>
-      <c r="D15" s="2"/>
-      <c r="E15" s="3"/>
-      <c r="H15" s="1">
+      <c r="C15" s="61"/>
+      <c r="D15" s="62"/>
+      <c r="E15" s="36"/>
+      <c r="F15" s="36"/>
+      <c r="G15" s="60">
         <v>2.2000000000000002</v>
       </c>
-      <c r="I15" s="2"/>
-      <c r="J15" s="3"/>
-      <c r="M15" s="1"/>
-      <c r="N15" s="2"/>
-      <c r="O15" s="3"/>
-      <c r="R15" s="1"/>
-      <c r="S15" s="2"/>
-      <c r="T15" s="3"/>
-      <c r="W15" s="1"/>
-      <c r="X15" s="2"/>
-      <c r="Y15" s="3"/>
-      <c r="AB15" s="1"/>
-      <c r="AC15" s="2"/>
-      <c r="AD15" s="3"/>
-    </row>
-    <row r="16" spans="2:30" x14ac:dyDescent="0.55000000000000004">
-      <c r="C16" s="4"/>
-      <c r="E16" s="5"/>
-      <c r="H16" s="4"/>
-      <c r="J16" s="5"/>
-      <c r="M16" s="4"/>
-      <c r="O16" s="5"/>
-      <c r="R16" s="4"/>
-      <c r="T16" s="5"/>
-      <c r="W16" s="4"/>
-      <c r="Y16" s="5"/>
-      <c r="AB16" s="4"/>
-      <c r="AD16" s="5"/>
-    </row>
-    <row r="17" spans="3:30" ht="18.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="C17" s="6"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="8"/>
-      <c r="H17" s="6"/>
-      <c r="I17" s="7"/>
-      <c r="J17" s="8"/>
-      <c r="M17" s="6"/>
-      <c r="N17" s="7"/>
-      <c r="O17" s="8"/>
-      <c r="R17" s="6"/>
-      <c r="S17" s="7"/>
-      <c r="T17" s="8"/>
-      <c r="W17" s="6"/>
-      <c r="X17" s="7"/>
-      <c r="Y17" s="8"/>
-      <c r="AB17" s="6"/>
-      <c r="AC17" s="7"/>
-      <c r="AD17" s="8"/>
-    </row>
-    <row r="18" spans="3:30" ht="18.5" thickBot="1" x14ac:dyDescent="0.6"/>
-    <row r="19" spans="3:30" x14ac:dyDescent="0.55000000000000004">
-      <c r="C19" s="1">
+      <c r="H15" s="61"/>
+      <c r="I15" s="62"/>
+      <c r="J15" s="36"/>
+      <c r="K15" s="36"/>
+      <c r="L15" s="60"/>
+      <c r="M15" s="61"/>
+      <c r="N15" s="62"/>
+      <c r="O15" s="36"/>
+      <c r="P15" s="36"/>
+      <c r="Q15" s="60"/>
+      <c r="R15" s="61"/>
+      <c r="S15" s="62"/>
+      <c r="T15" s="36"/>
+      <c r="U15" s="36"/>
+      <c r="V15" s="60"/>
+      <c r="W15" s="61"/>
+      <c r="X15" s="62"/>
+      <c r="Y15" s="36"/>
+      <c r="Z15" s="36"/>
+      <c r="AA15" s="60"/>
+      <c r="AB15" s="61"/>
+      <c r="AC15" s="62"/>
+      <c r="AD15" s="36"/>
+    </row>
+    <row r="16" spans="1:30" ht="20" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" s="36"/>
+      <c r="B16" s="63"/>
+      <c r="C16" s="36"/>
+      <c r="D16" s="64"/>
+      <c r="E16" s="36"/>
+      <c r="F16" s="36"/>
+      <c r="G16" s="63"/>
+      <c r="H16" s="36"/>
+      <c r="I16" s="64"/>
+      <c r="J16" s="36"/>
+      <c r="K16" s="36"/>
+      <c r="L16" s="63"/>
+      <c r="M16" s="36"/>
+      <c r="N16" s="64"/>
+      <c r="O16" s="36"/>
+      <c r="P16" s="36"/>
+      <c r="Q16" s="63"/>
+      <c r="R16" s="36"/>
+      <c r="S16" s="64"/>
+      <c r="T16" s="36"/>
+      <c r="U16" s="36"/>
+      <c r="V16" s="63"/>
+      <c r="W16" s="36"/>
+      <c r="X16" s="64"/>
+      <c r="Y16" s="36"/>
+      <c r="Z16" s="36"/>
+      <c r="AA16" s="63"/>
+      <c r="AB16" s="36"/>
+      <c r="AC16" s="64"/>
+      <c r="AD16" s="36"/>
+    </row>
+    <row r="17" spans="1:30" ht="20.5" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A17" s="36"/>
+      <c r="B17" s="65"/>
+      <c r="C17" s="66"/>
+      <c r="D17" s="67"/>
+      <c r="E17" s="36"/>
+      <c r="F17" s="36"/>
+      <c r="G17" s="65"/>
+      <c r="H17" s="66"/>
+      <c r="I17" s="67"/>
+      <c r="J17" s="36"/>
+      <c r="K17" s="36"/>
+      <c r="L17" s="65"/>
+      <c r="M17" s="66"/>
+      <c r="N17" s="67"/>
+      <c r="O17" s="36"/>
+      <c r="P17" s="36"/>
+      <c r="Q17" s="65"/>
+      <c r="R17" s="66"/>
+      <c r="S17" s="67"/>
+      <c r="T17" s="36"/>
+      <c r="U17" s="36"/>
+      <c r="V17" s="65"/>
+      <c r="W17" s="66"/>
+      <c r="X17" s="67"/>
+      <c r="Y17" s="36"/>
+      <c r="Z17" s="36"/>
+      <c r="AA17" s="65"/>
+      <c r="AB17" s="66"/>
+      <c r="AC17" s="67"/>
+      <c r="AD17" s="36"/>
+    </row>
+    <row r="18" spans="1:30" ht="20.5" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A18" s="36"/>
+      <c r="B18" s="36"/>
+      <c r="C18" s="36"/>
+      <c r="D18" s="36"/>
+      <c r="E18" s="36"/>
+      <c r="F18" s="36"/>
+      <c r="G18" s="36"/>
+      <c r="H18" s="36"/>
+      <c r="I18" s="36"/>
+      <c r="J18" s="36"/>
+      <c r="K18" s="36"/>
+      <c r="L18" s="36"/>
+      <c r="M18" s="36"/>
+      <c r="N18" s="36"/>
+      <c r="O18" s="36"/>
+      <c r="P18" s="36"/>
+      <c r="Q18" s="36"/>
+      <c r="R18" s="36"/>
+      <c r="S18" s="36"/>
+      <c r="T18" s="36"/>
+      <c r="U18" s="36"/>
+      <c r="V18" s="36"/>
+      <c r="W18" s="36"/>
+      <c r="X18" s="36"/>
+      <c r="Y18" s="36"/>
+      <c r="Z18" s="36"/>
+      <c r="AA18" s="36"/>
+      <c r="AB18" s="36"/>
+      <c r="AC18" s="36"/>
+      <c r="AD18" s="36"/>
+    </row>
+    <row r="19" spans="1:30" ht="20" x14ac:dyDescent="0.55000000000000004">
+      <c r="A19" s="36"/>
+      <c r="B19" s="60">
         <v>1.3</v>
       </c>
-      <c r="D19" s="2"/>
-      <c r="E19" s="3"/>
-      <c r="H19" s="1">
+      <c r="C19" s="61"/>
+      <c r="D19" s="62"/>
+      <c r="E19" s="36"/>
+      <c r="F19" s="36"/>
+      <c r="G19" s="60">
         <v>2.2999999999999998</v>
       </c>
-      <c r="I19" s="2"/>
-      <c r="J19" s="3"/>
-      <c r="M19" s="1"/>
-      <c r="N19" s="2"/>
-      <c r="O19" s="3"/>
-      <c r="R19" s="1"/>
-      <c r="S19" s="2"/>
-      <c r="T19" s="3"/>
-      <c r="W19" s="1"/>
-      <c r="X19" s="2"/>
-      <c r="Y19" s="3"/>
-      <c r="AB19" s="1"/>
-      <c r="AC19" s="2"/>
-      <c r="AD19" s="3"/>
-    </row>
-    <row r="20" spans="3:30" x14ac:dyDescent="0.55000000000000004">
-      <c r="C20" s="4"/>
-      <c r="E20" s="5"/>
-      <c r="H20" s="4"/>
-      <c r="J20" s="5"/>
-      <c r="M20" s="4"/>
-      <c r="O20" s="5"/>
-      <c r="R20" s="4"/>
-      <c r="T20" s="5"/>
-      <c r="W20" s="4"/>
-      <c r="Y20" s="5"/>
-      <c r="AB20" s="4"/>
-      <c r="AD20" s="5"/>
-    </row>
-    <row r="21" spans="3:30" ht="18.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="C21" s="6"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="8"/>
-      <c r="H21" s="6"/>
-      <c r="I21" s="7"/>
-      <c r="J21" s="8"/>
-      <c r="M21" s="6"/>
-      <c r="N21" s="7"/>
-      <c r="O21" s="8"/>
-      <c r="R21" s="6"/>
-      <c r="S21" s="7"/>
-      <c r="T21" s="8"/>
-      <c r="W21" s="6"/>
-      <c r="X21" s="7"/>
-      <c r="Y21" s="8"/>
-      <c r="AB21" s="6"/>
-      <c r="AC21" s="7"/>
-      <c r="AD21" s="8"/>
-    </row>
-    <row r="22" spans="3:30" ht="18.5" thickBot="1" x14ac:dyDescent="0.6"/>
-    <row r="23" spans="3:30" x14ac:dyDescent="0.55000000000000004">
-      <c r="C23" s="1"/>
-      <c r="D23" s="2"/>
-      <c r="E23" s="3"/>
-      <c r="H23" s="1"/>
-      <c r="I23" s="2"/>
-      <c r="J23" s="3"/>
-      <c r="M23" s="1"/>
-      <c r="N23" s="2"/>
-      <c r="O23" s="3"/>
-      <c r="R23" s="1"/>
-      <c r="S23" s="2"/>
-      <c r="T23" s="3"/>
-      <c r="W23" s="1"/>
-      <c r="X23" s="2"/>
-      <c r="Y23" s="3"/>
-      <c r="AB23" s="1"/>
-      <c r="AC23" s="2"/>
-      <c r="AD23" s="3"/>
-    </row>
-    <row r="24" spans="3:30" x14ac:dyDescent="0.55000000000000004">
-      <c r="C24" s="4"/>
-      <c r="E24" s="5"/>
-      <c r="H24" s="4"/>
-      <c r="J24" s="5"/>
-      <c r="M24" s="4"/>
-      <c r="O24" s="5"/>
-      <c r="R24" s="4"/>
-      <c r="T24" s="5"/>
-      <c r="W24" s="4"/>
-      <c r="Y24" s="5"/>
-      <c r="AB24" s="4"/>
-      <c r="AD24" s="5"/>
-    </row>
-    <row r="25" spans="3:30" ht="18.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="C25" s="6"/>
-      <c r="D25" s="7"/>
-      <c r="E25" s="8"/>
-      <c r="H25" s="6"/>
-      <c r="I25" s="7"/>
-      <c r="J25" s="8"/>
-      <c r="M25" s="6"/>
-      <c r="N25" s="7"/>
-      <c r="O25" s="8"/>
-      <c r="R25" s="6"/>
-      <c r="S25" s="7"/>
-      <c r="T25" s="8"/>
-      <c r="W25" s="6"/>
-      <c r="X25" s="7"/>
-      <c r="Y25" s="8"/>
-      <c r="AB25" s="6"/>
-      <c r="AC25" s="7"/>
-      <c r="AD25" s="8"/>
+      <c r="H19" s="61"/>
+      <c r="I19" s="62"/>
+      <c r="J19" s="36"/>
+      <c r="K19" s="36"/>
+      <c r="L19" s="60"/>
+      <c r="M19" s="61"/>
+      <c r="N19" s="62"/>
+      <c r="O19" s="36"/>
+      <c r="P19" s="36"/>
+      <c r="Q19" s="60"/>
+      <c r="R19" s="61"/>
+      <c r="S19" s="62"/>
+      <c r="T19" s="36"/>
+      <c r="U19" s="36"/>
+      <c r="V19" s="60"/>
+      <c r="W19" s="61"/>
+      <c r="X19" s="62"/>
+      <c r="Y19" s="36"/>
+      <c r="Z19" s="36"/>
+      <c r="AA19" s="60"/>
+      <c r="AB19" s="61"/>
+      <c r="AC19" s="62"/>
+      <c r="AD19" s="36"/>
+    </row>
+    <row r="20" spans="1:30" ht="20" x14ac:dyDescent="0.55000000000000004">
+      <c r="A20" s="36"/>
+      <c r="B20" s="63"/>
+      <c r="C20" s="36"/>
+      <c r="D20" s="64"/>
+      <c r="E20" s="36"/>
+      <c r="F20" s="36"/>
+      <c r="G20" s="63"/>
+      <c r="H20" s="36"/>
+      <c r="I20" s="64"/>
+      <c r="J20" s="36"/>
+      <c r="K20" s="36"/>
+      <c r="L20" s="63"/>
+      <c r="M20" s="36"/>
+      <c r="N20" s="64"/>
+      <c r="O20" s="36"/>
+      <c r="P20" s="36"/>
+      <c r="Q20" s="63"/>
+      <c r="R20" s="36"/>
+      <c r="S20" s="64"/>
+      <c r="T20" s="36"/>
+      <c r="U20" s="36"/>
+      <c r="V20" s="63"/>
+      <c r="W20" s="36"/>
+      <c r="X20" s="64"/>
+      <c r="Y20" s="36"/>
+      <c r="Z20" s="36"/>
+      <c r="AA20" s="63"/>
+      <c r="AB20" s="36"/>
+      <c r="AC20" s="64"/>
+      <c r="AD20" s="36"/>
+    </row>
+    <row r="21" spans="1:30" ht="20.5" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A21" s="36"/>
+      <c r="B21" s="65"/>
+      <c r="C21" s="66"/>
+      <c r="D21" s="67"/>
+      <c r="E21" s="36"/>
+      <c r="F21" s="36"/>
+      <c r="G21" s="65"/>
+      <c r="H21" s="66"/>
+      <c r="I21" s="67"/>
+      <c r="J21" s="36"/>
+      <c r="K21" s="36"/>
+      <c r="L21" s="65"/>
+      <c r="M21" s="66"/>
+      <c r="N21" s="67"/>
+      <c r="O21" s="36"/>
+      <c r="P21" s="36"/>
+      <c r="Q21" s="65"/>
+      <c r="R21" s="66"/>
+      <c r="S21" s="67"/>
+      <c r="T21" s="36"/>
+      <c r="U21" s="36"/>
+      <c r="V21" s="65"/>
+      <c r="W21" s="66"/>
+      <c r="X21" s="67"/>
+      <c r="Y21" s="36"/>
+      <c r="Z21" s="36"/>
+      <c r="AA21" s="65"/>
+      <c r="AB21" s="66"/>
+      <c r="AC21" s="67"/>
+      <c r="AD21" s="36"/>
+    </row>
+    <row r="22" spans="1:30" ht="20.5" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A22" s="36"/>
+      <c r="B22" s="36"/>
+      <c r="C22" s="36"/>
+      <c r="D22" s="36"/>
+      <c r="E22" s="36"/>
+      <c r="F22" s="36"/>
+      <c r="G22" s="36"/>
+      <c r="H22" s="36"/>
+      <c r="I22" s="36"/>
+      <c r="J22" s="36"/>
+      <c r="K22" s="36"/>
+      <c r="L22" s="36"/>
+      <c r="M22" s="36"/>
+      <c r="N22" s="36"/>
+      <c r="O22" s="36"/>
+      <c r="P22" s="36"/>
+      <c r="Q22" s="36"/>
+      <c r="R22" s="36"/>
+      <c r="S22" s="36"/>
+      <c r="T22" s="36"/>
+      <c r="U22" s="36"/>
+      <c r="V22" s="36"/>
+      <c r="W22" s="36"/>
+      <c r="X22" s="36"/>
+      <c r="Y22" s="36"/>
+      <c r="Z22" s="36"/>
+      <c r="AA22" s="36"/>
+      <c r="AB22" s="36"/>
+      <c r="AC22" s="36"/>
+      <c r="AD22" s="36"/>
+    </row>
+    <row r="23" spans="1:30" ht="20" x14ac:dyDescent="0.55000000000000004">
+      <c r="A23" s="36"/>
+      <c r="B23" s="60"/>
+      <c r="C23" s="61"/>
+      <c r="D23" s="62"/>
+      <c r="E23" s="36"/>
+      <c r="F23" s="36"/>
+      <c r="G23" s="60"/>
+      <c r="H23" s="61"/>
+      <c r="I23" s="62"/>
+      <c r="J23" s="36"/>
+      <c r="K23" s="36"/>
+      <c r="L23" s="60"/>
+      <c r="M23" s="61"/>
+      <c r="N23" s="62"/>
+      <c r="O23" s="36"/>
+      <c r="P23" s="36"/>
+      <c r="Q23" s="60"/>
+      <c r="R23" s="61"/>
+      <c r="S23" s="62"/>
+      <c r="T23" s="36"/>
+      <c r="U23" s="36"/>
+      <c r="V23" s="60"/>
+      <c r="W23" s="61"/>
+      <c r="X23" s="62"/>
+      <c r="Y23" s="36"/>
+      <c r="Z23" s="36"/>
+      <c r="AA23" s="60"/>
+      <c r="AB23" s="61"/>
+      <c r="AC23" s="62"/>
+      <c r="AD23" s="36"/>
+    </row>
+    <row r="24" spans="1:30" ht="20" x14ac:dyDescent="0.55000000000000004">
+      <c r="A24" s="36"/>
+      <c r="B24" s="63"/>
+      <c r="C24" s="36"/>
+      <c r="D24" s="64"/>
+      <c r="E24" s="36"/>
+      <c r="F24" s="36"/>
+      <c r="G24" s="63"/>
+      <c r="H24" s="36"/>
+      <c r="I24" s="64"/>
+      <c r="J24" s="36"/>
+      <c r="K24" s="36"/>
+      <c r="L24" s="63"/>
+      <c r="M24" s="36"/>
+      <c r="N24" s="64"/>
+      <c r="O24" s="36"/>
+      <c r="P24" s="36"/>
+      <c r="Q24" s="63"/>
+      <c r="R24" s="36"/>
+      <c r="S24" s="64"/>
+      <c r="T24" s="36"/>
+      <c r="U24" s="36"/>
+      <c r="V24" s="63"/>
+      <c r="W24" s="36"/>
+      <c r="X24" s="64"/>
+      <c r="Y24" s="36"/>
+      <c r="Z24" s="36"/>
+      <c r="AA24" s="63"/>
+      <c r="AB24" s="36"/>
+      <c r="AC24" s="64"/>
+      <c r="AD24" s="36"/>
+    </row>
+    <row r="25" spans="1:30" ht="20.5" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A25" s="36"/>
+      <c r="B25" s="65"/>
+      <c r="C25" s="66"/>
+      <c r="D25" s="67"/>
+      <c r="E25" s="36"/>
+      <c r="F25" s="36"/>
+      <c r="G25" s="65"/>
+      <c r="H25" s="66"/>
+      <c r="I25" s="67"/>
+      <c r="J25" s="36"/>
+      <c r="K25" s="36"/>
+      <c r="L25" s="65"/>
+      <c r="M25" s="66"/>
+      <c r="N25" s="67"/>
+      <c r="O25" s="36"/>
+      <c r="P25" s="36"/>
+      <c r="Q25" s="65"/>
+      <c r="R25" s="66"/>
+      <c r="S25" s="67"/>
+      <c r="T25" s="36"/>
+      <c r="U25" s="36"/>
+      <c r="V25" s="65"/>
+      <c r="W25" s="66"/>
+      <c r="X25" s="67"/>
+      <c r="Y25" s="36"/>
+      <c r="Z25" s="36"/>
+      <c r="AA25" s="65"/>
+      <c r="AB25" s="66"/>
+      <c r="AC25" s="67"/>
+      <c r="AD25" s="36"/>
+    </row>
+    <row r="26" spans="1:30" ht="20" x14ac:dyDescent="0.55000000000000004">
+      <c r="A26" s="36"/>
+      <c r="B26" s="36"/>
+      <c r="C26" s="36"/>
+      <c r="D26" s="36"/>
+      <c r="E26" s="36"/>
+      <c r="F26" s="36"/>
+      <c r="G26" s="36"/>
+      <c r="H26" s="36"/>
+      <c r="I26" s="36"/>
+      <c r="J26" s="36"/>
+      <c r="K26" s="36"/>
+      <c r="L26" s="36"/>
+      <c r="M26" s="36"/>
+      <c r="N26" s="36"/>
+      <c r="O26" s="36"/>
+      <c r="P26" s="36"/>
+      <c r="Q26" s="36"/>
+      <c r="R26" s="36"/>
+      <c r="S26" s="36"/>
+      <c r="T26" s="36"/>
+      <c r="U26" s="36"/>
+      <c r="V26" s="36"/>
+      <c r="W26" s="36"/>
+      <c r="X26" s="36"/>
+      <c r="Y26" s="36"/>
+      <c r="Z26" s="36"/>
+      <c r="AA26" s="36"/>
+      <c r="AB26" s="36"/>
+      <c r="AC26" s="36"/>
+      <c r="AD26" s="36"/>
+    </row>
+    <row r="27" spans="1:30" ht="20" x14ac:dyDescent="0.55000000000000004">
+      <c r="A27" s="36"/>
+      <c r="B27" s="36"/>
+      <c r="C27" s="36"/>
+      <c r="D27" s="36"/>
+      <c r="E27" s="36"/>
+      <c r="F27" s="36"/>
+      <c r="G27" s="36"/>
+      <c r="H27" s="36"/>
+      <c r="I27" s="36"/>
+      <c r="J27" s="36"/>
+      <c r="K27" s="36"/>
+      <c r="L27" s="36"/>
+      <c r="M27" s="36"/>
+      <c r="N27" s="36"/>
+      <c r="O27" s="36"/>
+      <c r="P27" s="36"/>
+      <c r="Q27" s="36"/>
+      <c r="R27" s="36"/>
+      <c r="S27" s="36"/>
+      <c r="T27" s="36"/>
+      <c r="U27" s="36"/>
+      <c r="V27" s="36"/>
+      <c r="W27" s="36"/>
+      <c r="X27" s="36"/>
+      <c r="Y27" s="36"/>
+      <c r="Z27" s="36"/>
+      <c r="AA27" s="36"/>
+      <c r="AB27" s="36"/>
+      <c r="AC27" s="36"/>
+      <c r="AD27" s="36"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="2"/>
+  <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
   <headerFooter>
@@ -6166,110 +8854,339 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD121E88-4C85-4901-85C7-0FB3D413DD24}">
-  <dimension ref="A2:Z20"/>
-  <sheetFormatPr defaultColWidth="4.58203125" defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <dimension ref="B1:AB16"/>
+  <sheetFormatPr defaultColWidth="4.58203125" defaultRowHeight="25" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
   <sheetData>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.55000000000000004">
-      <c r="N2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="3" spans="1:26" ht="18.5" thickBot="1" x14ac:dyDescent="0.6"/>
-    <row r="4" spans="1:26" ht="18.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="E4" s="48" t="s">
-        <v>39</v>
-      </c>
-      <c r="F4" s="10"/>
-      <c r="G4" s="10"/>
-      <c r="H4" s="10"/>
-      <c r="I4" s="11"/>
-      <c r="L4" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="M4" s="10"/>
-      <c r="N4" s="10"/>
-      <c r="O4" s="10"/>
-      <c r="P4" s="11"/>
-      <c r="S4" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="T4" s="10"/>
-      <c r="U4" s="10"/>
-      <c r="V4" s="11"/>
-    </row>
-    <row r="6" spans="1:26" ht="18.5" thickBot="1" x14ac:dyDescent="0.6"/>
-    <row r="7" spans="1:26" ht="18.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="E7" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="F7" s="10"/>
-      <c r="G7" s="10"/>
-      <c r="H7" s="10"/>
-      <c r="I7" s="11"/>
-      <c r="L7" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="M7" s="10"/>
-      <c r="N7" s="10"/>
-      <c r="O7" s="10"/>
-      <c r="P7" s="11"/>
-      <c r="S7" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="T7" s="10"/>
-      <c r="U7" s="10"/>
-      <c r="V7" s="11"/>
-    </row>
-    <row r="8" spans="1:26" ht="18.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A8" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="B8" s="11"/>
-    </row>
-    <row r="9" spans="1:26" ht="18.5" thickBot="1" x14ac:dyDescent="0.6"/>
-    <row r="10" spans="1:26" ht="18.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="E10" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="F10" s="10"/>
-      <c r="G10" s="10"/>
-      <c r="H10" s="10"/>
-      <c r="I10" s="11"/>
-      <c r="L10" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="M10" s="10"/>
-      <c r="N10" s="10"/>
-      <c r="O10" s="10"/>
-      <c r="P10" s="11"/>
-      <c r="S10" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="T10" s="10"/>
-      <c r="U10" s="10"/>
-      <c r="V10" s="11"/>
-      <c r="Y10" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="Z10" s="11"/>
-    </row>
-    <row r="12" spans="1:26" ht="18.5" thickBot="1" x14ac:dyDescent="0.6"/>
-    <row r="13" spans="1:26" ht="18.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="L13" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="M13" s="10"/>
-      <c r="N13" s="10"/>
-      <c r="O13" s="10"/>
-      <c r="P13" s="11"/>
-    </row>
-    <row r="20" spans="6:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="F20" t="s">
-        <v>36</v>
+    <row r="1" spans="2:28" ht="25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="K1" s="34" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" spans="2:28" ht="25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B4" s="38"/>
+      <c r="C4" s="38"/>
+      <c r="D4" s="38"/>
+      <c r="E4" s="38"/>
+      <c r="F4" s="69"/>
+      <c r="G4" s="38"/>
+      <c r="H4" s="38"/>
+      <c r="I4" s="38"/>
+      <c r="J4" s="38"/>
+      <c r="K4" s="38"/>
+      <c r="L4" s="38"/>
+      <c r="N4" s="38"/>
+      <c r="O4" s="38"/>
+      <c r="P4" s="38"/>
+      <c r="Q4" s="38"/>
+      <c r="R4" s="38"/>
+      <c r="S4" s="38"/>
+      <c r="T4" s="38"/>
+      <c r="U4" s="38"/>
+      <c r="V4" s="38"/>
+      <c r="W4" s="38"/>
+      <c r="X4" s="38"/>
+      <c r="Y4" s="38"/>
+      <c r="Z4" s="38"/>
+      <c r="AA4" s="38"/>
+      <c r="AB4" s="38"/>
+    </row>
+    <row r="5" spans="2:28" ht="25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B5" s="38"/>
+      <c r="C5" s="38"/>
+      <c r="D5" s="38"/>
+      <c r="E5" s="38"/>
+      <c r="F5" s="38"/>
+      <c r="G5" s="38"/>
+      <c r="H5" s="38"/>
+      <c r="I5" s="38"/>
+      <c r="J5" s="38"/>
+      <c r="K5" s="38"/>
+      <c r="L5" s="38"/>
+      <c r="M5" s="38"/>
+      <c r="N5" s="38"/>
+      <c r="O5" s="38"/>
+      <c r="P5" s="38"/>
+      <c r="Q5" s="38"/>
+      <c r="R5" s="38"/>
+      <c r="S5" s="38"/>
+      <c r="T5" s="38"/>
+      <c r="U5" s="38"/>
+      <c r="V5" s="38"/>
+      <c r="W5" s="38"/>
+      <c r="X5" s="38"/>
+      <c r="Y5" s="38"/>
+      <c r="Z5" s="38"/>
+      <c r="AA5" s="38"/>
+      <c r="AB5" s="38"/>
+    </row>
+    <row r="6" spans="2:28" ht="25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B6" s="38"/>
+      <c r="C6" s="38"/>
+      <c r="D6" s="38"/>
+      <c r="E6" s="38"/>
+      <c r="F6" s="38"/>
+      <c r="G6" s="38"/>
+      <c r="H6" s="38"/>
+      <c r="I6" s="38"/>
+      <c r="J6" s="38"/>
+      <c r="K6" s="38"/>
+      <c r="L6" s="38"/>
+      <c r="M6" s="38"/>
+      <c r="N6" s="38"/>
+      <c r="O6" s="38"/>
+      <c r="P6" s="38"/>
+      <c r="Q6" s="38"/>
+      <c r="R6" s="38"/>
+      <c r="S6" s="38"/>
+      <c r="T6" s="38"/>
+      <c r="U6" s="38"/>
+      <c r="V6" s="38"/>
+      <c r="W6" s="38"/>
+      <c r="X6" s="38"/>
+      <c r="Y6" s="38"/>
+      <c r="Z6" s="38"/>
+      <c r="AA6" s="38"/>
+      <c r="AB6" s="38"/>
+    </row>
+    <row r="7" spans="2:28" ht="25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B7" s="38"/>
+      <c r="C7" s="38"/>
+      <c r="D7" s="38"/>
+      <c r="E7" s="38"/>
+      <c r="F7" s="38"/>
+      <c r="G7" s="38"/>
+      <c r="H7" s="38"/>
+      <c r="I7" s="38"/>
+      <c r="J7" s="38"/>
+      <c r="K7" s="38"/>
+      <c r="L7" s="38"/>
+      <c r="M7" s="38"/>
+      <c r="N7" s="38"/>
+      <c r="O7" s="38"/>
+      <c r="P7" s="38"/>
+      <c r="Q7" s="38"/>
+      <c r="R7" s="38"/>
+      <c r="S7" s="38"/>
+      <c r="T7" s="38"/>
+      <c r="U7" s="38"/>
+      <c r="V7" s="38"/>
+      <c r="W7" s="38"/>
+      <c r="X7" s="38"/>
+      <c r="Y7" s="38"/>
+      <c r="Z7" s="38"/>
+      <c r="AA7" s="38"/>
+      <c r="AB7" s="38"/>
+    </row>
+    <row r="8" spans="2:28" ht="25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B8" s="38"/>
+      <c r="C8" s="38"/>
+      <c r="D8" s="38"/>
+      <c r="E8" s="38"/>
+      <c r="F8" s="38"/>
+      <c r="G8" s="38"/>
+      <c r="H8" s="38"/>
+      <c r="I8" s="38"/>
+      <c r="J8" s="38"/>
+      <c r="K8" s="38"/>
+      <c r="L8" s="38"/>
+      <c r="M8" s="38"/>
+      <c r="N8" s="38"/>
+      <c r="O8" s="38"/>
+      <c r="P8" s="38"/>
+      <c r="Q8" s="38"/>
+      <c r="R8" s="38"/>
+      <c r="S8" s="38"/>
+      <c r="T8" s="38"/>
+      <c r="U8" s="38"/>
+      <c r="V8" s="38"/>
+      <c r="W8" s="38"/>
+      <c r="X8" s="38"/>
+      <c r="Y8" s="38"/>
+      <c r="Z8" s="38"/>
+      <c r="AA8" s="38"/>
+      <c r="AB8" s="38"/>
+    </row>
+    <row r="9" spans="2:28" ht="25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B9" s="38"/>
+      <c r="C9" s="38"/>
+      <c r="D9" s="38"/>
+      <c r="E9" s="38"/>
+      <c r="F9" s="38"/>
+      <c r="G9" s="38"/>
+      <c r="H9" s="38"/>
+      <c r="I9" s="38"/>
+      <c r="J9" s="38"/>
+      <c r="K9" s="38"/>
+      <c r="L9" s="38"/>
+      <c r="M9" s="38"/>
+      <c r="N9" s="38"/>
+      <c r="O9" s="38"/>
+      <c r="P9" s="38"/>
+      <c r="Q9" s="38"/>
+      <c r="R9" s="38"/>
+      <c r="S9" s="38"/>
+      <c r="T9" s="38"/>
+      <c r="U9" s="38"/>
+      <c r="V9" s="38"/>
+      <c r="W9" s="38"/>
+      <c r="X9" s="38"/>
+      <c r="Y9" s="38"/>
+      <c r="Z9" s="38"/>
+      <c r="AA9" s="38"/>
+      <c r="AB9" s="38"/>
+    </row>
+    <row r="10" spans="2:28" ht="25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B10" s="38"/>
+      <c r="C10" s="38"/>
+      <c r="D10" s="38"/>
+      <c r="E10" s="38"/>
+      <c r="F10" s="38"/>
+      <c r="G10" s="38"/>
+      <c r="H10" s="38"/>
+      <c r="I10" s="38"/>
+      <c r="J10" s="38"/>
+      <c r="K10" s="38"/>
+      <c r="L10" s="38"/>
+      <c r="M10" s="38"/>
+      <c r="N10" s="38"/>
+      <c r="O10" s="38"/>
+      <c r="P10" s="38"/>
+      <c r="Q10" s="38"/>
+      <c r="R10" s="38"/>
+      <c r="S10" s="38"/>
+      <c r="T10" s="38"/>
+      <c r="U10" s="38"/>
+      <c r="V10" s="38"/>
+      <c r="W10" s="38"/>
+      <c r="X10" s="38"/>
+      <c r="Y10" s="38"/>
+      <c r="Z10" s="38"/>
+      <c r="AA10" s="38"/>
+      <c r="AB10" s="38"/>
+    </row>
+    <row r="11" spans="2:28" ht="25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B11" s="38"/>
+      <c r="C11" s="38"/>
+      <c r="D11" s="38"/>
+      <c r="E11" s="38"/>
+      <c r="F11" s="38"/>
+      <c r="G11" s="38"/>
+      <c r="H11" s="38"/>
+      <c r="I11" s="38"/>
+      <c r="J11" s="38"/>
+      <c r="K11" s="38"/>
+      <c r="L11" s="38"/>
+      <c r="M11" s="38"/>
+      <c r="N11" s="38"/>
+      <c r="O11" s="38"/>
+      <c r="P11" s="38"/>
+      <c r="Q11" s="38"/>
+      <c r="R11" s="38"/>
+      <c r="S11" s="38"/>
+      <c r="T11" s="38"/>
+      <c r="U11" s="38"/>
+      <c r="V11" s="38"/>
+      <c r="W11" s="38"/>
+      <c r="X11" s="38"/>
+      <c r="Y11" s="38"/>
+      <c r="Z11" s="38"/>
+      <c r="AA11" s="38"/>
+      <c r="AB11" s="38"/>
+    </row>
+    <row r="12" spans="2:28" ht="25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B12" s="38"/>
+      <c r="C12" s="38"/>
+      <c r="D12" s="38"/>
+      <c r="E12" s="38"/>
+      <c r="F12" s="38"/>
+      <c r="G12" s="38"/>
+      <c r="H12" s="38"/>
+      <c r="I12" s="38"/>
+      <c r="J12" s="38"/>
+      <c r="K12" s="38"/>
+      <c r="L12" s="38"/>
+      <c r="M12" s="38"/>
+      <c r="N12" s="38"/>
+      <c r="O12" s="38"/>
+      <c r="P12" s="38"/>
+      <c r="Q12" s="38"/>
+      <c r="R12" s="38"/>
+      <c r="S12" s="38"/>
+      <c r="T12" s="38"/>
+      <c r="U12" s="38"/>
+      <c r="V12" s="38"/>
+      <c r="W12" s="38"/>
+      <c r="X12" s="38"/>
+      <c r="Y12" s="38"/>
+      <c r="Z12" s="38"/>
+      <c r="AA12" s="38"/>
+      <c r="AB12" s="38"/>
+    </row>
+    <row r="13" spans="2:28" ht="25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B13" s="38"/>
+      <c r="C13" s="38"/>
+      <c r="D13" s="38"/>
+      <c r="E13" s="38"/>
+      <c r="F13" s="38"/>
+      <c r="G13" s="38"/>
+      <c r="H13" s="38"/>
+      <c r="I13" s="38"/>
+      <c r="J13" s="38"/>
+      <c r="K13" s="38"/>
+      <c r="L13" s="38"/>
+      <c r="M13" s="38"/>
+      <c r="N13" s="38"/>
+      <c r="O13" s="38"/>
+      <c r="P13" s="38"/>
+      <c r="Q13" s="38"/>
+      <c r="R13" s="38"/>
+      <c r="S13" s="38"/>
+      <c r="T13" s="38"/>
+      <c r="U13" s="38"/>
+      <c r="V13" s="38"/>
+      <c r="W13" s="38"/>
+      <c r="X13" s="38"/>
+      <c r="Y13" s="38"/>
+      <c r="Z13" s="38"/>
+      <c r="AA13" s="38"/>
+      <c r="AB13" s="38"/>
+    </row>
+    <row r="14" spans="2:28" ht="25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B14" s="38"/>
+      <c r="C14" s="38"/>
+      <c r="D14" s="38"/>
+      <c r="E14" s="38"/>
+      <c r="F14" s="38"/>
+      <c r="G14" s="38"/>
+      <c r="H14" s="38"/>
+      <c r="I14" s="38"/>
+      <c r="J14" s="38"/>
+      <c r="K14" s="38"/>
+      <c r="L14" s="38"/>
+      <c r="M14" s="38"/>
+      <c r="N14" s="38"/>
+      <c r="O14" s="38"/>
+      <c r="P14" s="38"/>
+      <c r="Q14" s="38"/>
+      <c r="R14" s="38"/>
+      <c r="S14" s="38"/>
+      <c r="T14" s="38"/>
+      <c r="U14" s="38"/>
+      <c r="V14" s="38"/>
+      <c r="W14" s="38"/>
+      <c r="X14" s="38"/>
+      <c r="Y14" s="38"/>
+      <c r="Z14" s="38"/>
+      <c r="AA14" s="38"/>
+      <c r="AB14" s="38"/>
+    </row>
+    <row r="16" spans="2:28" ht="25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="K16" s="34" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2"/>
+  <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
   <headerFooter>
@@ -6285,956 +9202,961 @@
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="5.83203125" customWidth="1"/>
-    <col min="2" max="2" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="13.6640625" customWidth="1"/>
     <col min="5" max="5" width="9.83203125" customWidth="1"/>
-    <col min="6" max="25" width="5.58203125" customWidth="1"/>
+    <col min="6" max="17" width="6.58203125" customWidth="1"/>
+    <col min="18" max="25" width="5.58203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="18.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="F1" t="s">
-        <v>101</v>
-      </c>
-      <c r="K1" s="46" t="s">
-        <v>102</v>
+    <row r="1" spans="1:17" ht="20.5" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="F1" s="36" t="s">
+        <v>85</v>
+      </c>
+      <c r="G1" s="50"/>
+      <c r="H1" s="50"/>
+      <c r="I1" s="50"/>
+      <c r="J1" s="50"/>
+      <c r="K1" s="50" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="2" spans="1:17" ht="18.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="F2" s="65"/>
-      <c r="G2" s="66"/>
-      <c r="H2" s="66"/>
-      <c r="I2" s="66"/>
-      <c r="J2" s="66"/>
-      <c r="K2" s="66"/>
-      <c r="L2" s="66"/>
-      <c r="M2" s="66"/>
-      <c r="N2" s="66"/>
-      <c r="O2" s="66"/>
-      <c r="P2" s="66"/>
-      <c r="Q2" s="67"/>
-    </row>
-    <row r="3" spans="1:17" ht="32" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B3" s="24" t="s">
+      <c r="F2" s="28"/>
+      <c r="G2" s="29"/>
+      <c r="H2" s="29"/>
+      <c r="I2" s="29"/>
+      <c r="J2" s="29"/>
+      <c r="K2" s="29"/>
+      <c r="L2" s="29"/>
+      <c r="M2" s="29"/>
+      <c r="N2" s="29"/>
+      <c r="O2" s="29"/>
+      <c r="P2" s="29"/>
+      <c r="Q2" s="30"/>
+    </row>
+    <row r="3" spans="1:17" ht="45.5" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="B3" s="45" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" s="47" t="s">
+        <v>113</v>
+      </c>
+      <c r="D3" s="47" t="s">
+        <v>112</v>
+      </c>
+      <c r="E3" s="70" t="s">
+        <v>34</v>
+      </c>
+      <c r="F3" s="71" t="s">
+        <v>35</v>
+      </c>
+      <c r="G3" s="71" t="s">
+        <v>36</v>
+      </c>
+      <c r="H3" s="71" t="s">
+        <v>37</v>
+      </c>
+      <c r="I3" s="71" t="s">
+        <v>38</v>
+      </c>
+      <c r="J3" s="71" t="s">
+        <v>39</v>
+      </c>
+      <c r="K3" s="71" t="s">
+        <v>40</v>
+      </c>
+      <c r="L3" s="71" t="s">
+        <v>41</v>
+      </c>
+      <c r="M3" s="71" t="s">
+        <v>42</v>
+      </c>
+      <c r="N3" s="71" t="s">
+        <v>43</v>
+      </c>
+      <c r="O3" s="71" t="s">
+        <v>44</v>
+      </c>
+      <c r="P3" s="71" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q3" s="72" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" s="73">
+        <v>1</v>
+      </c>
+      <c r="B4" s="74" t="s">
         <v>47</v>
       </c>
-      <c r="C3" s="26" t="s">
+      <c r="C4" s="74"/>
+      <c r="D4" s="74"/>
+      <c r="E4" s="75"/>
+      <c r="F4" s="76"/>
+      <c r="G4" s="76"/>
+      <c r="H4" s="76"/>
+      <c r="I4" s="76"/>
+      <c r="J4" s="76"/>
+      <c r="K4" s="76"/>
+      <c r="L4" s="76"/>
+      <c r="M4" s="76"/>
+      <c r="N4" s="76"/>
+      <c r="O4" s="76"/>
+      <c r="P4" s="76"/>
+      <c r="Q4" s="77"/>
+    </row>
+    <row r="5" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" s="78">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B5" s="79"/>
+      <c r="C5" s="79" t="s">
+        <v>78</v>
+      </c>
+      <c r="D5" s="79"/>
+      <c r="E5" s="80" t="s">
+        <v>87</v>
+      </c>
+      <c r="F5" s="79"/>
+      <c r="G5" s="79"/>
+      <c r="H5" s="79"/>
+      <c r="I5" s="79"/>
+      <c r="J5" s="79"/>
+      <c r="K5" s="79"/>
+      <c r="L5" s="79"/>
+      <c r="M5" s="79"/>
+      <c r="N5" s="79"/>
+      <c r="O5" s="79"/>
+      <c r="P5" s="79"/>
+      <c r="Q5" s="81"/>
+    </row>
+    <row r="6" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" s="78" t="s">
+        <v>48</v>
+      </c>
+      <c r="B6" s="79"/>
+      <c r="C6" s="79"/>
+      <c r="D6" s="79"/>
+      <c r="E6" s="80" t="s">
+        <v>88</v>
+      </c>
+      <c r="F6" s="79"/>
+      <c r="G6" s="79"/>
+      <c r="H6" s="79"/>
+      <c r="I6" s="79"/>
+      <c r="J6" s="79"/>
+      <c r="K6" s="79"/>
+      <c r="L6" s="79"/>
+      <c r="M6" s="79"/>
+      <c r="N6" s="79"/>
+      <c r="O6" s="79"/>
+      <c r="P6" s="79"/>
+      <c r="Q6" s="81"/>
+    </row>
+    <row r="7" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" s="78" t="s">
+        <v>49</v>
+      </c>
+      <c r="B7" s="79"/>
+      <c r="C7" s="79"/>
+      <c r="D7" s="79"/>
+      <c r="E7" s="80" t="s">
+        <v>89</v>
+      </c>
+      <c r="F7" s="79"/>
+      <c r="G7" s="79"/>
+      <c r="H7" s="79"/>
+      <c r="I7" s="79"/>
+      <c r="J7" s="79"/>
+      <c r="K7" s="79"/>
+      <c r="L7" s="79"/>
+      <c r="M7" s="79"/>
+      <c r="N7" s="79"/>
+      <c r="O7" s="79"/>
+      <c r="P7" s="79"/>
+      <c r="Q7" s="81"/>
+    </row>
+    <row r="8" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" s="78">
+        <v>1.2</v>
+      </c>
+      <c r="B8" s="79"/>
+      <c r="C8" s="79" t="s">
+        <v>79</v>
+      </c>
+      <c r="D8" s="79"/>
+      <c r="E8" s="80"/>
+      <c r="F8" s="79"/>
+      <c r="G8" s="79"/>
+      <c r="H8" s="79"/>
+      <c r="I8" s="79"/>
+      <c r="J8" s="79"/>
+      <c r="K8" s="79"/>
+      <c r="L8" s="79"/>
+      <c r="M8" s="79"/>
+      <c r="N8" s="79"/>
+      <c r="O8" s="79"/>
+      <c r="P8" s="79"/>
+      <c r="Q8" s="81"/>
+    </row>
+    <row r="9" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" s="78" t="s">
+        <v>50</v>
+      </c>
+      <c r="B9" s="79"/>
+      <c r="C9" s="79"/>
+      <c r="D9" s="79"/>
+      <c r="E9" s="80"/>
+      <c r="F9" s="79"/>
+      <c r="G9" s="79"/>
+      <c r="H9" s="79"/>
+      <c r="I9" s="79"/>
+      <c r="J9" s="79"/>
+      <c r="K9" s="79"/>
+      <c r="L9" s="79"/>
+      <c r="M9" s="79"/>
+      <c r="N9" s="79"/>
+      <c r="O9" s="79"/>
+      <c r="P9" s="79"/>
+      <c r="Q9" s="81"/>
+    </row>
+    <row r="10" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" s="78" t="s">
+        <v>51</v>
+      </c>
+      <c r="B10" s="79"/>
+      <c r="C10" s="79"/>
+      <c r="D10" s="79"/>
+      <c r="E10" s="80"/>
+      <c r="F10" s="79"/>
+      <c r="G10" s="79"/>
+      <c r="H10" s="79"/>
+      <c r="I10" s="79"/>
+      <c r="J10" s="79"/>
+      <c r="K10" s="79"/>
+      <c r="L10" s="79"/>
+      <c r="M10" s="79"/>
+      <c r="N10" s="79"/>
+      <c r="O10" s="79"/>
+      <c r="P10" s="79"/>
+      <c r="Q10" s="81"/>
+    </row>
+    <row r="11" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" s="78" t="s">
+        <v>52</v>
+      </c>
+      <c r="B11" s="79"/>
+      <c r="C11" s="79"/>
+      <c r="D11" s="79"/>
+      <c r="E11" s="80"/>
+      <c r="F11" s="79"/>
+      <c r="G11" s="79"/>
+      <c r="H11" s="79"/>
+      <c r="I11" s="79"/>
+      <c r="J11" s="79"/>
+      <c r="K11" s="79"/>
+      <c r="L11" s="79"/>
+      <c r="M11" s="79"/>
+      <c r="N11" s="79"/>
+      <c r="O11" s="79"/>
+      <c r="P11" s="79"/>
+      <c r="Q11" s="81"/>
+    </row>
+    <row r="12" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" s="78">
+        <v>2</v>
+      </c>
+      <c r="B12" s="82" t="s">
+        <v>53</v>
+      </c>
+      <c r="C12" s="82"/>
+      <c r="D12" s="82"/>
+      <c r="E12" s="80"/>
+      <c r="F12" s="79"/>
+      <c r="G12" s="79"/>
+      <c r="H12" s="79"/>
+      <c r="I12" s="79"/>
+      <c r="J12" s="79"/>
+      <c r="K12" s="79"/>
+      <c r="L12" s="79"/>
+      <c r="M12" s="79"/>
+      <c r="N12" s="79"/>
+      <c r="O12" s="79"/>
+      <c r="P12" s="79"/>
+      <c r="Q12" s="81"/>
+    </row>
+    <row r="13" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" s="78">
+        <v>2.1</v>
+      </c>
+      <c r="B13" s="79"/>
+      <c r="C13" s="79" t="s">
+        <v>80</v>
+      </c>
+      <c r="D13" s="79"/>
+      <c r="E13" s="80"/>
+      <c r="F13" s="79"/>
+      <c r="G13" s="79"/>
+      <c r="H13" s="79"/>
+      <c r="I13" s="79"/>
+      <c r="J13" s="79"/>
+      <c r="K13" s="79"/>
+      <c r="L13" s="79"/>
+      <c r="M13" s="79"/>
+      <c r="N13" s="79"/>
+      <c r="O13" s="79"/>
+      <c r="P13" s="79"/>
+      <c r="Q13" s="81"/>
+    </row>
+    <row r="14" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" s="78" t="s">
+        <v>54</v>
+      </c>
+      <c r="B14" s="79"/>
+      <c r="C14" s="79"/>
+      <c r="D14" s="79"/>
+      <c r="E14" s="80"/>
+      <c r="F14" s="79"/>
+      <c r="G14" s="79"/>
+      <c r="H14" s="79"/>
+      <c r="I14" s="79"/>
+      <c r="J14" s="79"/>
+      <c r="K14" s="79"/>
+      <c r="L14" s="79"/>
+      <c r="M14" s="79"/>
+      <c r="N14" s="79"/>
+      <c r="O14" s="79"/>
+      <c r="P14" s="79"/>
+      <c r="Q14" s="81"/>
+    </row>
+    <row r="15" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" s="78" t="s">
+        <v>55</v>
+      </c>
+      <c r="B15" s="79"/>
+      <c r="C15" s="79"/>
+      <c r="D15" s="79"/>
+      <c r="E15" s="80"/>
+      <c r="F15" s="79"/>
+      <c r="G15" s="79"/>
+      <c r="H15" s="79"/>
+      <c r="I15" s="79"/>
+      <c r="J15" s="79"/>
+      <c r="K15" s="79"/>
+      <c r="L15" s="79"/>
+      <c r="M15" s="79"/>
+      <c r="N15" s="79"/>
+      <c r="O15" s="79"/>
+      <c r="P15" s="79"/>
+      <c r="Q15" s="81"/>
+    </row>
+    <row r="16" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" s="78" t="s">
+        <v>56</v>
+      </c>
+      <c r="B16" s="79"/>
+      <c r="C16" s="79"/>
+      <c r="D16" s="79"/>
+      <c r="E16" s="80"/>
+      <c r="F16" s="79"/>
+      <c r="G16" s="79"/>
+      <c r="H16" s="79"/>
+      <c r="I16" s="79"/>
+      <c r="J16" s="79"/>
+      <c r="K16" s="79"/>
+      <c r="L16" s="79"/>
+      <c r="M16" s="79"/>
+      <c r="N16" s="79"/>
+      <c r="O16" s="79"/>
+      <c r="P16" s="79"/>
+      <c r="Q16" s="81"/>
+    </row>
+    <row r="17" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" s="78" t="s">
         <v>57</v>
       </c>
-      <c r="D3" s="26" t="s">
-        <v>56</v>
-      </c>
-      <c r="E3" s="57" t="s">
-        <v>48</v>
-      </c>
-      <c r="F3" s="58" t="s">
-        <v>49</v>
-      </c>
-      <c r="G3" s="58" t="s">
-        <v>50</v>
-      </c>
-      <c r="H3" s="58" t="s">
-        <v>51</v>
-      </c>
-      <c r="I3" s="58" t="s">
-        <v>52</v>
-      </c>
-      <c r="J3" s="58" t="s">
-        <v>53</v>
-      </c>
-      <c r="K3" s="58" t="s">
-        <v>54</v>
-      </c>
-      <c r="L3" s="58" t="s">
-        <v>55</v>
-      </c>
-      <c r="M3" s="58" t="s">
+      <c r="B17" s="79"/>
+      <c r="C17" s="79"/>
+      <c r="D17" s="79"/>
+      <c r="E17" s="80"/>
+      <c r="F17" s="79"/>
+      <c r="G17" s="79"/>
+      <c r="H17" s="79"/>
+      <c r="I17" s="79"/>
+      <c r="J17" s="79"/>
+      <c r="K17" s="79"/>
+      <c r="L17" s="79"/>
+      <c r="M17" s="79"/>
+      <c r="N17" s="79"/>
+      <c r="O17" s="79"/>
+      <c r="P17" s="79"/>
+      <c r="Q17" s="81"/>
+    </row>
+    <row r="18" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18" s="78">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B18" s="79"/>
+      <c r="C18" s="79" t="s">
+        <v>81</v>
+      </c>
+      <c r="D18" s="79"/>
+      <c r="E18" s="80"/>
+      <c r="F18" s="79"/>
+      <c r="G18" s="79"/>
+      <c r="H18" s="79"/>
+      <c r="I18" s="79"/>
+      <c r="J18" s="79"/>
+      <c r="K18" s="79"/>
+      <c r="L18" s="79"/>
+      <c r="M18" s="79"/>
+      <c r="N18" s="79"/>
+      <c r="O18" s="79"/>
+      <c r="P18" s="79"/>
+      <c r="Q18" s="81"/>
+    </row>
+    <row r="19" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A19" s="78" t="s">
         <v>58</v>
       </c>
-      <c r="N3" s="58" t="s">
+      <c r="B19" s="79"/>
+      <c r="C19" s="79"/>
+      <c r="D19" s="79"/>
+      <c r="E19" s="80"/>
+      <c r="F19" s="79"/>
+      <c r="G19" s="79"/>
+      <c r="H19" s="79"/>
+      <c r="I19" s="79"/>
+      <c r="J19" s="79"/>
+      <c r="K19" s="79"/>
+      <c r="L19" s="79"/>
+      <c r="M19" s="79"/>
+      <c r="N19" s="79"/>
+      <c r="O19" s="79"/>
+      <c r="P19" s="79"/>
+      <c r="Q19" s="81"/>
+    </row>
+    <row r="20" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A20" s="78" t="s">
         <v>59</v>
       </c>
-      <c r="O3" s="58" t="s">
+      <c r="B20" s="79"/>
+      <c r="C20" s="79"/>
+      <c r="D20" s="79"/>
+      <c r="E20" s="80"/>
+      <c r="F20" s="79"/>
+      <c r="G20" s="79"/>
+      <c r="H20" s="79"/>
+      <c r="I20" s="79"/>
+      <c r="J20" s="79"/>
+      <c r="K20" s="79"/>
+      <c r="L20" s="79"/>
+      <c r="M20" s="79"/>
+      <c r="N20" s="79"/>
+      <c r="O20" s="79"/>
+      <c r="P20" s="79"/>
+      <c r="Q20" s="81"/>
+    </row>
+    <row r="21" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A21" s="78" t="s">
         <v>60</v>
       </c>
-      <c r="P3" s="58" t="s">
+      <c r="B21" s="79"/>
+      <c r="C21" s="79"/>
+      <c r="D21" s="79"/>
+      <c r="E21" s="80"/>
+      <c r="F21" s="79"/>
+      <c r="G21" s="79"/>
+      <c r="H21" s="79"/>
+      <c r="I21" s="79"/>
+      <c r="J21" s="79"/>
+      <c r="K21" s="79"/>
+      <c r="L21" s="79"/>
+      <c r="M21" s="79"/>
+      <c r="N21" s="79"/>
+      <c r="O21" s="79"/>
+      <c r="P21" s="79"/>
+      <c r="Q21" s="81"/>
+    </row>
+    <row r="22" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A22" s="78" t="s">
         <v>61</v>
       </c>
-      <c r="Q3" s="59" t="s">
+      <c r="B22" s="79"/>
+      <c r="C22" s="79"/>
+      <c r="D22" s="79"/>
+      <c r="E22" s="80"/>
+      <c r="F22" s="79"/>
+      <c r="G22" s="79"/>
+      <c r="H22" s="79"/>
+      <c r="I22" s="79"/>
+      <c r="J22" s="79"/>
+      <c r="K22" s="79"/>
+      <c r="L22" s="79"/>
+      <c r="M22" s="79"/>
+      <c r="N22" s="79"/>
+      <c r="O22" s="79"/>
+      <c r="P22" s="79"/>
+      <c r="Q22" s="81"/>
+    </row>
+    <row r="23" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A23" s="78">
+        <v>3.1</v>
+      </c>
+      <c r="B23" s="79"/>
+      <c r="C23" s="79" t="s">
+        <v>82</v>
+      </c>
+      <c r="D23" s="79"/>
+      <c r="E23" s="80"/>
+      <c r="F23" s="79"/>
+      <c r="G23" s="79"/>
+      <c r="H23" s="79"/>
+      <c r="I23" s="79"/>
+      <c r="J23" s="79"/>
+      <c r="K23" s="79"/>
+      <c r="L23" s="79"/>
+      <c r="M23" s="79"/>
+      <c r="N23" s="79"/>
+      <c r="O23" s="79"/>
+      <c r="P23" s="79"/>
+      <c r="Q23" s="81"/>
+    </row>
+    <row r="24" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A24" s="78" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="4" spans="1:17" ht="10" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="50">
-        <v>1</v>
-      </c>
-      <c r="B4" s="60" t="s">
+      <c r="B24" s="79"/>
+      <c r="C24" s="79"/>
+      <c r="D24" s="79"/>
+      <c r="E24" s="80"/>
+      <c r="F24" s="79"/>
+      <c r="G24" s="79"/>
+      <c r="H24" s="79"/>
+      <c r="I24" s="79"/>
+      <c r="J24" s="79"/>
+      <c r="K24" s="79"/>
+      <c r="L24" s="79"/>
+      <c r="M24" s="79"/>
+      <c r="N24" s="79"/>
+      <c r="O24" s="79"/>
+      <c r="P24" s="79"/>
+      <c r="Q24" s="81"/>
+    </row>
+    <row r="25" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A25" s="78" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="60"/>
-      <c r="D4" s="60"/>
-      <c r="E4" s="52"/>
-      <c r="F4" s="51"/>
-      <c r="G4" s="51"/>
-      <c r="H4" s="51"/>
-      <c r="I4" s="51"/>
-      <c r="J4" s="51"/>
-      <c r="K4" s="51"/>
-      <c r="L4" s="51"/>
-      <c r="M4" s="51"/>
-      <c r="N4" s="51"/>
-      <c r="O4" s="51"/>
-      <c r="P4" s="51"/>
-      <c r="Q4" s="53"/>
-    </row>
-    <row r="5" spans="1:17" ht="10" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="54">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="B5" s="15"/>
-      <c r="C5" s="15" t="s">
-        <v>94</v>
-      </c>
-      <c r="D5" s="15"/>
-      <c r="E5" s="49" t="s">
-        <v>103</v>
-      </c>
-      <c r="F5" s="15"/>
-      <c r="G5" s="15"/>
-      <c r="H5" s="15"/>
-      <c r="I5" s="15"/>
-      <c r="J5" s="15"/>
-      <c r="K5" s="15"/>
-      <c r="L5" s="15"/>
-      <c r="M5" s="15"/>
-      <c r="N5" s="15"/>
-      <c r="O5" s="15"/>
-      <c r="P5" s="15"/>
-      <c r="Q5" s="17"/>
-    </row>
-    <row r="6" spans="1:17" ht="10" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="54" t="s">
+      <c r="B25" s="79"/>
+      <c r="C25" s="79"/>
+      <c r="D25" s="79"/>
+      <c r="E25" s="80"/>
+      <c r="F25" s="79"/>
+      <c r="G25" s="79"/>
+      <c r="H25" s="79"/>
+      <c r="I25" s="79"/>
+      <c r="J25" s="79"/>
+      <c r="K25" s="79"/>
+      <c r="L25" s="79"/>
+      <c r="M25" s="79"/>
+      <c r="N25" s="79"/>
+      <c r="O25" s="79"/>
+      <c r="P25" s="79"/>
+      <c r="Q25" s="81"/>
+    </row>
+    <row r="26" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A26" s="78" t="s">
         <v>64</v>
       </c>
-      <c r="B6" s="15"/>
-      <c r="C6" s="15"/>
-      <c r="D6" s="15"/>
-      <c r="E6" s="49" t="s">
-        <v>104</v>
-      </c>
-      <c r="F6" s="15"/>
-      <c r="G6" s="15"/>
-      <c r="H6" s="15"/>
-      <c r="I6" s="15"/>
-      <c r="J6" s="15"/>
-      <c r="K6" s="15"/>
-      <c r="L6" s="15"/>
-      <c r="M6" s="15"/>
-      <c r="N6" s="15"/>
-      <c r="O6" s="15"/>
-      <c r="P6" s="15"/>
-      <c r="Q6" s="17"/>
-    </row>
-    <row r="7" spans="1:17" ht="10" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="54" t="s">
+      <c r="B26" s="79"/>
+      <c r="C26" s="79"/>
+      <c r="D26" s="79"/>
+      <c r="E26" s="80"/>
+      <c r="F26" s="79"/>
+      <c r="G26" s="79"/>
+      <c r="H26" s="79"/>
+      <c r="I26" s="79"/>
+      <c r="J26" s="79"/>
+      <c r="K26" s="79"/>
+      <c r="L26" s="79"/>
+      <c r="M26" s="79"/>
+      <c r="N26" s="79"/>
+      <c r="O26" s="79"/>
+      <c r="P26" s="79"/>
+      <c r="Q26" s="81"/>
+    </row>
+    <row r="27" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A27" s="78" t="s">
         <v>65</v>
       </c>
-      <c r="B7" s="15"/>
-      <c r="C7" s="15"/>
-      <c r="D7" s="15"/>
-      <c r="E7" s="49" t="s">
-        <v>105</v>
-      </c>
-      <c r="F7" s="15"/>
-      <c r="G7" s="15"/>
-      <c r="H7" s="15"/>
-      <c r="I7" s="15"/>
-      <c r="J7" s="15"/>
-      <c r="K7" s="15"/>
-      <c r="L7" s="15"/>
-      <c r="M7" s="15"/>
-      <c r="N7" s="15"/>
-      <c r="O7" s="15"/>
-      <c r="P7" s="15"/>
-      <c r="Q7" s="17"/>
-    </row>
-    <row r="8" spans="1:17" ht="10" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="54">
-        <v>1.2</v>
-      </c>
-      <c r="B8" s="15"/>
-      <c r="C8" s="15" t="s">
-        <v>95</v>
-      </c>
-      <c r="D8" s="15"/>
-      <c r="E8" s="49"/>
-      <c r="F8" s="15"/>
-      <c r="G8" s="15"/>
-      <c r="H8" s="15"/>
-      <c r="I8" s="15"/>
-      <c r="J8" s="15"/>
-      <c r="K8" s="15"/>
-      <c r="L8" s="15"/>
-      <c r="M8" s="15"/>
-      <c r="N8" s="15"/>
-      <c r="O8" s="15"/>
-      <c r="P8" s="15"/>
-      <c r="Q8" s="17"/>
-    </row>
-    <row r="9" spans="1:17" ht="10" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="54" t="s">
+      <c r="B27" s="79"/>
+      <c r="C27" s="79"/>
+      <c r="D27" s="79"/>
+      <c r="E27" s="80"/>
+      <c r="F27" s="79"/>
+      <c r="G27" s="79"/>
+      <c r="H27" s="79"/>
+      <c r="I27" s="79"/>
+      <c r="J27" s="79"/>
+      <c r="K27" s="79"/>
+      <c r="L27" s="79"/>
+      <c r="M27" s="79"/>
+      <c r="N27" s="79"/>
+      <c r="O27" s="79"/>
+      <c r="P27" s="79"/>
+      <c r="Q27" s="81"/>
+    </row>
+    <row r="28" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A28" s="78">
+        <v>3.2</v>
+      </c>
+      <c r="B28" s="79"/>
+      <c r="C28" s="79" t="s">
+        <v>83</v>
+      </c>
+      <c r="D28" s="79"/>
+      <c r="E28" s="80"/>
+      <c r="F28" s="79"/>
+      <c r="G28" s="79"/>
+      <c r="H28" s="79"/>
+      <c r="I28" s="79"/>
+      <c r="J28" s="79"/>
+      <c r="K28" s="79"/>
+      <c r="L28" s="79"/>
+      <c r="M28" s="79"/>
+      <c r="N28" s="79"/>
+      <c r="O28" s="79"/>
+      <c r="P28" s="79"/>
+      <c r="Q28" s="81"/>
+    </row>
+    <row r="29" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A29" s="78" t="s">
         <v>66</v>
       </c>
-      <c r="B9" s="15"/>
-      <c r="C9" s="15"/>
-      <c r="D9" s="15"/>
-      <c r="E9" s="49"/>
-      <c r="F9" s="15"/>
-      <c r="G9" s="15"/>
-      <c r="H9" s="15"/>
-      <c r="I9" s="15"/>
-      <c r="J9" s="15"/>
-      <c r="K9" s="15"/>
-      <c r="L9" s="15"/>
-      <c r="M9" s="15"/>
-      <c r="N9" s="15"/>
-      <c r="O9" s="15"/>
-      <c r="P9" s="15"/>
-      <c r="Q9" s="17"/>
-    </row>
-    <row r="10" spans="1:17" ht="10" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="54" t="s">
+      <c r="B29" s="79"/>
+      <c r="C29" s="79"/>
+      <c r="D29" s="79"/>
+      <c r="E29" s="80"/>
+      <c r="F29" s="79"/>
+      <c r="G29" s="79"/>
+      <c r="H29" s="79"/>
+      <c r="I29" s="79"/>
+      <c r="J29" s="79"/>
+      <c r="K29" s="79"/>
+      <c r="L29" s="79"/>
+      <c r="M29" s="79"/>
+      <c r="N29" s="79"/>
+      <c r="O29" s="79"/>
+      <c r="P29" s="79"/>
+      <c r="Q29" s="81"/>
+    </row>
+    <row r="30" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A30" s="78" t="s">
         <v>67</v>
       </c>
-      <c r="B10" s="15"/>
-      <c r="C10" s="15"/>
-      <c r="D10" s="15"/>
-      <c r="E10" s="49"/>
-      <c r="F10" s="15"/>
-      <c r="G10" s="15"/>
-      <c r="H10" s="15"/>
-      <c r="I10" s="15"/>
-      <c r="J10" s="15"/>
-      <c r="K10" s="15"/>
-      <c r="L10" s="15"/>
-      <c r="M10" s="15"/>
-      <c r="N10" s="15"/>
-      <c r="O10" s="15"/>
-      <c r="P10" s="15"/>
-      <c r="Q10" s="17"/>
-    </row>
-    <row r="11" spans="1:17" ht="10" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="54" t="s">
+      <c r="B30" s="79"/>
+      <c r="C30" s="79"/>
+      <c r="D30" s="79"/>
+      <c r="E30" s="80"/>
+      <c r="F30" s="79"/>
+      <c r="G30" s="79"/>
+      <c r="H30" s="79"/>
+      <c r="I30" s="79"/>
+      <c r="J30" s="79"/>
+      <c r="K30" s="79"/>
+      <c r="L30" s="79"/>
+      <c r="M30" s="79"/>
+      <c r="N30" s="79"/>
+      <c r="O30" s="79"/>
+      <c r="P30" s="79"/>
+      <c r="Q30" s="81"/>
+    </row>
+    <row r="31" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A31" s="78" t="s">
         <v>68</v>
       </c>
-      <c r="B11" s="15"/>
-      <c r="C11" s="15"/>
-      <c r="D11" s="15"/>
-      <c r="E11" s="49"/>
-      <c r="F11" s="15"/>
-      <c r="G11" s="15"/>
-      <c r="H11" s="15"/>
-      <c r="I11" s="15"/>
-      <c r="J11" s="15"/>
-      <c r="K11" s="15"/>
-      <c r="L11" s="15"/>
-      <c r="M11" s="15"/>
-      <c r="N11" s="15"/>
-      <c r="O11" s="15"/>
-      <c r="P11" s="15"/>
-      <c r="Q11" s="17"/>
-    </row>
-    <row r="12" spans="1:17" ht="10" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" s="54">
-        <v>2</v>
-      </c>
-      <c r="B12" s="61" t="s">
+      <c r="B31" s="79"/>
+      <c r="C31" s="79"/>
+      <c r="D31" s="79"/>
+      <c r="E31" s="80"/>
+      <c r="F31" s="79"/>
+      <c r="G31" s="79"/>
+      <c r="H31" s="79"/>
+      <c r="I31" s="79"/>
+      <c r="J31" s="79"/>
+      <c r="K31" s="79"/>
+      <c r="L31" s="79"/>
+      <c r="M31" s="79"/>
+      <c r="N31" s="79"/>
+      <c r="O31" s="79"/>
+      <c r="P31" s="79"/>
+      <c r="Q31" s="81"/>
+    </row>
+    <row r="32" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A32" s="78">
+        <v>3.3</v>
+      </c>
+      <c r="B32" s="79"/>
+      <c r="C32" s="79" t="s">
+        <v>84</v>
+      </c>
+      <c r="D32" s="79"/>
+      <c r="E32" s="80"/>
+      <c r="F32" s="79"/>
+      <c r="G32" s="79"/>
+      <c r="H32" s="79"/>
+      <c r="I32" s="79"/>
+      <c r="J32" s="79"/>
+      <c r="K32" s="79"/>
+      <c r="L32" s="79"/>
+      <c r="M32" s="79"/>
+      <c r="N32" s="79"/>
+      <c r="O32" s="79"/>
+      <c r="P32" s="79"/>
+      <c r="Q32" s="81"/>
+    </row>
+    <row r="33" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A33" s="78" t="s">
         <v>69</v>
       </c>
-      <c r="C12" s="61"/>
-      <c r="D12" s="61"/>
-      <c r="E12" s="49"/>
-      <c r="F12" s="15"/>
-      <c r="G12" s="15"/>
-      <c r="H12" s="15"/>
-      <c r="I12" s="15"/>
-      <c r="J12" s="15"/>
-      <c r="K12" s="15"/>
-      <c r="L12" s="15"/>
-      <c r="M12" s="15"/>
-      <c r="N12" s="15"/>
-      <c r="O12" s="15"/>
-      <c r="P12" s="15"/>
-      <c r="Q12" s="17"/>
-    </row>
-    <row r="13" spans="1:17" ht="10" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="54">
-        <v>2.1</v>
-      </c>
-      <c r="B13" s="15"/>
-      <c r="C13" s="15" t="s">
-        <v>96</v>
-      </c>
-      <c r="D13" s="15"/>
-      <c r="E13" s="49"/>
-      <c r="F13" s="15"/>
-      <c r="G13" s="15"/>
-      <c r="H13" s="15"/>
-      <c r="I13" s="15"/>
-      <c r="J13" s="15"/>
-      <c r="K13" s="15"/>
-      <c r="L13" s="15"/>
-      <c r="M13" s="15"/>
-      <c r="N13" s="15"/>
-      <c r="O13" s="15"/>
-      <c r="P13" s="15"/>
-      <c r="Q13" s="17"/>
-    </row>
-    <row r="14" spans="1:17" ht="10" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="54" t="s">
+      <c r="B33" s="79"/>
+      <c r="C33" s="79"/>
+      <c r="D33" s="79"/>
+      <c r="E33" s="80"/>
+      <c r="F33" s="79"/>
+      <c r="G33" s="79"/>
+      <c r="H33" s="79"/>
+      <c r="I33" s="79"/>
+      <c r="J33" s="79"/>
+      <c r="K33" s="79"/>
+      <c r="L33" s="79"/>
+      <c r="M33" s="79"/>
+      <c r="N33" s="79"/>
+      <c r="O33" s="79"/>
+      <c r="P33" s="79"/>
+      <c r="Q33" s="81"/>
+    </row>
+    <row r="34" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A34" s="78" t="s">
         <v>70</v>
       </c>
-      <c r="B14" s="15"/>
-      <c r="C14" s="15"/>
-      <c r="D14" s="15"/>
-      <c r="E14" s="49"/>
-      <c r="F14" s="15"/>
-      <c r="G14" s="15"/>
-      <c r="H14" s="15"/>
-      <c r="I14" s="15"/>
-      <c r="J14" s="15"/>
-      <c r="K14" s="15"/>
-      <c r="L14" s="15"/>
-      <c r="M14" s="15"/>
-      <c r="N14" s="15"/>
-      <c r="O14" s="15"/>
-      <c r="P14" s="15"/>
-      <c r="Q14" s="17"/>
-    </row>
-    <row r="15" spans="1:17" ht="10" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="54" t="s">
+      <c r="B34" s="79"/>
+      <c r="C34" s="79"/>
+      <c r="D34" s="79"/>
+      <c r="E34" s="80"/>
+      <c r="F34" s="79"/>
+      <c r="G34" s="79"/>
+      <c r="H34" s="79"/>
+      <c r="I34" s="79"/>
+      <c r="J34" s="79"/>
+      <c r="K34" s="79"/>
+      <c r="L34" s="79"/>
+      <c r="M34" s="79"/>
+      <c r="N34" s="79"/>
+      <c r="O34" s="79"/>
+      <c r="P34" s="79"/>
+      <c r="Q34" s="81"/>
+    </row>
+    <row r="35" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A35" s="78" t="s">
         <v>71</v>
       </c>
-      <c r="B15" s="15"/>
-      <c r="C15" s="15"/>
-      <c r="D15" s="15"/>
-      <c r="E15" s="49"/>
-      <c r="F15" s="15"/>
-      <c r="G15" s="15"/>
-      <c r="H15" s="15"/>
-      <c r="I15" s="15"/>
-      <c r="J15" s="15"/>
-      <c r="K15" s="15"/>
-      <c r="L15" s="15"/>
-      <c r="M15" s="15"/>
-      <c r="N15" s="15"/>
-      <c r="O15" s="15"/>
-      <c r="P15" s="15"/>
-      <c r="Q15" s="17"/>
-    </row>
-    <row r="16" spans="1:17" ht="10" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="54" t="s">
+      <c r="B35" s="79"/>
+      <c r="C35" s="79"/>
+      <c r="D35" s="79"/>
+      <c r="E35" s="80"/>
+      <c r="F35" s="79"/>
+      <c r="G35" s="79"/>
+      <c r="H35" s="79"/>
+      <c r="I35" s="79"/>
+      <c r="J35" s="79"/>
+      <c r="K35" s="79"/>
+      <c r="L35" s="79"/>
+      <c r="M35" s="79"/>
+      <c r="N35" s="79"/>
+      <c r="O35" s="79"/>
+      <c r="P35" s="79"/>
+      <c r="Q35" s="81"/>
+    </row>
+    <row r="36" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A36" s="78">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B36" s="79"/>
+      <c r="C36" s="79"/>
+      <c r="D36" s="79"/>
+      <c r="E36" s="80"/>
+      <c r="F36" s="79"/>
+      <c r="G36" s="79"/>
+      <c r="H36" s="79"/>
+      <c r="I36" s="79"/>
+      <c r="J36" s="79"/>
+      <c r="K36" s="79"/>
+      <c r="L36" s="79"/>
+      <c r="M36" s="79"/>
+      <c r="N36" s="79"/>
+      <c r="O36" s="79"/>
+      <c r="P36" s="79"/>
+      <c r="Q36" s="81"/>
+    </row>
+    <row r="37" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A37" s="78" t="s">
         <v>72</v>
       </c>
-      <c r="B16" s="15"/>
-      <c r="C16" s="15"/>
-      <c r="D16" s="15"/>
-      <c r="E16" s="49"/>
-      <c r="F16" s="15"/>
-      <c r="G16" s="15"/>
-      <c r="H16" s="15"/>
-      <c r="I16" s="15"/>
-      <c r="J16" s="15"/>
-      <c r="K16" s="15"/>
-      <c r="L16" s="15"/>
-      <c r="M16" s="15"/>
-      <c r="N16" s="15"/>
-      <c r="O16" s="15"/>
-      <c r="P16" s="15"/>
-      <c r="Q16" s="17"/>
-    </row>
-    <row r="17" spans="1:17" ht="10" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17" s="54" t="s">
+      <c r="B37" s="79"/>
+      <c r="C37" s="79"/>
+      <c r="D37" s="79"/>
+      <c r="E37" s="80"/>
+      <c r="F37" s="79"/>
+      <c r="G37" s="79"/>
+      <c r="H37" s="79"/>
+      <c r="I37" s="79"/>
+      <c r="J37" s="79"/>
+      <c r="K37" s="79"/>
+      <c r="L37" s="79"/>
+      <c r="M37" s="79"/>
+      <c r="N37" s="79"/>
+      <c r="O37" s="79"/>
+      <c r="P37" s="79"/>
+      <c r="Q37" s="81"/>
+    </row>
+    <row r="38" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A38" s="78" t="s">
         <v>73</v>
       </c>
-      <c r="B17" s="15"/>
-      <c r="C17" s="15"/>
-      <c r="D17" s="15"/>
-      <c r="E17" s="49"/>
-      <c r="F17" s="15"/>
-      <c r="G17" s="15"/>
-      <c r="H17" s="15"/>
-      <c r="I17" s="15"/>
-      <c r="J17" s="15"/>
-      <c r="K17" s="15"/>
-      <c r="L17" s="15"/>
-      <c r="M17" s="15"/>
-      <c r="N17" s="15"/>
-      <c r="O17" s="15"/>
-      <c r="P17" s="15"/>
-      <c r="Q17" s="17"/>
-    </row>
-    <row r="18" spans="1:17" ht="10" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18" s="54">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="B18" s="15"/>
-      <c r="C18" s="15" t="s">
-        <v>97</v>
-      </c>
-      <c r="D18" s="15"/>
-      <c r="E18" s="49"/>
-      <c r="F18" s="15"/>
-      <c r="G18" s="15"/>
-      <c r="H18" s="15"/>
-      <c r="I18" s="15"/>
-      <c r="J18" s="15"/>
-      <c r="K18" s="15"/>
-      <c r="L18" s="15"/>
-      <c r="M18" s="15"/>
-      <c r="N18" s="15"/>
-      <c r="O18" s="15"/>
-      <c r="P18" s="15"/>
-      <c r="Q18" s="17"/>
-    </row>
-    <row r="19" spans="1:17" ht="10" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19" s="54" t="s">
+      <c r="B38" s="79"/>
+      <c r="C38" s="79"/>
+      <c r="D38" s="79"/>
+      <c r="E38" s="80"/>
+      <c r="F38" s="79"/>
+      <c r="G38" s="79"/>
+      <c r="H38" s="79"/>
+      <c r="I38" s="79"/>
+      <c r="J38" s="79"/>
+      <c r="K38" s="79"/>
+      <c r="L38" s="79"/>
+      <c r="M38" s="79"/>
+      <c r="N38" s="79"/>
+      <c r="O38" s="79"/>
+      <c r="P38" s="79"/>
+      <c r="Q38" s="81"/>
+    </row>
+    <row r="39" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A39" s="78" t="s">
         <v>74</v>
       </c>
-      <c r="B19" s="15"/>
-      <c r="C19" s="15"/>
-      <c r="D19" s="15"/>
-      <c r="E19" s="49"/>
-      <c r="F19" s="15"/>
-      <c r="G19" s="15"/>
-      <c r="H19" s="15"/>
-      <c r="I19" s="15"/>
-      <c r="J19" s="15"/>
-      <c r="K19" s="15"/>
-      <c r="L19" s="15"/>
-      <c r="M19" s="15"/>
-      <c r="N19" s="15"/>
-      <c r="O19" s="15"/>
-      <c r="P19" s="15"/>
-      <c r="Q19" s="17"/>
-    </row>
-    <row r="20" spans="1:17" ht="10" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A20" s="54" t="s">
+      <c r="B39" s="79"/>
+      <c r="C39" s="79"/>
+      <c r="D39" s="79"/>
+      <c r="E39" s="80"/>
+      <c r="F39" s="79"/>
+      <c r="G39" s="79"/>
+      <c r="H39" s="79"/>
+      <c r="I39" s="79"/>
+      <c r="J39" s="79"/>
+      <c r="K39" s="79"/>
+      <c r="L39" s="79"/>
+      <c r="M39" s="79"/>
+      <c r="N39" s="79"/>
+      <c r="O39" s="79"/>
+      <c r="P39" s="79"/>
+      <c r="Q39" s="81"/>
+    </row>
+    <row r="40" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A40" s="78">
+        <v>4.2</v>
+      </c>
+      <c r="B40" s="79"/>
+      <c r="C40" s="79"/>
+      <c r="D40" s="79"/>
+      <c r="E40" s="80"/>
+      <c r="F40" s="79"/>
+      <c r="G40" s="79"/>
+      <c r="H40" s="79"/>
+      <c r="I40" s="79"/>
+      <c r="J40" s="79"/>
+      <c r="K40" s="79"/>
+      <c r="L40" s="79"/>
+      <c r="M40" s="79"/>
+      <c r="N40" s="79"/>
+      <c r="O40" s="79"/>
+      <c r="P40" s="79"/>
+      <c r="Q40" s="81"/>
+    </row>
+    <row r="41" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A41" s="78" t="s">
         <v>75</v>
       </c>
-      <c r="B20" s="15"/>
-      <c r="C20" s="15"/>
-      <c r="D20" s="15"/>
-      <c r="E20" s="49"/>
-      <c r="F20" s="15"/>
-      <c r="G20" s="15"/>
-      <c r="H20" s="15"/>
-      <c r="I20" s="15"/>
-      <c r="J20" s="15"/>
-      <c r="K20" s="15"/>
-      <c r="L20" s="15"/>
-      <c r="M20" s="15"/>
-      <c r="N20" s="15"/>
-      <c r="O20" s="15"/>
-      <c r="P20" s="15"/>
-      <c r="Q20" s="17"/>
-    </row>
-    <row r="21" spans="1:17" ht="10" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A21" s="54" t="s">
+      <c r="B41" s="79"/>
+      <c r="C41" s="79"/>
+      <c r="D41" s="79"/>
+      <c r="E41" s="80"/>
+      <c r="F41" s="79"/>
+      <c r="G41" s="79"/>
+      <c r="H41" s="79"/>
+      <c r="I41" s="79"/>
+      <c r="J41" s="79"/>
+      <c r="K41" s="79"/>
+      <c r="L41" s="79"/>
+      <c r="M41" s="79"/>
+      <c r="N41" s="79"/>
+      <c r="O41" s="79"/>
+      <c r="P41" s="79"/>
+      <c r="Q41" s="81"/>
+    </row>
+    <row r="42" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A42" s="78" t="s">
         <v>76</v>
       </c>
-      <c r="B21" s="15"/>
-      <c r="C21" s="15"/>
-      <c r="D21" s="15"/>
-      <c r="E21" s="49"/>
-      <c r="F21" s="15"/>
-      <c r="G21" s="15"/>
-      <c r="H21" s="15"/>
-      <c r="I21" s="15"/>
-      <c r="J21" s="15"/>
-      <c r="K21" s="15"/>
-      <c r="L21" s="15"/>
-      <c r="M21" s="15"/>
-      <c r="N21" s="15"/>
-      <c r="O21" s="15"/>
-      <c r="P21" s="15"/>
-      <c r="Q21" s="17"/>
-    </row>
-    <row r="22" spans="1:17" ht="10" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22" s="54" t="s">
+      <c r="B42" s="79"/>
+      <c r="C42" s="79"/>
+      <c r="D42" s="79"/>
+      <c r="E42" s="80"/>
+      <c r="F42" s="79"/>
+      <c r="G42" s="79"/>
+      <c r="H42" s="79"/>
+      <c r="I42" s="79"/>
+      <c r="J42" s="79"/>
+      <c r="K42" s="79"/>
+      <c r="L42" s="79"/>
+      <c r="M42" s="79"/>
+      <c r="N42" s="79"/>
+      <c r="O42" s="79"/>
+      <c r="P42" s="79"/>
+      <c r="Q42" s="81"/>
+    </row>
+    <row r="43" spans="1:17" ht="25" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A43" s="83" t="s">
         <v>77</v>
       </c>
-      <c r="B22" s="15"/>
-      <c r="C22" s="15"/>
-      <c r="D22" s="15"/>
-      <c r="E22" s="49"/>
-      <c r="F22" s="15"/>
-      <c r="G22" s="15"/>
-      <c r="H22" s="15"/>
-      <c r="I22" s="15"/>
-      <c r="J22" s="15"/>
-      <c r="K22" s="15"/>
-      <c r="L22" s="15"/>
-      <c r="M22" s="15"/>
-      <c r="N22" s="15"/>
-      <c r="O22" s="15"/>
-      <c r="P22" s="15"/>
-      <c r="Q22" s="17"/>
-    </row>
-    <row r="23" spans="1:17" ht="10" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A23" s="54">
-        <v>3.1</v>
-      </c>
-      <c r="B23" s="15"/>
-      <c r="C23" s="15" t="s">
-        <v>98</v>
-      </c>
-      <c r="D23" s="15"/>
-      <c r="E23" s="49"/>
-      <c r="F23" s="15"/>
-      <c r="G23" s="15"/>
-      <c r="H23" s="15"/>
-      <c r="I23" s="15"/>
-      <c r="J23" s="15"/>
-      <c r="K23" s="15"/>
-      <c r="L23" s="15"/>
-      <c r="M23" s="15"/>
-      <c r="N23" s="15"/>
-      <c r="O23" s="15"/>
-      <c r="P23" s="15"/>
-      <c r="Q23" s="17"/>
-    </row>
-    <row r="24" spans="1:17" ht="10" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A24" s="54" t="s">
-        <v>78</v>
-      </c>
-      <c r="B24" s="15"/>
-      <c r="C24" s="15"/>
-      <c r="D24" s="15"/>
-      <c r="E24" s="49"/>
-      <c r="F24" s="15"/>
-      <c r="G24" s="15"/>
-      <c r="H24" s="15"/>
-      <c r="I24" s="15"/>
-      <c r="J24" s="15"/>
-      <c r="K24" s="15"/>
-      <c r="L24" s="15"/>
-      <c r="M24" s="15"/>
-      <c r="N24" s="15"/>
-      <c r="O24" s="15"/>
-      <c r="P24" s="15"/>
-      <c r="Q24" s="17"/>
-    </row>
-    <row r="25" spans="1:17" ht="10" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A25" s="54" t="s">
-        <v>79</v>
-      </c>
-      <c r="B25" s="15"/>
-      <c r="C25" s="15"/>
-      <c r="D25" s="15"/>
-      <c r="E25" s="49"/>
-      <c r="F25" s="15"/>
-      <c r="G25" s="15"/>
-      <c r="H25" s="15"/>
-      <c r="I25" s="15"/>
-      <c r="J25" s="15"/>
-      <c r="K25" s="15"/>
-      <c r="L25" s="15"/>
-      <c r="M25" s="15"/>
-      <c r="N25" s="15"/>
-      <c r="O25" s="15"/>
-      <c r="P25" s="15"/>
-      <c r="Q25" s="17"/>
-    </row>
-    <row r="26" spans="1:17" ht="10" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26" s="54" t="s">
-        <v>80</v>
-      </c>
-      <c r="B26" s="15"/>
-      <c r="C26" s="15"/>
-      <c r="D26" s="15"/>
-      <c r="E26" s="49"/>
-      <c r="F26" s="15"/>
-      <c r="G26" s="15"/>
-      <c r="H26" s="15"/>
-      <c r="I26" s="15"/>
-      <c r="J26" s="15"/>
-      <c r="K26" s="15"/>
-      <c r="L26" s="15"/>
-      <c r="M26" s="15"/>
-      <c r="N26" s="15"/>
-      <c r="O26" s="15"/>
-      <c r="P26" s="15"/>
-      <c r="Q26" s="17"/>
-    </row>
-    <row r="27" spans="1:17" ht="10" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A27" s="54" t="s">
-        <v>81</v>
-      </c>
-      <c r="B27" s="15"/>
-      <c r="C27" s="15"/>
-      <c r="D27" s="15"/>
-      <c r="E27" s="49"/>
-      <c r="F27" s="15"/>
-      <c r="G27" s="15"/>
-      <c r="H27" s="15"/>
-      <c r="I27" s="15"/>
-      <c r="J27" s="15"/>
-      <c r="K27" s="15"/>
-      <c r="L27" s="15"/>
-      <c r="M27" s="15"/>
-      <c r="N27" s="15"/>
-      <c r="O27" s="15"/>
-      <c r="P27" s="15"/>
-      <c r="Q27" s="17"/>
-    </row>
-    <row r="28" spans="1:17" ht="10" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A28" s="54">
-        <v>3.2</v>
-      </c>
-      <c r="B28" s="15"/>
-      <c r="C28" s="15" t="s">
-        <v>99</v>
-      </c>
-      <c r="D28" s="15"/>
-      <c r="E28" s="49"/>
-      <c r="F28" s="15"/>
-      <c r="G28" s="15"/>
-      <c r="H28" s="15"/>
-      <c r="I28" s="15"/>
-      <c r="J28" s="15"/>
-      <c r="K28" s="15"/>
-      <c r="L28" s="15"/>
-      <c r="M28" s="15"/>
-      <c r="N28" s="15"/>
-      <c r="O28" s="15"/>
-      <c r="P28" s="15"/>
-      <c r="Q28" s="17"/>
-    </row>
-    <row r="29" spans="1:17" ht="10" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A29" s="54" t="s">
-        <v>82</v>
-      </c>
-      <c r="B29" s="15"/>
-      <c r="C29" s="15"/>
-      <c r="D29" s="15"/>
-      <c r="E29" s="49"/>
-      <c r="F29" s="15"/>
-      <c r="G29" s="15"/>
-      <c r="H29" s="15"/>
-      <c r="I29" s="15"/>
-      <c r="J29" s="15"/>
-      <c r="K29" s="15"/>
-      <c r="L29" s="15"/>
-      <c r="M29" s="15"/>
-      <c r="N29" s="15"/>
-      <c r="O29" s="15"/>
-      <c r="P29" s="15"/>
-      <c r="Q29" s="17"/>
-    </row>
-    <row r="30" spans="1:17" ht="10" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A30" s="54" t="s">
-        <v>83</v>
-      </c>
-      <c r="B30" s="15"/>
-      <c r="C30" s="15"/>
-      <c r="D30" s="15"/>
-      <c r="E30" s="49"/>
-      <c r="F30" s="15"/>
-      <c r="G30" s="15"/>
-      <c r="H30" s="15"/>
-      <c r="I30" s="15"/>
-      <c r="J30" s="15"/>
-      <c r="K30" s="15"/>
-      <c r="L30" s="15"/>
-      <c r="M30" s="15"/>
-      <c r="N30" s="15"/>
-      <c r="O30" s="15"/>
-      <c r="P30" s="15"/>
-      <c r="Q30" s="17"/>
-    </row>
-    <row r="31" spans="1:17" ht="10" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A31" s="54" t="s">
-        <v>84</v>
-      </c>
-      <c r="B31" s="15"/>
-      <c r="C31" s="15"/>
-      <c r="D31" s="15"/>
-      <c r="E31" s="49"/>
-      <c r="F31" s="15"/>
-      <c r="G31" s="15"/>
-      <c r="H31" s="15"/>
-      <c r="I31" s="15"/>
-      <c r="J31" s="15"/>
-      <c r="K31" s="15"/>
-      <c r="L31" s="15"/>
-      <c r="M31" s="15"/>
-      <c r="N31" s="15"/>
-      <c r="O31" s="15"/>
-      <c r="P31" s="15"/>
-      <c r="Q31" s="17"/>
-    </row>
-    <row r="32" spans="1:17" ht="10" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A32" s="54">
-        <v>3.3</v>
-      </c>
-      <c r="B32" s="15"/>
-      <c r="C32" s="15" t="s">
-        <v>100</v>
-      </c>
-      <c r="D32" s="15"/>
-      <c r="E32" s="49"/>
-      <c r="F32" s="15"/>
-      <c r="G32" s="15"/>
-      <c r="H32" s="15"/>
-      <c r="I32" s="15"/>
-      <c r="J32" s="15"/>
-      <c r="K32" s="15"/>
-      <c r="L32" s="15"/>
-      <c r="M32" s="15"/>
-      <c r="N32" s="15"/>
-      <c r="O32" s="15"/>
-      <c r="P32" s="15"/>
-      <c r="Q32" s="17"/>
-    </row>
-    <row r="33" spans="1:17" ht="10" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A33" s="54" t="s">
-        <v>85</v>
-      </c>
-      <c r="B33" s="15"/>
-      <c r="C33" s="15"/>
-      <c r="D33" s="15"/>
-      <c r="E33" s="49"/>
-      <c r="F33" s="15"/>
-      <c r="G33" s="15"/>
-      <c r="H33" s="15"/>
-      <c r="I33" s="15"/>
-      <c r="J33" s="15"/>
-      <c r="K33" s="15"/>
-      <c r="L33" s="15"/>
-      <c r="M33" s="15"/>
-      <c r="N33" s="15"/>
-      <c r="O33" s="15"/>
-      <c r="P33" s="15"/>
-      <c r="Q33" s="17"/>
-    </row>
-    <row r="34" spans="1:17" ht="10" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A34" s="54" t="s">
-        <v>86</v>
-      </c>
-      <c r="B34" s="15"/>
-      <c r="C34" s="15"/>
-      <c r="D34" s="15"/>
-      <c r="E34" s="49"/>
-      <c r="F34" s="15"/>
-      <c r="G34" s="15"/>
-      <c r="H34" s="15"/>
-      <c r="I34" s="15"/>
-      <c r="J34" s="15"/>
-      <c r="K34" s="15"/>
-      <c r="L34" s="15"/>
-      <c r="M34" s="15"/>
-      <c r="N34" s="15"/>
-      <c r="O34" s="15"/>
-      <c r="P34" s="15"/>
-      <c r="Q34" s="17"/>
-    </row>
-    <row r="35" spans="1:17" ht="10" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A35" s="54" t="s">
-        <v>87</v>
-      </c>
-      <c r="B35" s="15"/>
-      <c r="C35" s="15"/>
-      <c r="D35" s="15"/>
-      <c r="E35" s="49"/>
-      <c r="F35" s="15"/>
-      <c r="G35" s="15"/>
-      <c r="H35" s="15"/>
-      <c r="I35" s="15"/>
-      <c r="J35" s="15"/>
-      <c r="K35" s="15"/>
-      <c r="L35" s="15"/>
-      <c r="M35" s="15"/>
-      <c r="N35" s="15"/>
-      <c r="O35" s="15"/>
-      <c r="P35" s="15"/>
-      <c r="Q35" s="17"/>
-    </row>
-    <row r="36" spans="1:17" ht="10" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A36" s="54">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="B36" s="15"/>
-      <c r="C36" s="15"/>
-      <c r="D36" s="15"/>
-      <c r="E36" s="49"/>
-      <c r="F36" s="15"/>
-      <c r="G36" s="15"/>
-      <c r="H36" s="15"/>
-      <c r="I36" s="15"/>
-      <c r="J36" s="15"/>
-      <c r="K36" s="15"/>
-      <c r="L36" s="15"/>
-      <c r="M36" s="15"/>
-      <c r="N36" s="15"/>
-      <c r="O36" s="15"/>
-      <c r="P36" s="15"/>
-      <c r="Q36" s="17"/>
-    </row>
-    <row r="37" spans="1:17" ht="10" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A37" s="54" t="s">
-        <v>88</v>
-      </c>
-      <c r="B37" s="15"/>
-      <c r="C37" s="15"/>
-      <c r="D37" s="15"/>
-      <c r="E37" s="49"/>
-      <c r="F37" s="15"/>
-      <c r="G37" s="15"/>
-      <c r="H37" s="15"/>
-      <c r="I37" s="15"/>
-      <c r="J37" s="15"/>
-      <c r="K37" s="15"/>
-      <c r="L37" s="15"/>
-      <c r="M37" s="15"/>
-      <c r="N37" s="15"/>
-      <c r="O37" s="15"/>
-      <c r="P37" s="15"/>
-      <c r="Q37" s="17"/>
-    </row>
-    <row r="38" spans="1:17" ht="10" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A38" s="54" t="s">
-        <v>89</v>
-      </c>
-      <c r="B38" s="15"/>
-      <c r="C38" s="15"/>
-      <c r="D38" s="15"/>
-      <c r="E38" s="49"/>
-      <c r="F38" s="15"/>
-      <c r="G38" s="15"/>
-      <c r="H38" s="15"/>
-      <c r="I38" s="15"/>
-      <c r="J38" s="15"/>
-      <c r="K38" s="15"/>
-      <c r="L38" s="15"/>
-      <c r="M38" s="15"/>
-      <c r="N38" s="15"/>
-      <c r="O38" s="15"/>
-      <c r="P38" s="15"/>
-      <c r="Q38" s="17"/>
-    </row>
-    <row r="39" spans="1:17" ht="10" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A39" s="54" t="s">
-        <v>90</v>
-      </c>
-      <c r="B39" s="15"/>
-      <c r="C39" s="15"/>
-      <c r="D39" s="15"/>
-      <c r="E39" s="49"/>
-      <c r="F39" s="15"/>
-      <c r="G39" s="15"/>
-      <c r="H39" s="15"/>
-      <c r="I39" s="15"/>
-      <c r="J39" s="15"/>
-      <c r="K39" s="15"/>
-      <c r="L39" s="15"/>
-      <c r="M39" s="15"/>
-      <c r="N39" s="15"/>
-      <c r="O39" s="15"/>
-      <c r="P39" s="15"/>
-      <c r="Q39" s="17"/>
-    </row>
-    <row r="40" spans="1:17" ht="10" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A40" s="54">
-        <v>4.2</v>
-      </c>
-      <c r="B40" s="15"/>
-      <c r="C40" s="15"/>
-      <c r="D40" s="15"/>
-      <c r="E40" s="49"/>
-      <c r="F40" s="15"/>
-      <c r="G40" s="15"/>
-      <c r="H40" s="15"/>
-      <c r="I40" s="15"/>
-      <c r="J40" s="15"/>
-      <c r="K40" s="15"/>
-      <c r="L40" s="15"/>
-      <c r="M40" s="15"/>
-      <c r="N40" s="15"/>
-      <c r="O40" s="15"/>
-      <c r="P40" s="15"/>
-      <c r="Q40" s="17"/>
-    </row>
-    <row r="41" spans="1:17" ht="10" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A41" s="54" t="s">
-        <v>91</v>
-      </c>
-      <c r="B41" s="15"/>
-      <c r="C41" s="15"/>
-      <c r="D41" s="15"/>
-      <c r="E41" s="49"/>
-      <c r="F41" s="15"/>
-      <c r="G41" s="15"/>
-      <c r="H41" s="15"/>
-      <c r="I41" s="15"/>
-      <c r="J41" s="15"/>
-      <c r="K41" s="15"/>
-      <c r="L41" s="15"/>
-      <c r="M41" s="15"/>
-      <c r="N41" s="15"/>
-      <c r="O41" s="15"/>
-      <c r="P41" s="15"/>
-      <c r="Q41" s="17"/>
-    </row>
-    <row r="42" spans="1:17" ht="10" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A42" s="54" t="s">
-        <v>92</v>
-      </c>
-      <c r="B42" s="15"/>
-      <c r="C42" s="15"/>
-      <c r="D42" s="15"/>
-      <c r="E42" s="49"/>
-      <c r="F42" s="15"/>
-      <c r="G42" s="15"/>
-      <c r="H42" s="15"/>
-      <c r="I42" s="15"/>
-      <c r="J42" s="15"/>
-      <c r="K42" s="15"/>
-      <c r="L42" s="15"/>
-      <c r="M42" s="15"/>
-      <c r="N42" s="15"/>
-      <c r="O42" s="15"/>
-      <c r="P42" s="15"/>
-      <c r="Q42" s="17"/>
-    </row>
-    <row r="43" spans="1:17" ht="10" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A43" s="55" t="s">
-        <v>93</v>
-      </c>
-      <c r="B43" s="19"/>
-      <c r="C43" s="19"/>
-      <c r="D43" s="19"/>
-      <c r="E43" s="56"/>
-      <c r="F43" s="19"/>
-      <c r="G43" s="19"/>
-      <c r="H43" s="19"/>
-      <c r="I43" s="19"/>
-      <c r="J43" s="19"/>
-      <c r="K43" s="19"/>
-      <c r="L43" s="19"/>
-      <c r="M43" s="19"/>
-      <c r="N43" s="19"/>
-      <c r="O43" s="19"/>
-      <c r="P43" s="19"/>
-      <c r="Q43" s="20"/>
-    </row>
-    <row r="44" spans="1:17" ht="10" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="45" spans="1:17" ht="10" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="46" spans="1:17" ht="10" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="47" spans="1:17" ht="10" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="48" spans="1:17" ht="10" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="49" ht="10" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="50" ht="10" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="51" ht="10" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+      <c r="B43" s="84"/>
+      <c r="C43" s="84"/>
+      <c r="D43" s="84"/>
+      <c r="E43" s="85"/>
+      <c r="F43" s="84"/>
+      <c r="G43" s="84"/>
+      <c r="H43" s="84"/>
+      <c r="I43" s="84"/>
+      <c r="J43" s="84"/>
+      <c r="K43" s="84"/>
+      <c r="L43" s="84"/>
+      <c r="M43" s="84"/>
+      <c r="N43" s="84"/>
+      <c r="O43" s="84"/>
+      <c r="P43" s="84"/>
+      <c r="Q43" s="86"/>
+    </row>
+    <row r="44" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="45" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="46" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="47" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="48" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="49" ht="25" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="50" ht="25" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="51" ht="25" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
     <row r="52" ht="10" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
     <row r="53" ht="10" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
     <row r="54" ht="10" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
@@ -7254,7 +10176,7 @@
     <mergeCell ref="J2:M2"/>
     <mergeCell ref="N2:Q2"/>
   </mergeCells>
-  <phoneticPr fontId="2"/>
+  <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
   <headerFooter>
@@ -7266,225 +10188,221 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A72293E1-9681-4529-A931-167C8261205C}">
-  <dimension ref="A2:H22"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <dimension ref="A2:G22"/>
+  <sheetFormatPr defaultRowHeight="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="4.4140625" customWidth="1"/>
-    <col min="2" max="2" width="10.4140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="25" customWidth="1"/>
-    <col min="4" max="4" width="29" customWidth="1"/>
-    <col min="5" max="5" width="7.5" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="11.4140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.6640625" customWidth="1"/>
+    <col min="1" max="1" width="10.83203125" customWidth="1"/>
+    <col min="2" max="2" width="28.58203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.33203125" customWidth="1"/>
+    <col min="5" max="6" width="12.83203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.4140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="E2" s="14" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="B4" s="62" t="s">
-        <v>106</v>
-      </c>
-      <c r="C4" s="62" t="s">
-        <v>107</v>
-      </c>
-      <c r="D4" s="62" t="s">
-        <v>108</v>
-      </c>
-      <c r="E4" s="62" t="s">
-        <v>109</v>
-      </c>
-      <c r="F4" s="62" t="s">
-        <v>110</v>
-      </c>
-      <c r="G4" s="62" t="s">
-        <v>111</v>
-      </c>
-      <c r="H4" s="62" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" t="s">
-        <v>118</v>
-      </c>
-      <c r="B5" s="15" t="s">
-        <v>113</v>
-      </c>
-      <c r="C5" s="15" t="s">
-        <v>114</v>
-      </c>
-      <c r="D5" s="15" t="s">
-        <v>115</v>
-      </c>
-      <c r="E5" s="15" t="s">
-        <v>116</v>
-      </c>
-      <c r="F5" s="15" t="s">
-        <v>117</v>
-      </c>
-      <c r="G5" s="15" t="s">
-        <v>117</v>
-      </c>
-      <c r="H5" s="15"/>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="B6" s="15"/>
-      <c r="C6" s="15"/>
-      <c r="D6" s="15"/>
-      <c r="E6" s="15"/>
-      <c r="F6" s="15"/>
-      <c r="G6" s="15"/>
-      <c r="H6" s="15"/>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="B7" s="15"/>
-      <c r="C7" s="15"/>
-      <c r="D7" s="15"/>
-      <c r="E7" s="15"/>
-      <c r="F7" s="15"/>
-      <c r="G7" s="15"/>
-      <c r="H7" s="15"/>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="B8" s="15"/>
-      <c r="C8" s="15"/>
-      <c r="D8" s="15"/>
-      <c r="E8" s="15"/>
-      <c r="F8" s="15"/>
-      <c r="G8" s="15"/>
-      <c r="H8" s="15"/>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="B9" s="15"/>
-      <c r="C9" s="15"/>
-      <c r="D9" s="15"/>
-      <c r="E9" s="15"/>
-      <c r="F9" s="15"/>
-      <c r="G9" s="15"/>
-      <c r="H9" s="15"/>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="B10" s="15"/>
-      <c r="C10" s="15"/>
-      <c r="D10" s="15"/>
-      <c r="E10" s="15"/>
-      <c r="F10" s="15"/>
-      <c r="G10" s="15"/>
-      <c r="H10" s="15"/>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="B11" s="15"/>
-      <c r="C11" s="15"/>
-      <c r="D11" s="15"/>
-      <c r="E11" s="15"/>
-      <c r="F11" s="15"/>
-      <c r="G11" s="15"/>
-      <c r="H11" s="15"/>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="B12" s="15"/>
-      <c r="C12" s="15"/>
-      <c r="D12" s="15"/>
-      <c r="E12" s="15"/>
-      <c r="F12" s="15"/>
-      <c r="G12" s="15"/>
-      <c r="H12" s="15"/>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="B13" s="15"/>
-      <c r="C13" s="15"/>
-      <c r="D13" s="15"/>
-      <c r="E13" s="15"/>
-      <c r="F13" s="15"/>
-      <c r="G13" s="15"/>
-      <c r="H13" s="15"/>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="B14" s="15"/>
-      <c r="C14" s="15"/>
-      <c r="D14" s="15"/>
-      <c r="E14" s="15"/>
-      <c r="F14" s="15"/>
-      <c r="G14" s="15"/>
-      <c r="H14" s="15"/>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="B15" s="15"/>
-      <c r="C15" s="15"/>
-      <c r="D15" s="15"/>
-      <c r="E15" s="15"/>
-      <c r="F15" s="15"/>
-      <c r="G15" s="15"/>
-      <c r="H15" s="15"/>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="B16" s="15"/>
-      <c r="C16" s="15"/>
-      <c r="D16" s="15"/>
-      <c r="E16" s="15"/>
-      <c r="F16" s="15"/>
-      <c r="G16" s="15"/>
-      <c r="H16" s="15"/>
-    </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="B17" s="15"/>
-      <c r="C17" s="15"/>
-      <c r="D17" s="15"/>
-      <c r="E17" s="15"/>
-      <c r="F17" s="15"/>
-      <c r="G17" s="15"/>
-      <c r="H17" s="15"/>
-    </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="B18" s="15"/>
-      <c r="C18" s="15"/>
-      <c r="D18" s="15"/>
-      <c r="E18" s="15"/>
-      <c r="F18" s="15"/>
-      <c r="G18" s="15"/>
-      <c r="H18" s="15"/>
-    </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="B19" s="15"/>
-      <c r="C19" s="15"/>
-      <c r="D19" s="15"/>
-      <c r="E19" s="15"/>
-      <c r="F19" s="15"/>
-      <c r="G19" s="15"/>
-      <c r="H19" s="15"/>
-    </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="B20" s="15"/>
-      <c r="C20" s="15"/>
-      <c r="D20" s="15"/>
-      <c r="E20" s="15"/>
-      <c r="F20" s="15"/>
-      <c r="G20" s="15"/>
-      <c r="H20" s="15"/>
-    </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="B21" s="15"/>
-      <c r="C21" s="15"/>
-      <c r="D21" s="15"/>
-      <c r="E21" s="15"/>
-      <c r="F21" s="15"/>
-      <c r="G21" s="15"/>
-      <c r="H21" s="15"/>
-    </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="B22" s="15"/>
-      <c r="C22" s="15"/>
-      <c r="D22" s="15"/>
-      <c r="E22" s="15"/>
-      <c r="F22" s="15"/>
-      <c r="G22" s="15"/>
-      <c r="H22" s="15"/>
+    <row r="2" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="D2" s="89" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" s="87" t="s">
+        <v>90</v>
+      </c>
+      <c r="B4" s="88" t="s">
+        <v>91</v>
+      </c>
+      <c r="C4" s="88" t="s">
+        <v>92</v>
+      </c>
+      <c r="D4" s="88" t="s">
+        <v>93</v>
+      </c>
+      <c r="E4" s="88" t="s">
+        <v>94</v>
+      </c>
+      <c r="F4" s="88" t="s">
+        <v>95</v>
+      </c>
+      <c r="G4" s="88" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" s="90" t="s">
+        <v>97</v>
+      </c>
+      <c r="B5" s="90" t="s">
+        <v>98</v>
+      </c>
+      <c r="C5" s="90" t="s">
+        <v>99</v>
+      </c>
+      <c r="D5" s="90" t="s">
+        <v>100</v>
+      </c>
+      <c r="E5" s="90" t="s">
+        <v>101</v>
+      </c>
+      <c r="F5" s="90" t="s">
+        <v>101</v>
+      </c>
+      <c r="G5" s="90"/>
+    </row>
+    <row r="6" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" s="90"/>
+      <c r="B6" s="90"/>
+      <c r="C6" s="90"/>
+      <c r="D6" s="90"/>
+      <c r="E6" s="90"/>
+      <c r="F6" s="90"/>
+      <c r="G6" s="90"/>
+    </row>
+    <row r="7" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" s="90"/>
+      <c r="B7" s="90"/>
+      <c r="C7" s="90"/>
+      <c r="D7" s="90"/>
+      <c r="E7" s="90"/>
+      <c r="F7" s="90"/>
+      <c r="G7" s="90"/>
+    </row>
+    <row r="8" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" s="90"/>
+      <c r="B8" s="90"/>
+      <c r="C8" s="90"/>
+      <c r="D8" s="90"/>
+      <c r="E8" s="90"/>
+      <c r="F8" s="90"/>
+      <c r="G8" s="90"/>
+    </row>
+    <row r="9" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" s="90"/>
+      <c r="B9" s="90"/>
+      <c r="C9" s="90"/>
+      <c r="D9" s="90"/>
+      <c r="E9" s="90"/>
+      <c r="F9" s="90"/>
+      <c r="G9" s="90"/>
+    </row>
+    <row r="10" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" s="90"/>
+      <c r="B10" s="90"/>
+      <c r="C10" s="90"/>
+      <c r="D10" s="90"/>
+      <c r="E10" s="90"/>
+      <c r="F10" s="90"/>
+      <c r="G10" s="90"/>
+    </row>
+    <row r="11" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" s="90"/>
+      <c r="B11" s="90"/>
+      <c r="C11" s="90"/>
+      <c r="D11" s="90"/>
+      <c r="E11" s="90"/>
+      <c r="F11" s="90"/>
+      <c r="G11" s="90"/>
+    </row>
+    <row r="12" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" s="90"/>
+      <c r="B12" s="90"/>
+      <c r="C12" s="90"/>
+      <c r="D12" s="90"/>
+      <c r="E12" s="90"/>
+      <c r="F12" s="90"/>
+      <c r="G12" s="90"/>
+    </row>
+    <row r="13" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" s="90"/>
+      <c r="B13" s="90"/>
+      <c r="C13" s="90"/>
+      <c r="D13" s="90"/>
+      <c r="E13" s="90"/>
+      <c r="F13" s="90"/>
+      <c r="G13" s="90"/>
+    </row>
+    <row r="14" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" s="90"/>
+      <c r="B14" s="90"/>
+      <c r="C14" s="90"/>
+      <c r="D14" s="90"/>
+      <c r="E14" s="90"/>
+      <c r="F14" s="90"/>
+      <c r="G14" s="90"/>
+    </row>
+    <row r="15" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" s="90"/>
+      <c r="B15" s="90"/>
+      <c r="C15" s="90"/>
+      <c r="D15" s="90"/>
+      <c r="E15" s="90"/>
+      <c r="F15" s="90"/>
+      <c r="G15" s="90"/>
+    </row>
+    <row r="16" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" s="90"/>
+      <c r="B16" s="90"/>
+      <c r="C16" s="90"/>
+      <c r="D16" s="90"/>
+      <c r="E16" s="90"/>
+      <c r="F16" s="90"/>
+      <c r="G16" s="90"/>
+    </row>
+    <row r="17" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" s="90"/>
+      <c r="B17" s="90"/>
+      <c r="C17" s="90"/>
+      <c r="D17" s="90"/>
+      <c r="E17" s="90"/>
+      <c r="F17" s="90"/>
+      <c r="G17" s="90"/>
+    </row>
+    <row r="18" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18" s="90"/>
+      <c r="B18" s="90"/>
+      <c r="C18" s="90"/>
+      <c r="D18" s="90"/>
+      <c r="E18" s="90"/>
+      <c r="F18" s="90"/>
+      <c r="G18" s="90"/>
+    </row>
+    <row r="19" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A19" s="90"/>
+      <c r="B19" s="90"/>
+      <c r="C19" s="90"/>
+      <c r="D19" s="90"/>
+      <c r="E19" s="90"/>
+      <c r="F19" s="90"/>
+      <c r="G19" s="90"/>
+    </row>
+    <row r="20" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A20" s="90"/>
+      <c r="B20" s="90"/>
+      <c r="C20" s="90"/>
+      <c r="D20" s="90"/>
+      <c r="E20" s="90"/>
+      <c r="F20" s="90"/>
+      <c r="G20" s="90"/>
+    </row>
+    <row r="21" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A21" s="90"/>
+      <c r="B21" s="90"/>
+      <c r="C21" s="90"/>
+      <c r="D21" s="90"/>
+      <c r="E21" s="90"/>
+      <c r="F21" s="90"/>
+      <c r="G21" s="90"/>
+    </row>
+    <row r="22" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A22" s="90"/>
+      <c r="B22" s="90"/>
+      <c r="C22" s="90"/>
+      <c r="D22" s="90"/>
+      <c r="E22" s="90"/>
+      <c r="F22" s="90"/>
+      <c r="G22" s="90"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="2"/>
+  <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
   <headerFooter>
@@ -7503,39 +10421,39 @@
   <sheetData>
     <row r="1" spans="1:3" ht="11.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
     <row r="2" spans="1:3" ht="26.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="63" t="s">
-        <v>120</v>
-      </c>
-      <c r="B2" s="63" t="s">
-        <v>121</v>
-      </c>
-      <c r="C2" s="63" t="s">
-        <v>122</v>
+      <c r="A2" s="91" t="s">
+        <v>103</v>
+      </c>
+      <c r="B2" s="91" t="s">
+        <v>104</v>
+      </c>
+      <c r="C2" s="91" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="120" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="64" t="s">
-        <v>123</v>
-      </c>
-      <c r="B3" s="15"/>
-      <c r="C3" s="15"/>
+      <c r="A3" s="92" t="s">
+        <v>106</v>
+      </c>
+      <c r="B3" s="79"/>
+      <c r="C3" s="79"/>
     </row>
     <row r="4" spans="1:3" ht="131.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="64" t="s">
-        <v>124</v>
-      </c>
-      <c r="B4" s="15"/>
-      <c r="C4" s="15"/>
+      <c r="A4" s="93" t="s">
+        <v>107</v>
+      </c>
+      <c r="B4" s="79"/>
+      <c r="C4" s="79"/>
     </row>
     <row r="5" spans="1:3" ht="171" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="64" t="s">
-        <v>125</v>
-      </c>
-      <c r="B5" s="15"/>
-      <c r="C5" s="15"/>
+      <c r="A5" s="93" t="s">
+        <v>108</v>
+      </c>
+      <c r="B5" s="79"/>
+      <c r="C5" s="79"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="2"/>
+  <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
   <headerFooter>

--- a/高橋さん用フォルダ/テンプレート集.xlsx
+++ b/高橋さん用フォルダ/テンプレート集.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\iret_pm\高橋さん用フォルダ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4FBAA3E-AB07-416A-88E0-6E97C3E6FC43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26132DF6-CFF8-4E5E-8532-0193962019DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" xr2:uid="{C2D9C0E7-7181-4507-8D76-FFF1980A0610}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" firstSheet="2" activeTab="7" xr2:uid="{C2D9C0E7-7181-4507-8D76-FFF1980A0610}"/>
   </bookViews>
   <sheets>
     <sheet name="組織のビジネスモデル" sheetId="1" r:id="rId1"/>
@@ -868,7 +868,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -953,14 +953,6 @@
       <color theme="1"/>
       <name val="游ゴシック"/>
       <family val="3"/>
-      <charset val="128"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FFFF0000"/>
-      <name val="游ゴシック"/>
-      <family val="2"/>
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
@@ -1397,7 +1389,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="97">
+  <cellXfs count="94">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1482,15 +1474,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -1509,19 +1492,13 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1">
@@ -1547,9 +1524,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
@@ -1605,7 +1579,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1665,9 +1639,6 @@
     <xf numFmtId="0" fontId="6" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -1680,14 +1651,26 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -7109,7 +7092,7 @@
   <sheetData>
     <row r="1" spans="1:30" ht="18.5" thickBot="1" x14ac:dyDescent="0.6"/>
     <row r="2" spans="1:30" ht="22.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="31" t="s">
+      <c r="A2" s="28" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="1"/>
@@ -7117,7 +7100,7 @@
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
-      <c r="G2" s="31" t="s">
+      <c r="G2" s="28" t="s">
         <v>1</v>
       </c>
       <c r="H2" s="1"/>
@@ -7125,7 +7108,7 @@
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
       <c r="L2" s="2"/>
-      <c r="M2" s="32" t="s">
+      <c r="M2" s="29" t="s">
         <v>2</v>
       </c>
       <c r="N2" s="1"/>
@@ -7133,7 +7116,7 @@
       <c r="P2" s="1"/>
       <c r="Q2" s="1"/>
       <c r="R2" s="1"/>
-      <c r="S2" s="33" t="s">
+      <c r="S2" s="30" t="s">
         <v>4</v>
       </c>
       <c r="T2" s="1"/>
@@ -7141,7 +7124,7 @@
       <c r="V2" s="1"/>
       <c r="W2" s="1"/>
       <c r="X2" s="2"/>
-      <c r="Y2" s="32" t="s">
+      <c r="Y2" s="29" t="s">
         <v>6</v>
       </c>
       <c r="Z2" s="1"/>
@@ -7216,7 +7199,7 @@
     </row>
     <row r="11" spans="1:30" ht="22.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="3"/>
-      <c r="G11" s="33" t="s">
+      <c r="G11" s="30" t="s">
         <v>3</v>
       </c>
       <c r="H11" s="1"/>
@@ -7224,7 +7207,7 @@
       <c r="J11" s="1"/>
       <c r="K11" s="1"/>
       <c r="L11" s="2"/>
-      <c r="S11" s="33" t="s">
+      <c r="S11" s="30" t="s">
         <v>5</v>
       </c>
       <c r="T11" s="1"/>
@@ -7307,7 +7290,7 @@
       <c r="AD19" s="4"/>
     </row>
     <row r="20" spans="1:30" ht="22.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A20" s="33" t="s">
+      <c r="A20" s="30" t="s">
         <v>7</v>
       </c>
       <c r="B20" s="1"/>
@@ -7324,7 +7307,7 @@
       <c r="M20" s="1"/>
       <c r="N20" s="1"/>
       <c r="O20" s="2"/>
-      <c r="P20" s="33" t="s">
+      <c r="P20" s="30" t="s">
         <v>8</v>
       </c>
       <c r="Q20" s="1"/>
@@ -7411,487 +7394,128 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A1D089F-0221-4E40-8DDE-87C4BED11CF2}">
-  <dimension ref="A1:P42"/>
+  <dimension ref="A1:L42"/>
   <sheetFormatPr defaultColWidth="3.58203125" defaultRowHeight="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
   <sheetData>
-    <row r="1" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="34" t="s">
+    <row r="1" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" s="31" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="38"/>
-      <c r="B2" s="38"/>
-      <c r="C2" s="38"/>
-      <c r="D2" s="38"/>
-      <c r="E2" s="38"/>
-      <c r="F2" s="38"/>
-      <c r="G2" s="38"/>
-      <c r="H2" s="38"/>
-      <c r="I2" s="38"/>
-      <c r="J2" s="38"/>
-    </row>
-    <row r="3" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="35" t="s">
+    <row r="3" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" s="32" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="38"/>
-      <c r="B4" s="38"/>
-      <c r="C4" s="38"/>
-      <c r="D4" s="38"/>
-      <c r="E4" s="38"/>
-      <c r="F4" s="38"/>
-      <c r="G4" s="38"/>
-      <c r="H4" s="38"/>
-      <c r="I4" s="38"/>
-      <c r="J4" s="38"/>
-    </row>
-    <row r="5" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="35" t="s">
+    <row r="5" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" s="32" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="39"/>
-      <c r="B6" s="38"/>
-      <c r="C6" s="38"/>
-      <c r="D6" s="38"/>
-      <c r="E6" s="38"/>
-      <c r="F6" s="38"/>
-      <c r="G6" s="38"/>
-      <c r="H6" s="38"/>
-      <c r="I6" s="38"/>
-      <c r="J6" s="38"/>
-    </row>
-    <row r="7" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="35" t="s">
+    <row r="6" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" s="32"/>
+    </row>
+    <row r="7" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" s="32" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="36" t="s">
+    <row r="8" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" s="33" t="s">
         <v>20</v>
       </c>
       <c r="E8" s="10"/>
     </row>
-    <row r="9" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="38"/>
-      <c r="B9" s="38"/>
-      <c r="C9" s="38"/>
-      <c r="D9" s="38"/>
-      <c r="E9" s="38"/>
-      <c r="F9" s="38"/>
-      <c r="G9" s="38"/>
-      <c r="H9" s="38"/>
-      <c r="I9" s="38"/>
-      <c r="J9" s="38"/>
-      <c r="L9" s="37"/>
-      <c r="M9" s="38"/>
-      <c r="N9" s="38"/>
-      <c r="O9" s="38"/>
-      <c r="P9" s="38"/>
-    </row>
-    <row r="10" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="38"/>
-      <c r="B10" s="38"/>
-      <c r="C10" s="38"/>
-      <c r="D10" s="38"/>
-      <c r="E10" s="38"/>
-      <c r="F10" s="38"/>
-      <c r="G10" s="38"/>
-      <c r="H10" s="38"/>
-      <c r="I10" s="38"/>
-      <c r="J10" s="38"/>
-      <c r="L10" s="38"/>
-      <c r="M10" s="38"/>
-      <c r="N10" s="38"/>
-      <c r="O10" s="38"/>
-      <c r="P10" s="38"/>
-    </row>
-    <row r="11" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="38"/>
-      <c r="B11" s="38"/>
-      <c r="C11" s="38"/>
-      <c r="D11" s="38"/>
-      <c r="E11" s="38"/>
-      <c r="F11" s="38"/>
-      <c r="G11" s="38"/>
-      <c r="H11" s="38"/>
-      <c r="I11" s="38"/>
-      <c r="J11" s="38"/>
-      <c r="L11" s="38"/>
-      <c r="M11" s="38"/>
-      <c r="N11" s="38"/>
-      <c r="O11" s="38"/>
-      <c r="P11" s="38"/>
-    </row>
-    <row r="12" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" s="38"/>
-      <c r="B12" s="38"/>
-      <c r="C12" s="38"/>
-      <c r="D12" s="38"/>
-      <c r="E12" s="38"/>
-      <c r="F12" s="38"/>
-      <c r="G12" s="38"/>
-      <c r="H12" s="38"/>
-      <c r="I12" s="38"/>
-      <c r="J12" s="38"/>
-      <c r="L12" s="38"/>
-      <c r="M12" s="38"/>
-      <c r="N12" s="38"/>
-      <c r="O12" s="38"/>
-      <c r="P12" s="38"/>
-    </row>
-    <row r="13" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="35" t="s">
+    <row r="9" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="L9" s="34"/>
+    </row>
+    <row r="13" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" s="32" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="36" t="s">
+    <row r="14" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" s="33" t="s">
         <v>22</v>
       </c>
       <c r="E14" s="10"/>
     </row>
-    <row r="15" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="38"/>
-      <c r="B15" s="38"/>
-      <c r="C15" s="38"/>
-      <c r="D15" s="38"/>
-      <c r="E15" s="38"/>
-      <c r="F15" s="38"/>
-      <c r="G15" s="38"/>
-      <c r="H15" s="38"/>
-      <c r="I15" s="38"/>
-      <c r="J15" s="38"/>
-    </row>
-    <row r="16" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="38"/>
-      <c r="B16" s="38"/>
-      <c r="C16" s="38"/>
-      <c r="D16" s="38"/>
-      <c r="E16" s="38"/>
-      <c r="F16" s="38"/>
-      <c r="G16" s="38"/>
-      <c r="H16" s="38"/>
-      <c r="I16" s="38"/>
-      <c r="J16" s="38"/>
-    </row>
-    <row r="17" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17" s="38"/>
-      <c r="B17" s="38"/>
-      <c r="C17" s="38"/>
-      <c r="D17" s="38"/>
-      <c r="E17" s="38"/>
-      <c r="F17" s="38"/>
-      <c r="G17" s="38"/>
-      <c r="H17" s="38"/>
-      <c r="I17" s="38"/>
-      <c r="J17" s="38"/>
-    </row>
-    <row r="18" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18" s="40" t="s">
+    <row r="18" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18" s="35" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="19" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19" s="36" t="s">
+    <row r="19" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A19" s="33" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="20" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A20" s="38"/>
-      <c r="B20" s="38"/>
-      <c r="C20" s="38"/>
-      <c r="D20" s="38"/>
-      <c r="E20" s="38"/>
-      <c r="F20" s="38"/>
-      <c r="G20" s="38"/>
-      <c r="H20" s="38"/>
-      <c r="I20" s="38"/>
-      <c r="J20" s="38"/>
-      <c r="L20" s="41"/>
-      <c r="M20" s="38"/>
-      <c r="N20" s="38"/>
-      <c r="O20" s="38"/>
-      <c r="P20" s="38"/>
-    </row>
-    <row r="21" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A21" s="38"/>
-      <c r="B21" s="38"/>
-      <c r="C21" s="38"/>
-      <c r="D21" s="38"/>
-      <c r="E21" s="38"/>
-      <c r="F21" s="38"/>
-      <c r="G21" s="38"/>
-      <c r="H21" s="38"/>
-      <c r="I21" s="38"/>
-      <c r="J21" s="38"/>
-      <c r="L21" s="38"/>
-      <c r="M21" s="38"/>
-      <c r="N21" s="38"/>
-      <c r="O21" s="38"/>
-      <c r="P21" s="38"/>
-    </row>
-    <row r="22" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22" s="38"/>
-      <c r="B22" s="38"/>
-      <c r="C22" s="38"/>
-      <c r="D22" s="38"/>
-      <c r="E22" s="38"/>
-      <c r="F22" s="38"/>
-      <c r="G22" s="38"/>
-      <c r="H22" s="38"/>
-      <c r="I22" s="38"/>
-      <c r="J22" s="38"/>
-      <c r="L22" s="38"/>
-      <c r="M22" s="38"/>
-      <c r="N22" s="38"/>
-      <c r="O22" s="38"/>
-      <c r="P22" s="38"/>
-    </row>
-    <row r="23" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A23" s="38"/>
-      <c r="B23" s="38"/>
-      <c r="C23" s="38"/>
-      <c r="D23" s="38"/>
-      <c r="E23" s="38"/>
-      <c r="F23" s="38"/>
-      <c r="G23" s="38"/>
-      <c r="H23" s="38"/>
-      <c r="I23" s="38"/>
-      <c r="J23" s="38"/>
-      <c r="L23" s="38"/>
-      <c r="M23" s="38"/>
-      <c r="N23" s="38"/>
-      <c r="O23" s="38"/>
-      <c r="P23" s="38"/>
-    </row>
-    <row r="24" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A24" s="38"/>
-      <c r="B24" s="38"/>
-      <c r="C24" s="38"/>
-      <c r="D24" s="38"/>
-      <c r="E24" s="38"/>
-      <c r="F24" s="38"/>
-      <c r="G24" s="38"/>
-      <c r="H24" s="38"/>
-      <c r="I24" s="38"/>
-      <c r="J24" s="38"/>
-      <c r="L24" s="38"/>
-      <c r="M24" s="38"/>
-      <c r="N24" s="38"/>
-      <c r="O24" s="38"/>
-      <c r="P24" s="38"/>
-    </row>
-    <row r="25" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A25" s="34" t="s">
+    <row r="20" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="L20" s="36"/>
+    </row>
+    <row r="25" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A25" s="31" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="26" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26" s="36" t="s">
+    <row r="26" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A26" s="33" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="27" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A27" s="38"/>
-      <c r="B27" s="38"/>
-      <c r="C27" s="38"/>
-      <c r="D27" s="38"/>
-      <c r="E27" s="38"/>
-      <c r="F27" s="38"/>
-      <c r="G27" s="38"/>
-      <c r="H27" s="38"/>
-      <c r="I27" s="38"/>
-      <c r="J27" s="38"/>
-    </row>
-    <row r="28" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A28" s="38"/>
-      <c r="B28" s="38"/>
-      <c r="C28" s="38"/>
-      <c r="D28" s="38"/>
-      <c r="E28" s="38"/>
-      <c r="F28" s="38"/>
-      <c r="G28" s="38"/>
-      <c r="H28" s="38"/>
-      <c r="I28" s="38"/>
-      <c r="J28" s="38"/>
-    </row>
-    <row r="29" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A29" s="38"/>
-      <c r="B29" s="38"/>
-      <c r="C29" s="38"/>
-      <c r="D29" s="38"/>
-      <c r="E29" s="38"/>
-      <c r="F29" s="38"/>
-      <c r="G29" s="38"/>
-      <c r="H29" s="38"/>
-      <c r="I29" s="38"/>
-      <c r="J29" s="38"/>
-    </row>
-    <row r="30" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A30" s="38"/>
-      <c r="B30" s="38"/>
-      <c r="C30" s="38"/>
-      <c r="D30" s="38"/>
-      <c r="E30" s="38"/>
-      <c r="F30" s="38"/>
-      <c r="G30" s="38"/>
-      <c r="H30" s="38"/>
-      <c r="I30" s="38"/>
-      <c r="J30" s="38"/>
-    </row>
-    <row r="31" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A31" s="38"/>
-      <c r="B31" s="38"/>
-      <c r="C31" s="38"/>
-      <c r="D31" s="38"/>
-      <c r="E31" s="38"/>
-      <c r="F31" s="38"/>
-      <c r="G31" s="38"/>
-      <c r="H31" s="38"/>
-      <c r="I31" s="38"/>
-      <c r="J31" s="38"/>
-    </row>
-    <row r="32" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A32" s="34" t="s">
+    <row r="32" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A32" s="31" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="33" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A33" s="36" t="s">
+    <row r="33" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A33" s="33" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="34" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A34" s="38"/>
-      <c r="B34" s="38"/>
-      <c r="C34" s="38"/>
-      <c r="D34" s="38"/>
-      <c r="E34" s="38"/>
-      <c r="F34" s="38"/>
-      <c r="G34" s="38"/>
-      <c r="H34" s="38"/>
-      <c r="I34" s="38"/>
-      <c r="J34" s="38"/>
-      <c r="L34" s="41"/>
-      <c r="M34" s="38"/>
-      <c r="N34" s="38"/>
-      <c r="O34" s="38"/>
-      <c r="P34" s="38"/>
-    </row>
-    <row r="35" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A35" s="38"/>
-      <c r="B35" s="38"/>
-      <c r="C35" s="38"/>
-      <c r="D35" s="38"/>
-      <c r="E35" s="38"/>
-      <c r="F35" s="38"/>
-      <c r="G35" s="38"/>
-      <c r="H35" s="38"/>
-      <c r="I35" s="38"/>
-      <c r="J35" s="38"/>
-      <c r="L35" s="38"/>
-      <c r="M35" s="38"/>
-      <c r="N35" s="38"/>
-      <c r="O35" s="38"/>
-      <c r="P35" s="38"/>
-    </row>
-    <row r="36" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A36" s="38"/>
-      <c r="B36" s="38"/>
-      <c r="C36" s="38"/>
-      <c r="D36" s="38"/>
-      <c r="E36" s="38"/>
-      <c r="F36" s="38"/>
-      <c r="G36" s="38"/>
-      <c r="H36" s="38"/>
-      <c r="I36" s="38"/>
-      <c r="J36" s="38"/>
-      <c r="L36" s="38"/>
-      <c r="M36" s="38"/>
-      <c r="N36" s="38"/>
-      <c r="O36" s="38"/>
-      <c r="P36" s="38"/>
-    </row>
-    <row r="37" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A37" s="38"/>
-      <c r="B37" s="38"/>
-      <c r="C37" s="38"/>
-      <c r="D37" s="38"/>
-      <c r="E37" s="38"/>
-      <c r="F37" s="38"/>
-      <c r="G37" s="38"/>
-      <c r="H37" s="38"/>
-      <c r="I37" s="38"/>
-      <c r="J37" s="38"/>
-      <c r="L37" s="38"/>
-      <c r="M37" s="38"/>
-      <c r="N37" s="38"/>
-      <c r="O37" s="38"/>
-      <c r="P37" s="38"/>
-    </row>
-    <row r="39" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="L34" s="36"/>
+    </row>
+    <row r="39" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" t="s">
         <v>17</v>
       </c>
-      <c r="B39" s="38"/>
-      <c r="C39" s="38"/>
-      <c r="D39" s="38"/>
-      <c r="E39" s="38"/>
-      <c r="F39" s="38"/>
       <c r="I39" t="s">
         <v>19</v>
       </c>
-      <c r="J39" s="38"/>
-      <c r="K39" s="38"/>
-      <c r="L39" s="38"/>
-    </row>
-    <row r="40" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A40" s="42"/>
-      <c r="B40" s="42"/>
-      <c r="C40" s="42"/>
-      <c r="D40" s="42"/>
-      <c r="E40" s="42"/>
-      <c r="F40" s="38"/>
-      <c r="G40" s="38"/>
-      <c r="H40" s="38"/>
-      <c r="I40" s="42"/>
-      <c r="J40" s="42"/>
-      <c r="K40" s="42"/>
-      <c r="L40" s="42"/>
-    </row>
-    <row r="41" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A41" s="38" t="s">
+    </row>
+    <row r="40" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A40" s="37"/>
+      <c r="B40" s="37"/>
+      <c r="C40" s="37"/>
+      <c r="D40" s="37"/>
+      <c r="E40" s="37"/>
+      <c r="I40" s="37"/>
+      <c r="J40" s="37"/>
+      <c r="K40" s="37"/>
+      <c r="L40" s="37"/>
+    </row>
+    <row r="41" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A41" t="s">
         <v>18</v>
       </c>
-      <c r="B41" s="38"/>
-      <c r="C41" s="38"/>
-      <c r="D41" s="38"/>
-      <c r="E41" s="38"/>
-      <c r="F41" s="38"/>
-      <c r="G41" s="38"/>
-      <c r="H41" s="38"/>
-      <c r="I41" s="43" t="s">
+      <c r="I41" s="38" t="s">
         <v>19</v>
       </c>
-      <c r="J41" s="43"/>
-      <c r="K41" s="43"/>
-      <c r="L41" s="43"/>
-    </row>
-    <row r="42" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A42" s="42"/>
-      <c r="B42" s="42"/>
-      <c r="C42" s="42"/>
-      <c r="D42" s="42"/>
-      <c r="E42" s="42"/>
-      <c r="I42" s="44"/>
-      <c r="J42" s="44"/>
-      <c r="K42" s="44"/>
-      <c r="L42" s="44"/>
+      <c r="J41" s="38"/>
+      <c r="K41" s="38"/>
+      <c r="L41" s="38"/>
+    </row>
+    <row r="42" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A42" s="37"/>
+      <c r="B42" s="37"/>
+      <c r="C42" s="37"/>
+      <c r="D42" s="37"/>
+      <c r="E42" s="37"/>
+      <c r="I42" s="39"/>
+      <c r="J42" s="39"/>
+      <c r="K42" s="39"/>
+      <c r="L42" s="39"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
@@ -7917,46 +7541,46 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1" s="94" t="s">
+      <c r="A1" s="32" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="94"/>
-      <c r="C1" s="94"/>
+      <c r="B1" s="87"/>
+      <c r="C1" s="87"/>
     </row>
     <row r="2" spans="1:5" ht="26" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A2" s="95"/>
-      <c r="B2" s="96"/>
-      <c r="C2" s="96"/>
+      <c r="A2" s="88"/>
+      <c r="B2" s="89"/>
+      <c r="C2" s="89"/>
       <c r="D2" s="8"/>
       <c r="E2" s="9"/>
     </row>
     <row r="3" spans="1:5" ht="11.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="94"/>
-      <c r="B3" s="94"/>
-      <c r="C3" s="94"/>
+      <c r="A3" s="87"/>
+      <c r="B3" s="87"/>
+      <c r="C3" s="87"/>
     </row>
     <row r="4" spans="1:5" ht="26.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="94" t="s">
+      <c r="A4" s="32" t="s">
         <v>25</v>
       </c>
-      <c r="B4" s="94"/>
-      <c r="C4" s="94"/>
+      <c r="B4" s="87"/>
+      <c r="C4" s="87"/>
     </row>
     <row r="5" spans="1:5" ht="11.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.6"/>
     <row r="6" spans="1:5" ht="68" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A6" s="45" t="s">
+      <c r="A6" s="40" t="s">
         <v>26</v>
       </c>
-      <c r="B6" s="46" t="s">
+      <c r="B6" s="41" t="s">
         <v>27</v>
       </c>
-      <c r="C6" s="47" t="s">
+      <c r="C6" s="42" t="s">
         <v>28</v>
       </c>
-      <c r="D6" s="47" t="s">
+      <c r="D6" s="42" t="s">
         <v>109</v>
       </c>
-      <c r="E6" s="48" t="s">
+      <c r="E6" s="43" t="s">
         <v>29</v>
       </c>
     </row>
@@ -8069,7 +7693,7 @@
       <c r="Q2" s="22"/>
     </row>
     <row r="3" spans="1:30" ht="22.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="M3" s="49" t="s">
+      <c r="M3" s="44" t="s">
         <v>30</v>
       </c>
       <c r="N3" s="23"/>
@@ -8083,763 +7707,763 @@
       <c r="O4" s="26"/>
       <c r="P4" s="26"/>
       <c r="Q4" s="27"/>
-      <c r="R4" s="50" t="s">
+      <c r="R4" s="34" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="5" spans="1:30" ht="20" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="36"/>
-      <c r="B5" s="36"/>
-      <c r="C5" s="36"/>
-      <c r="D5" s="36"/>
-      <c r="E5" s="36"/>
-      <c r="F5" s="36"/>
-      <c r="G5" s="36"/>
-      <c r="H5" s="36"/>
-      <c r="I5" s="36"/>
-      <c r="J5" s="36"/>
-      <c r="K5" s="36"/>
-      <c r="L5" s="36"/>
-      <c r="M5" s="36"/>
-      <c r="N5" s="36"/>
-      <c r="O5" s="36"/>
-      <c r="P5" s="36"/>
-      <c r="Q5" s="36"/>
-      <c r="R5" s="50" t="s">
+      <c r="A5" s="33"/>
+      <c r="B5" s="33"/>
+      <c r="C5" s="33"/>
+      <c r="D5" s="33"/>
+      <c r="E5" s="33"/>
+      <c r="F5" s="33"/>
+      <c r="G5" s="33"/>
+      <c r="H5" s="33"/>
+      <c r="I5" s="33"/>
+      <c r="J5" s="33"/>
+      <c r="K5" s="33"/>
+      <c r="L5" s="33"/>
+      <c r="M5" s="33"/>
+      <c r="N5" s="33"/>
+      <c r="O5" s="33"/>
+      <c r="P5" s="33"/>
+      <c r="Q5" s="33"/>
+      <c r="R5" s="34" t="s">
         <v>111</v>
       </c>
-      <c r="S5" s="36"/>
-      <c r="T5" s="36"/>
-      <c r="U5" s="36"/>
-      <c r="V5" s="36"/>
-      <c r="W5" s="36"/>
-      <c r="X5" s="36"/>
-      <c r="Y5" s="36"/>
-      <c r="Z5" s="36"/>
-      <c r="AA5" s="36"/>
-      <c r="AB5" s="36"/>
-      <c r="AC5" s="36"/>
-      <c r="AD5" s="36"/>
+      <c r="S5" s="33"/>
+      <c r="T5" s="33"/>
+      <c r="U5" s="33"/>
+      <c r="V5" s="33"/>
+      <c r="W5" s="33"/>
+      <c r="X5" s="33"/>
+      <c r="Y5" s="33"/>
+      <c r="Z5" s="33"/>
+      <c r="AA5" s="33"/>
+      <c r="AB5" s="33"/>
+      <c r="AC5" s="33"/>
+      <c r="AD5" s="33"/>
     </row>
     <row r="6" spans="1:30" ht="20.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A6" s="36"/>
-      <c r="B6" s="36"/>
-      <c r="C6" s="36"/>
-      <c r="D6" s="36"/>
-      <c r="E6" s="36"/>
-      <c r="F6" s="36"/>
-      <c r="G6" s="36"/>
-      <c r="H6" s="36"/>
-      <c r="I6" s="36"/>
-      <c r="J6" s="36"/>
-      <c r="K6" s="36"/>
-      <c r="L6" s="36"/>
-      <c r="M6" s="36"/>
-      <c r="N6" s="36"/>
-      <c r="O6" s="36"/>
-      <c r="P6" s="36"/>
-      <c r="Q6" s="36"/>
-      <c r="R6" s="36"/>
-      <c r="S6" s="36"/>
-      <c r="T6" s="36"/>
-      <c r="U6" s="36"/>
-      <c r="V6" s="36"/>
-      <c r="W6" s="36"/>
-      <c r="X6" s="36"/>
-      <c r="Y6" s="36"/>
-      <c r="Z6" s="36"/>
-      <c r="AA6" s="36"/>
-      <c r="AB6" s="36"/>
-      <c r="AC6" s="36"/>
-      <c r="AD6" s="36"/>
+      <c r="A6" s="33"/>
+      <c r="B6" s="33"/>
+      <c r="C6" s="33"/>
+      <c r="D6" s="33"/>
+      <c r="E6" s="33"/>
+      <c r="F6" s="33"/>
+      <c r="G6" s="33"/>
+      <c r="H6" s="33"/>
+      <c r="I6" s="33"/>
+      <c r="J6" s="33"/>
+      <c r="K6" s="33"/>
+      <c r="L6" s="33"/>
+      <c r="M6" s="33"/>
+      <c r="N6" s="33"/>
+      <c r="O6" s="33"/>
+      <c r="P6" s="33"/>
+      <c r="Q6" s="33"/>
+      <c r="R6" s="33"/>
+      <c r="S6" s="33"/>
+      <c r="T6" s="33"/>
+      <c r="U6" s="33"/>
+      <c r="V6" s="33"/>
+      <c r="W6" s="33"/>
+      <c r="X6" s="33"/>
+      <c r="Y6" s="33"/>
+      <c r="Z6" s="33"/>
+      <c r="AA6" s="33"/>
+      <c r="AB6" s="33"/>
+      <c r="AC6" s="33"/>
+      <c r="AD6" s="33"/>
     </row>
     <row r="7" spans="1:30" ht="20" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="51">
+      <c r="A7" s="45">
         <v>1</v>
       </c>
-      <c r="B7" s="52"/>
-      <c r="C7" s="52"/>
-      <c r="D7" s="53"/>
-      <c r="E7" s="36"/>
-      <c r="F7" s="51">
+      <c r="B7" s="46"/>
+      <c r="C7" s="46"/>
+      <c r="D7" s="47"/>
+      <c r="E7" s="33"/>
+      <c r="F7" s="45">
         <v>2</v>
       </c>
-      <c r="G7" s="52"/>
-      <c r="H7" s="52"/>
-      <c r="I7" s="53"/>
-      <c r="J7" s="36"/>
-      <c r="K7" s="51"/>
-      <c r="L7" s="52"/>
-      <c r="M7" s="52"/>
-      <c r="N7" s="53"/>
-      <c r="O7" s="36"/>
-      <c r="P7" s="51"/>
-      <c r="Q7" s="52"/>
-      <c r="R7" s="52"/>
-      <c r="S7" s="53"/>
-      <c r="T7" s="36"/>
-      <c r="U7" s="51"/>
-      <c r="V7" s="52"/>
-      <c r="W7" s="52"/>
-      <c r="X7" s="53"/>
-      <c r="Y7" s="36"/>
-      <c r="Z7" s="51"/>
-      <c r="AA7" s="52"/>
-      <c r="AB7" s="52"/>
-      <c r="AC7" s="53"/>
-      <c r="AD7" s="36"/>
+      <c r="G7" s="46"/>
+      <c r="H7" s="46"/>
+      <c r="I7" s="47"/>
+      <c r="J7" s="33"/>
+      <c r="K7" s="45"/>
+      <c r="L7" s="46"/>
+      <c r="M7" s="46"/>
+      <c r="N7" s="47"/>
+      <c r="O7" s="33"/>
+      <c r="P7" s="45"/>
+      <c r="Q7" s="46"/>
+      <c r="R7" s="46"/>
+      <c r="S7" s="47"/>
+      <c r="T7" s="33"/>
+      <c r="U7" s="45"/>
+      <c r="V7" s="46"/>
+      <c r="W7" s="46"/>
+      <c r="X7" s="47"/>
+      <c r="Y7" s="33"/>
+      <c r="Z7" s="45"/>
+      <c r="AA7" s="46"/>
+      <c r="AB7" s="46"/>
+      <c r="AC7" s="47"/>
+      <c r="AD7" s="33"/>
     </row>
     <row r="8" spans="1:30" ht="20" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="54"/>
-      <c r="B8" s="55"/>
-      <c r="C8" s="55"/>
-      <c r="D8" s="56"/>
-      <c r="E8" s="36"/>
-      <c r="F8" s="54"/>
-      <c r="G8" s="55"/>
-      <c r="H8" s="55"/>
-      <c r="I8" s="56"/>
-      <c r="J8" s="36"/>
-      <c r="K8" s="54"/>
-      <c r="L8" s="55"/>
-      <c r="M8" s="55"/>
-      <c r="N8" s="56"/>
-      <c r="O8" s="36"/>
-      <c r="P8" s="54"/>
-      <c r="Q8" s="55"/>
-      <c r="R8" s="55"/>
-      <c r="S8" s="56"/>
-      <c r="T8" s="36"/>
-      <c r="U8" s="54"/>
-      <c r="V8" s="55"/>
-      <c r="W8" s="55"/>
-      <c r="X8" s="56"/>
-      <c r="Y8" s="36"/>
-      <c r="Z8" s="54"/>
-      <c r="AA8" s="55"/>
-      <c r="AB8" s="55"/>
-      <c r="AC8" s="56"/>
-      <c r="AD8" s="36"/>
+      <c r="A8" s="48"/>
+      <c r="B8" s="49"/>
+      <c r="C8" s="49"/>
+      <c r="D8" s="50"/>
+      <c r="E8" s="33"/>
+      <c r="F8" s="48"/>
+      <c r="G8" s="49"/>
+      <c r="H8" s="49"/>
+      <c r="I8" s="50"/>
+      <c r="J8" s="33"/>
+      <c r="K8" s="48"/>
+      <c r="L8" s="49"/>
+      <c r="M8" s="49"/>
+      <c r="N8" s="50"/>
+      <c r="O8" s="33"/>
+      <c r="P8" s="48"/>
+      <c r="Q8" s="49"/>
+      <c r="R8" s="49"/>
+      <c r="S8" s="50"/>
+      <c r="T8" s="33"/>
+      <c r="U8" s="48"/>
+      <c r="V8" s="49"/>
+      <c r="W8" s="49"/>
+      <c r="X8" s="50"/>
+      <c r="Y8" s="33"/>
+      <c r="Z8" s="48"/>
+      <c r="AA8" s="49"/>
+      <c r="AB8" s="49"/>
+      <c r="AC8" s="50"/>
+      <c r="AD8" s="33"/>
     </row>
     <row r="9" spans="1:30" ht="20.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A9" s="57"/>
-      <c r="B9" s="58"/>
-      <c r="C9" s="58"/>
-      <c r="D9" s="59"/>
-      <c r="E9" s="36"/>
-      <c r="F9" s="57"/>
-      <c r="G9" s="58"/>
-      <c r="H9" s="58"/>
-      <c r="I9" s="59"/>
-      <c r="J9" s="36"/>
-      <c r="K9" s="57"/>
-      <c r="L9" s="58"/>
-      <c r="M9" s="58"/>
-      <c r="N9" s="59"/>
-      <c r="O9" s="36"/>
-      <c r="P9" s="57"/>
-      <c r="Q9" s="58"/>
-      <c r="R9" s="58"/>
-      <c r="S9" s="59"/>
-      <c r="T9" s="36"/>
-      <c r="U9" s="57"/>
-      <c r="V9" s="58"/>
-      <c r="W9" s="58"/>
-      <c r="X9" s="59"/>
-      <c r="Y9" s="36"/>
-      <c r="Z9" s="57"/>
-      <c r="AA9" s="58"/>
-      <c r="AB9" s="58"/>
-      <c r="AC9" s="59"/>
-      <c r="AD9" s="36"/>
+      <c r="A9" s="51"/>
+      <c r="B9" s="52"/>
+      <c r="C9" s="52"/>
+      <c r="D9" s="53"/>
+      <c r="E9" s="33"/>
+      <c r="F9" s="51"/>
+      <c r="G9" s="52"/>
+      <c r="H9" s="52"/>
+      <c r="I9" s="53"/>
+      <c r="J9" s="33"/>
+      <c r="K9" s="51"/>
+      <c r="L9" s="52"/>
+      <c r="M9" s="52"/>
+      <c r="N9" s="53"/>
+      <c r="O9" s="33"/>
+      <c r="P9" s="51"/>
+      <c r="Q9" s="52"/>
+      <c r="R9" s="52"/>
+      <c r="S9" s="53"/>
+      <c r="T9" s="33"/>
+      <c r="U9" s="51"/>
+      <c r="V9" s="52"/>
+      <c r="W9" s="52"/>
+      <c r="X9" s="53"/>
+      <c r="Y9" s="33"/>
+      <c r="Z9" s="51"/>
+      <c r="AA9" s="52"/>
+      <c r="AB9" s="52"/>
+      <c r="AC9" s="53"/>
+      <c r="AD9" s="33"/>
     </row>
     <row r="10" spans="1:30" ht="20.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A10" s="36"/>
-      <c r="B10" s="36"/>
-      <c r="C10" s="36"/>
-      <c r="D10" s="36"/>
-      <c r="E10" s="36"/>
-      <c r="F10" s="36"/>
-      <c r="G10" s="36"/>
-      <c r="H10" s="36"/>
-      <c r="I10" s="36"/>
-      <c r="J10" s="36"/>
-      <c r="K10" s="36"/>
-      <c r="L10" s="36"/>
-      <c r="M10" s="36"/>
-      <c r="N10" s="36"/>
-      <c r="O10" s="36"/>
-      <c r="P10" s="36"/>
-      <c r="Q10" s="36"/>
-      <c r="R10" s="36"/>
-      <c r="S10" s="36"/>
-      <c r="T10" s="36"/>
-      <c r="U10" s="36"/>
-      <c r="V10" s="36"/>
-      <c r="W10" s="36"/>
-      <c r="X10" s="36"/>
-      <c r="Y10" s="36"/>
-      <c r="Z10" s="36"/>
-      <c r="AA10" s="36"/>
-      <c r="AB10" s="36"/>
-      <c r="AC10" s="36"/>
-      <c r="AD10" s="36"/>
+      <c r="A10" s="33"/>
+      <c r="B10" s="33"/>
+      <c r="C10" s="33"/>
+      <c r="D10" s="33"/>
+      <c r="E10" s="33"/>
+      <c r="F10" s="33"/>
+      <c r="G10" s="33"/>
+      <c r="H10" s="33"/>
+      <c r="I10" s="33"/>
+      <c r="J10" s="33"/>
+      <c r="K10" s="33"/>
+      <c r="L10" s="33"/>
+      <c r="M10" s="33"/>
+      <c r="N10" s="33"/>
+      <c r="O10" s="33"/>
+      <c r="P10" s="33"/>
+      <c r="Q10" s="33"/>
+      <c r="R10" s="33"/>
+      <c r="S10" s="33"/>
+      <c r="T10" s="33"/>
+      <c r="U10" s="33"/>
+      <c r="V10" s="33"/>
+      <c r="W10" s="33"/>
+      <c r="X10" s="33"/>
+      <c r="Y10" s="33"/>
+      <c r="Z10" s="33"/>
+      <c r="AA10" s="33"/>
+      <c r="AB10" s="33"/>
+      <c r="AC10" s="33"/>
+      <c r="AD10" s="33"/>
     </row>
     <row r="11" spans="1:30" ht="20" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="36"/>
-      <c r="B11" s="68">
+      <c r="A11" s="33"/>
+      <c r="B11" s="62">
         <v>1.1000000000000001</v>
       </c>
-      <c r="C11" s="61"/>
-      <c r="D11" s="62"/>
-      <c r="E11" s="36"/>
-      <c r="F11" s="36"/>
-      <c r="G11" s="60">
+      <c r="C11" s="55"/>
+      <c r="D11" s="56"/>
+      <c r="E11" s="33"/>
+      <c r="F11" s="33"/>
+      <c r="G11" s="54">
         <v>2.1</v>
       </c>
-      <c r="H11" s="61"/>
-      <c r="I11" s="62"/>
-      <c r="J11" s="36"/>
-      <c r="K11" s="36"/>
-      <c r="L11" s="60"/>
-      <c r="M11" s="61"/>
-      <c r="N11" s="62"/>
-      <c r="O11" s="36"/>
-      <c r="P11" s="36"/>
-      <c r="Q11" s="60"/>
-      <c r="R11" s="61"/>
-      <c r="S11" s="62"/>
-      <c r="T11" s="36"/>
-      <c r="U11" s="36"/>
-      <c r="V11" s="60"/>
-      <c r="W11" s="61"/>
-      <c r="X11" s="62"/>
-      <c r="Y11" s="36"/>
-      <c r="Z11" s="36"/>
-      <c r="AA11" s="60"/>
-      <c r="AB11" s="61"/>
-      <c r="AC11" s="62"/>
-      <c r="AD11" s="36"/>
+      <c r="H11" s="55"/>
+      <c r="I11" s="56"/>
+      <c r="J11" s="33"/>
+      <c r="K11" s="33"/>
+      <c r="L11" s="54"/>
+      <c r="M11" s="55"/>
+      <c r="N11" s="56"/>
+      <c r="O11" s="33"/>
+      <c r="P11" s="33"/>
+      <c r="Q11" s="54"/>
+      <c r="R11" s="55"/>
+      <c r="S11" s="56"/>
+      <c r="T11" s="33"/>
+      <c r="U11" s="33"/>
+      <c r="V11" s="54"/>
+      <c r="W11" s="55"/>
+      <c r="X11" s="56"/>
+      <c r="Y11" s="33"/>
+      <c r="Z11" s="33"/>
+      <c r="AA11" s="54"/>
+      <c r="AB11" s="55"/>
+      <c r="AC11" s="56"/>
+      <c r="AD11" s="33"/>
     </row>
     <row r="12" spans="1:30" ht="20" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" s="36"/>
-      <c r="B12" s="63"/>
-      <c r="C12" s="36"/>
-      <c r="D12" s="64"/>
-      <c r="E12" s="36"/>
-      <c r="F12" s="36"/>
-      <c r="G12" s="63"/>
-      <c r="H12" s="36"/>
-      <c r="I12" s="64"/>
-      <c r="J12" s="36"/>
-      <c r="K12" s="36"/>
-      <c r="L12" s="63"/>
-      <c r="M12" s="36"/>
-      <c r="N12" s="64"/>
-      <c r="O12" s="36"/>
-      <c r="P12" s="36"/>
-      <c r="Q12" s="63"/>
-      <c r="R12" s="36"/>
-      <c r="S12" s="64"/>
-      <c r="T12" s="36"/>
-      <c r="U12" s="36"/>
-      <c r="V12" s="63"/>
-      <c r="W12" s="36"/>
-      <c r="X12" s="64"/>
-      <c r="Y12" s="36"/>
-      <c r="Z12" s="36"/>
-      <c r="AA12" s="63"/>
-      <c r="AB12" s="36"/>
-      <c r="AC12" s="64"/>
-      <c r="AD12" s="36"/>
+      <c r="A12" s="33"/>
+      <c r="B12" s="57"/>
+      <c r="C12" s="33"/>
+      <c r="D12" s="58"/>
+      <c r="E12" s="33"/>
+      <c r="F12" s="33"/>
+      <c r="G12" s="57"/>
+      <c r="H12" s="33"/>
+      <c r="I12" s="58"/>
+      <c r="J12" s="33"/>
+      <c r="K12" s="33"/>
+      <c r="L12" s="57"/>
+      <c r="M12" s="33"/>
+      <c r="N12" s="58"/>
+      <c r="O12" s="33"/>
+      <c r="P12" s="33"/>
+      <c r="Q12" s="57"/>
+      <c r="R12" s="33"/>
+      <c r="S12" s="58"/>
+      <c r="T12" s="33"/>
+      <c r="U12" s="33"/>
+      <c r="V12" s="57"/>
+      <c r="W12" s="33"/>
+      <c r="X12" s="58"/>
+      <c r="Y12" s="33"/>
+      <c r="Z12" s="33"/>
+      <c r="AA12" s="57"/>
+      <c r="AB12" s="33"/>
+      <c r="AC12" s="58"/>
+      <c r="AD12" s="33"/>
     </row>
     <row r="13" spans="1:30" ht="20.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A13" s="36"/>
-      <c r="B13" s="65"/>
-      <c r="C13" s="66"/>
-      <c r="D13" s="67"/>
-      <c r="E13" s="36"/>
-      <c r="F13" s="36"/>
-      <c r="G13" s="65"/>
-      <c r="H13" s="66"/>
-      <c r="I13" s="67"/>
-      <c r="J13" s="36"/>
-      <c r="K13" s="36"/>
-      <c r="L13" s="65"/>
-      <c r="M13" s="66"/>
-      <c r="N13" s="67"/>
-      <c r="O13" s="36"/>
-      <c r="P13" s="36"/>
-      <c r="Q13" s="65"/>
-      <c r="R13" s="66"/>
-      <c r="S13" s="67"/>
-      <c r="T13" s="36"/>
-      <c r="U13" s="36"/>
-      <c r="V13" s="65"/>
-      <c r="W13" s="66"/>
-      <c r="X13" s="67"/>
-      <c r="Y13" s="36"/>
-      <c r="Z13" s="36"/>
-      <c r="AA13" s="65"/>
-      <c r="AB13" s="66"/>
-      <c r="AC13" s="67"/>
-      <c r="AD13" s="36"/>
+      <c r="A13" s="33"/>
+      <c r="B13" s="59"/>
+      <c r="C13" s="60"/>
+      <c r="D13" s="61"/>
+      <c r="E13" s="33"/>
+      <c r="F13" s="33"/>
+      <c r="G13" s="59"/>
+      <c r="H13" s="60"/>
+      <c r="I13" s="61"/>
+      <c r="J13" s="33"/>
+      <c r="K13" s="33"/>
+      <c r="L13" s="59"/>
+      <c r="M13" s="60"/>
+      <c r="N13" s="61"/>
+      <c r="O13" s="33"/>
+      <c r="P13" s="33"/>
+      <c r="Q13" s="59"/>
+      <c r="R13" s="60"/>
+      <c r="S13" s="61"/>
+      <c r="T13" s="33"/>
+      <c r="U13" s="33"/>
+      <c r="V13" s="59"/>
+      <c r="W13" s="60"/>
+      <c r="X13" s="61"/>
+      <c r="Y13" s="33"/>
+      <c r="Z13" s="33"/>
+      <c r="AA13" s="59"/>
+      <c r="AB13" s="60"/>
+      <c r="AC13" s="61"/>
+      <c r="AD13" s="33"/>
     </row>
     <row r="14" spans="1:30" ht="20.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A14" s="36"/>
-      <c r="B14" s="36"/>
-      <c r="C14" s="36"/>
-      <c r="D14" s="36"/>
-      <c r="E14" s="36"/>
-      <c r="F14" s="36"/>
-      <c r="G14" s="36"/>
-      <c r="H14" s="36"/>
-      <c r="I14" s="36"/>
-      <c r="J14" s="36"/>
-      <c r="K14" s="36"/>
-      <c r="L14" s="36"/>
-      <c r="M14" s="36"/>
-      <c r="N14" s="36"/>
-      <c r="O14" s="36"/>
-      <c r="P14" s="36"/>
-      <c r="Q14" s="36"/>
-      <c r="R14" s="36"/>
-      <c r="S14" s="36"/>
-      <c r="T14" s="36"/>
-      <c r="U14" s="36"/>
-      <c r="V14" s="36"/>
-      <c r="W14" s="36"/>
-      <c r="X14" s="36"/>
-      <c r="Y14" s="36"/>
-      <c r="Z14" s="36"/>
-      <c r="AA14" s="36"/>
-      <c r="AB14" s="36"/>
-      <c r="AC14" s="36"/>
-      <c r="AD14" s="36"/>
+      <c r="A14" s="33"/>
+      <c r="B14" s="33"/>
+      <c r="C14" s="33"/>
+      <c r="D14" s="33"/>
+      <c r="E14" s="33"/>
+      <c r="F14" s="33"/>
+      <c r="G14" s="33"/>
+      <c r="H14" s="33"/>
+      <c r="I14" s="33"/>
+      <c r="J14" s="33"/>
+      <c r="K14" s="33"/>
+      <c r="L14" s="33"/>
+      <c r="M14" s="33"/>
+      <c r="N14" s="33"/>
+      <c r="O14" s="33"/>
+      <c r="P14" s="33"/>
+      <c r="Q14" s="33"/>
+      <c r="R14" s="33"/>
+      <c r="S14" s="33"/>
+      <c r="T14" s="33"/>
+      <c r="U14" s="33"/>
+      <c r="V14" s="33"/>
+      <c r="W14" s="33"/>
+      <c r="X14" s="33"/>
+      <c r="Y14" s="33"/>
+      <c r="Z14" s="33"/>
+      <c r="AA14" s="33"/>
+      <c r="AB14" s="33"/>
+      <c r="AC14" s="33"/>
+      <c r="AD14" s="33"/>
     </row>
     <row r="15" spans="1:30" ht="20" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="36"/>
-      <c r="B15" s="60">
+      <c r="A15" s="33"/>
+      <c r="B15" s="54">
         <v>1.2</v>
       </c>
-      <c r="C15" s="61"/>
-      <c r="D15" s="62"/>
-      <c r="E15" s="36"/>
-      <c r="F15" s="36"/>
-      <c r="G15" s="60">
+      <c r="C15" s="55"/>
+      <c r="D15" s="56"/>
+      <c r="E15" s="33"/>
+      <c r="F15" s="33"/>
+      <c r="G15" s="54">
         <v>2.2000000000000002</v>
       </c>
-      <c r="H15" s="61"/>
-      <c r="I15" s="62"/>
-      <c r="J15" s="36"/>
-      <c r="K15" s="36"/>
-      <c r="L15" s="60"/>
-      <c r="M15" s="61"/>
-      <c r="N15" s="62"/>
-      <c r="O15" s="36"/>
-      <c r="P15" s="36"/>
-      <c r="Q15" s="60"/>
-      <c r="R15" s="61"/>
-      <c r="S15" s="62"/>
-      <c r="T15" s="36"/>
-      <c r="U15" s="36"/>
-      <c r="V15" s="60"/>
-      <c r="W15" s="61"/>
-      <c r="X15" s="62"/>
-      <c r="Y15" s="36"/>
-      <c r="Z15" s="36"/>
-      <c r="AA15" s="60"/>
-      <c r="AB15" s="61"/>
-      <c r="AC15" s="62"/>
-      <c r="AD15" s="36"/>
+      <c r="H15" s="55"/>
+      <c r="I15" s="56"/>
+      <c r="J15" s="33"/>
+      <c r="K15" s="33"/>
+      <c r="L15" s="54"/>
+      <c r="M15" s="55"/>
+      <c r="N15" s="56"/>
+      <c r="O15" s="33"/>
+      <c r="P15" s="33"/>
+      <c r="Q15" s="54"/>
+      <c r="R15" s="55"/>
+      <c r="S15" s="56"/>
+      <c r="T15" s="33"/>
+      <c r="U15" s="33"/>
+      <c r="V15" s="54"/>
+      <c r="W15" s="55"/>
+      <c r="X15" s="56"/>
+      <c r="Y15" s="33"/>
+      <c r="Z15" s="33"/>
+      <c r="AA15" s="54"/>
+      <c r="AB15" s="55"/>
+      <c r="AC15" s="56"/>
+      <c r="AD15" s="33"/>
     </row>
     <row r="16" spans="1:30" ht="20" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="36"/>
-      <c r="B16" s="63"/>
-      <c r="C16" s="36"/>
-      <c r="D16" s="64"/>
-      <c r="E16" s="36"/>
-      <c r="F16" s="36"/>
-      <c r="G16" s="63"/>
-      <c r="H16" s="36"/>
-      <c r="I16" s="64"/>
-      <c r="J16" s="36"/>
-      <c r="K16" s="36"/>
-      <c r="L16" s="63"/>
-      <c r="M16" s="36"/>
-      <c r="N16" s="64"/>
-      <c r="O16" s="36"/>
-      <c r="P16" s="36"/>
-      <c r="Q16" s="63"/>
-      <c r="R16" s="36"/>
-      <c r="S16" s="64"/>
-      <c r="T16" s="36"/>
-      <c r="U16" s="36"/>
-      <c r="V16" s="63"/>
-      <c r="W16" s="36"/>
-      <c r="X16" s="64"/>
-      <c r="Y16" s="36"/>
-      <c r="Z16" s="36"/>
-      <c r="AA16" s="63"/>
-      <c r="AB16" s="36"/>
-      <c r="AC16" s="64"/>
-      <c r="AD16" s="36"/>
+      <c r="A16" s="33"/>
+      <c r="B16" s="57"/>
+      <c r="C16" s="33"/>
+      <c r="D16" s="58"/>
+      <c r="E16" s="33"/>
+      <c r="F16" s="33"/>
+      <c r="G16" s="57"/>
+      <c r="H16" s="33"/>
+      <c r="I16" s="58"/>
+      <c r="J16" s="33"/>
+      <c r="K16" s="33"/>
+      <c r="L16" s="57"/>
+      <c r="M16" s="33"/>
+      <c r="N16" s="58"/>
+      <c r="O16" s="33"/>
+      <c r="P16" s="33"/>
+      <c r="Q16" s="57"/>
+      <c r="R16" s="33"/>
+      <c r="S16" s="58"/>
+      <c r="T16" s="33"/>
+      <c r="U16" s="33"/>
+      <c r="V16" s="57"/>
+      <c r="W16" s="33"/>
+      <c r="X16" s="58"/>
+      <c r="Y16" s="33"/>
+      <c r="Z16" s="33"/>
+      <c r="AA16" s="57"/>
+      <c r="AB16" s="33"/>
+      <c r="AC16" s="58"/>
+      <c r="AD16" s="33"/>
     </row>
     <row r="17" spans="1:30" ht="20.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A17" s="36"/>
-      <c r="B17" s="65"/>
-      <c r="C17" s="66"/>
-      <c r="D17" s="67"/>
-      <c r="E17" s="36"/>
-      <c r="F17" s="36"/>
-      <c r="G17" s="65"/>
-      <c r="H17" s="66"/>
-      <c r="I17" s="67"/>
-      <c r="J17" s="36"/>
-      <c r="K17" s="36"/>
-      <c r="L17" s="65"/>
-      <c r="M17" s="66"/>
-      <c r="N17" s="67"/>
-      <c r="O17" s="36"/>
-      <c r="P17" s="36"/>
-      <c r="Q17" s="65"/>
-      <c r="R17" s="66"/>
-      <c r="S17" s="67"/>
-      <c r="T17" s="36"/>
-      <c r="U17" s="36"/>
-      <c r="V17" s="65"/>
-      <c r="W17" s="66"/>
-      <c r="X17" s="67"/>
-      <c r="Y17" s="36"/>
-      <c r="Z17" s="36"/>
-      <c r="AA17" s="65"/>
-      <c r="AB17" s="66"/>
-      <c r="AC17" s="67"/>
-      <c r="AD17" s="36"/>
+      <c r="A17" s="33"/>
+      <c r="B17" s="59"/>
+      <c r="C17" s="60"/>
+      <c r="D17" s="61"/>
+      <c r="E17" s="33"/>
+      <c r="F17" s="33"/>
+      <c r="G17" s="59"/>
+      <c r="H17" s="60"/>
+      <c r="I17" s="61"/>
+      <c r="J17" s="33"/>
+      <c r="K17" s="33"/>
+      <c r="L17" s="59"/>
+      <c r="M17" s="60"/>
+      <c r="N17" s="61"/>
+      <c r="O17" s="33"/>
+      <c r="P17" s="33"/>
+      <c r="Q17" s="59"/>
+      <c r="R17" s="60"/>
+      <c r="S17" s="61"/>
+      <c r="T17" s="33"/>
+      <c r="U17" s="33"/>
+      <c r="V17" s="59"/>
+      <c r="W17" s="60"/>
+      <c r="X17" s="61"/>
+      <c r="Y17" s="33"/>
+      <c r="Z17" s="33"/>
+      <c r="AA17" s="59"/>
+      <c r="AB17" s="60"/>
+      <c r="AC17" s="61"/>
+      <c r="AD17" s="33"/>
     </row>
     <row r="18" spans="1:30" ht="20.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A18" s="36"/>
-      <c r="B18" s="36"/>
-      <c r="C18" s="36"/>
-      <c r="D18" s="36"/>
-      <c r="E18" s="36"/>
-      <c r="F18" s="36"/>
-      <c r="G18" s="36"/>
-      <c r="H18" s="36"/>
-      <c r="I18" s="36"/>
-      <c r="J18" s="36"/>
-      <c r="K18" s="36"/>
-      <c r="L18" s="36"/>
-      <c r="M18" s="36"/>
-      <c r="N18" s="36"/>
-      <c r="O18" s="36"/>
-      <c r="P18" s="36"/>
-      <c r="Q18" s="36"/>
-      <c r="R18" s="36"/>
-      <c r="S18" s="36"/>
-      <c r="T18" s="36"/>
-      <c r="U18" s="36"/>
-      <c r="V18" s="36"/>
-      <c r="W18" s="36"/>
-      <c r="X18" s="36"/>
-      <c r="Y18" s="36"/>
-      <c r="Z18" s="36"/>
-      <c r="AA18" s="36"/>
-      <c r="AB18" s="36"/>
-      <c r="AC18" s="36"/>
-      <c r="AD18" s="36"/>
+      <c r="A18" s="33"/>
+      <c r="B18" s="33"/>
+      <c r="C18" s="33"/>
+      <c r="D18" s="33"/>
+      <c r="E18" s="33"/>
+      <c r="F18" s="33"/>
+      <c r="G18" s="33"/>
+      <c r="H18" s="33"/>
+      <c r="I18" s="33"/>
+      <c r="J18" s="33"/>
+      <c r="K18" s="33"/>
+      <c r="L18" s="33"/>
+      <c r="M18" s="33"/>
+      <c r="N18" s="33"/>
+      <c r="O18" s="33"/>
+      <c r="P18" s="33"/>
+      <c r="Q18" s="33"/>
+      <c r="R18" s="33"/>
+      <c r="S18" s="33"/>
+      <c r="T18" s="33"/>
+      <c r="U18" s="33"/>
+      <c r="V18" s="33"/>
+      <c r="W18" s="33"/>
+      <c r="X18" s="33"/>
+      <c r="Y18" s="33"/>
+      <c r="Z18" s="33"/>
+      <c r="AA18" s="33"/>
+      <c r="AB18" s="33"/>
+      <c r="AC18" s="33"/>
+      <c r="AD18" s="33"/>
     </row>
     <row r="19" spans="1:30" ht="20" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19" s="36"/>
-      <c r="B19" s="60">
+      <c r="A19" s="33"/>
+      <c r="B19" s="54">
         <v>1.3</v>
       </c>
-      <c r="C19" s="61"/>
-      <c r="D19" s="62"/>
-      <c r="E19" s="36"/>
-      <c r="F19" s="36"/>
-      <c r="G19" s="60">
+      <c r="C19" s="55"/>
+      <c r="D19" s="56"/>
+      <c r="E19" s="33"/>
+      <c r="F19" s="33"/>
+      <c r="G19" s="54">
         <v>2.2999999999999998</v>
       </c>
-      <c r="H19" s="61"/>
-      <c r="I19" s="62"/>
-      <c r="J19" s="36"/>
-      <c r="K19" s="36"/>
-      <c r="L19" s="60"/>
-      <c r="M19" s="61"/>
-      <c r="N19" s="62"/>
-      <c r="O19" s="36"/>
-      <c r="P19" s="36"/>
-      <c r="Q19" s="60"/>
-      <c r="R19" s="61"/>
-      <c r="S19" s="62"/>
-      <c r="T19" s="36"/>
-      <c r="U19" s="36"/>
-      <c r="V19" s="60"/>
-      <c r="W19" s="61"/>
-      <c r="X19" s="62"/>
-      <c r="Y19" s="36"/>
-      <c r="Z19" s="36"/>
-      <c r="AA19" s="60"/>
-      <c r="AB19" s="61"/>
-      <c r="AC19" s="62"/>
-      <c r="AD19" s="36"/>
+      <c r="H19" s="55"/>
+      <c r="I19" s="56"/>
+      <c r="J19" s="33"/>
+      <c r="K19" s="33"/>
+      <c r="L19" s="54"/>
+      <c r="M19" s="55"/>
+      <c r="N19" s="56"/>
+      <c r="O19" s="33"/>
+      <c r="P19" s="33"/>
+      <c r="Q19" s="54"/>
+      <c r="R19" s="55"/>
+      <c r="S19" s="56"/>
+      <c r="T19" s="33"/>
+      <c r="U19" s="33"/>
+      <c r="V19" s="54"/>
+      <c r="W19" s="55"/>
+      <c r="X19" s="56"/>
+      <c r="Y19" s="33"/>
+      <c r="Z19" s="33"/>
+      <c r="AA19" s="54"/>
+      <c r="AB19" s="55"/>
+      <c r="AC19" s="56"/>
+      <c r="AD19" s="33"/>
     </row>
     <row r="20" spans="1:30" ht="20" x14ac:dyDescent="0.55000000000000004">
-      <c r="A20" s="36"/>
-      <c r="B20" s="63"/>
-      <c r="C20" s="36"/>
-      <c r="D20" s="64"/>
-      <c r="E20" s="36"/>
-      <c r="F20" s="36"/>
-      <c r="G20" s="63"/>
-      <c r="H20" s="36"/>
-      <c r="I20" s="64"/>
-      <c r="J20" s="36"/>
-      <c r="K20" s="36"/>
-      <c r="L20" s="63"/>
-      <c r="M20" s="36"/>
-      <c r="N20" s="64"/>
-      <c r="O20" s="36"/>
-      <c r="P20" s="36"/>
-      <c r="Q20" s="63"/>
-      <c r="R20" s="36"/>
-      <c r="S20" s="64"/>
-      <c r="T20" s="36"/>
-      <c r="U20" s="36"/>
-      <c r="V20" s="63"/>
-      <c r="W20" s="36"/>
-      <c r="X20" s="64"/>
-      <c r="Y20" s="36"/>
-      <c r="Z20" s="36"/>
-      <c r="AA20" s="63"/>
-      <c r="AB20" s="36"/>
-      <c r="AC20" s="64"/>
-      <c r="AD20" s="36"/>
+      <c r="A20" s="33"/>
+      <c r="B20" s="57"/>
+      <c r="C20" s="33"/>
+      <c r="D20" s="58"/>
+      <c r="E20" s="33"/>
+      <c r="F20" s="33"/>
+      <c r="G20" s="57"/>
+      <c r="H20" s="33"/>
+      <c r="I20" s="58"/>
+      <c r="J20" s="33"/>
+      <c r="K20" s="33"/>
+      <c r="L20" s="57"/>
+      <c r="M20" s="33"/>
+      <c r="N20" s="58"/>
+      <c r="O20" s="33"/>
+      <c r="P20" s="33"/>
+      <c r="Q20" s="57"/>
+      <c r="R20" s="33"/>
+      <c r="S20" s="58"/>
+      <c r="T20" s="33"/>
+      <c r="U20" s="33"/>
+      <c r="V20" s="57"/>
+      <c r="W20" s="33"/>
+      <c r="X20" s="58"/>
+      <c r="Y20" s="33"/>
+      <c r="Z20" s="33"/>
+      <c r="AA20" s="57"/>
+      <c r="AB20" s="33"/>
+      <c r="AC20" s="58"/>
+      <c r="AD20" s="33"/>
     </row>
     <row r="21" spans="1:30" ht="20.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A21" s="36"/>
-      <c r="B21" s="65"/>
-      <c r="C21" s="66"/>
-      <c r="D21" s="67"/>
-      <c r="E21" s="36"/>
-      <c r="F21" s="36"/>
-      <c r="G21" s="65"/>
-      <c r="H21" s="66"/>
-      <c r="I21" s="67"/>
-      <c r="J21" s="36"/>
-      <c r="K21" s="36"/>
-      <c r="L21" s="65"/>
-      <c r="M21" s="66"/>
-      <c r="N21" s="67"/>
-      <c r="O21" s="36"/>
-      <c r="P21" s="36"/>
-      <c r="Q21" s="65"/>
-      <c r="R21" s="66"/>
-      <c r="S21" s="67"/>
-      <c r="T21" s="36"/>
-      <c r="U21" s="36"/>
-      <c r="V21" s="65"/>
-      <c r="W21" s="66"/>
-      <c r="X21" s="67"/>
-      <c r="Y21" s="36"/>
-      <c r="Z21" s="36"/>
-      <c r="AA21" s="65"/>
-      <c r="AB21" s="66"/>
-      <c r="AC21" s="67"/>
-      <c r="AD21" s="36"/>
+      <c r="A21" s="33"/>
+      <c r="B21" s="59"/>
+      <c r="C21" s="60"/>
+      <c r="D21" s="61"/>
+      <c r="E21" s="33"/>
+      <c r="F21" s="33"/>
+      <c r="G21" s="59"/>
+      <c r="H21" s="60"/>
+      <c r="I21" s="61"/>
+      <c r="J21" s="33"/>
+      <c r="K21" s="33"/>
+      <c r="L21" s="59"/>
+      <c r="M21" s="60"/>
+      <c r="N21" s="61"/>
+      <c r="O21" s="33"/>
+      <c r="P21" s="33"/>
+      <c r="Q21" s="59"/>
+      <c r="R21" s="60"/>
+      <c r="S21" s="61"/>
+      <c r="T21" s="33"/>
+      <c r="U21" s="33"/>
+      <c r="V21" s="59"/>
+      <c r="W21" s="60"/>
+      <c r="X21" s="61"/>
+      <c r="Y21" s="33"/>
+      <c r="Z21" s="33"/>
+      <c r="AA21" s="59"/>
+      <c r="AB21" s="60"/>
+      <c r="AC21" s="61"/>
+      <c r="AD21" s="33"/>
     </row>
     <row r="22" spans="1:30" ht="20.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A22" s="36"/>
-      <c r="B22" s="36"/>
-      <c r="C22" s="36"/>
-      <c r="D22" s="36"/>
-      <c r="E22" s="36"/>
-      <c r="F22" s="36"/>
-      <c r="G22" s="36"/>
-      <c r="H22" s="36"/>
-      <c r="I22" s="36"/>
-      <c r="J22" s="36"/>
-      <c r="K22" s="36"/>
-      <c r="L22" s="36"/>
-      <c r="M22" s="36"/>
-      <c r="N22" s="36"/>
-      <c r="O22" s="36"/>
-      <c r="P22" s="36"/>
-      <c r="Q22" s="36"/>
-      <c r="R22" s="36"/>
-      <c r="S22" s="36"/>
-      <c r="T22" s="36"/>
-      <c r="U22" s="36"/>
-      <c r="V22" s="36"/>
-      <c r="W22" s="36"/>
-      <c r="X22" s="36"/>
-      <c r="Y22" s="36"/>
-      <c r="Z22" s="36"/>
-      <c r="AA22" s="36"/>
-      <c r="AB22" s="36"/>
-      <c r="AC22" s="36"/>
-      <c r="AD22" s="36"/>
+      <c r="A22" s="33"/>
+      <c r="B22" s="33"/>
+      <c r="C22" s="33"/>
+      <c r="D22" s="33"/>
+      <c r="E22" s="33"/>
+      <c r="F22" s="33"/>
+      <c r="G22" s="33"/>
+      <c r="H22" s="33"/>
+      <c r="I22" s="33"/>
+      <c r="J22" s="33"/>
+      <c r="K22" s="33"/>
+      <c r="L22" s="33"/>
+      <c r="M22" s="33"/>
+      <c r="N22" s="33"/>
+      <c r="O22" s="33"/>
+      <c r="P22" s="33"/>
+      <c r="Q22" s="33"/>
+      <c r="R22" s="33"/>
+      <c r="S22" s="33"/>
+      <c r="T22" s="33"/>
+      <c r="U22" s="33"/>
+      <c r="V22" s="33"/>
+      <c r="W22" s="33"/>
+      <c r="X22" s="33"/>
+      <c r="Y22" s="33"/>
+      <c r="Z22" s="33"/>
+      <c r="AA22" s="33"/>
+      <c r="AB22" s="33"/>
+      <c r="AC22" s="33"/>
+      <c r="AD22" s="33"/>
     </row>
     <row r="23" spans="1:30" ht="20" x14ac:dyDescent="0.55000000000000004">
-      <c r="A23" s="36"/>
-      <c r="B23" s="60"/>
-      <c r="C23" s="61"/>
-      <c r="D23" s="62"/>
-      <c r="E23" s="36"/>
-      <c r="F23" s="36"/>
-      <c r="G23" s="60"/>
-      <c r="H23" s="61"/>
-      <c r="I23" s="62"/>
-      <c r="J23" s="36"/>
-      <c r="K23" s="36"/>
-      <c r="L23" s="60"/>
-      <c r="M23" s="61"/>
-      <c r="N23" s="62"/>
-      <c r="O23" s="36"/>
-      <c r="P23" s="36"/>
-      <c r="Q23" s="60"/>
-      <c r="R23" s="61"/>
-      <c r="S23" s="62"/>
-      <c r="T23" s="36"/>
-      <c r="U23" s="36"/>
-      <c r="V23" s="60"/>
-      <c r="W23" s="61"/>
-      <c r="X23" s="62"/>
-      <c r="Y23" s="36"/>
-      <c r="Z23" s="36"/>
-      <c r="AA23" s="60"/>
-      <c r="AB23" s="61"/>
-      <c r="AC23" s="62"/>
-      <c r="AD23" s="36"/>
+      <c r="A23" s="33"/>
+      <c r="B23" s="54"/>
+      <c r="C23" s="55"/>
+      <c r="D23" s="56"/>
+      <c r="E23" s="33"/>
+      <c r="F23" s="33"/>
+      <c r="G23" s="54"/>
+      <c r="H23" s="55"/>
+      <c r="I23" s="56"/>
+      <c r="J23" s="33"/>
+      <c r="K23" s="33"/>
+      <c r="L23" s="54"/>
+      <c r="M23" s="55"/>
+      <c r="N23" s="56"/>
+      <c r="O23" s="33"/>
+      <c r="P23" s="33"/>
+      <c r="Q23" s="54"/>
+      <c r="R23" s="55"/>
+      <c r="S23" s="56"/>
+      <c r="T23" s="33"/>
+      <c r="U23" s="33"/>
+      <c r="V23" s="54"/>
+      <c r="W23" s="55"/>
+      <c r="X23" s="56"/>
+      <c r="Y23" s="33"/>
+      <c r="Z23" s="33"/>
+      <c r="AA23" s="54"/>
+      <c r="AB23" s="55"/>
+      <c r="AC23" s="56"/>
+      <c r="AD23" s="33"/>
     </row>
     <row r="24" spans="1:30" ht="20" x14ac:dyDescent="0.55000000000000004">
-      <c r="A24" s="36"/>
-      <c r="B24" s="63"/>
-      <c r="C24" s="36"/>
-      <c r="D24" s="64"/>
-      <c r="E24" s="36"/>
-      <c r="F24" s="36"/>
-      <c r="G24" s="63"/>
-      <c r="H24" s="36"/>
-      <c r="I24" s="64"/>
-      <c r="J24" s="36"/>
-      <c r="K24" s="36"/>
-      <c r="L24" s="63"/>
-      <c r="M24" s="36"/>
-      <c r="N24" s="64"/>
-      <c r="O24" s="36"/>
-      <c r="P24" s="36"/>
-      <c r="Q24" s="63"/>
-      <c r="R24" s="36"/>
-      <c r="S24" s="64"/>
-      <c r="T24" s="36"/>
-      <c r="U24" s="36"/>
-      <c r="V24" s="63"/>
-      <c r="W24" s="36"/>
-      <c r="X24" s="64"/>
-      <c r="Y24" s="36"/>
-      <c r="Z24" s="36"/>
-      <c r="AA24" s="63"/>
-      <c r="AB24" s="36"/>
-      <c r="AC24" s="64"/>
-      <c r="AD24" s="36"/>
+      <c r="A24" s="33"/>
+      <c r="B24" s="57"/>
+      <c r="C24" s="33"/>
+      <c r="D24" s="58"/>
+      <c r="E24" s="33"/>
+      <c r="F24" s="33"/>
+      <c r="G24" s="57"/>
+      <c r="H24" s="33"/>
+      <c r="I24" s="58"/>
+      <c r="J24" s="33"/>
+      <c r="K24" s="33"/>
+      <c r="L24" s="57"/>
+      <c r="M24" s="33"/>
+      <c r="N24" s="58"/>
+      <c r="O24" s="33"/>
+      <c r="P24" s="33"/>
+      <c r="Q24" s="57"/>
+      <c r="R24" s="33"/>
+      <c r="S24" s="58"/>
+      <c r="T24" s="33"/>
+      <c r="U24" s="33"/>
+      <c r="V24" s="57"/>
+      <c r="W24" s="33"/>
+      <c r="X24" s="58"/>
+      <c r="Y24" s="33"/>
+      <c r="Z24" s="33"/>
+      <c r="AA24" s="57"/>
+      <c r="AB24" s="33"/>
+      <c r="AC24" s="58"/>
+      <c r="AD24" s="33"/>
     </row>
     <row r="25" spans="1:30" ht="20.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A25" s="36"/>
-      <c r="B25" s="65"/>
-      <c r="C25" s="66"/>
-      <c r="D25" s="67"/>
-      <c r="E25" s="36"/>
-      <c r="F25" s="36"/>
-      <c r="G25" s="65"/>
-      <c r="H25" s="66"/>
-      <c r="I25" s="67"/>
-      <c r="J25" s="36"/>
-      <c r="K25" s="36"/>
-      <c r="L25" s="65"/>
-      <c r="M25" s="66"/>
-      <c r="N25" s="67"/>
-      <c r="O25" s="36"/>
-      <c r="P25" s="36"/>
-      <c r="Q25" s="65"/>
-      <c r="R25" s="66"/>
-      <c r="S25" s="67"/>
-      <c r="T25" s="36"/>
-      <c r="U25" s="36"/>
-      <c r="V25" s="65"/>
-      <c r="W25" s="66"/>
-      <c r="X25" s="67"/>
-      <c r="Y25" s="36"/>
-      <c r="Z25" s="36"/>
-      <c r="AA25" s="65"/>
-      <c r="AB25" s="66"/>
-      <c r="AC25" s="67"/>
-      <c r="AD25" s="36"/>
+      <c r="A25" s="33"/>
+      <c r="B25" s="59"/>
+      <c r="C25" s="60"/>
+      <c r="D25" s="61"/>
+      <c r="E25" s="33"/>
+      <c r="F25" s="33"/>
+      <c r="G25" s="59"/>
+      <c r="H25" s="60"/>
+      <c r="I25" s="61"/>
+      <c r="J25" s="33"/>
+      <c r="K25" s="33"/>
+      <c r="L25" s="59"/>
+      <c r="M25" s="60"/>
+      <c r="N25" s="61"/>
+      <c r="O25" s="33"/>
+      <c r="P25" s="33"/>
+      <c r="Q25" s="59"/>
+      <c r="R25" s="60"/>
+      <c r="S25" s="61"/>
+      <c r="T25" s="33"/>
+      <c r="U25" s="33"/>
+      <c r="V25" s="59"/>
+      <c r="W25" s="60"/>
+      <c r="X25" s="61"/>
+      <c r="Y25" s="33"/>
+      <c r="Z25" s="33"/>
+      <c r="AA25" s="59"/>
+      <c r="AB25" s="60"/>
+      <c r="AC25" s="61"/>
+      <c r="AD25" s="33"/>
     </row>
     <row r="26" spans="1:30" ht="20" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26" s="36"/>
-      <c r="B26" s="36"/>
-      <c r="C26" s="36"/>
-      <c r="D26" s="36"/>
-      <c r="E26" s="36"/>
-      <c r="F26" s="36"/>
-      <c r="G26" s="36"/>
-      <c r="H26" s="36"/>
-      <c r="I26" s="36"/>
-      <c r="J26" s="36"/>
-      <c r="K26" s="36"/>
-      <c r="L26" s="36"/>
-      <c r="M26" s="36"/>
-      <c r="N26" s="36"/>
-      <c r="O26" s="36"/>
-      <c r="P26" s="36"/>
-      <c r="Q26" s="36"/>
-      <c r="R26" s="36"/>
-      <c r="S26" s="36"/>
-      <c r="T26" s="36"/>
-      <c r="U26" s="36"/>
-      <c r="V26" s="36"/>
-      <c r="W26" s="36"/>
-      <c r="X26" s="36"/>
-      <c r="Y26" s="36"/>
-      <c r="Z26" s="36"/>
-      <c r="AA26" s="36"/>
-      <c r="AB26" s="36"/>
-      <c r="AC26" s="36"/>
-      <c r="AD26" s="36"/>
+      <c r="A26" s="33"/>
+      <c r="B26" s="33"/>
+      <c r="C26" s="33"/>
+      <c r="D26" s="33"/>
+      <c r="E26" s="33"/>
+      <c r="F26" s="33"/>
+      <c r="G26" s="33"/>
+      <c r="H26" s="33"/>
+      <c r="I26" s="33"/>
+      <c r="J26" s="33"/>
+      <c r="K26" s="33"/>
+      <c r="L26" s="33"/>
+      <c r="M26" s="33"/>
+      <c r="N26" s="33"/>
+      <c r="O26" s="33"/>
+      <c r="P26" s="33"/>
+      <c r="Q26" s="33"/>
+      <c r="R26" s="33"/>
+      <c r="S26" s="33"/>
+      <c r="T26" s="33"/>
+      <c r="U26" s="33"/>
+      <c r="V26" s="33"/>
+      <c r="W26" s="33"/>
+      <c r="X26" s="33"/>
+      <c r="Y26" s="33"/>
+      <c r="Z26" s="33"/>
+      <c r="AA26" s="33"/>
+      <c r="AB26" s="33"/>
+      <c r="AC26" s="33"/>
+      <c r="AD26" s="33"/>
     </row>
     <row r="27" spans="1:30" ht="20" x14ac:dyDescent="0.55000000000000004">
-      <c r="A27" s="36"/>
-      <c r="B27" s="36"/>
-      <c r="C27" s="36"/>
-      <c r="D27" s="36"/>
-      <c r="E27" s="36"/>
-      <c r="F27" s="36"/>
-      <c r="G27" s="36"/>
-      <c r="H27" s="36"/>
-      <c r="I27" s="36"/>
-      <c r="J27" s="36"/>
-      <c r="K27" s="36"/>
-      <c r="L27" s="36"/>
-      <c r="M27" s="36"/>
-      <c r="N27" s="36"/>
-      <c r="O27" s="36"/>
-      <c r="P27" s="36"/>
-      <c r="Q27" s="36"/>
-      <c r="R27" s="36"/>
-      <c r="S27" s="36"/>
-      <c r="T27" s="36"/>
-      <c r="U27" s="36"/>
-      <c r="V27" s="36"/>
-      <c r="W27" s="36"/>
-      <c r="X27" s="36"/>
-      <c r="Y27" s="36"/>
-      <c r="Z27" s="36"/>
-      <c r="AA27" s="36"/>
-      <c r="AB27" s="36"/>
-      <c r="AC27" s="36"/>
-      <c r="AD27" s="36"/>
+      <c r="A27" s="33"/>
+      <c r="B27" s="33"/>
+      <c r="C27" s="33"/>
+      <c r="D27" s="33"/>
+      <c r="E27" s="33"/>
+      <c r="F27" s="33"/>
+      <c r="G27" s="33"/>
+      <c r="H27" s="33"/>
+      <c r="I27" s="33"/>
+      <c r="J27" s="33"/>
+      <c r="K27" s="33"/>
+      <c r="L27" s="33"/>
+      <c r="M27" s="33"/>
+      <c r="N27" s="33"/>
+      <c r="O27" s="33"/>
+      <c r="P27" s="33"/>
+      <c r="Q27" s="33"/>
+      <c r="R27" s="33"/>
+      <c r="S27" s="33"/>
+      <c r="T27" s="33"/>
+      <c r="U27" s="33"/>
+      <c r="V27" s="33"/>
+      <c r="W27" s="33"/>
+      <c r="X27" s="33"/>
+      <c r="Y27" s="33"/>
+      <c r="Z27" s="33"/>
+      <c r="AA27" s="33"/>
+      <c r="AB27" s="33"/>
+      <c r="AC27" s="33"/>
+      <c r="AD27" s="33"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
@@ -8854,334 +8478,19 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD121E88-4C85-4901-85C7-0FB3D413DD24}">
-  <dimension ref="B1:AB16"/>
+  <dimension ref="F1:K16"/>
   <sheetFormatPr defaultColWidth="4.58203125" defaultRowHeight="25" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
   <sheetData>
-    <row r="1" spans="2:28" ht="25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="K1" s="34" t="s">
+    <row r="1" spans="6:11" ht="25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="K1" s="31" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="4" spans="2:28" ht="25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B4" s="38"/>
-      <c r="C4" s="38"/>
-      <c r="D4" s="38"/>
-      <c r="E4" s="38"/>
-      <c r="F4" s="69"/>
-      <c r="G4" s="38"/>
-      <c r="H4" s="38"/>
-      <c r="I4" s="38"/>
-      <c r="J4" s="38"/>
-      <c r="K4" s="38"/>
-      <c r="L4" s="38"/>
-      <c r="N4" s="38"/>
-      <c r="O4" s="38"/>
-      <c r="P4" s="38"/>
-      <c r="Q4" s="38"/>
-      <c r="R4" s="38"/>
-      <c r="S4" s="38"/>
-      <c r="T4" s="38"/>
-      <c r="U4" s="38"/>
-      <c r="V4" s="38"/>
-      <c r="W4" s="38"/>
-      <c r="X4" s="38"/>
-      <c r="Y4" s="38"/>
-      <c r="Z4" s="38"/>
-      <c r="AA4" s="38"/>
-      <c r="AB4" s="38"/>
-    </row>
-    <row r="5" spans="2:28" ht="25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B5" s="38"/>
-      <c r="C5" s="38"/>
-      <c r="D5" s="38"/>
-      <c r="E5" s="38"/>
-      <c r="F5" s="38"/>
-      <c r="G5" s="38"/>
-      <c r="H5" s="38"/>
-      <c r="I5" s="38"/>
-      <c r="J5" s="38"/>
-      <c r="K5" s="38"/>
-      <c r="L5" s="38"/>
-      <c r="M5" s="38"/>
-      <c r="N5" s="38"/>
-      <c r="O5" s="38"/>
-      <c r="P5" s="38"/>
-      <c r="Q5" s="38"/>
-      <c r="R5" s="38"/>
-      <c r="S5" s="38"/>
-      <c r="T5" s="38"/>
-      <c r="U5" s="38"/>
-      <c r="V5" s="38"/>
-      <c r="W5" s="38"/>
-      <c r="X5" s="38"/>
-      <c r="Y5" s="38"/>
-      <c r="Z5" s="38"/>
-      <c r="AA5" s="38"/>
-      <c r="AB5" s="38"/>
-    </row>
-    <row r="6" spans="2:28" ht="25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B6" s="38"/>
-      <c r="C6" s="38"/>
-      <c r="D6" s="38"/>
-      <c r="E6" s="38"/>
-      <c r="F6" s="38"/>
-      <c r="G6" s="38"/>
-      <c r="H6" s="38"/>
-      <c r="I6" s="38"/>
-      <c r="J6" s="38"/>
-      <c r="K6" s="38"/>
-      <c r="L6" s="38"/>
-      <c r="M6" s="38"/>
-      <c r="N6" s="38"/>
-      <c r="O6" s="38"/>
-      <c r="P6" s="38"/>
-      <c r="Q6" s="38"/>
-      <c r="R6" s="38"/>
-      <c r="S6" s="38"/>
-      <c r="T6" s="38"/>
-      <c r="U6" s="38"/>
-      <c r="V6" s="38"/>
-      <c r="W6" s="38"/>
-      <c r="X6" s="38"/>
-      <c r="Y6" s="38"/>
-      <c r="Z6" s="38"/>
-      <c r="AA6" s="38"/>
-      <c r="AB6" s="38"/>
-    </row>
-    <row r="7" spans="2:28" ht="25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B7" s="38"/>
-      <c r="C7" s="38"/>
-      <c r="D7" s="38"/>
-      <c r="E7" s="38"/>
-      <c r="F7" s="38"/>
-      <c r="G7" s="38"/>
-      <c r="H7" s="38"/>
-      <c r="I7" s="38"/>
-      <c r="J7" s="38"/>
-      <c r="K7" s="38"/>
-      <c r="L7" s="38"/>
-      <c r="M7" s="38"/>
-      <c r="N7" s="38"/>
-      <c r="O7" s="38"/>
-      <c r="P7" s="38"/>
-      <c r="Q7" s="38"/>
-      <c r="R7" s="38"/>
-      <c r="S7" s="38"/>
-      <c r="T7" s="38"/>
-      <c r="U7" s="38"/>
-      <c r="V7" s="38"/>
-      <c r="W7" s="38"/>
-      <c r="X7" s="38"/>
-      <c r="Y7" s="38"/>
-      <c r="Z7" s="38"/>
-      <c r="AA7" s="38"/>
-      <c r="AB7" s="38"/>
-    </row>
-    <row r="8" spans="2:28" ht="25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B8" s="38"/>
-      <c r="C8" s="38"/>
-      <c r="D8" s="38"/>
-      <c r="E8" s="38"/>
-      <c r="F8" s="38"/>
-      <c r="G8" s="38"/>
-      <c r="H8" s="38"/>
-      <c r="I8" s="38"/>
-      <c r="J8" s="38"/>
-      <c r="K8" s="38"/>
-      <c r="L8" s="38"/>
-      <c r="M8" s="38"/>
-      <c r="N8" s="38"/>
-      <c r="O8" s="38"/>
-      <c r="P8" s="38"/>
-      <c r="Q8" s="38"/>
-      <c r="R8" s="38"/>
-      <c r="S8" s="38"/>
-      <c r="T8" s="38"/>
-      <c r="U8" s="38"/>
-      <c r="V8" s="38"/>
-      <c r="W8" s="38"/>
-      <c r="X8" s="38"/>
-      <c r="Y8" s="38"/>
-      <c r="Z8" s="38"/>
-      <c r="AA8" s="38"/>
-      <c r="AB8" s="38"/>
-    </row>
-    <row r="9" spans="2:28" ht="25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B9" s="38"/>
-      <c r="C9" s="38"/>
-      <c r="D9" s="38"/>
-      <c r="E9" s="38"/>
-      <c r="F9" s="38"/>
-      <c r="G9" s="38"/>
-      <c r="H9" s="38"/>
-      <c r="I9" s="38"/>
-      <c r="J9" s="38"/>
-      <c r="K9" s="38"/>
-      <c r="L9" s="38"/>
-      <c r="M9" s="38"/>
-      <c r="N9" s="38"/>
-      <c r="O9" s="38"/>
-      <c r="P9" s="38"/>
-      <c r="Q9" s="38"/>
-      <c r="R9" s="38"/>
-      <c r="S9" s="38"/>
-      <c r="T9" s="38"/>
-      <c r="U9" s="38"/>
-      <c r="V9" s="38"/>
-      <c r="W9" s="38"/>
-      <c r="X9" s="38"/>
-      <c r="Y9" s="38"/>
-      <c r="Z9" s="38"/>
-      <c r="AA9" s="38"/>
-      <c r="AB9" s="38"/>
-    </row>
-    <row r="10" spans="2:28" ht="25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B10" s="38"/>
-      <c r="C10" s="38"/>
-      <c r="D10" s="38"/>
-      <c r="E10" s="38"/>
-      <c r="F10" s="38"/>
-      <c r="G10" s="38"/>
-      <c r="H10" s="38"/>
-      <c r="I10" s="38"/>
-      <c r="J10" s="38"/>
-      <c r="K10" s="38"/>
-      <c r="L10" s="38"/>
-      <c r="M10" s="38"/>
-      <c r="N10" s="38"/>
-      <c r="O10" s="38"/>
-      <c r="P10" s="38"/>
-      <c r="Q10" s="38"/>
-      <c r="R10" s="38"/>
-      <c r="S10" s="38"/>
-      <c r="T10" s="38"/>
-      <c r="U10" s="38"/>
-      <c r="V10" s="38"/>
-      <c r="W10" s="38"/>
-      <c r="X10" s="38"/>
-      <c r="Y10" s="38"/>
-      <c r="Z10" s="38"/>
-      <c r="AA10" s="38"/>
-      <c r="AB10" s="38"/>
-    </row>
-    <row r="11" spans="2:28" ht="25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B11" s="38"/>
-      <c r="C11" s="38"/>
-      <c r="D11" s="38"/>
-      <c r="E11" s="38"/>
-      <c r="F11" s="38"/>
-      <c r="G11" s="38"/>
-      <c r="H11" s="38"/>
-      <c r="I11" s="38"/>
-      <c r="J11" s="38"/>
-      <c r="K11" s="38"/>
-      <c r="L11" s="38"/>
-      <c r="M11" s="38"/>
-      <c r="N11" s="38"/>
-      <c r="O11" s="38"/>
-      <c r="P11" s="38"/>
-      <c r="Q11" s="38"/>
-      <c r="R11" s="38"/>
-      <c r="S11" s="38"/>
-      <c r="T11" s="38"/>
-      <c r="U11" s="38"/>
-      <c r="V11" s="38"/>
-      <c r="W11" s="38"/>
-      <c r="X11" s="38"/>
-      <c r="Y11" s="38"/>
-      <c r="Z11" s="38"/>
-      <c r="AA11" s="38"/>
-      <c r="AB11" s="38"/>
-    </row>
-    <row r="12" spans="2:28" ht="25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B12" s="38"/>
-      <c r="C12" s="38"/>
-      <c r="D12" s="38"/>
-      <c r="E12" s="38"/>
-      <c r="F12" s="38"/>
-      <c r="G12" s="38"/>
-      <c r="H12" s="38"/>
-      <c r="I12" s="38"/>
-      <c r="J12" s="38"/>
-      <c r="K12" s="38"/>
-      <c r="L12" s="38"/>
-      <c r="M12" s="38"/>
-      <c r="N12" s="38"/>
-      <c r="O12" s="38"/>
-      <c r="P12" s="38"/>
-      <c r="Q12" s="38"/>
-      <c r="R12" s="38"/>
-      <c r="S12" s="38"/>
-      <c r="T12" s="38"/>
-      <c r="U12" s="38"/>
-      <c r="V12" s="38"/>
-      <c r="W12" s="38"/>
-      <c r="X12" s="38"/>
-      <c r="Y12" s="38"/>
-      <c r="Z12" s="38"/>
-      <c r="AA12" s="38"/>
-      <c r="AB12" s="38"/>
-    </row>
-    <row r="13" spans="2:28" ht="25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B13" s="38"/>
-      <c r="C13" s="38"/>
-      <c r="D13" s="38"/>
-      <c r="E13" s="38"/>
-      <c r="F13" s="38"/>
-      <c r="G13" s="38"/>
-      <c r="H13" s="38"/>
-      <c r="I13" s="38"/>
-      <c r="J13" s="38"/>
-      <c r="K13" s="38"/>
-      <c r="L13" s="38"/>
-      <c r="M13" s="38"/>
-      <c r="N13" s="38"/>
-      <c r="O13" s="38"/>
-      <c r="P13" s="38"/>
-      <c r="Q13" s="38"/>
-      <c r="R13" s="38"/>
-      <c r="S13" s="38"/>
-      <c r="T13" s="38"/>
-      <c r="U13" s="38"/>
-      <c r="V13" s="38"/>
-      <c r="W13" s="38"/>
-      <c r="X13" s="38"/>
-      <c r="Y13" s="38"/>
-      <c r="Z13" s="38"/>
-      <c r="AA13" s="38"/>
-      <c r="AB13" s="38"/>
-    </row>
-    <row r="14" spans="2:28" ht="25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B14" s="38"/>
-      <c r="C14" s="38"/>
-      <c r="D14" s="38"/>
-      <c r="E14" s="38"/>
-      <c r="F14" s="38"/>
-      <c r="G14" s="38"/>
-      <c r="H14" s="38"/>
-      <c r="I14" s="38"/>
-      <c r="J14" s="38"/>
-      <c r="K14" s="38"/>
-      <c r="L14" s="38"/>
-      <c r="M14" s="38"/>
-      <c r="N14" s="38"/>
-      <c r="O14" s="38"/>
-      <c r="P14" s="38"/>
-      <c r="Q14" s="38"/>
-      <c r="R14" s="38"/>
-      <c r="S14" s="38"/>
-      <c r="T14" s="38"/>
-      <c r="U14" s="38"/>
-      <c r="V14" s="38"/>
-      <c r="W14" s="38"/>
-      <c r="X14" s="38"/>
-      <c r="Y14" s="38"/>
-      <c r="Z14" s="38"/>
-      <c r="AA14" s="38"/>
-      <c r="AB14" s="38"/>
-    </row>
-    <row r="16" spans="2:28" ht="25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="K16" s="34" t="s">
+    <row r="4" spans="6:11" ht="25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="F4" s="63"/>
+    </row>
+    <row r="16" spans="6:11" ht="25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="K16" s="31" t="s">
         <v>32</v>
       </c>
     </row>
@@ -9209,945 +8518,944 @@
     <col min="18" max="25" width="5.58203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="20.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="F1" s="36" t="s">
+    <row r="1" spans="1:17" ht="23" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="F1" s="31" t="s">
         <v>85</v>
       </c>
-      <c r="G1" s="50"/>
-      <c r="H1" s="50"/>
-      <c r="I1" s="50"/>
-      <c r="J1" s="50"/>
-      <c r="K1" s="50" t="s">
+      <c r="G1" s="34"/>
+      <c r="H1" s="34"/>
+      <c r="I1" s="34"/>
+      <c r="J1" s="32" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="2" spans="1:17" ht="18.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="F2" s="28"/>
-      <c r="G2" s="29"/>
-      <c r="H2" s="29"/>
-      <c r="I2" s="29"/>
-      <c r="J2" s="29"/>
-      <c r="K2" s="29"/>
-      <c r="L2" s="29"/>
-      <c r="M2" s="29"/>
-      <c r="N2" s="29"/>
-      <c r="O2" s="29"/>
-      <c r="P2" s="29"/>
-      <c r="Q2" s="30"/>
+      <c r="F2" s="90"/>
+      <c r="G2" s="91"/>
+      <c r="H2" s="91"/>
+      <c r="I2" s="91"/>
+      <c r="J2" s="91"/>
+      <c r="K2" s="91"/>
+      <c r="L2" s="91"/>
+      <c r="M2" s="91"/>
+      <c r="N2" s="91"/>
+      <c r="O2" s="91"/>
+      <c r="P2" s="91"/>
+      <c r="Q2" s="92"/>
     </row>
     <row r="3" spans="1:17" ht="45.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B3" s="45" t="s">
+      <c r="B3" s="40" t="s">
         <v>33</v>
       </c>
-      <c r="C3" s="47" t="s">
+      <c r="C3" s="42" t="s">
         <v>113</v>
       </c>
-      <c r="D3" s="47" t="s">
+      <c r="D3" s="42" t="s">
         <v>112</v>
       </c>
-      <c r="E3" s="70" t="s">
+      <c r="E3" s="64" t="s">
         <v>34</v>
       </c>
-      <c r="F3" s="71" t="s">
+      <c r="F3" s="65" t="s">
         <v>35</v>
       </c>
-      <c r="G3" s="71" t="s">
+      <c r="G3" s="65" t="s">
         <v>36</v>
       </c>
-      <c r="H3" s="71" t="s">
+      <c r="H3" s="65" t="s">
         <v>37</v>
       </c>
-      <c r="I3" s="71" t="s">
+      <c r="I3" s="65" t="s">
         <v>38</v>
       </c>
-      <c r="J3" s="71" t="s">
+      <c r="J3" s="65" t="s">
         <v>39</v>
       </c>
-      <c r="K3" s="71" t="s">
+      <c r="K3" s="65" t="s">
         <v>40</v>
       </c>
-      <c r="L3" s="71" t="s">
+      <c r="L3" s="65" t="s">
         <v>41</v>
       </c>
-      <c r="M3" s="71" t="s">
+      <c r="M3" s="65" t="s">
         <v>42</v>
       </c>
-      <c r="N3" s="71" t="s">
+      <c r="N3" s="65" t="s">
         <v>43</v>
       </c>
-      <c r="O3" s="71" t="s">
+      <c r="O3" s="65" t="s">
         <v>44</v>
       </c>
-      <c r="P3" s="71" t="s">
+      <c r="P3" s="65" t="s">
         <v>45</v>
       </c>
-      <c r="Q3" s="72" t="s">
+      <c r="Q3" s="66" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="4" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="73">
+      <c r="A4" s="67">
         <v>1</v>
       </c>
-      <c r="B4" s="74" t="s">
+      <c r="B4" s="68" t="s">
         <v>47</v>
       </c>
-      <c r="C4" s="74"/>
-      <c r="D4" s="74"/>
-      <c r="E4" s="75"/>
-      <c r="F4" s="76"/>
-      <c r="G4" s="76"/>
-      <c r="H4" s="76"/>
-      <c r="I4" s="76"/>
-      <c r="J4" s="76"/>
-      <c r="K4" s="76"/>
-      <c r="L4" s="76"/>
-      <c r="M4" s="76"/>
-      <c r="N4" s="76"/>
-      <c r="O4" s="76"/>
-      <c r="P4" s="76"/>
-      <c r="Q4" s="77"/>
+      <c r="C4" s="68"/>
+      <c r="D4" s="68"/>
+      <c r="E4" s="69"/>
+      <c r="F4" s="70"/>
+      <c r="G4" s="70"/>
+      <c r="H4" s="70"/>
+      <c r="I4" s="70"/>
+      <c r="J4" s="70"/>
+      <c r="K4" s="70"/>
+      <c r="L4" s="70"/>
+      <c r="M4" s="70"/>
+      <c r="N4" s="70"/>
+      <c r="O4" s="70"/>
+      <c r="P4" s="70"/>
+      <c r="Q4" s="71"/>
     </row>
     <row r="5" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="78">
+      <c r="A5" s="72">
         <v>1.1000000000000001</v>
       </c>
-      <c r="B5" s="79"/>
-      <c r="C5" s="79" t="s">
+      <c r="B5" s="73"/>
+      <c r="C5" s="73" t="s">
         <v>78</v>
       </c>
-      <c r="D5" s="79"/>
-      <c r="E5" s="80" t="s">
+      <c r="D5" s="73"/>
+      <c r="E5" s="74" t="s">
         <v>87</v>
       </c>
-      <c r="F5" s="79"/>
-      <c r="G5" s="79"/>
-      <c r="H5" s="79"/>
-      <c r="I5" s="79"/>
-      <c r="J5" s="79"/>
-      <c r="K5" s="79"/>
-      <c r="L5" s="79"/>
-      <c r="M5" s="79"/>
-      <c r="N5" s="79"/>
-      <c r="O5" s="79"/>
-      <c r="P5" s="79"/>
-      <c r="Q5" s="81"/>
+      <c r="F5" s="73"/>
+      <c r="G5" s="73"/>
+      <c r="H5" s="73"/>
+      <c r="I5" s="73"/>
+      <c r="J5" s="73"/>
+      <c r="K5" s="73"/>
+      <c r="L5" s="73"/>
+      <c r="M5" s="73"/>
+      <c r="N5" s="73"/>
+      <c r="O5" s="73"/>
+      <c r="P5" s="73"/>
+      <c r="Q5" s="75"/>
     </row>
     <row r="6" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="78" t="s">
+      <c r="A6" s="72" t="s">
         <v>48</v>
       </c>
-      <c r="B6" s="79"/>
-      <c r="C6" s="79"/>
-      <c r="D6" s="79"/>
-      <c r="E6" s="80" t="s">
+      <c r="B6" s="73"/>
+      <c r="C6" s="73"/>
+      <c r="D6" s="73"/>
+      <c r="E6" s="74" t="s">
         <v>88</v>
       </c>
-      <c r="F6" s="79"/>
-      <c r="G6" s="79"/>
-      <c r="H6" s="79"/>
-      <c r="I6" s="79"/>
-      <c r="J6" s="79"/>
-      <c r="K6" s="79"/>
-      <c r="L6" s="79"/>
-      <c r="M6" s="79"/>
-      <c r="N6" s="79"/>
-      <c r="O6" s="79"/>
-      <c r="P6" s="79"/>
-      <c r="Q6" s="81"/>
+      <c r="F6" s="73"/>
+      <c r="G6" s="73"/>
+      <c r="H6" s="73"/>
+      <c r="I6" s="73"/>
+      <c r="J6" s="73"/>
+      <c r="K6" s="73"/>
+      <c r="L6" s="73"/>
+      <c r="M6" s="73"/>
+      <c r="N6" s="73"/>
+      <c r="O6" s="73"/>
+      <c r="P6" s="73"/>
+      <c r="Q6" s="75"/>
     </row>
     <row r="7" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="78" t="s">
+      <c r="A7" s="72" t="s">
         <v>49</v>
       </c>
-      <c r="B7" s="79"/>
-      <c r="C7" s="79"/>
-      <c r="D7" s="79"/>
-      <c r="E7" s="80" t="s">
+      <c r="B7" s="73"/>
+      <c r="C7" s="73"/>
+      <c r="D7" s="73"/>
+      <c r="E7" s="74" t="s">
         <v>89</v>
       </c>
-      <c r="F7" s="79"/>
-      <c r="G7" s="79"/>
-      <c r="H7" s="79"/>
-      <c r="I7" s="79"/>
-      <c r="J7" s="79"/>
-      <c r="K7" s="79"/>
-      <c r="L7" s="79"/>
-      <c r="M7" s="79"/>
-      <c r="N7" s="79"/>
-      <c r="O7" s="79"/>
-      <c r="P7" s="79"/>
-      <c r="Q7" s="81"/>
+      <c r="F7" s="73"/>
+      <c r="G7" s="73"/>
+      <c r="H7" s="73"/>
+      <c r="I7" s="73"/>
+      <c r="J7" s="73"/>
+      <c r="K7" s="73"/>
+      <c r="L7" s="73"/>
+      <c r="M7" s="73"/>
+      <c r="N7" s="73"/>
+      <c r="O7" s="73"/>
+      <c r="P7" s="73"/>
+      <c r="Q7" s="75"/>
     </row>
     <row r="8" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="78">
+      <c r="A8" s="72">
         <v>1.2</v>
       </c>
-      <c r="B8" s="79"/>
-      <c r="C8" s="79" t="s">
+      <c r="B8" s="73"/>
+      <c r="C8" s="73" t="s">
         <v>79</v>
       </c>
-      <c r="D8" s="79"/>
-      <c r="E8" s="80"/>
-      <c r="F8" s="79"/>
-      <c r="G8" s="79"/>
-      <c r="H8" s="79"/>
-      <c r="I8" s="79"/>
-      <c r="J8" s="79"/>
-      <c r="K8" s="79"/>
-      <c r="L8" s="79"/>
-      <c r="M8" s="79"/>
-      <c r="N8" s="79"/>
-      <c r="O8" s="79"/>
-      <c r="P8" s="79"/>
-      <c r="Q8" s="81"/>
+      <c r="D8" s="73"/>
+      <c r="E8" s="74"/>
+      <c r="F8" s="73"/>
+      <c r="G8" s="73"/>
+      <c r="H8" s="73"/>
+      <c r="I8" s="73"/>
+      <c r="J8" s="73"/>
+      <c r="K8" s="73"/>
+      <c r="L8" s="73"/>
+      <c r="M8" s="73"/>
+      <c r="N8" s="73"/>
+      <c r="O8" s="73"/>
+      <c r="P8" s="73"/>
+      <c r="Q8" s="75"/>
     </row>
     <row r="9" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="78" t="s">
+      <c r="A9" s="72" t="s">
         <v>50</v>
       </c>
-      <c r="B9" s="79"/>
-      <c r="C9" s="79"/>
-      <c r="D9" s="79"/>
-      <c r="E9" s="80"/>
-      <c r="F9" s="79"/>
-      <c r="G9" s="79"/>
-      <c r="H9" s="79"/>
-      <c r="I9" s="79"/>
-      <c r="J9" s="79"/>
-      <c r="K9" s="79"/>
-      <c r="L9" s="79"/>
-      <c r="M9" s="79"/>
-      <c r="N9" s="79"/>
-      <c r="O9" s="79"/>
-      <c r="P9" s="79"/>
-      <c r="Q9" s="81"/>
+      <c r="B9" s="73"/>
+      <c r="C9" s="73"/>
+      <c r="D9" s="73"/>
+      <c r="E9" s="74"/>
+      <c r="F9" s="73"/>
+      <c r="G9" s="73"/>
+      <c r="H9" s="73"/>
+      <c r="I9" s="73"/>
+      <c r="J9" s="73"/>
+      <c r="K9" s="73"/>
+      <c r="L9" s="73"/>
+      <c r="M9" s="73"/>
+      <c r="N9" s="73"/>
+      <c r="O9" s="73"/>
+      <c r="P9" s="73"/>
+      <c r="Q9" s="75"/>
     </row>
     <row r="10" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="78" t="s">
+      <c r="A10" s="72" t="s">
         <v>51</v>
       </c>
-      <c r="B10" s="79"/>
-      <c r="C10" s="79"/>
-      <c r="D10" s="79"/>
-      <c r="E10" s="80"/>
-      <c r="F10" s="79"/>
-      <c r="G10" s="79"/>
-      <c r="H10" s="79"/>
-      <c r="I10" s="79"/>
-      <c r="J10" s="79"/>
-      <c r="K10" s="79"/>
-      <c r="L10" s="79"/>
-      <c r="M10" s="79"/>
-      <c r="N10" s="79"/>
-      <c r="O10" s="79"/>
-      <c r="P10" s="79"/>
-      <c r="Q10" s="81"/>
+      <c r="B10" s="73"/>
+      <c r="C10" s="73"/>
+      <c r="D10" s="73"/>
+      <c r="E10" s="74"/>
+      <c r="F10" s="73"/>
+      <c r="G10" s="73"/>
+      <c r="H10" s="73"/>
+      <c r="I10" s="73"/>
+      <c r="J10" s="73"/>
+      <c r="K10" s="73"/>
+      <c r="L10" s="73"/>
+      <c r="M10" s="73"/>
+      <c r="N10" s="73"/>
+      <c r="O10" s="73"/>
+      <c r="P10" s="73"/>
+      <c r="Q10" s="75"/>
     </row>
     <row r="11" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="78" t="s">
+      <c r="A11" s="72" t="s">
         <v>52</v>
       </c>
-      <c r="B11" s="79"/>
-      <c r="C11" s="79"/>
-      <c r="D11" s="79"/>
-      <c r="E11" s="80"/>
-      <c r="F11" s="79"/>
-      <c r="G11" s="79"/>
-      <c r="H11" s="79"/>
-      <c r="I11" s="79"/>
-      <c r="J11" s="79"/>
-      <c r="K11" s="79"/>
-      <c r="L11" s="79"/>
-      <c r="M11" s="79"/>
-      <c r="N11" s="79"/>
-      <c r="O11" s="79"/>
-      <c r="P11" s="79"/>
-      <c r="Q11" s="81"/>
+      <c r="B11" s="73"/>
+      <c r="C11" s="73"/>
+      <c r="D11" s="73"/>
+      <c r="E11" s="74"/>
+      <c r="F11" s="73"/>
+      <c r="G11" s="73"/>
+      <c r="H11" s="73"/>
+      <c r="I11" s="73"/>
+      <c r="J11" s="73"/>
+      <c r="K11" s="73"/>
+      <c r="L11" s="73"/>
+      <c r="M11" s="73"/>
+      <c r="N11" s="73"/>
+      <c r="O11" s="73"/>
+      <c r="P11" s="73"/>
+      <c r="Q11" s="75"/>
     </row>
     <row r="12" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" s="78">
+      <c r="A12" s="72">
         <v>2</v>
       </c>
-      <c r="B12" s="82" t="s">
+      <c r="B12" s="76" t="s">
         <v>53</v>
       </c>
-      <c r="C12" s="82"/>
-      <c r="D12" s="82"/>
-      <c r="E12" s="80"/>
-      <c r="F12" s="79"/>
-      <c r="G12" s="79"/>
-      <c r="H12" s="79"/>
-      <c r="I12" s="79"/>
-      <c r="J12" s="79"/>
-      <c r="K12" s="79"/>
-      <c r="L12" s="79"/>
-      <c r="M12" s="79"/>
-      <c r="N12" s="79"/>
-      <c r="O12" s="79"/>
-      <c r="P12" s="79"/>
-      <c r="Q12" s="81"/>
+      <c r="C12" s="76"/>
+      <c r="D12" s="76"/>
+      <c r="E12" s="74"/>
+      <c r="F12" s="73"/>
+      <c r="G12" s="73"/>
+      <c r="H12" s="73"/>
+      <c r="I12" s="73"/>
+      <c r="J12" s="73"/>
+      <c r="K12" s="73"/>
+      <c r="L12" s="73"/>
+      <c r="M12" s="73"/>
+      <c r="N12" s="73"/>
+      <c r="O12" s="73"/>
+      <c r="P12" s="73"/>
+      <c r="Q12" s="75"/>
     </row>
     <row r="13" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="78">
+      <c r="A13" s="72">
         <v>2.1</v>
       </c>
-      <c r="B13" s="79"/>
-      <c r="C13" s="79" t="s">
+      <c r="B13" s="73"/>
+      <c r="C13" s="73" t="s">
         <v>80</v>
       </c>
-      <c r="D13" s="79"/>
-      <c r="E13" s="80"/>
-      <c r="F13" s="79"/>
-      <c r="G13" s="79"/>
-      <c r="H13" s="79"/>
-      <c r="I13" s="79"/>
-      <c r="J13" s="79"/>
-      <c r="K13" s="79"/>
-      <c r="L13" s="79"/>
-      <c r="M13" s="79"/>
-      <c r="N13" s="79"/>
-      <c r="O13" s="79"/>
-      <c r="P13" s="79"/>
-      <c r="Q13" s="81"/>
+      <c r="D13" s="73"/>
+      <c r="E13" s="74"/>
+      <c r="F13" s="73"/>
+      <c r="G13" s="73"/>
+      <c r="H13" s="73"/>
+      <c r="I13" s="73"/>
+      <c r="J13" s="73"/>
+      <c r="K13" s="73"/>
+      <c r="L13" s="73"/>
+      <c r="M13" s="73"/>
+      <c r="N13" s="73"/>
+      <c r="O13" s="73"/>
+      <c r="P13" s="73"/>
+      <c r="Q13" s="75"/>
     </row>
     <row r="14" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="78" t="s">
+      <c r="A14" s="72" t="s">
         <v>54</v>
       </c>
-      <c r="B14" s="79"/>
-      <c r="C14" s="79"/>
-      <c r="D14" s="79"/>
-      <c r="E14" s="80"/>
-      <c r="F14" s="79"/>
-      <c r="G14" s="79"/>
-      <c r="H14" s="79"/>
-      <c r="I14" s="79"/>
-      <c r="J14" s="79"/>
-      <c r="K14" s="79"/>
-      <c r="L14" s="79"/>
-      <c r="M14" s="79"/>
-      <c r="N14" s="79"/>
-      <c r="O14" s="79"/>
-      <c r="P14" s="79"/>
-      <c r="Q14" s="81"/>
+      <c r="B14" s="73"/>
+      <c r="C14" s="73"/>
+      <c r="D14" s="73"/>
+      <c r="E14" s="74"/>
+      <c r="F14" s="73"/>
+      <c r="G14" s="73"/>
+      <c r="H14" s="73"/>
+      <c r="I14" s="73"/>
+      <c r="J14" s="73"/>
+      <c r="K14" s="73"/>
+      <c r="L14" s="73"/>
+      <c r="M14" s="73"/>
+      <c r="N14" s="73"/>
+      <c r="O14" s="73"/>
+      <c r="P14" s="73"/>
+      <c r="Q14" s="75"/>
     </row>
     <row r="15" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="78" t="s">
+      <c r="A15" s="72" t="s">
         <v>55</v>
       </c>
-      <c r="B15" s="79"/>
-      <c r="C15" s="79"/>
-      <c r="D15" s="79"/>
-      <c r="E15" s="80"/>
-      <c r="F15" s="79"/>
-      <c r="G15" s="79"/>
-      <c r="H15" s="79"/>
-      <c r="I15" s="79"/>
-      <c r="J15" s="79"/>
-      <c r="K15" s="79"/>
-      <c r="L15" s="79"/>
-      <c r="M15" s="79"/>
-      <c r="N15" s="79"/>
-      <c r="O15" s="79"/>
-      <c r="P15" s="79"/>
-      <c r="Q15" s="81"/>
+      <c r="B15" s="73"/>
+      <c r="C15" s="73"/>
+      <c r="D15" s="73"/>
+      <c r="E15" s="74"/>
+      <c r="F15" s="73"/>
+      <c r="G15" s="73"/>
+      <c r="H15" s="73"/>
+      <c r="I15" s="73"/>
+      <c r="J15" s="73"/>
+      <c r="K15" s="73"/>
+      <c r="L15" s="73"/>
+      <c r="M15" s="73"/>
+      <c r="N15" s="73"/>
+      <c r="O15" s="73"/>
+      <c r="P15" s="73"/>
+      <c r="Q15" s="75"/>
     </row>
     <row r="16" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="78" t="s">
+      <c r="A16" s="72" t="s">
         <v>56</v>
       </c>
-      <c r="B16" s="79"/>
-      <c r="C16" s="79"/>
-      <c r="D16" s="79"/>
-      <c r="E16" s="80"/>
-      <c r="F16" s="79"/>
-      <c r="G16" s="79"/>
-      <c r="H16" s="79"/>
-      <c r="I16" s="79"/>
-      <c r="J16" s="79"/>
-      <c r="K16" s="79"/>
-      <c r="L16" s="79"/>
-      <c r="M16" s="79"/>
-      <c r="N16" s="79"/>
-      <c r="O16" s="79"/>
-      <c r="P16" s="79"/>
-      <c r="Q16" s="81"/>
+      <c r="B16" s="73"/>
+      <c r="C16" s="73"/>
+      <c r="D16" s="73"/>
+      <c r="E16" s="74"/>
+      <c r="F16" s="73"/>
+      <c r="G16" s="73"/>
+      <c r="H16" s="73"/>
+      <c r="I16" s="73"/>
+      <c r="J16" s="73"/>
+      <c r="K16" s="73"/>
+      <c r="L16" s="73"/>
+      <c r="M16" s="73"/>
+      <c r="N16" s="73"/>
+      <c r="O16" s="73"/>
+      <c r="P16" s="73"/>
+      <c r="Q16" s="75"/>
     </row>
     <row r="17" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17" s="78" t="s">
+      <c r="A17" s="72" t="s">
         <v>57</v>
       </c>
-      <c r="B17" s="79"/>
-      <c r="C17" s="79"/>
-      <c r="D17" s="79"/>
-      <c r="E17" s="80"/>
-      <c r="F17" s="79"/>
-      <c r="G17" s="79"/>
-      <c r="H17" s="79"/>
-      <c r="I17" s="79"/>
-      <c r="J17" s="79"/>
-      <c r="K17" s="79"/>
-      <c r="L17" s="79"/>
-      <c r="M17" s="79"/>
-      <c r="N17" s="79"/>
-      <c r="O17" s="79"/>
-      <c r="P17" s="79"/>
-      <c r="Q17" s="81"/>
+      <c r="B17" s="73"/>
+      <c r="C17" s="73"/>
+      <c r="D17" s="73"/>
+      <c r="E17" s="74"/>
+      <c r="F17" s="73"/>
+      <c r="G17" s="73"/>
+      <c r="H17" s="73"/>
+      <c r="I17" s="73"/>
+      <c r="J17" s="73"/>
+      <c r="K17" s="73"/>
+      <c r="L17" s="73"/>
+      <c r="M17" s="73"/>
+      <c r="N17" s="73"/>
+      <c r="O17" s="73"/>
+      <c r="P17" s="73"/>
+      <c r="Q17" s="75"/>
     </row>
     <row r="18" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18" s="78">
+      <c r="A18" s="72">
         <v>2.2000000000000002</v>
       </c>
-      <c r="B18" s="79"/>
-      <c r="C18" s="79" t="s">
+      <c r="B18" s="73"/>
+      <c r="C18" s="73" t="s">
         <v>81</v>
       </c>
-      <c r="D18" s="79"/>
-      <c r="E18" s="80"/>
-      <c r="F18" s="79"/>
-      <c r="G18" s="79"/>
-      <c r="H18" s="79"/>
-      <c r="I18" s="79"/>
-      <c r="J18" s="79"/>
-      <c r="K18" s="79"/>
-      <c r="L18" s="79"/>
-      <c r="M18" s="79"/>
-      <c r="N18" s="79"/>
-      <c r="O18" s="79"/>
-      <c r="P18" s="79"/>
-      <c r="Q18" s="81"/>
+      <c r="D18" s="73"/>
+      <c r="E18" s="74"/>
+      <c r="F18" s="73"/>
+      <c r="G18" s="73"/>
+      <c r="H18" s="73"/>
+      <c r="I18" s="73"/>
+      <c r="J18" s="73"/>
+      <c r="K18" s="73"/>
+      <c r="L18" s="73"/>
+      <c r="M18" s="73"/>
+      <c r="N18" s="73"/>
+      <c r="O18" s="73"/>
+      <c r="P18" s="73"/>
+      <c r="Q18" s="75"/>
     </row>
     <row r="19" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19" s="78" t="s">
+      <c r="A19" s="72" t="s">
         <v>58</v>
       </c>
-      <c r="B19" s="79"/>
-      <c r="C19" s="79"/>
-      <c r="D19" s="79"/>
-      <c r="E19" s="80"/>
-      <c r="F19" s="79"/>
-      <c r="G19" s="79"/>
-      <c r="H19" s="79"/>
-      <c r="I19" s="79"/>
-      <c r="J19" s="79"/>
-      <c r="K19" s="79"/>
-      <c r="L19" s="79"/>
-      <c r="M19" s="79"/>
-      <c r="N19" s="79"/>
-      <c r="O19" s="79"/>
-      <c r="P19" s="79"/>
-      <c r="Q19" s="81"/>
+      <c r="B19" s="73"/>
+      <c r="C19" s="73"/>
+      <c r="D19" s="73"/>
+      <c r="E19" s="74"/>
+      <c r="F19" s="73"/>
+      <c r="G19" s="73"/>
+      <c r="H19" s="73"/>
+      <c r="I19" s="73"/>
+      <c r="J19" s="73"/>
+      <c r="K19" s="73"/>
+      <c r="L19" s="73"/>
+      <c r="M19" s="73"/>
+      <c r="N19" s="73"/>
+      <c r="O19" s="73"/>
+      <c r="P19" s="73"/>
+      <c r="Q19" s="75"/>
     </row>
     <row r="20" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A20" s="78" t="s">
+      <c r="A20" s="72" t="s">
         <v>59</v>
       </c>
-      <c r="B20" s="79"/>
-      <c r="C20" s="79"/>
-      <c r="D20" s="79"/>
-      <c r="E20" s="80"/>
-      <c r="F20" s="79"/>
-      <c r="G20" s="79"/>
-      <c r="H20" s="79"/>
-      <c r="I20" s="79"/>
-      <c r="J20" s="79"/>
-      <c r="K20" s="79"/>
-      <c r="L20" s="79"/>
-      <c r="M20" s="79"/>
-      <c r="N20" s="79"/>
-      <c r="O20" s="79"/>
-      <c r="P20" s="79"/>
-      <c r="Q20" s="81"/>
+      <c r="B20" s="73"/>
+      <c r="C20" s="73"/>
+      <c r="D20" s="73"/>
+      <c r="E20" s="74"/>
+      <c r="F20" s="73"/>
+      <c r="G20" s="73"/>
+      <c r="H20" s="73"/>
+      <c r="I20" s="73"/>
+      <c r="J20" s="73"/>
+      <c r="K20" s="73"/>
+      <c r="L20" s="73"/>
+      <c r="M20" s="73"/>
+      <c r="N20" s="73"/>
+      <c r="O20" s="73"/>
+      <c r="P20" s="73"/>
+      <c r="Q20" s="75"/>
     </row>
     <row r="21" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A21" s="78" t="s">
+      <c r="A21" s="72" t="s">
         <v>60</v>
       </c>
-      <c r="B21" s="79"/>
-      <c r="C21" s="79"/>
-      <c r="D21" s="79"/>
-      <c r="E21" s="80"/>
-      <c r="F21" s="79"/>
-      <c r="G21" s="79"/>
-      <c r="H21" s="79"/>
-      <c r="I21" s="79"/>
-      <c r="J21" s="79"/>
-      <c r="K21" s="79"/>
-      <c r="L21" s="79"/>
-      <c r="M21" s="79"/>
-      <c r="N21" s="79"/>
-      <c r="O21" s="79"/>
-      <c r="P21" s="79"/>
-      <c r="Q21" s="81"/>
+      <c r="B21" s="73"/>
+      <c r="C21" s="73"/>
+      <c r="D21" s="73"/>
+      <c r="E21" s="74"/>
+      <c r="F21" s="73"/>
+      <c r="G21" s="73"/>
+      <c r="H21" s="73"/>
+      <c r="I21" s="73"/>
+      <c r="J21" s="73"/>
+      <c r="K21" s="73"/>
+      <c r="L21" s="73"/>
+      <c r="M21" s="73"/>
+      <c r="N21" s="73"/>
+      <c r="O21" s="73"/>
+      <c r="P21" s="73"/>
+      <c r="Q21" s="75"/>
     </row>
     <row r="22" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22" s="78" t="s">
+      <c r="A22" s="72" t="s">
         <v>61</v>
       </c>
-      <c r="B22" s="79"/>
-      <c r="C22" s="79"/>
-      <c r="D22" s="79"/>
-      <c r="E22" s="80"/>
-      <c r="F22" s="79"/>
-      <c r="G22" s="79"/>
-      <c r="H22" s="79"/>
-      <c r="I22" s="79"/>
-      <c r="J22" s="79"/>
-      <c r="K22" s="79"/>
-      <c r="L22" s="79"/>
-      <c r="M22" s="79"/>
-      <c r="N22" s="79"/>
-      <c r="O22" s="79"/>
-      <c r="P22" s="79"/>
-      <c r="Q22" s="81"/>
+      <c r="B22" s="73"/>
+      <c r="C22" s="73"/>
+      <c r="D22" s="73"/>
+      <c r="E22" s="74"/>
+      <c r="F22" s="73"/>
+      <c r="G22" s="73"/>
+      <c r="H22" s="73"/>
+      <c r="I22" s="73"/>
+      <c r="J22" s="73"/>
+      <c r="K22" s="73"/>
+      <c r="L22" s="73"/>
+      <c r="M22" s="73"/>
+      <c r="N22" s="73"/>
+      <c r="O22" s="73"/>
+      <c r="P22" s="73"/>
+      <c r="Q22" s="75"/>
     </row>
     <row r="23" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A23" s="78">
+      <c r="A23" s="72">
         <v>3.1</v>
       </c>
-      <c r="B23" s="79"/>
-      <c r="C23" s="79" t="s">
+      <c r="B23" s="73"/>
+      <c r="C23" s="73" t="s">
         <v>82</v>
       </c>
-      <c r="D23" s="79"/>
-      <c r="E23" s="80"/>
-      <c r="F23" s="79"/>
-      <c r="G23" s="79"/>
-      <c r="H23" s="79"/>
-      <c r="I23" s="79"/>
-      <c r="J23" s="79"/>
-      <c r="K23" s="79"/>
-      <c r="L23" s="79"/>
-      <c r="M23" s="79"/>
-      <c r="N23" s="79"/>
-      <c r="O23" s="79"/>
-      <c r="P23" s="79"/>
-      <c r="Q23" s="81"/>
+      <c r="D23" s="73"/>
+      <c r="E23" s="74"/>
+      <c r="F23" s="73"/>
+      <c r="G23" s="73"/>
+      <c r="H23" s="73"/>
+      <c r="I23" s="73"/>
+      <c r="J23" s="73"/>
+      <c r="K23" s="73"/>
+      <c r="L23" s="73"/>
+      <c r="M23" s="73"/>
+      <c r="N23" s="73"/>
+      <c r="O23" s="73"/>
+      <c r="P23" s="73"/>
+      <c r="Q23" s="75"/>
     </row>
     <row r="24" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A24" s="78" t="s">
+      <c r="A24" s="72" t="s">
         <v>62</v>
       </c>
-      <c r="B24" s="79"/>
-      <c r="C24" s="79"/>
-      <c r="D24" s="79"/>
-      <c r="E24" s="80"/>
-      <c r="F24" s="79"/>
-      <c r="G24" s="79"/>
-      <c r="H24" s="79"/>
-      <c r="I24" s="79"/>
-      <c r="J24" s="79"/>
-      <c r="K24" s="79"/>
-      <c r="L24" s="79"/>
-      <c r="M24" s="79"/>
-      <c r="N24" s="79"/>
-      <c r="O24" s="79"/>
-      <c r="P24" s="79"/>
-      <c r="Q24" s="81"/>
+      <c r="B24" s="73"/>
+      <c r="C24" s="73"/>
+      <c r="D24" s="73"/>
+      <c r="E24" s="74"/>
+      <c r="F24" s="73"/>
+      <c r="G24" s="73"/>
+      <c r="H24" s="73"/>
+      <c r="I24" s="73"/>
+      <c r="J24" s="73"/>
+      <c r="K24" s="73"/>
+      <c r="L24" s="73"/>
+      <c r="M24" s="73"/>
+      <c r="N24" s="73"/>
+      <c r="O24" s="73"/>
+      <c r="P24" s="73"/>
+      <c r="Q24" s="75"/>
     </row>
     <row r="25" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A25" s="78" t="s">
+      <c r="A25" s="72" t="s">
         <v>63</v>
       </c>
-      <c r="B25" s="79"/>
-      <c r="C25" s="79"/>
-      <c r="D25" s="79"/>
-      <c r="E25" s="80"/>
-      <c r="F25" s="79"/>
-      <c r="G25" s="79"/>
-      <c r="H25" s="79"/>
-      <c r="I25" s="79"/>
-      <c r="J25" s="79"/>
-      <c r="K25" s="79"/>
-      <c r="L25" s="79"/>
-      <c r="M25" s="79"/>
-      <c r="N25" s="79"/>
-      <c r="O25" s="79"/>
-      <c r="P25" s="79"/>
-      <c r="Q25" s="81"/>
+      <c r="B25" s="73"/>
+      <c r="C25" s="73"/>
+      <c r="D25" s="73"/>
+      <c r="E25" s="74"/>
+      <c r="F25" s="73"/>
+      <c r="G25" s="73"/>
+      <c r="H25" s="73"/>
+      <c r="I25" s="73"/>
+      <c r="J25" s="73"/>
+      <c r="K25" s="73"/>
+      <c r="L25" s="73"/>
+      <c r="M25" s="73"/>
+      <c r="N25" s="73"/>
+      <c r="O25" s="73"/>
+      <c r="P25" s="73"/>
+      <c r="Q25" s="75"/>
     </row>
     <row r="26" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26" s="78" t="s">
+      <c r="A26" s="72" t="s">
         <v>64</v>
       </c>
-      <c r="B26" s="79"/>
-      <c r="C26" s="79"/>
-      <c r="D26" s="79"/>
-      <c r="E26" s="80"/>
-      <c r="F26" s="79"/>
-      <c r="G26" s="79"/>
-      <c r="H26" s="79"/>
-      <c r="I26" s="79"/>
-      <c r="J26" s="79"/>
-      <c r="K26" s="79"/>
-      <c r="L26" s="79"/>
-      <c r="M26" s="79"/>
-      <c r="N26" s="79"/>
-      <c r="O26" s="79"/>
-      <c r="P26" s="79"/>
-      <c r="Q26" s="81"/>
+      <c r="B26" s="73"/>
+      <c r="C26" s="73"/>
+      <c r="D26" s="73"/>
+      <c r="E26" s="74"/>
+      <c r="F26" s="73"/>
+      <c r="G26" s="73"/>
+      <c r="H26" s="73"/>
+      <c r="I26" s="73"/>
+      <c r="J26" s="73"/>
+      <c r="K26" s="73"/>
+      <c r="L26" s="73"/>
+      <c r="M26" s="73"/>
+      <c r="N26" s="73"/>
+      <c r="O26" s="73"/>
+      <c r="P26" s="73"/>
+      <c r="Q26" s="75"/>
     </row>
     <row r="27" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A27" s="78" t="s">
+      <c r="A27" s="72" t="s">
         <v>65</v>
       </c>
-      <c r="B27" s="79"/>
-      <c r="C27" s="79"/>
-      <c r="D27" s="79"/>
-      <c r="E27" s="80"/>
-      <c r="F27" s="79"/>
-      <c r="G27" s="79"/>
-      <c r="H27" s="79"/>
-      <c r="I27" s="79"/>
-      <c r="J27" s="79"/>
-      <c r="K27" s="79"/>
-      <c r="L27" s="79"/>
-      <c r="M27" s="79"/>
-      <c r="N27" s="79"/>
-      <c r="O27" s="79"/>
-      <c r="P27" s="79"/>
-      <c r="Q27" s="81"/>
+      <c r="B27" s="73"/>
+      <c r="C27" s="73"/>
+      <c r="D27" s="73"/>
+      <c r="E27" s="74"/>
+      <c r="F27" s="73"/>
+      <c r="G27" s="73"/>
+      <c r="H27" s="73"/>
+      <c r="I27" s="73"/>
+      <c r="J27" s="73"/>
+      <c r="K27" s="73"/>
+      <c r="L27" s="73"/>
+      <c r="M27" s="73"/>
+      <c r="N27" s="73"/>
+      <c r="O27" s="73"/>
+      <c r="P27" s="73"/>
+      <c r="Q27" s="75"/>
     </row>
     <row r="28" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A28" s="78">
+      <c r="A28" s="72">
         <v>3.2</v>
       </c>
-      <c r="B28" s="79"/>
-      <c r="C28" s="79" t="s">
+      <c r="B28" s="73"/>
+      <c r="C28" s="73" t="s">
         <v>83</v>
       </c>
-      <c r="D28" s="79"/>
-      <c r="E28" s="80"/>
-      <c r="F28" s="79"/>
-      <c r="G28" s="79"/>
-      <c r="H28" s="79"/>
-      <c r="I28" s="79"/>
-      <c r="J28" s="79"/>
-      <c r="K28" s="79"/>
-      <c r="L28" s="79"/>
-      <c r="M28" s="79"/>
-      <c r="N28" s="79"/>
-      <c r="O28" s="79"/>
-      <c r="P28" s="79"/>
-      <c r="Q28" s="81"/>
+      <c r="D28" s="73"/>
+      <c r="E28" s="74"/>
+      <c r="F28" s="73"/>
+      <c r="G28" s="73"/>
+      <c r="H28" s="73"/>
+      <c r="I28" s="73"/>
+      <c r="J28" s="73"/>
+      <c r="K28" s="73"/>
+      <c r="L28" s="73"/>
+      <c r="M28" s="73"/>
+      <c r="N28" s="73"/>
+      <c r="O28" s="73"/>
+      <c r="P28" s="73"/>
+      <c r="Q28" s="75"/>
     </row>
     <row r="29" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A29" s="78" t="s">
+      <c r="A29" s="72" t="s">
         <v>66</v>
       </c>
-      <c r="B29" s="79"/>
-      <c r="C29" s="79"/>
-      <c r="D29" s="79"/>
-      <c r="E29" s="80"/>
-      <c r="F29" s="79"/>
-      <c r="G29" s="79"/>
-      <c r="H29" s="79"/>
-      <c r="I29" s="79"/>
-      <c r="J29" s="79"/>
-      <c r="K29" s="79"/>
-      <c r="L29" s="79"/>
-      <c r="M29" s="79"/>
-      <c r="N29" s="79"/>
-      <c r="O29" s="79"/>
-      <c r="P29" s="79"/>
-      <c r="Q29" s="81"/>
+      <c r="B29" s="73"/>
+      <c r="C29" s="73"/>
+      <c r="D29" s="73"/>
+      <c r="E29" s="74"/>
+      <c r="F29" s="73"/>
+      <c r="G29" s="73"/>
+      <c r="H29" s="73"/>
+      <c r="I29" s="73"/>
+      <c r="J29" s="73"/>
+      <c r="K29" s="73"/>
+      <c r="L29" s="73"/>
+      <c r="M29" s="73"/>
+      <c r="N29" s="73"/>
+      <c r="O29" s="73"/>
+      <c r="P29" s="73"/>
+      <c r="Q29" s="75"/>
     </row>
     <row r="30" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A30" s="78" t="s">
+      <c r="A30" s="72" t="s">
         <v>67</v>
       </c>
-      <c r="B30" s="79"/>
-      <c r="C30" s="79"/>
-      <c r="D30" s="79"/>
-      <c r="E30" s="80"/>
-      <c r="F30" s="79"/>
-      <c r="G30" s="79"/>
-      <c r="H30" s="79"/>
-      <c r="I30" s="79"/>
-      <c r="J30" s="79"/>
-      <c r="K30" s="79"/>
-      <c r="L30" s="79"/>
-      <c r="M30" s="79"/>
-      <c r="N30" s="79"/>
-      <c r="O30" s="79"/>
-      <c r="P30" s="79"/>
-      <c r="Q30" s="81"/>
+      <c r="B30" s="73"/>
+      <c r="C30" s="73"/>
+      <c r="D30" s="73"/>
+      <c r="E30" s="74"/>
+      <c r="F30" s="73"/>
+      <c r="G30" s="73"/>
+      <c r="H30" s="73"/>
+      <c r="I30" s="73"/>
+      <c r="J30" s="73"/>
+      <c r="K30" s="73"/>
+      <c r="L30" s="73"/>
+      <c r="M30" s="73"/>
+      <c r="N30" s="73"/>
+      <c r="O30" s="73"/>
+      <c r="P30" s="73"/>
+      <c r="Q30" s="75"/>
     </row>
     <row r="31" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A31" s="78" t="s">
+      <c r="A31" s="72" t="s">
         <v>68</v>
       </c>
-      <c r="B31" s="79"/>
-      <c r="C31" s="79"/>
-      <c r="D31" s="79"/>
-      <c r="E31" s="80"/>
-      <c r="F31" s="79"/>
-      <c r="G31" s="79"/>
-      <c r="H31" s="79"/>
-      <c r="I31" s="79"/>
-      <c r="J31" s="79"/>
-      <c r="K31" s="79"/>
-      <c r="L31" s="79"/>
-      <c r="M31" s="79"/>
-      <c r="N31" s="79"/>
-      <c r="O31" s="79"/>
-      <c r="P31" s="79"/>
-      <c r="Q31" s="81"/>
+      <c r="B31" s="73"/>
+      <c r="C31" s="73"/>
+      <c r="D31" s="73"/>
+      <c r="E31" s="74"/>
+      <c r="F31" s="73"/>
+      <c r="G31" s="73"/>
+      <c r="H31" s="73"/>
+      <c r="I31" s="73"/>
+      <c r="J31" s="73"/>
+      <c r="K31" s="73"/>
+      <c r="L31" s="73"/>
+      <c r="M31" s="73"/>
+      <c r="N31" s="73"/>
+      <c r="O31" s="73"/>
+      <c r="P31" s="73"/>
+      <c r="Q31" s="75"/>
     </row>
     <row r="32" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A32" s="78">
+      <c r="A32" s="72">
         <v>3.3</v>
       </c>
-      <c r="B32" s="79"/>
-      <c r="C32" s="79" t="s">
+      <c r="B32" s="73"/>
+      <c r="C32" s="73" t="s">
         <v>84</v>
       </c>
-      <c r="D32" s="79"/>
-      <c r="E32" s="80"/>
-      <c r="F32" s="79"/>
-      <c r="G32" s="79"/>
-      <c r="H32" s="79"/>
-      <c r="I32" s="79"/>
-      <c r="J32" s="79"/>
-      <c r="K32" s="79"/>
-      <c r="L32" s="79"/>
-      <c r="M32" s="79"/>
-      <c r="N32" s="79"/>
-      <c r="O32" s="79"/>
-      <c r="P32" s="79"/>
-      <c r="Q32" s="81"/>
+      <c r="D32" s="73"/>
+      <c r="E32" s="74"/>
+      <c r="F32" s="73"/>
+      <c r="G32" s="73"/>
+      <c r="H32" s="73"/>
+      <c r="I32" s="73"/>
+      <c r="J32" s="73"/>
+      <c r="K32" s="73"/>
+      <c r="L32" s="73"/>
+      <c r="M32" s="73"/>
+      <c r="N32" s="73"/>
+      <c r="O32" s="73"/>
+      <c r="P32" s="73"/>
+      <c r="Q32" s="75"/>
     </row>
     <row r="33" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A33" s="78" t="s">
+      <c r="A33" s="72" t="s">
         <v>69</v>
       </c>
-      <c r="B33" s="79"/>
-      <c r="C33" s="79"/>
-      <c r="D33" s="79"/>
-      <c r="E33" s="80"/>
-      <c r="F33" s="79"/>
-      <c r="G33" s="79"/>
-      <c r="H33" s="79"/>
-      <c r="I33" s="79"/>
-      <c r="J33" s="79"/>
-      <c r="K33" s="79"/>
-      <c r="L33" s="79"/>
-      <c r="M33" s="79"/>
-      <c r="N33" s="79"/>
-      <c r="O33" s="79"/>
-      <c r="P33" s="79"/>
-      <c r="Q33" s="81"/>
+      <c r="B33" s="73"/>
+      <c r="C33" s="73"/>
+      <c r="D33" s="73"/>
+      <c r="E33" s="74"/>
+      <c r="F33" s="73"/>
+      <c r="G33" s="73"/>
+      <c r="H33" s="73"/>
+      <c r="I33" s="73"/>
+      <c r="J33" s="73"/>
+      <c r="K33" s="73"/>
+      <c r="L33" s="73"/>
+      <c r="M33" s="73"/>
+      <c r="N33" s="73"/>
+      <c r="O33" s="73"/>
+      <c r="P33" s="73"/>
+      <c r="Q33" s="75"/>
     </row>
     <row r="34" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A34" s="78" t="s">
+      <c r="A34" s="72" t="s">
         <v>70</v>
       </c>
-      <c r="B34" s="79"/>
-      <c r="C34" s="79"/>
-      <c r="D34" s="79"/>
-      <c r="E34" s="80"/>
-      <c r="F34" s="79"/>
-      <c r="G34" s="79"/>
-      <c r="H34" s="79"/>
-      <c r="I34" s="79"/>
-      <c r="J34" s="79"/>
-      <c r="K34" s="79"/>
-      <c r="L34" s="79"/>
-      <c r="M34" s="79"/>
-      <c r="N34" s="79"/>
-      <c r="O34" s="79"/>
-      <c r="P34" s="79"/>
-      <c r="Q34" s="81"/>
+      <c r="B34" s="73"/>
+      <c r="C34" s="73"/>
+      <c r="D34" s="73"/>
+      <c r="E34" s="74"/>
+      <c r="F34" s="73"/>
+      <c r="G34" s="73"/>
+      <c r="H34" s="73"/>
+      <c r="I34" s="73"/>
+      <c r="J34" s="73"/>
+      <c r="K34" s="73"/>
+      <c r="L34" s="73"/>
+      <c r="M34" s="73"/>
+      <c r="N34" s="73"/>
+      <c r="O34" s="73"/>
+      <c r="P34" s="73"/>
+      <c r="Q34" s="75"/>
     </row>
     <row r="35" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A35" s="78" t="s">
+      <c r="A35" s="72" t="s">
         <v>71</v>
       </c>
-      <c r="B35" s="79"/>
-      <c r="C35" s="79"/>
-      <c r="D35" s="79"/>
-      <c r="E35" s="80"/>
-      <c r="F35" s="79"/>
-      <c r="G35" s="79"/>
-      <c r="H35" s="79"/>
-      <c r="I35" s="79"/>
-      <c r="J35" s="79"/>
-      <c r="K35" s="79"/>
-      <c r="L35" s="79"/>
-      <c r="M35" s="79"/>
-      <c r="N35" s="79"/>
-      <c r="O35" s="79"/>
-      <c r="P35" s="79"/>
-      <c r="Q35" s="81"/>
+      <c r="B35" s="73"/>
+      <c r="C35" s="73"/>
+      <c r="D35" s="73"/>
+      <c r="E35" s="74"/>
+      <c r="F35" s="73"/>
+      <c r="G35" s="73"/>
+      <c r="H35" s="73"/>
+      <c r="I35" s="73"/>
+      <c r="J35" s="73"/>
+      <c r="K35" s="73"/>
+      <c r="L35" s="73"/>
+      <c r="M35" s="73"/>
+      <c r="N35" s="73"/>
+      <c r="O35" s="73"/>
+      <c r="P35" s="73"/>
+      <c r="Q35" s="75"/>
     </row>
     <row r="36" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A36" s="78">
+      <c r="A36" s="72">
         <v>4.0999999999999996</v>
       </c>
-      <c r="B36" s="79"/>
-      <c r="C36" s="79"/>
-      <c r="D36" s="79"/>
-      <c r="E36" s="80"/>
-      <c r="F36" s="79"/>
-      <c r="G36" s="79"/>
-      <c r="H36" s="79"/>
-      <c r="I36" s="79"/>
-      <c r="J36" s="79"/>
-      <c r="K36" s="79"/>
-      <c r="L36" s="79"/>
-      <c r="M36" s="79"/>
-      <c r="N36" s="79"/>
-      <c r="O36" s="79"/>
-      <c r="P36" s="79"/>
-      <c r="Q36" s="81"/>
+      <c r="B36" s="73"/>
+      <c r="C36" s="73"/>
+      <c r="D36" s="73"/>
+      <c r="E36" s="74"/>
+      <c r="F36" s="73"/>
+      <c r="G36" s="73"/>
+      <c r="H36" s="73"/>
+      <c r="I36" s="73"/>
+      <c r="J36" s="73"/>
+      <c r="K36" s="73"/>
+      <c r="L36" s="73"/>
+      <c r="M36" s="73"/>
+      <c r="N36" s="73"/>
+      <c r="O36" s="73"/>
+      <c r="P36" s="73"/>
+      <c r="Q36" s="75"/>
     </row>
     <row r="37" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A37" s="78" t="s">
+      <c r="A37" s="72" t="s">
         <v>72</v>
       </c>
-      <c r="B37" s="79"/>
-      <c r="C37" s="79"/>
-      <c r="D37" s="79"/>
-      <c r="E37" s="80"/>
-      <c r="F37" s="79"/>
-      <c r="G37" s="79"/>
-      <c r="H37" s="79"/>
-      <c r="I37" s="79"/>
-      <c r="J37" s="79"/>
-      <c r="K37" s="79"/>
-      <c r="L37" s="79"/>
-      <c r="M37" s="79"/>
-      <c r="N37" s="79"/>
-      <c r="O37" s="79"/>
-      <c r="P37" s="79"/>
-      <c r="Q37" s="81"/>
+      <c r="B37" s="73"/>
+      <c r="C37" s="73"/>
+      <c r="D37" s="73"/>
+      <c r="E37" s="74"/>
+      <c r="F37" s="73"/>
+      <c r="G37" s="73"/>
+      <c r="H37" s="73"/>
+      <c r="I37" s="73"/>
+      <c r="J37" s="73"/>
+      <c r="K37" s="73"/>
+      <c r="L37" s="73"/>
+      <c r="M37" s="73"/>
+      <c r="N37" s="73"/>
+      <c r="O37" s="73"/>
+      <c r="P37" s="73"/>
+      <c r="Q37" s="75"/>
     </row>
     <row r="38" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A38" s="78" t="s">
+      <c r="A38" s="72" t="s">
         <v>73</v>
       </c>
-      <c r="B38" s="79"/>
-      <c r="C38" s="79"/>
-      <c r="D38" s="79"/>
-      <c r="E38" s="80"/>
-      <c r="F38" s="79"/>
-      <c r="G38" s="79"/>
-      <c r="H38" s="79"/>
-      <c r="I38" s="79"/>
-      <c r="J38" s="79"/>
-      <c r="K38" s="79"/>
-      <c r="L38" s="79"/>
-      <c r="M38" s="79"/>
-      <c r="N38" s="79"/>
-      <c r="O38" s="79"/>
-      <c r="P38" s="79"/>
-      <c r="Q38" s="81"/>
+      <c r="B38" s="73"/>
+      <c r="C38" s="73"/>
+      <c r="D38" s="73"/>
+      <c r="E38" s="74"/>
+      <c r="F38" s="73"/>
+      <c r="G38" s="73"/>
+      <c r="H38" s="73"/>
+      <c r="I38" s="73"/>
+      <c r="J38" s="73"/>
+      <c r="K38" s="73"/>
+      <c r="L38" s="73"/>
+      <c r="M38" s="73"/>
+      <c r="N38" s="73"/>
+      <c r="O38" s="73"/>
+      <c r="P38" s="73"/>
+      <c r="Q38" s="75"/>
     </row>
     <row r="39" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A39" s="78" t="s">
+      <c r="A39" s="72" t="s">
         <v>74</v>
       </c>
-      <c r="B39" s="79"/>
-      <c r="C39" s="79"/>
-      <c r="D39" s="79"/>
-      <c r="E39" s="80"/>
-      <c r="F39" s="79"/>
-      <c r="G39" s="79"/>
-      <c r="H39" s="79"/>
-      <c r="I39" s="79"/>
-      <c r="J39" s="79"/>
-      <c r="K39" s="79"/>
-      <c r="L39" s="79"/>
-      <c r="M39" s="79"/>
-      <c r="N39" s="79"/>
-      <c r="O39" s="79"/>
-      <c r="P39" s="79"/>
-      <c r="Q39" s="81"/>
+      <c r="B39" s="73"/>
+      <c r="C39" s="73"/>
+      <c r="D39" s="73"/>
+      <c r="E39" s="74"/>
+      <c r="F39" s="73"/>
+      <c r="G39" s="73"/>
+      <c r="H39" s="73"/>
+      <c r="I39" s="73"/>
+      <c r="J39" s="73"/>
+      <c r="K39" s="73"/>
+      <c r="L39" s="73"/>
+      <c r="M39" s="73"/>
+      <c r="N39" s="73"/>
+      <c r="O39" s="73"/>
+      <c r="P39" s="73"/>
+      <c r="Q39" s="75"/>
     </row>
     <row r="40" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A40" s="78">
+      <c r="A40" s="72">
         <v>4.2</v>
       </c>
-      <c r="B40" s="79"/>
-      <c r="C40" s="79"/>
-      <c r="D40" s="79"/>
-      <c r="E40" s="80"/>
-      <c r="F40" s="79"/>
-      <c r="G40" s="79"/>
-      <c r="H40" s="79"/>
-      <c r="I40" s="79"/>
-      <c r="J40" s="79"/>
-      <c r="K40" s="79"/>
-      <c r="L40" s="79"/>
-      <c r="M40" s="79"/>
-      <c r="N40" s="79"/>
-      <c r="O40" s="79"/>
-      <c r="P40" s="79"/>
-      <c r="Q40" s="81"/>
+      <c r="B40" s="73"/>
+      <c r="C40" s="73"/>
+      <c r="D40" s="73"/>
+      <c r="E40" s="74"/>
+      <c r="F40" s="73"/>
+      <c r="G40" s="73"/>
+      <c r="H40" s="73"/>
+      <c r="I40" s="73"/>
+      <c r="J40" s="73"/>
+      <c r="K40" s="73"/>
+      <c r="L40" s="73"/>
+      <c r="M40" s="73"/>
+      <c r="N40" s="73"/>
+      <c r="O40" s="73"/>
+      <c r="P40" s="73"/>
+      <c r="Q40" s="75"/>
     </row>
     <row r="41" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A41" s="78" t="s">
+      <c r="A41" s="72" t="s">
         <v>75</v>
       </c>
-      <c r="B41" s="79"/>
-      <c r="C41" s="79"/>
-      <c r="D41" s="79"/>
-      <c r="E41" s="80"/>
-      <c r="F41" s="79"/>
-      <c r="G41" s="79"/>
-      <c r="H41" s="79"/>
-      <c r="I41" s="79"/>
-      <c r="J41" s="79"/>
-      <c r="K41" s="79"/>
-      <c r="L41" s="79"/>
-      <c r="M41" s="79"/>
-      <c r="N41" s="79"/>
-      <c r="O41" s="79"/>
-      <c r="P41" s="79"/>
-      <c r="Q41" s="81"/>
+      <c r="B41" s="73"/>
+      <c r="C41" s="73"/>
+      <c r="D41" s="73"/>
+      <c r="E41" s="74"/>
+      <c r="F41" s="73"/>
+      <c r="G41" s="73"/>
+      <c r="H41" s="73"/>
+      <c r="I41" s="73"/>
+      <c r="J41" s="73"/>
+      <c r="K41" s="73"/>
+      <c r="L41" s="73"/>
+      <c r="M41" s="73"/>
+      <c r="N41" s="73"/>
+      <c r="O41" s="73"/>
+      <c r="P41" s="73"/>
+      <c r="Q41" s="75"/>
     </row>
     <row r="42" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A42" s="78" t="s">
+      <c r="A42" s="72" t="s">
         <v>76</v>
       </c>
-      <c r="B42" s="79"/>
-      <c r="C42" s="79"/>
-      <c r="D42" s="79"/>
-      <c r="E42" s="80"/>
-      <c r="F42" s="79"/>
-      <c r="G42" s="79"/>
-      <c r="H42" s="79"/>
-      <c r="I42" s="79"/>
-      <c r="J42" s="79"/>
-      <c r="K42" s="79"/>
-      <c r="L42" s="79"/>
-      <c r="M42" s="79"/>
-      <c r="N42" s="79"/>
-      <c r="O42" s="79"/>
-      <c r="P42" s="79"/>
-      <c r="Q42" s="81"/>
+      <c r="B42" s="73"/>
+      <c r="C42" s="73"/>
+      <c r="D42" s="73"/>
+      <c r="E42" s="74"/>
+      <c r="F42" s="73"/>
+      <c r="G42" s="73"/>
+      <c r="H42" s="73"/>
+      <c r="I42" s="73"/>
+      <c r="J42" s="73"/>
+      <c r="K42" s="73"/>
+      <c r="L42" s="73"/>
+      <c r="M42" s="73"/>
+      <c r="N42" s="73"/>
+      <c r="O42" s="73"/>
+      <c r="P42" s="73"/>
+      <c r="Q42" s="75"/>
     </row>
     <row r="43" spans="1:17" ht="25" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A43" s="83" t="s">
+      <c r="A43" s="77" t="s">
         <v>77</v>
       </c>
-      <c r="B43" s="84"/>
-      <c r="C43" s="84"/>
-      <c r="D43" s="84"/>
-      <c r="E43" s="85"/>
-      <c r="F43" s="84"/>
-      <c r="G43" s="84"/>
-      <c r="H43" s="84"/>
-      <c r="I43" s="84"/>
-      <c r="J43" s="84"/>
-      <c r="K43" s="84"/>
-      <c r="L43" s="84"/>
-      <c r="M43" s="84"/>
-      <c r="N43" s="84"/>
-      <c r="O43" s="84"/>
-      <c r="P43" s="84"/>
-      <c r="Q43" s="86"/>
+      <c r="B43" s="78"/>
+      <c r="C43" s="78"/>
+      <c r="D43" s="78"/>
+      <c r="E43" s="79"/>
+      <c r="F43" s="78"/>
+      <c r="G43" s="78"/>
+      <c r="H43" s="78"/>
+      <c r="I43" s="78"/>
+      <c r="J43" s="78"/>
+      <c r="K43" s="78"/>
+      <c r="L43" s="78"/>
+      <c r="M43" s="78"/>
+      <c r="N43" s="78"/>
+      <c r="O43" s="78"/>
+      <c r="P43" s="78"/>
+      <c r="Q43" s="80"/>
     </row>
     <row r="44" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
     <row r="45" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
@@ -10188,7 +9496,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A72293E1-9681-4529-A931-167C8261205C}">
-  <dimension ref="A2:G22"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr defaultRowHeight="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="10.83203125" customWidth="1"/>
@@ -10199,207 +9507,207 @@
     <col min="7" max="7" width="13.4140625" customWidth="1"/>
   </cols>
   <sheetData>
+    <row r="1" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="G1" s="93" t="s">
+        <v>102</v>
+      </c>
+    </row>
     <row r="2" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="D2" s="89" t="s">
-        <v>102</v>
-      </c>
+      <c r="A2" s="81" t="s">
+        <v>90</v>
+      </c>
+      <c r="B2" s="82" t="s">
+        <v>91</v>
+      </c>
+      <c r="C2" s="82" t="s">
+        <v>92</v>
+      </c>
+      <c r="D2" s="82" t="s">
+        <v>93</v>
+      </c>
+      <c r="E2" s="82" t="s">
+        <v>94</v>
+      </c>
+      <c r="F2" s="82" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2" s="82" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" s="83" t="s">
+        <v>97</v>
+      </c>
+      <c r="B3" s="83" t="s">
+        <v>98</v>
+      </c>
+      <c r="C3" s="83" t="s">
+        <v>99</v>
+      </c>
+      <c r="D3" s="83" t="s">
+        <v>100</v>
+      </c>
+      <c r="E3" s="83" t="s">
+        <v>101</v>
+      </c>
+      <c r="F3" s="83" t="s">
+        <v>101</v>
+      </c>
+      <c r="G3" s="83"/>
     </row>
     <row r="4" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="87" t="s">
-        <v>90</v>
-      </c>
-      <c r="B4" s="88" t="s">
-        <v>91</v>
-      </c>
-      <c r="C4" s="88" t="s">
-        <v>92</v>
-      </c>
-      <c r="D4" s="88" t="s">
-        <v>93</v>
-      </c>
-      <c r="E4" s="88" t="s">
-        <v>94</v>
-      </c>
-      <c r="F4" s="88" t="s">
-        <v>95</v>
-      </c>
-      <c r="G4" s="88" t="s">
-        <v>96</v>
-      </c>
+      <c r="A4" s="83"/>
+      <c r="B4" s="83"/>
+      <c r="C4" s="83"/>
+      <c r="D4" s="83"/>
+      <c r="E4" s="83"/>
+      <c r="F4" s="83"/>
+      <c r="G4" s="83"/>
     </row>
     <row r="5" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="90" t="s">
-        <v>97</v>
-      </c>
-      <c r="B5" s="90" t="s">
-        <v>98</v>
-      </c>
-      <c r="C5" s="90" t="s">
-        <v>99</v>
-      </c>
-      <c r="D5" s="90" t="s">
-        <v>100</v>
-      </c>
-      <c r="E5" s="90" t="s">
-        <v>101</v>
-      </c>
-      <c r="F5" s="90" t="s">
-        <v>101</v>
-      </c>
-      <c r="G5" s="90"/>
+      <c r="A5" s="83"/>
+      <c r="B5" s="83"/>
+      <c r="C5" s="83"/>
+      <c r="D5" s="83"/>
+      <c r="E5" s="83"/>
+      <c r="F5" s="83"/>
+      <c r="G5" s="83"/>
     </row>
     <row r="6" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="90"/>
-      <c r="B6" s="90"/>
-      <c r="C6" s="90"/>
-      <c r="D6" s="90"/>
-      <c r="E6" s="90"/>
-      <c r="F6" s="90"/>
-      <c r="G6" s="90"/>
+      <c r="A6" s="83"/>
+      <c r="B6" s="83"/>
+      <c r="C6" s="83"/>
+      <c r="D6" s="83"/>
+      <c r="E6" s="83"/>
+      <c r="F6" s="83"/>
+      <c r="G6" s="83"/>
     </row>
     <row r="7" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="90"/>
-      <c r="B7" s="90"/>
-      <c r="C7" s="90"/>
-      <c r="D7" s="90"/>
-      <c r="E7" s="90"/>
-      <c r="F7" s="90"/>
-      <c r="G7" s="90"/>
+      <c r="A7" s="83"/>
+      <c r="B7" s="83"/>
+      <c r="C7" s="83"/>
+      <c r="D7" s="83"/>
+      <c r="E7" s="83"/>
+      <c r="F7" s="83"/>
+      <c r="G7" s="83"/>
     </row>
     <row r="8" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="90"/>
-      <c r="B8" s="90"/>
-      <c r="C8" s="90"/>
-      <c r="D8" s="90"/>
-      <c r="E8" s="90"/>
-      <c r="F8" s="90"/>
-      <c r="G8" s="90"/>
+      <c r="A8" s="83"/>
+      <c r="B8" s="83"/>
+      <c r="C8" s="83"/>
+      <c r="D8" s="83"/>
+      <c r="E8" s="83"/>
+      <c r="F8" s="83"/>
+      <c r="G8" s="83"/>
     </row>
     <row r="9" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="90"/>
-      <c r="B9" s="90"/>
-      <c r="C9" s="90"/>
-      <c r="D9" s="90"/>
-      <c r="E9" s="90"/>
-      <c r="F9" s="90"/>
-      <c r="G9" s="90"/>
+      <c r="A9" s="83"/>
+      <c r="B9" s="83"/>
+      <c r="C9" s="83"/>
+      <c r="D9" s="83"/>
+      <c r="E9" s="83"/>
+      <c r="F9" s="83"/>
+      <c r="G9" s="83"/>
     </row>
     <row r="10" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="90"/>
-      <c r="B10" s="90"/>
-      <c r="C10" s="90"/>
-      <c r="D10" s="90"/>
-      <c r="E10" s="90"/>
-      <c r="F10" s="90"/>
-      <c r="G10" s="90"/>
+      <c r="A10" s="83"/>
+      <c r="B10" s="83"/>
+      <c r="C10" s="83"/>
+      <c r="D10" s="83"/>
+      <c r="E10" s="83"/>
+      <c r="F10" s="83"/>
+      <c r="G10" s="83"/>
     </row>
     <row r="11" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="90"/>
-      <c r="B11" s="90"/>
-      <c r="C11" s="90"/>
-      <c r="D11" s="90"/>
-      <c r="E11" s="90"/>
-      <c r="F11" s="90"/>
-      <c r="G11" s="90"/>
+      <c r="A11" s="83"/>
+      <c r="B11" s="83"/>
+      <c r="C11" s="83"/>
+      <c r="D11" s="83"/>
+      <c r="E11" s="83"/>
+      <c r="F11" s="83"/>
+      <c r="G11" s="83"/>
     </row>
     <row r="12" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" s="90"/>
-      <c r="B12" s="90"/>
-      <c r="C12" s="90"/>
-      <c r="D12" s="90"/>
-      <c r="E12" s="90"/>
-      <c r="F12" s="90"/>
-      <c r="G12" s="90"/>
+      <c r="A12" s="83"/>
+      <c r="B12" s="83"/>
+      <c r="C12" s="83"/>
+      <c r="D12" s="83"/>
+      <c r="E12" s="83"/>
+      <c r="F12" s="83"/>
+      <c r="G12" s="83"/>
     </row>
     <row r="13" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="90"/>
-      <c r="B13" s="90"/>
-      <c r="C13" s="90"/>
-      <c r="D13" s="90"/>
-      <c r="E13" s="90"/>
-      <c r="F13" s="90"/>
-      <c r="G13" s="90"/>
+      <c r="A13" s="83"/>
+      <c r="B13" s="83"/>
+      <c r="C13" s="83"/>
+      <c r="D13" s="83"/>
+      <c r="E13" s="83"/>
+      <c r="F13" s="83"/>
+      <c r="G13" s="83"/>
     </row>
     <row r="14" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="90"/>
-      <c r="B14" s="90"/>
-      <c r="C14" s="90"/>
-      <c r="D14" s="90"/>
-      <c r="E14" s="90"/>
-      <c r="F14" s="90"/>
-      <c r="G14" s="90"/>
+      <c r="A14" s="83"/>
+      <c r="B14" s="83"/>
+      <c r="C14" s="83"/>
+      <c r="D14" s="83"/>
+      <c r="E14" s="83"/>
+      <c r="F14" s="83"/>
+      <c r="G14" s="83"/>
     </row>
     <row r="15" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="90"/>
-      <c r="B15" s="90"/>
-      <c r="C15" s="90"/>
-      <c r="D15" s="90"/>
-      <c r="E15" s="90"/>
-      <c r="F15" s="90"/>
-      <c r="G15" s="90"/>
+      <c r="A15" s="83"/>
+      <c r="B15" s="83"/>
+      <c r="C15" s="83"/>
+      <c r="D15" s="83"/>
+      <c r="E15" s="83"/>
+      <c r="F15" s="83"/>
+      <c r="G15" s="83"/>
     </row>
     <row r="16" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="90"/>
-      <c r="B16" s="90"/>
-      <c r="C16" s="90"/>
-      <c r="D16" s="90"/>
-      <c r="E16" s="90"/>
-      <c r="F16" s="90"/>
-      <c r="G16" s="90"/>
+      <c r="A16" s="83"/>
+      <c r="B16" s="83"/>
+      <c r="C16" s="83"/>
+      <c r="D16" s="83"/>
+      <c r="E16" s="83"/>
+      <c r="F16" s="83"/>
+      <c r="G16" s="83"/>
     </row>
     <row r="17" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17" s="90"/>
-      <c r="B17" s="90"/>
-      <c r="C17" s="90"/>
-      <c r="D17" s="90"/>
-      <c r="E17" s="90"/>
-      <c r="F17" s="90"/>
-      <c r="G17" s="90"/>
+      <c r="A17" s="83"/>
+      <c r="B17" s="83"/>
+      <c r="C17" s="83"/>
+      <c r="D17" s="83"/>
+      <c r="E17" s="83"/>
+      <c r="F17" s="83"/>
+      <c r="G17" s="83"/>
     </row>
     <row r="18" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18" s="90"/>
-      <c r="B18" s="90"/>
-      <c r="C18" s="90"/>
-      <c r="D18" s="90"/>
-      <c r="E18" s="90"/>
-      <c r="F18" s="90"/>
-      <c r="G18" s="90"/>
+      <c r="A18" s="83"/>
+      <c r="B18" s="83"/>
+      <c r="C18" s="83"/>
+      <c r="D18" s="83"/>
+      <c r="E18" s="83"/>
+      <c r="F18" s="83"/>
+      <c r="G18" s="83"/>
     </row>
     <row r="19" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19" s="90"/>
-      <c r="B19" s="90"/>
-      <c r="C19" s="90"/>
-      <c r="D19" s="90"/>
-      <c r="E19" s="90"/>
-      <c r="F19" s="90"/>
-      <c r="G19" s="90"/>
+      <c r="A19" s="83"/>
+      <c r="B19" s="83"/>
+      <c r="C19" s="83"/>
+      <c r="D19" s="83"/>
+      <c r="E19" s="83"/>
+      <c r="F19" s="83"/>
+      <c r="G19" s="83"/>
     </row>
     <row r="20" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A20" s="90"/>
-      <c r="B20" s="90"/>
-      <c r="C20" s="90"/>
-      <c r="D20" s="90"/>
-      <c r="E20" s="90"/>
-      <c r="F20" s="90"/>
-      <c r="G20" s="90"/>
-    </row>
-    <row r="21" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A21" s="90"/>
-      <c r="B21" s="90"/>
-      <c r="C21" s="90"/>
-      <c r="D21" s="90"/>
-      <c r="E21" s="90"/>
-      <c r="F21" s="90"/>
-      <c r="G21" s="90"/>
-    </row>
-    <row r="22" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22" s="90"/>
-      <c r="B22" s="90"/>
-      <c r="C22" s="90"/>
-      <c r="D22" s="90"/>
-      <c r="E22" s="90"/>
-      <c r="F22" s="90"/>
-      <c r="G22" s="90"/>
+      <c r="A20" s="83"/>
+      <c r="B20" s="83"/>
+      <c r="C20" s="83"/>
+      <c r="D20" s="83"/>
+      <c r="E20" s="83"/>
+      <c r="F20" s="83"/>
+      <c r="G20" s="83"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
@@ -10421,36 +9729,36 @@
   <sheetData>
     <row r="1" spans="1:3" ht="11.5" customHeight="1" x14ac:dyDescent="0.55000000000000004"/>
     <row r="2" spans="1:3" ht="26.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="91" t="s">
+      <c r="A2" s="84" t="s">
         <v>103</v>
       </c>
-      <c r="B2" s="91" t="s">
+      <c r="B2" s="84" t="s">
         <v>104</v>
       </c>
-      <c r="C2" s="91" t="s">
+      <c r="C2" s="84" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="120" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="92" t="s">
+      <c r="A3" s="85" t="s">
         <v>106</v>
       </c>
-      <c r="B3" s="79"/>
-      <c r="C3" s="79"/>
+      <c r="B3" s="73"/>
+      <c r="C3" s="73"/>
     </row>
     <row r="4" spans="1:3" ht="131.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="93" t="s">
+      <c r="A4" s="86" t="s">
         <v>107</v>
       </c>
-      <c r="B4" s="79"/>
-      <c r="C4" s="79"/>
+      <c r="B4" s="73"/>
+      <c r="C4" s="73"/>
     </row>
     <row r="5" spans="1:3" ht="171" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="93" t="s">
+      <c r="A5" s="86" t="s">
         <v>108</v>
       </c>
-      <c r="B5" s="79"/>
-      <c r="C5" s="79"/>
+      <c r="B5" s="73"/>
+      <c r="C5" s="73"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>

--- a/高橋さん用フォルダ/テンプレート集.xlsx
+++ b/高橋さん用フォルダ/テンプレート集.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26132DF6-CFF8-4E5E-8532-0193962019DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" firstSheet="2" activeTab="7" xr2:uid="{C2D9C0E7-7181-4507-8D76-FFF1980A0610}"/>
+    <workbookView xWindow="-90" yWindow="0" windowWidth="11380" windowHeight="13370" firstSheet="6" activeTab="7" xr2:uid="{C2D9C0E7-7181-4507-8D76-FFF1980A0610}"/>
   </bookViews>
   <sheets>
     <sheet name="組織のビジネスモデル" sheetId="1" r:id="rId1"/>
@@ -1660,6 +1660,9 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1668,9 +1671,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -8530,18 +8530,18 @@
       </c>
     </row>
     <row r="2" spans="1:17" ht="18.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="F2" s="90"/>
-      <c r="G2" s="91"/>
-      <c r="H2" s="91"/>
-      <c r="I2" s="91"/>
-      <c r="J2" s="91"/>
-      <c r="K2" s="91"/>
-      <c r="L2" s="91"/>
-      <c r="M2" s="91"/>
-      <c r="N2" s="91"/>
-      <c r="O2" s="91"/>
-      <c r="P2" s="91"/>
-      <c r="Q2" s="92"/>
+      <c r="F2" s="91"/>
+      <c r="G2" s="92"/>
+      <c r="H2" s="92"/>
+      <c r="I2" s="92"/>
+      <c r="J2" s="92"/>
+      <c r="K2" s="92"/>
+      <c r="L2" s="92"/>
+      <c r="M2" s="92"/>
+      <c r="N2" s="92"/>
+      <c r="O2" s="92"/>
+      <c r="P2" s="92"/>
+      <c r="Q2" s="93"/>
     </row>
     <row r="3" spans="1:17" ht="45.5" thickBot="1" x14ac:dyDescent="0.6">
       <c r="B3" s="40" t="s">
@@ -9508,7 +9508,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="G1" s="93" t="s">
+      <c r="G1" s="90" t="s">
         <v>102</v>
       </c>
     </row>
